--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F71BF2B-5FA5-4765-BE7F-28DDFEFA497D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D651CB2-E718-401C-BE05-08A0F54C629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23205" yWindow="7320" windowWidth="17925" windowHeight="9825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2235" yWindow="1695" windowWidth="24585" windowHeight="12945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$7</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="28">
   <si>
     <t>OID</t>
   </si>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>no-net-effect</t>
+  </si>
+  <si>
+    <t>DOI</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -465,11 +468,11 @@
     <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,8 +509,11 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -542,7 +548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -577,7 +583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -612,7 +618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -647,7 +653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -682,7 +688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -717,11 +723,11 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="I8" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D651CB2-E718-401C-BE05-08A0F54C629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF30AEF-5F58-4D44-AB0A-5751F858867C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2235" yWindow="1695" windowWidth="24585" windowHeight="12945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,26 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$7</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="60">
   <si>
     <t>OID</t>
   </si>
@@ -112,6 +121,102 @@
   </si>
   <si>
     <t>DOI</t>
+  </si>
+  <si>
+    <t>CHRNA1</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>GOF</t>
+  </si>
+  <si>
+    <t>Patch-clamp</t>
+  </si>
+  <si>
+    <t>SCCMS</t>
+  </si>
+  <si>
+    <t>FCCMS</t>
+  </si>
+  <si>
+    <t>https://linkinghub.elsevier.com/retrieve/pii/S0092867421002385</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/15609996/</t>
+  </si>
+  <si>
+    <t>Substitution</t>
+  </si>
+  <si>
+    <t>LOF/GOF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage-clamp </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6971</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6972</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6973</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6974</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6975</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.90.15.6976</t>
+  </si>
+  <si>
+    <t>Schizophrenia/Inflammation context</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>TEVC(Two Electrode Voltage Clamp)</t>
+  </si>
+  <si>
+    <t>GOF (for ACh)</t>
+  </si>
+  <si>
+    <t>No net effect</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1371/journal.pone.0137588</t>
   </si>
 </sst>
 </file>
@@ -121,7 +226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-407]General"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,6 +254,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -167,19 +294,56 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Excel Built-in Normal 1" xfId="1" xr:uid="{D585C33E-D382-4BD9-8030-CD231C838104}"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -458,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -467,9 +631,10 @@
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="60" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -547,6 +712,9 @@
       <c r="K2" t="s">
         <v>18</v>
       </c>
+      <c r="M2" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -582,6 +750,9 @@
       <c r="K3" t="s">
         <v>18</v>
       </c>
+      <c r="M3" s="6" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
@@ -617,6 +788,9 @@
       <c r="K4" t="s">
         <v>18</v>
       </c>
+      <c r="M4" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -652,6 +826,9 @@
       <c r="K5" t="s">
         <v>18</v>
       </c>
+      <c r="M5" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -687,6 +864,9 @@
       <c r="K6" t="s">
         <v>18</v>
       </c>
+      <c r="M6" s="6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -722,14 +902,917 @@
       <c r="K7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="I8" s="2"/>
+      <c r="M7" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4">
+        <v>237</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="4">
+        <v>251</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="4">
+        <v>254</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="4">
+        <v>254</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="3"/>
+      <c r="M11" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="4">
+        <v>255</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="4">
+        <v>255</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="4">
+        <v>8346083</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="15">
+        <v>47</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="4">
+        <v>55</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="4">
+        <v>26340455</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="15">
+        <v>93</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="15">
+        <v>171</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="15">
+        <v>173</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="15">
+        <v>191</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="15">
+        <v>192</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="12"/>
+      <c r="M20" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="15">
+        <v>197</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="12"/>
+      <c r="M21" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="15">
+        <v>205</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="12"/>
+      <c r="M22" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="15">
+        <v>205</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J23" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="12"/>
+      <c r="M23" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="15">
+        <v>206</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="12"/>
+      <c r="M24" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="15">
+        <v>211</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="15">
+        <v>212</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J26" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="12"/>
+      <c r="M26" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="15">
+        <v>212</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="15">
+        <v>26340455</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="4">
+        <v>249</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J36" s="4">
+        <v>9158151</v>
+      </c>
+      <c r="K36" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="4">
+        <v>254</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="4">
+        <v>9158151</v>
+      </c>
+      <c r="K37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="4">
+        <v>269</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J38" s="4">
+        <v>9158151</v>
+      </c>
+      <c r="K38" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="4">
+        <v>285</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" s="4">
+        <v>12513135</v>
+      </c>
+      <c r="K39" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="4">
+        <v>418</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J40" s="4">
+        <v>16567362</v>
+      </c>
+      <c r="K40" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{3F906776-66FE-47E6-8465-F6CECBC27CE5}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{CC18B795-F530-44DA-89AE-9F99B65B2D24}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{799A0867-AD16-4A54-A6AA-5B298AE243FA}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{775BF6B6-3997-4FF6-BE68-574F46240D71}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{44A94267-FC24-41C0-A88B-41ED8737D59A}"/>
+    <hyperlink ref="M7" r:id="rId6" xr:uid="{A8846366-6D32-4BB8-98D6-CCEC05E633F8}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{87A5E94E-2CC0-43A2-A62B-F1F66B9F07E8}"/>
+    <hyperlink ref="M14" r:id="rId8" xr:uid="{B80AA495-D52C-41FA-B9DF-540C9B9A4EEF}"/>
+    <hyperlink ref="M15" r:id="rId9" xr:uid="{E920832F-5389-4202-8936-DAC18C511E14}"/>
+    <hyperlink ref="M16" r:id="rId10" xr:uid="{769FE194-5119-4D77-9BD9-AB3B00EB203B}"/>
+    <hyperlink ref="M18" r:id="rId11" xr:uid="{39F1A90B-B1B8-4579-A9A9-1FDE6FD165B2}"/>
+    <hyperlink ref="M20" r:id="rId12" xr:uid="{4B841C4F-3B73-4581-9EDB-E7690FBF06E1}"/>
+    <hyperlink ref="M22" r:id="rId13" xr:uid="{544EF01F-E27F-4368-A0DE-B56D3F639DD7}"/>
+    <hyperlink ref="M24" r:id="rId14" xr:uid="{D21D1F8C-247A-4EC2-B00E-036B683A84AC}"/>
+    <hyperlink ref="M26" r:id="rId15" xr:uid="{9AA5400C-30B9-4D13-B862-E12117A874AF}"/>
+    <hyperlink ref="M17" r:id="rId16" xr:uid="{A14DA58B-95D0-4860-9298-DBCA90D30CB1}"/>
+    <hyperlink ref="M19" r:id="rId17" xr:uid="{0FA1E567-C84E-4E6D-BCF2-6235A6E047E4}"/>
+    <hyperlink ref="M21" r:id="rId18" xr:uid="{7E0E6BD0-AB31-4EED-9849-78A5230897BA}"/>
+    <hyperlink ref="M23" r:id="rId19" xr:uid="{A67DBAC1-DFE3-46B7-A74F-F78BFEFD079F}"/>
+    <hyperlink ref="M25" r:id="rId20" xr:uid="{824FFBA1-4F25-4A53-882A-39220133F80B}"/>
+    <hyperlink ref="M27" r:id="rId21" xr:uid="{F5AC65C6-1381-4733-999F-179DDED61E77}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF30AEF-5F58-4D44-AB0A-5751F858867C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F003FB4-483A-4017-9193-9B1597BE40E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="60">
   <si>
     <t>OID</t>
   </si>
@@ -96,9 +97,6 @@
     <t>HM</t>
   </si>
   <si>
-    <t>undefined</t>
-  </si>
-  <si>
     <t>Q</t>
   </si>
   <si>
@@ -198,18 +196,12 @@
     <t>https://doi.org/10.1073/pnas.90.15.6976</t>
   </si>
   <si>
-    <t>Schizophrenia/Inflammation context</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>H</t>
   </si>
   <si>
-    <t>TEVC(Two Electrode Voltage Clamp)</t>
-  </si>
-  <si>
     <t>GOF (for ACh)</t>
   </si>
   <si>
@@ -217,6 +209,15 @@
   </si>
   <si>
     <t>https://doi.org/10.1371/journal.pone.0137588</t>
+  </si>
+  <si>
+    <t>TVEC</t>
+  </si>
+  <si>
+    <t>Schizophrenia</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1523/JNEUROSCI.3497-05.2005</t>
   </si>
 </sst>
 </file>
@@ -299,46 +300,49 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -622,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:Z40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -675,7 +679,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -703,17 +707,15 @@
       <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I2" s="2"/>
       <c r="J2">
         <v>33735609</v>
       </c>
       <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="6" t="s">
-        <v>42</v>
+      <c r="M2" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -730,10 +732,10 @@
         <v>139</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -741,17 +743,15 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I3" s="2"/>
       <c r="J3">
         <v>15609996</v>
       </c>
       <c r="K3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>43</v>
+      <c r="M3" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -768,28 +768,26 @@
         <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I4" s="2"/>
       <c r="J4">
         <v>33735609</v>
       </c>
       <c r="K4" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>42</v>
+      <c r="M4" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -806,28 +804,26 @@
         <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I5" s="2"/>
       <c r="J5">
         <v>33735609</v>
       </c>
       <c r="K5" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>42</v>
+      <c r="M5" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -844,7 +840,7 @@
         <v>491</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -855,17 +851,15 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I6" s="2"/>
       <c r="J6">
         <v>33735609</v>
       </c>
       <c r="K6" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>42</v>
+      <c r="M6" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -882,36 +876,34 @@
         <v>500</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I7" s="2"/>
       <c r="J7">
         <v>33735609</v>
       </c>
       <c r="K7" t="s">
         <v>18</v>
       </c>
-      <c r="M7" s="6" t="s">
-        <v>42</v>
+      <c r="M7" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4">
         <v>237</v>
@@ -926,709 +918,797 @@
         <v>16</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>19</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="I8" s="6"/>
       <c r="J8" s="4">
         <v>8346083</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" t="s">
         <v>18</v>
       </c>
       <c r="L8" s="3"/>
-      <c r="M8" s="9" t="s">
-        <v>47</v>
+      <c r="M8" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4">
         <v>251</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>19</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="I9" s="6"/>
       <c r="J9" s="4">
         <v>8346083</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" t="s">
         <v>18</v>
       </c>
       <c r="L9" s="3"/>
-      <c r="M9" s="9" t="s">
-        <v>48</v>
+      <c r="M9" s="7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" s="4">
         <v>254</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="I10" s="6"/>
       <c r="J10" s="4">
         <v>8346083</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" t="s">
         <v>18</v>
       </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="13" t="s">
-        <v>49</v>
+      <c r="M10" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="4">
         <v>254</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="I11" s="6"/>
       <c r="J11" s="4">
         <v>8346083</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" t="s">
         <v>18</v>
       </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="13" t="s">
-        <v>50</v>
+      <c r="M11" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="4">
         <v>255</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="I12" s="6"/>
       <c r="J12" s="4">
         <v>8346083</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" t="s">
         <v>18</v>
       </c>
       <c r="L12" s="3"/>
-      <c r="M12" s="13" t="s">
-        <v>51</v>
+      <c r="M12" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="4">
         <v>255</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="I13" s="6"/>
       <c r="J13" s="4">
         <v>8346083</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" t="s">
         <v>18</v>
       </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="13" t="s">
-        <v>52</v>
+      <c r="M13" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="10">
         <v>47</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>25</v>
+      <c r="E14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
+    </row>
+    <row r="15" spans="1:13" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" s="4">
         <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>53</v>
+      <c r="I15" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="J15" s="4">
         <v>26340455</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="17" t="s">
-        <v>59</v>
+      <c r="M15" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="10">
         <v>93</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>37</v>
+      <c r="E16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="9"/>
+      <c r="M16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J16" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" s="12"/>
-      <c r="M16" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="15">
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="10">
         <v>171</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>21</v>
+      <c r="E17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J17" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="15">
+    </row>
+    <row r="18" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="10">
         <v>173</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>32</v>
+      <c r="F18" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J18" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="15">
+    </row>
+    <row r="19" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="10">
         <v>191</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>54</v>
+      <c r="E19" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="15">
+    </row>
+    <row r="20" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="10">
+        <v>192</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="10">
         <v>26340455</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="12"/>
-      <c r="M19" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="15">
-        <v>192</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="K20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="9"/>
+      <c r="M20" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I20" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="15">
+    </row>
+    <row r="21" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="10">
         <v>197</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>31</v>
+      <c r="E21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="12"/>
-      <c r="M21" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="15">
+    </row>
+    <row r="22" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="10">
         <v>205</v>
       </c>
-      <c r="E22" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>37</v>
+      <c r="E22" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="9"/>
+      <c r="M22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="12" t="s">
+    </row>
+    <row r="23" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="10">
+        <v>205</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>53</v>
-      </c>
-      <c r="J22" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="15">
-        <v>205</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>55</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="12"/>
-      <c r="M23" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="15">
+    </row>
+    <row r="24" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="10">
         <v>206</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>37</v>
+      <c r="E24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J24" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" s="12"/>
-      <c r="M24" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="15">
+    </row>
+    <row r="25" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="10">
         <v>211</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>37</v>
+      <c r="E25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="9"/>
+      <c r="M25" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I25" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="15">
+    </row>
+    <row r="26" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="10">
+        <v>212</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" s="10">
         <v>26340455</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L25" s="12"/>
-      <c r="M25" s="13" t="s">
+      <c r="K26" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="9"/>
+      <c r="M26" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="10">
+        <v>212</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="10">
+        <v>26340455</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="9"/>
+      <c r="M27" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="16">
+        <v>442</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="J28" s="16">
+        <v>16251438</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="17"/>
+      <c r="M28" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="15">
-        <v>212</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
+    </row>
+    <row r="29" spans="1:26" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="16">
+        <v>386</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="13" t="s">
+      <c r="J29" s="16">
+        <v>16251438</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="17"/>
+      <c r="M29" s="7" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="15">
-        <v>212</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J27" s="15">
-        <v>26340455</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="13" t="s">
-        <v>59</v>
-      </c>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="18"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>13</v>
@@ -1637,19 +1717,19 @@
         <v>249</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="I36" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J36" s="4">
         <v>9158151</v>
@@ -1660,7 +1740,7 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>13</v>
@@ -1669,19 +1749,19 @@
         <v>254</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="I37" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J37" s="4">
         <v>9158151</v>
@@ -1692,7 +1772,7 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>13</v>
@@ -1701,19 +1781,19 @@
         <v>269</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="I38" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J38" s="4">
         <v>9158151</v>
@@ -1724,7 +1804,7 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>13</v>
@@ -1733,19 +1813,19 @@
         <v>285</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G39" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="5" t="s">
-        <v>39</v>
+      <c r="H39" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J39" s="4">
         <v>12513135</v>
@@ -1756,7 +1836,7 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>13</v>
@@ -1765,19 +1845,19 @@
         <v>418</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G40" s="5" t="s">
+      <c r="H40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="I40" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="J40" s="4">
         <v>16567362</v>
@@ -1811,8 +1891,10 @@
     <hyperlink ref="M23" r:id="rId19" xr:uid="{A67DBAC1-DFE3-46B7-A74F-F78BFEFD079F}"/>
     <hyperlink ref="M25" r:id="rId20" xr:uid="{824FFBA1-4F25-4A53-882A-39220133F80B}"/>
     <hyperlink ref="M27" r:id="rId21" xr:uid="{F5AC65C6-1381-4733-999F-179DDED61E77}"/>
+    <hyperlink ref="M28" r:id="rId22" xr:uid="{07B8C34B-A691-48AE-8B61-F66FBA1D6A75}"/>
+    <hyperlink ref="M29" r:id="rId23" xr:uid="{99B63BB4-BFDF-48AA-B500-F6699533459B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1879B6F-0B82-46F1-BF3F-C578B428F0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFB81F7-4D74-42D3-833A-B5EF35E37308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="83">
   <si>
     <t>OID</t>
   </si>
@@ -222,9 +222,6 @@
     <t>M</t>
   </si>
   <si>
-    <t>Gemini</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1021/bi048918g</t>
   </si>
   <si>
@@ -274,6 +271,21 @@
   </si>
   <si>
     <t>https://doi.org/10.1002/ana.20861</t>
+  </si>
+  <si>
+    <t>CMS</t>
+  </si>
+  <si>
+    <t>Frameshift</t>
+  </si>
+  <si>
+    <t>Cell surface binding</t>
+  </si>
+  <si>
+    <t>shift</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1172/jci16997</t>
   </si>
 </sst>
 </file>
@@ -822,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z59"/>
+  <dimension ref="A1:Z61"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="2" customWidth="1"/>
@@ -1203,7 +1215,7 @@
         <v>37</v>
       </c>
       <c r="N8" s="45" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O8" s="45"/>
       <c r="P8" s="45"/>
@@ -2459,7 +2471,7 @@
         <v>45</v>
       </c>
       <c r="M35" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N35" s="29"/>
       <c r="O35" s="29"/>
@@ -2511,7 +2523,7 @@
         <v>45</v>
       </c>
       <c r="M36" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N36" s="29"/>
       <c r="O36" s="29"/>
@@ -2563,7 +2575,7 @@
         <v>45</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N37" s="29"/>
       <c r="O37" s="29"/>
@@ -2615,7 +2627,7 @@
         <v>45</v>
       </c>
       <c r="M38" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N38" s="29"/>
       <c r="O38" s="29"/>
@@ -2667,7 +2679,7 @@
         <v>45</v>
       </c>
       <c r="M39" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N39" s="29"/>
       <c r="O39" s="29"/>
@@ -2719,7 +2731,7 @@
         <v>45</v>
       </c>
       <c r="M40" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N40" s="29"/>
       <c r="O40" s="29"/>
@@ -2771,7 +2783,7 @@
         <v>45</v>
       </c>
       <c r="M41" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N41" s="29"/>
       <c r="O41" s="29"/>
@@ -2823,7 +2835,7 @@
         <v>45</v>
       </c>
       <c r="M42" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N42" s="29"/>
       <c r="O42" s="29"/>
@@ -2875,7 +2887,7 @@
         <v>45</v>
       </c>
       <c r="M43" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N43" s="29"/>
       <c r="O43" s="29"/>
@@ -2928,7 +2940,7 @@
         <v>57</v>
       </c>
       <c r="N44" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O44" s="38"/>
       <c r="P44" s="38"/>
@@ -3029,7 +3041,7 @@
         <v>45</v>
       </c>
       <c r="M46" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N46" s="29"/>
       <c r="O46" s="29"/>
@@ -3081,7 +3093,7 @@
         <v>45</v>
       </c>
       <c r="M47" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N47" s="29"/>
       <c r="O47" s="29"/>
@@ -3133,7 +3145,7 @@
         <v>45</v>
       </c>
       <c r="M48" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N48" s="29"/>
       <c r="O48" s="29"/>
@@ -3185,7 +3197,7 @@
         <v>45</v>
       </c>
       <c r="M49" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N49" s="29"/>
       <c r="O49" s="29"/>
@@ -3206,7 +3218,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" s="34" t="s">
         <v>34</v>
@@ -3224,10 +3236,10 @@
         <v>33</v>
       </c>
       <c r="H50" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I50" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I50" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J50" s="33">
         <v>9158151</v>
@@ -3239,7 +3251,7 @@
         <v>45</v>
       </c>
       <c r="M50" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N50" s="29"/>
       <c r="O50" s="29"/>
@@ -3260,7 +3272,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" s="34" t="s">
         <v>34</v>
@@ -3278,10 +3290,10 @@
         <v>33</v>
       </c>
       <c r="H51" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I51" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J51" s="33">
         <v>9158151</v>
@@ -3293,7 +3305,7 @@
         <v>45</v>
       </c>
       <c r="M51" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N51" s="29"/>
       <c r="O51" s="29"/>
@@ -3314,7 +3326,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="34" t="s">
         <v>34</v>
@@ -3326,16 +3338,16 @@
         <v>31</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G52" s="34" t="s">
         <v>33</v>
       </c>
       <c r="H52" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I52" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I52" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J52" s="33">
         <v>9158151</v>
@@ -3347,7 +3359,7 @@
         <v>45</v>
       </c>
       <c r="M52" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N52" s="29"/>
       <c r="O52" s="29"/>
@@ -3368,7 +3380,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" s="34" t="s">
         <v>34</v>
@@ -3380,16 +3392,16 @@
         <v>20</v>
       </c>
       <c r="F53" s="34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G53" s="34" t="s">
         <v>33</v>
       </c>
       <c r="H53" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I53" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J53" s="33">
         <v>7611281</v>
@@ -3401,7 +3413,7 @@
         <v>45</v>
       </c>
       <c r="M53" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N53" s="29"/>
       <c r="O53" s="29"/>
@@ -3422,7 +3434,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>34</v>
@@ -3440,10 +3452,10 @@
         <v>33</v>
       </c>
       <c r="H54" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I54" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I54" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J54" s="41">
         <v>8872460</v>
@@ -3455,7 +3467,7 @@
         <v>45</v>
       </c>
       <c r="M54" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N54" s="29"/>
       <c r="O54" s="29"/>
@@ -3476,7 +3488,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="34" t="s">
         <v>34</v>
@@ -3494,10 +3506,10 @@
         <v>33</v>
       </c>
       <c r="H55" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I55" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I55" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J55" s="41">
         <v>8872460</v>
@@ -3509,7 +3521,7 @@
         <v>45</v>
       </c>
       <c r="M55" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N55" s="29"/>
       <c r="O55" s="29"/>
@@ -3530,7 +3542,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>34</v>
@@ -3548,10 +3560,10 @@
         <v>33</v>
       </c>
       <c r="H56" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I56" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I56" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J56" s="41">
         <v>8872460</v>
@@ -3563,7 +3575,7 @@
         <v>45</v>
       </c>
       <c r="M56" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N56" s="29"/>
       <c r="O56" s="29"/>
@@ -3584,7 +3596,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="34" t="s">
         <v>34</v>
@@ -3602,7 +3614,7 @@
         <v>40</v>
       </c>
       <c r="H57" s="34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I57" s="34"/>
       <c r="J57" s="41">
@@ -3615,7 +3627,7 @@
         <v>45</v>
       </c>
       <c r="M57" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N57" s="29"/>
       <c r="O57" s="29"/>
@@ -3636,7 +3648,7 @@
         <v>14</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="34" t="s">
         <v>34</v>
@@ -3654,10 +3666,10 @@
         <v>33</v>
       </c>
       <c r="H58" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I58" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I58" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J58" s="40">
         <v>9221765</v>
@@ -3669,7 +3681,7 @@
         <v>45</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N58" s="29"/>
       <c r="O58" s="29"/>
@@ -3690,7 +3702,7 @@
         <v>14</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" s="34" t="s">
         <v>34</v>
@@ -3708,22 +3720,22 @@
         <v>33</v>
       </c>
       <c r="H59" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I59" s="34" t="s">
         <v>69</v>
-      </c>
-      <c r="I59" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="J59" s="40">
         <v>16685696</v>
       </c>
-      <c r="K59" s="34" t="s">
-        <v>61</v>
+      <c r="K59" s="24" t="s">
+        <v>18</v>
       </c>
       <c r="L59" s="34" t="s">
         <v>45</v>
       </c>
       <c r="M59" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N59" s="29"/>
       <c r="O59" s="29"/>
@@ -3738,6 +3750,114 @@
       <c r="X59" s="29"/>
       <c r="Y59" s="29"/>
       <c r="Z59" s="29"/>
+    </row>
+    <row r="60" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A60" s="33">
+        <v>1</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="33">
+        <v>132</v>
+      </c>
+      <c r="E60" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="J60" s="40">
+        <v>12588888</v>
+      </c>
+      <c r="K60" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M60" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="N60" s="29"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="29"/>
+      <c r="Q60" s="29"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="29"/>
+      <c r="T60" s="29"/>
+      <c r="U60" s="29"/>
+      <c r="V60" s="29"/>
+      <c r="W60" s="29"/>
+      <c r="X60" s="29"/>
+      <c r="Y60" s="29"/>
+      <c r="Z60" s="29"/>
+    </row>
+    <row r="61" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A61" s="33">
+        <v>2</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="D61" s="33">
+        <v>127</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G61" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="J61" s="40">
+        <v>12588888</v>
+      </c>
+      <c r="K61" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M61" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="29"/>
+      <c r="X61" s="29"/>
+      <c r="Y61" s="29"/>
+      <c r="Z61" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -3801,8 +3921,10 @@
     <hyperlink ref="M57" r:id="rId56" xr:uid="{637ACCB4-AA60-4599-BECD-20CA6D332165}"/>
     <hyperlink ref="M58" r:id="rId57" xr:uid="{A78FD088-FEAC-4300-8C68-E03E3E2FC0D5}"/>
     <hyperlink ref="M59" r:id="rId58" xr:uid="{43813E1F-9E2D-4988-AD96-C98268965EFF}"/>
+    <hyperlink ref="M60" r:id="rId59" xr:uid="{ACED4252-8ECF-48C4-B544-D228285A0631}"/>
+    <hyperlink ref="M61" r:id="rId60" xr:uid="{82F3DD28-A78A-44E8-AD35-D416503455F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId59"/>
+  <pageSetup orientation="portrait" r:id="rId61"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AFB81F7-4D74-42D3-833A-B5EF35E37308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1869C3D6-A5BC-4773-893A-5E2396736052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="115">
   <si>
     <t>OID</t>
   </si>
@@ -273,19 +273,115 @@
     <t>https://doi.org/10.1002/ana.20861</t>
   </si>
   <si>
+    <t>Frameshift</t>
+  </si>
+  <si>
+    <t>Cell surface binding</t>
+  </si>
+  <si>
+    <t>shift</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1172/jci16997</t>
+  </si>
+  <si>
+    <t>Single-channel recording</t>
+  </si>
+  <si>
+    <t>DNA Sequencing</t>
+  </si>
+  <si>
+    <t>FADS / LMPS</t>
+  </si>
+  <si>
+    <t>Stop</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ajhg.2007.11.006</t>
+  </si>
+  <si>
+    <t>Single-channel patch-clamp</t>
+  </si>
+  <si>
     <t>CMS</t>
   </si>
   <si>
-    <t>Frameshift</t>
-  </si>
-  <si>
-    <t>Cell surface binding</t>
-  </si>
-  <si>
-    <t>shift</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1172/jci16997</t>
+    <t>https://doi.org/10.1038/6326</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1113/jphysiol.1995.sp021090</t>
+  </si>
+  <si>
+    <t>Congenital myasthenic syndrome</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.92.3.758</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/hmg/6.5.753</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/ana.410400521</t>
+  </si>
+  <si>
+    <t>Congenital Myasthenic Syndrome</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/s0896-6273(00)80289-5</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1212/01.WNL.0000042422.87384.2F</t>
+  </si>
+  <si>
+    <t>CMS/AMC</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1172/jci12935</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/ana.410390607</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/humu.23043</t>
+  </si>
+  <si>
+    <t>Microelectrode / Patch-clamp</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.mcn.2006.02.004</t>
+  </si>
+  <si>
+    <t>RNS / SFEMG</t>
+  </si>
+  <si>
+    <t>AChR Deficiency</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.nmd.2017.11.013</t>
+  </si>
+  <si>
+    <t>FCCMS</t>
+  </si>
+  <si>
+    <t>Single channel recording</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1196/annals.1254.013</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/hmg/ddn305</t>
+  </si>
+  <si>
+    <t>HEK 293 expression</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s00415-009-5190-7</t>
   </si>
 </sst>
 </file>
@@ -432,7 +528,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -473,16 +569,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -536,7 +622,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -552,6 +637,11 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Excel Built-in Normal 1" xfId="1" xr:uid="{D585C33E-D382-4BD9-8030-CD231C838104}"/>
@@ -834,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Z104"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="2" customWidth="1"/>
@@ -895,211 +985,211 @@
       </c>
     </row>
     <row r="2" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A2" s="27">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="27">
+      <c r="C2" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="23">
         <v>97</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="24" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="29"/>
-      <c r="J2" s="27">
+      <c r="I2" s="25"/>
+      <c r="J2" s="23">
         <v>33740418</v>
       </c>
-      <c r="K2" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="K2" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
     </row>
     <row r="3" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A3" s="27">
+      <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="27">
+      <c r="C3" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="23">
         <v>468</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="24" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="27">
+      <c r="I3" s="25"/>
+      <c r="J3" s="23">
         <v>33740418</v>
       </c>
-      <c r="K3" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="30" t="s">
+      <c r="K3" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
-      <c r="X3" s="29"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="29"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
     </row>
     <row r="4" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A4" s="27">
+      <c r="A4" s="23">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="23">
         <v>467</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28" t="s">
+      <c r="F4" s="24"/>
+      <c r="G4" s="24" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="29"/>
-      <c r="J4" s="27">
+      <c r="I4" s="25"/>
+      <c r="J4" s="23">
         <v>33740418</v>
       </c>
-      <c r="K4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="K4" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="29"/>
-      <c r="S4" s="29"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="29"/>
-      <c r="Y4" s="29"/>
-      <c r="Z4" s="29"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
     </row>
     <row r="5" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A5" s="27">
+      <c r="A5" s="23">
         <v>4</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28" t="s">
+      <c r="F5" s="24"/>
+      <c r="G5" s="24" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="29"/>
-      <c r="J5" s="27">
+      <c r="I5" s="25"/>
+      <c r="J5" s="23">
         <v>33740418</v>
       </c>
-      <c r="K5" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="L5" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="30" t="s">
+      <c r="K5" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
     </row>
     <row r="6" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A6" s="27">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1130,7 +1220,7 @@
       <c r="K6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="24" t="s">
         <v>45</v>
       </c>
       <c r="M6" s="7" t="s">
@@ -1138,7 +1228,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A7" s="27">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1148,7 +1238,7 @@
         <v>34</v>
       </c>
       <c r="D7" s="5">
-        <v>237</v>
+        <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>14</v>
@@ -1169,7 +1259,7 @@
       <c r="K7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="24" t="s">
         <v>45</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -1177,425 +1267,425 @@
       </c>
     </row>
     <row r="8" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A8" s="31">
+      <c r="A8" s="27">
         <v>7</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="43">
+      <c r="C8" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="38">
         <v>254</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="44" t="s">
+      <c r="H8" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="43">
+      <c r="I8" s="40"/>
+      <c r="J8" s="38">
         <v>8346083</v>
       </c>
-      <c r="K8" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="44" t="s">
+      <c r="K8" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="45" t="s">
+      <c r="N8" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="45"/>
-      <c r="X8" s="45"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="45"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="40"/>
+      <c r="T8" s="40"/>
+      <c r="U8" s="40"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
     </row>
     <row r="9" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A9" s="31">
+      <c r="A9" s="27">
         <v>8</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="43">
+      <c r="C9" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="38">
         <v>254</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="44" t="s">
+      <c r="G9" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="43">
+      <c r="I9" s="40"/>
+      <c r="J9" s="38">
         <v>8346083</v>
       </c>
-      <c r="K9" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="44" t="s">
+      <c r="K9" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45"/>
-      <c r="Z9" s="45"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="40"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
     </row>
     <row r="10" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A10" s="31">
+      <c r="A10" s="27">
         <v>9</v>
       </c>
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="43">
+      <c r="C10" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="38">
         <v>254</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G10" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="45"/>
-      <c r="J10" s="43">
+      <c r="I10" s="40"/>
+      <c r="J10" s="38">
         <v>8346083</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+      <c r="R10" s="40"/>
+      <c r="S10" s="40"/>
+      <c r="T10" s="40"/>
+      <c r="U10" s="40"/>
+      <c r="V10" s="40"/>
+      <c r="W10" s="40"/>
+      <c r="X10" s="40"/>
+      <c r="Y10" s="40"/>
+      <c r="Z10" s="40"/>
     </row>
     <row r="11" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A11" s="31">
+      <c r="A11" s="27">
         <v>10</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="43">
+      <c r="C11" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="38">
         <v>254</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="G11" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="45"/>
-      <c r="J11" s="43">
+      <c r="I11" s="40"/>
+      <c r="J11" s="38">
         <v>8346083</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="44" t="s">
+      <c r="L11" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="45"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="45"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-      <c r="V11" s="45"/>
-      <c r="W11" s="45"/>
-      <c r="X11" s="45"/>
-      <c r="Y11" s="45"/>
-      <c r="Z11" s="45"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
     </row>
     <row r="12" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A12" s="31">
+      <c r="A12" s="27">
         <v>11</v>
       </c>
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="43">
+      <c r="C12" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="38">
         <v>255</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="45"/>
-      <c r="J12" s="43">
+      <c r="I12" s="40"/>
+      <c r="J12" s="38">
         <v>8346083</v>
       </c>
-      <c r="K12" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="44" t="s">
+      <c r="K12" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="45"/>
-      <c r="O12" s="45"/>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="45"/>
-      <c r="S12" s="45"/>
-      <c r="T12" s="45"/>
-      <c r="U12" s="45"/>
-      <c r="V12" s="45"/>
-      <c r="W12" s="45"/>
-      <c r="X12" s="45"/>
-      <c r="Y12" s="45"/>
-      <c r="Z12" s="45"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40"/>
+      <c r="S12" s="40"/>
+      <c r="T12" s="40"/>
+      <c r="U12" s="40"/>
+      <c r="V12" s="40"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
     </row>
     <row r="13" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A13" s="31">
+      <c r="A13" s="27">
         <v>12</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="43">
+      <c r="C13" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="38">
         <v>255</v>
       </c>
-      <c r="E13" s="44" t="s">
+      <c r="E13" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="45"/>
-      <c r="J13" s="43">
+      <c r="I13" s="40"/>
+      <c r="J13" s="38">
         <v>8346083</v>
       </c>
-      <c r="K13" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="44" t="s">
+      <c r="K13" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="45"/>
-      <c r="S13" s="45"/>
-      <c r="T13" s="45"/>
-      <c r="U13" s="45"/>
-      <c r="V13" s="45"/>
-      <c r="W13" s="45"/>
-      <c r="X13" s="45"/>
-      <c r="Y13" s="45"/>
-      <c r="Z13" s="45"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
     </row>
     <row r="14" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A14" s="31">
+      <c r="A14" s="27">
         <v>13</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="43">
+      <c r="C14" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="38">
         <v>255</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="43">
+      <c r="I14" s="40"/>
+      <c r="J14" s="38">
         <v>8346083</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="44" t="s">
+      <c r="L14" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="45"/>
-      <c r="W14" s="45"/>
-      <c r="X14" s="45"/>
-      <c r="Y14" s="45"/>
-      <c r="Z14" s="45"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
     </row>
     <row r="15" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A15" s="31">
+      <c r="A15" s="27">
         <v>14</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="43">
+      <c r="C15" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="38">
         <v>255</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="45"/>
-      <c r="J15" s="43">
+      <c r="I15" s="40"/>
+      <c r="J15" s="38">
         <v>8346083</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="44" t="s">
+      <c r="L15" s="39" t="s">
         <v>45</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-      <c r="V15" s="45"/>
-      <c r="W15" s="45"/>
-      <c r="X15" s="45"/>
-      <c r="Y15" s="45"/>
-      <c r="Z15" s="45"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
     </row>
     <row r="16" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A16" s="27">
+      <c r="A16" s="23">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
@@ -1636,7 +1726,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" s="14" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A17" s="27">
+      <c r="A17" s="23">
         <v>16</v>
       </c>
       <c r="B17" s="14" t="s">
@@ -1677,7 +1767,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A18" s="27">
+      <c r="A18" s="23">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
@@ -1718,7 +1808,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A19" s="27">
+      <c r="A19" s="23">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
@@ -1762,7 +1852,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A20" s="27">
+      <c r="A20" s="23">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
@@ -1806,7 +1896,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A21" s="27">
+      <c r="A21" s="23">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
@@ -1846,47 +1936,47 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A22" s="32">
+    <row r="22" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A22" s="43">
         <v>21</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="19">
+      <c r="C22" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="12">
         <v>192</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="18"/>
-      <c r="J22" s="19">
+      <c r="I22" s="11"/>
+      <c r="J22" s="12">
         <v>26340455</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="M22" s="21" t="s">
+      <c r="K22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M22" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A23" s="27">
+      <c r="A23" s="23">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
@@ -1927,7 +2017,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A24" s="27">
+      <c r="A24" s="23">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
@@ -1968,7 +2058,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A25" s="27">
+      <c r="A25" s="23">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
@@ -2009,7 +2099,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A26" s="27">
+      <c r="A26" s="23">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
@@ -2050,7 +2140,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A27" s="27">
+      <c r="A27" s="23">
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
@@ -2090,95 +2180,95 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A28" s="32">
+    <row r="28" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A28" s="43">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="19">
+      <c r="C28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="12">
         <v>212</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="G28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H28" s="18" t="s">
+      <c r="H28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="18"/>
-      <c r="J28" s="19">
+      <c r="I28" s="11"/>
+      <c r="J28" s="12">
         <v>26340455</v>
       </c>
-      <c r="K28" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L28" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="M28" s="21" t="s">
+      <c r="K28" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N28" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A29" s="32">
+    <row r="29" spans="1:26" s="10" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A29" s="43">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="19">
+      <c r="C29" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="12">
         <v>212</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="G29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H29" s="18" t="s">
+      <c r="H29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="18"/>
-      <c r="J29" s="19">
+      <c r="I29" s="11"/>
+      <c r="J29" s="12">
         <v>26340455</v>
       </c>
-      <c r="K29" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L29" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="M29" s="21" t="s">
+      <c r="K29" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A30" s="27">
+      <c r="A30" s="23">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="5">
@@ -2196,7 +2286,7 @@
       <c r="H30" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="18" t="s">
         <v>42</v>
       </c>
       <c r="J30" s="5">
@@ -2209,28 +2299,28 @@
       <c r="M30" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N30" s="23"/>
-      <c r="O30" s="23"/>
-      <c r="P30" s="23"/>
-      <c r="Q30" s="23"/>
-      <c r="R30" s="23"/>
-      <c r="S30" s="23"/>
-      <c r="T30" s="23"/>
-      <c r="U30" s="23"/>
-      <c r="V30" s="23"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="23"/>
-      <c r="Y30" s="23"/>
-      <c r="Z30" s="23"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="19"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="19"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="19"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="19"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="19"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A31" s="27">
+      <c r="A31" s="23">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="18" t="s">
         <v>34</v>
       </c>
       <c r="D31" s="5">
@@ -2248,7 +2338,7 @@
       <c r="H31" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="18" t="s">
         <v>42</v>
       </c>
       <c r="J31" s="5">
@@ -2261,1606 +2351,3898 @@
       <c r="M31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="23"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
-      <c r="S31" s="23"/>
-      <c r="T31" s="23"/>
-      <c r="U31" s="23"/>
-      <c r="V31" s="23"/>
-      <c r="W31" s="23"/>
-      <c r="X31" s="23"/>
-      <c r="Y31" s="23"/>
-      <c r="Z31" s="23"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="19"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="19"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="19"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="19"/>
     </row>
     <row r="32" spans="1:26" ht="52.5" thickBot="1">
-      <c r="A32" s="27">
+      <c r="A32" s="23">
         <v>31</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C32" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="25">
+      <c r="C32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="21">
         <v>250</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="24" t="s">
+      <c r="I32" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="21">
         <v>11879686</v>
       </c>
-      <c r="K32" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L32" s="24" t="s">
+      <c r="K32" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="20" t="s">
         <v>45</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
     </row>
     <row r="33" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A33" s="27">
+      <c r="A33" s="23">
         <v>32</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="25">
+      <c r="C33" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="21">
         <v>423</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="24" t="s">
+      <c r="G33" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I33" s="24"/>
-      <c r="J33" s="25">
+      <c r="I33" s="20"/>
+      <c r="J33" s="21">
         <v>17158315</v>
       </c>
-      <c r="K33" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="24" t="s">
+      <c r="K33" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="20" t="s">
         <v>45</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-      <c r="P33" s="26"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="22"/>
+      <c r="X33" s="22"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="22"/>
     </row>
     <row r="34" spans="1:26" ht="39.75" thickBot="1">
-      <c r="A34" s="27">
+      <c r="A34" s="23">
         <v>33</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="21">
         <v>250</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="20" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="21">
         <v>11877686</v>
       </c>
-      <c r="K34" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L34" s="24" t="s">
+      <c r="K34" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="20" t="s">
         <v>45</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="26"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="26"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A35" s="27">
-        <v>34</v>
-      </c>
-      <c r="B35" s="34" t="s">
+      <c r="A35" s="23">
+        <v>34</v>
+      </c>
+      <c r="B35" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="33">
+      <c r="C35" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="29">
         <v>195</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="34" t="s">
+      <c r="F35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="34" t="s">
+      <c r="G35" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H35" s="34" t="s">
+      <c r="H35" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I35" s="29"/>
-      <c r="J35" s="33">
+      <c r="I35" s="25"/>
+      <c r="J35" s="29">
         <v>15568807</v>
       </c>
-      <c r="K35" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L35" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M35" s="35" t="s">
+      <c r="K35" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M35" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="N35" s="29"/>
-      <c r="O35" s="29"/>
-      <c r="P35" s="29"/>
-      <c r="Q35" s="29"/>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29"/>
-      <c r="Y35" s="29"/>
-      <c r="Z35" s="29"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
     </row>
     <row r="36" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A36" s="27">
+      <c r="A36" s="23">
         <v>35</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="33">
+      <c r="C36" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="29">
         <v>149</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E36" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="F36" s="34" t="s">
+      <c r="F36" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G36" s="34" t="s">
+      <c r="G36" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H36" s="34" t="s">
+      <c r="H36" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I36" s="29"/>
-      <c r="J36" s="33">
+      <c r="I36" s="25"/>
+      <c r="J36" s="29">
         <v>15568807</v>
       </c>
-      <c r="K36" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L36" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M36" s="35" t="s">
+      <c r="K36" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M36" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29"/>
-      <c r="Q36" s="29"/>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29"/>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29"/>
-      <c r="Y36" s="29"/>
-      <c r="Z36" s="29"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A37" s="27">
+      <c r="A37" s="23">
         <v>36</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="33">
+      <c r="C37" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="29">
         <v>111</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="E37" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="34" t="s">
+      <c r="F37" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G37" s="34" t="s">
+      <c r="G37" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H37" s="34" t="s">
+      <c r="H37" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I37" s="29"/>
-      <c r="J37" s="33">
+      <c r="I37" s="25"/>
+      <c r="J37" s="29">
         <v>15568807</v>
       </c>
-      <c r="K37" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L37" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M37" s="35" t="s">
+      <c r="K37" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M37" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
+      <c r="Q37" s="25"/>
+      <c r="R37" s="25"/>
+      <c r="S37" s="25"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A38" s="27">
+      <c r="A38" s="23">
         <v>37</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C38" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="33">
+      <c r="C38" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="29">
         <v>117</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F38" s="34" t="s">
+      <c r="F38" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G38" s="34" t="s">
+      <c r="G38" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="34" t="s">
+      <c r="H38" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I38" s="29"/>
-      <c r="J38" s="33">
+      <c r="I38" s="25"/>
+      <c r="J38" s="29">
         <v>15568807</v>
       </c>
-      <c r="K38" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L38" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M38" s="35" t="s">
+      <c r="K38" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M38" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="29"/>
-      <c r="Y38" s="29"/>
-      <c r="Z38" s="29"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
+      <c r="Q38" s="25"/>
+      <c r="R38" s="25"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A39" s="27">
+      <c r="A39" s="23">
         <v>38</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D39" s="33">
+      <c r="C39" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="29">
         <v>188</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F39" s="34" t="s">
+      <c r="F39" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G39" s="28" t="s">
+      <c r="G39" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="H39" s="34" t="s">
+      <c r="H39" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I39" s="29"/>
-      <c r="J39" s="33">
+      <c r="I39" s="25"/>
+      <c r="J39" s="29">
         <v>18817371</v>
       </c>
-      <c r="K39" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L39" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M39" s="30" t="s">
+      <c r="K39" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N39" s="29"/>
-      <c r="O39" s="29"/>
-      <c r="P39" s="29"/>
-      <c r="Q39" s="29"/>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29"/>
-      <c r="T39" s="29"/>
-      <c r="U39" s="29"/>
-      <c r="V39" s="29"/>
-      <c r="W39" s="29"/>
-      <c r="X39" s="29"/>
-      <c r="Y39" s="29"/>
-      <c r="Z39" s="29"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
+      <c r="Q39" s="25"/>
+      <c r="R39" s="25"/>
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A40" s="27">
+      <c r="A40" s="23">
         <v>39</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C40" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D40" s="33">
+      <c r="C40" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="29">
         <v>197</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="34" t="s">
+      <c r="F40" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="G40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="H40" s="34" t="s">
+      <c r="H40" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I40" s="29"/>
-      <c r="J40" s="33">
+      <c r="I40" s="25"/>
+      <c r="J40" s="29">
         <v>18817371</v>
       </c>
-      <c r="K40" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M40" s="30" t="s">
+      <c r="K40" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M40" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="25"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="25"/>
+      <c r="S40" s="25"/>
+      <c r="T40" s="25"/>
+      <c r="U40" s="25"/>
+      <c r="V40" s="25"/>
+      <c r="W40" s="25"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A41" s="27">
+      <c r="A41" s="23">
         <v>40</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" s="33">
+      <c r="C41" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="29">
         <v>117</v>
       </c>
-      <c r="E41" s="34" t="s">
+      <c r="E41" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="34" t="s">
+      <c r="F41" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G41" s="34" t="s">
+      <c r="G41" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H41" s="34" t="s">
+      <c r="H41" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="I41" s="29"/>
-      <c r="J41" s="33">
+      <c r="I41" s="25"/>
+      <c r="J41" s="29">
         <v>18826295</v>
       </c>
-      <c r="K41" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L41" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M41" s="35" t="s">
+      <c r="K41" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M41" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-      <c r="W41" s="29"/>
-      <c r="X41" s="29"/>
-      <c r="Y41" s="29"/>
-      <c r="Z41" s="29"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="25"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="25"/>
+      <c r="S41" s="25"/>
+      <c r="T41" s="25"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="25"/>
+      <c r="W41" s="25"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A42" s="27">
+      <c r="A42" s="23">
         <v>41</v>
       </c>
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="33">
+      <c r="C42" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="29">
         <v>253</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F42" s="34" t="s">
+      <c r="F42" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G42" s="34" t="s">
+      <c r="G42" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H42" s="34" t="s">
+      <c r="H42" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I42" s="29"/>
-      <c r="J42" s="33">
+      <c r="I42" s="25"/>
+      <c r="J42" s="29">
         <v>25548277</v>
       </c>
-      <c r="K42" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L42" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M42" s="30" t="s">
+      <c r="K42" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M42" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N42" s="29"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="29"/>
-      <c r="Q42" s="29"/>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29"/>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29"/>
-      <c r="V42" s="29"/>
-      <c r="W42" s="29"/>
-      <c r="X42" s="29"/>
-      <c r="Y42" s="29"/>
-      <c r="Z42" s="29"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25"/>
+      <c r="R42" s="25"/>
+      <c r="S42" s="25"/>
+      <c r="T42" s="25"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="25"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
     </row>
     <row r="43" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A43" s="27">
+      <c r="A43" s="23">
         <v>42</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D43" s="33">
+      <c r="C43" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="29">
         <v>247</v>
       </c>
-      <c r="E43" s="34" t="s">
+      <c r="E43" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="34" t="s">
+      <c r="F43" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G43" s="34" t="s">
+      <c r="G43" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="34" t="s">
+      <c r="H43" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I43" s="29"/>
-      <c r="J43" s="33">
+      <c r="I43" s="25"/>
+      <c r="J43" s="29">
         <v>25548277</v>
       </c>
-      <c r="K43" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L43" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M43" s="30" t="s">
+      <c r="K43" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M43" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="25"/>
+      <c r="P43" s="25"/>
+      <c r="Q43" s="25"/>
+      <c r="R43" s="25"/>
+      <c r="S43" s="25"/>
+      <c r="T43" s="25"/>
+      <c r="U43" s="25"/>
+      <c r="V43" s="25"/>
+      <c r="W43" s="25"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+      <c r="Z43" s="25"/>
     </row>
     <row r="44" spans="1:26" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A44" s="32">
+      <c r="A44" s="28">
         <v>43</v>
       </c>
-      <c r="B44" s="36" t="s">
+      <c r="B44" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="37">
+      <c r="C44" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="33">
         <v>101</v>
       </c>
-      <c r="E44" s="36" t="s">
+      <c r="E44" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="36" t="s">
+      <c r="F44" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G44" s="36" t="s">
+      <c r="G44" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="36" t="s">
+      <c r="H44" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I44" s="38"/>
-      <c r="J44" s="37">
+      <c r="I44" s="34"/>
+      <c r="J44" s="33">
         <v>26742843</v>
       </c>
-      <c r="K44" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="L44" s="36"/>
-      <c r="M44" s="42" t="s">
+      <c r="K44" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" s="32"/>
+      <c r="M44" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="N44" s="38" t="s">
+      <c r="N44" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="O44" s="38"/>
-      <c r="P44" s="38"/>
-      <c r="Q44" s="38"/>
-      <c r="R44" s="38"/>
-      <c r="S44" s="38"/>
-      <c r="T44" s="38"/>
-      <c r="U44" s="38"/>
-      <c r="V44" s="38"/>
-      <c r="W44" s="38"/>
-      <c r="X44" s="38"/>
-      <c r="Y44" s="38"/>
-      <c r="Z44" s="38"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="34"/>
+      <c r="W44" s="34"/>
+      <c r="X44" s="34"/>
+      <c r="Y44" s="34"/>
+      <c r="Z44" s="34"/>
     </row>
     <row r="45" spans="1:26" s="17" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A45" s="32">
+      <c r="A45" s="28">
         <v>44</v>
       </c>
-      <c r="B45" s="36" t="s">
+      <c r="B45" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C45" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" s="37">
+      <c r="C45" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="33">
         <v>190</v>
       </c>
-      <c r="E45" s="36" t="s">
+      <c r="E45" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="F45" s="36" t="s">
+      <c r="F45" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G45" s="36" t="s">
+      <c r="G45" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="36" t="s">
+      <c r="H45" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I45" s="38"/>
-      <c r="J45" s="37">
+      <c r="I45" s="34"/>
+      <c r="J45" s="33">
         <v>30944209</v>
       </c>
-      <c r="K45" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="L45" s="36"/>
-      <c r="M45" s="42" t="s">
+      <c r="K45" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="32"/>
+      <c r="M45" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="N45" s="38"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="38"/>
-      <c r="T45" s="38"/>
-      <c r="U45" s="38"/>
-      <c r="V45" s="38"/>
-      <c r="W45" s="38"/>
-      <c r="X45" s="38"/>
-      <c r="Y45" s="38"/>
-      <c r="Z45" s="38"/>
+      <c r="N45" s="34"/>
+      <c r="O45" s="34"/>
+      <c r="P45" s="34"/>
+      <c r="Q45" s="34"/>
+      <c r="R45" s="34"/>
+      <c r="S45" s="34"/>
+      <c r="T45" s="34"/>
+      <c r="U45" s="34"/>
+      <c r="V45" s="34"/>
+      <c r="W45" s="34"/>
+      <c r="X45" s="34"/>
+      <c r="Y45" s="34"/>
+      <c r="Z45" s="34"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A46" s="27">
-        <v>45</v>
-      </c>
-      <c r="B46" s="34" t="s">
+      <c r="A46" s="23">
+        <v>45</v>
+      </c>
+      <c r="B46" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C46" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" s="33">
+      <c r="C46" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="29">
         <v>117</v>
       </c>
-      <c r="E46" s="34" t="s">
+      <c r="E46" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F46" s="34" t="s">
+      <c r="F46" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="G46" s="34" t="s">
+      <c r="G46" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H46" s="34" t="s">
+      <c r="H46" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I46" s="29"/>
-      <c r="J46" s="41">
+      <c r="I46" s="25"/>
+      <c r="J46">
         <v>18826295</v>
       </c>
-      <c r="K46" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L46" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M46" s="30" t="s">
+      <c r="K46" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M46" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="25"/>
+      <c r="P46" s="25"/>
+      <c r="Q46" s="25"/>
+      <c r="R46" s="25"/>
+      <c r="S46" s="25"/>
+      <c r="T46" s="25"/>
+      <c r="U46" s="25"/>
+      <c r="V46" s="25"/>
+      <c r="W46" s="25"/>
+      <c r="X46" s="25"/>
+      <c r="Y46" s="25"/>
+      <c r="Z46" s="25"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A47" s="27">
+      <c r="A47" s="23">
         <v>46</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="33">
+      <c r="C47" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="29">
         <v>93</v>
       </c>
-      <c r="E47" s="34" t="s">
+      <c r="E47" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="34" t="s">
+      <c r="F47" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G47" s="34" t="s">
+      <c r="G47" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H47" s="34" t="s">
+      <c r="H47" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I47" s="29"/>
-      <c r="J47" s="33">
+      <c r="I47" s="25"/>
+      <c r="J47" s="29">
         <v>30337385</v>
       </c>
-      <c r="K47" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L47" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M47" s="30" t="s">
+      <c r="K47" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
-      <c r="V47" s="29"/>
-      <c r="W47" s="29"/>
-      <c r="X47" s="29"/>
-      <c r="Y47" s="29"/>
-      <c r="Z47" s="29"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="25"/>
+      <c r="P47" s="25"/>
+      <c r="Q47" s="25"/>
+      <c r="R47" s="25"/>
+      <c r="S47" s="25"/>
+      <c r="T47" s="25"/>
+      <c r="U47" s="25"/>
+      <c r="V47" s="25"/>
+      <c r="W47" s="25"/>
+      <c r="X47" s="25"/>
+      <c r="Y47" s="25"/>
+      <c r="Z47" s="25"/>
     </row>
     <row r="48" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A48" s="27">
+      <c r="A48" s="23">
         <v>47</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D48" s="33">
+      <c r="C48" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="29">
         <v>190</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="34" t="s">
+      <c r="F48" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="G48" s="34" t="s">
+      <c r="G48" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="34" t="s">
+      <c r="H48" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="29"/>
-      <c r="J48" s="33">
+      <c r="I48" s="25"/>
+      <c r="J48" s="29">
         <v>30337385</v>
       </c>
-      <c r="K48" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L48" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M48" s="30" t="s">
+      <c r="K48" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M48" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
-      <c r="Z48" s="29"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="25"/>
+      <c r="P48" s="25"/>
+      <c r="Q48" s="25"/>
+      <c r="R48" s="25"/>
+      <c r="S48" s="25"/>
+      <c r="T48" s="25"/>
+      <c r="U48" s="25"/>
+      <c r="V48" s="25"/>
+      <c r="W48" s="25"/>
+      <c r="X48" s="25"/>
+      <c r="Y48" s="25"/>
+      <c r="Z48" s="25"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A49" s="27">
+      <c r="A49" s="23">
         <v>48</v>
       </c>
-      <c r="B49" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="33">
+      <c r="B49" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="29">
+        <v>153</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I49" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J49" s="29">
+        <v>9158151</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M49" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="N49" s="25"/>
+      <c r="O49" s="25"/>
+      <c r="P49" s="25"/>
+      <c r="Q49" s="25"/>
+      <c r="R49" s="25"/>
+      <c r="S49" s="25"/>
+      <c r="T49" s="25"/>
+      <c r="U49" s="25"/>
+      <c r="V49" s="25"/>
+      <c r="W49" s="25"/>
+      <c r="X49" s="25"/>
+      <c r="Y49" s="25"/>
+      <c r="Z49" s="25"/>
+    </row>
+    <row r="50" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A50" s="23">
+        <v>49</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" s="29">
+        <v>156</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G50" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I50" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J50" s="29">
+        <v>9158151</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M50" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="25"/>
+      <c r="S50" s="25"/>
+      <c r="T50" s="25"/>
+      <c r="U50" s="25"/>
+      <c r="V50" s="25"/>
+      <c r="W50" s="25"/>
+      <c r="X50" s="25"/>
+      <c r="Y50" s="25"/>
+      <c r="Z50" s="25"/>
+    </row>
+    <row r="51" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A51" s="23">
+        <v>50</v>
+      </c>
+      <c r="B51" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="29">
         <v>254</v>
       </c>
-      <c r="E49" s="34" t="s">
+      <c r="E51" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G51" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I51" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J51" s="29">
+        <v>9158151</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M51" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="25"/>
+      <c r="R51" s="25"/>
+      <c r="S51" s="25"/>
+      <c r="T51" s="25"/>
+      <c r="U51" s="25"/>
+      <c r="V51" s="25"/>
+      <c r="W51" s="25"/>
+      <c r="X51" s="25"/>
+      <c r="Y51" s="25"/>
+      <c r="Z51" s="25"/>
+    </row>
+    <row r="52" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A52" s="23">
+        <v>51</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="29">
+        <v>269</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I52" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J52" s="29">
+        <v>7611281</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M52" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="25"/>
+      <c r="S52" s="25"/>
+      <c r="T52" s="25"/>
+      <c r="U52" s="25"/>
+      <c r="V52" s="25"/>
+      <c r="W52" s="25"/>
+      <c r="X52" s="25"/>
+      <c r="Y52" s="25"/>
+      <c r="Z52" s="25"/>
+    </row>
+    <row r="53" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A53" s="23">
+        <v>52</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="29">
+        <v>269</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G53" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J53">
+        <v>8872460</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M53" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N53" s="25"/>
+      <c r="O53" s="25"/>
+      <c r="P53" s="25"/>
+      <c r="Q53" s="25"/>
+      <c r="R53" s="25"/>
+      <c r="S53" s="25"/>
+      <c r="T53" s="25"/>
+      <c r="U53" s="25"/>
+      <c r="V53" s="25"/>
+      <c r="W53" s="25"/>
+      <c r="X53" s="25"/>
+      <c r="Y53" s="25"/>
+      <c r="Z53" s="25"/>
+    </row>
+    <row r="54" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A54" s="23">
+        <v>53</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="29">
+        <v>266</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="34" t="s">
+      <c r="G54" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I54" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J54">
+        <v>8872460</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M54" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N54" s="25"/>
+      <c r="O54" s="25"/>
+      <c r="P54" s="25"/>
+      <c r="Q54" s="25"/>
+      <c r="R54" s="25"/>
+      <c r="S54" s="25"/>
+      <c r="T54" s="25"/>
+      <c r="U54" s="25"/>
+      <c r="V54" s="25"/>
+      <c r="W54" s="25"/>
+      <c r="X54" s="25"/>
+      <c r="Y54" s="25"/>
+      <c r="Z54" s="25"/>
+    </row>
+    <row r="55" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A55" s="23">
+        <v>54</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="29">
+        <v>217</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G55" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H55" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I55" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J55">
+        <v>8872460</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M55" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25"/>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="25"/>
+      <c r="S55" s="25"/>
+      <c r="T55" s="25"/>
+      <c r="U55" s="25"/>
+      <c r="V55" s="25"/>
+      <c r="W55" s="25"/>
+      <c r="X55" s="25"/>
+      <c r="Y55" s="25"/>
+      <c r="Z55" s="25"/>
+    </row>
+    <row r="56" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A56" s="23">
+        <v>55</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="29">
+        <v>267</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I56" s="30"/>
+      <c r="J56" s="42">
+        <v>8872460</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M56" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="N56" s="25"/>
+      <c r="O56" s="25"/>
+      <c r="P56" s="25"/>
+      <c r="Q56" s="25"/>
+      <c r="R56" s="25"/>
+      <c r="S56" s="25"/>
+      <c r="T56" s="25"/>
+      <c r="U56" s="25"/>
+      <c r="V56" s="25"/>
+      <c r="W56" s="25"/>
+      <c r="X56" s="25"/>
+      <c r="Y56" s="25"/>
+      <c r="Z56" s="25"/>
+    </row>
+    <row r="57" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A57" s="23">
+        <v>56</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="29">
+        <v>249</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G57" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I57" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J57" s="42">
+        <v>9221765</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M57" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="N57" s="25"/>
+      <c r="O57" s="25"/>
+      <c r="P57" s="25"/>
+      <c r="Q57" s="25"/>
+      <c r="R57" s="25"/>
+      <c r="S57" s="25"/>
+      <c r="T57" s="25"/>
+      <c r="U57" s="25"/>
+      <c r="V57" s="25"/>
+      <c r="W57" s="25"/>
+      <c r="X57" s="25"/>
+      <c r="Y57" s="25"/>
+      <c r="Z57" s="25"/>
+    </row>
+    <row r="58" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A58" s="23">
+        <v>57</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="29">
+        <v>418</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I58" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J58" s="42">
+        <v>16685696</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M58" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="N58" s="25"/>
+      <c r="O58" s="25"/>
+      <c r="P58" s="25"/>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="25"/>
+      <c r="S58" s="25"/>
+      <c r="T58" s="25"/>
+      <c r="U58" s="25"/>
+      <c r="V58" s="25"/>
+      <c r="W58" s="25"/>
+      <c r="X58" s="25"/>
+      <c r="Y58" s="25"/>
+      <c r="Z58" s="25"/>
+    </row>
+    <row r="59" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A59" s="23">
+        <v>58</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="29">
+        <v>132</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="G49" s="34" t="s">
+      <c r="G59" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H49" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="I49" s="29"/>
-      <c r="J49" s="33">
-        <v>30337385</v>
-      </c>
-      <c r="K49" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L49" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M49" s="30" t="s">
+      <c r="H59" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I59" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J59" s="42">
+        <v>12588888</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M59" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="N59" s="25"/>
+      <c r="O59" s="25"/>
+      <c r="P59" s="25"/>
+      <c r="Q59" s="25"/>
+      <c r="R59" s="25"/>
+      <c r="S59" s="25"/>
+      <c r="T59" s="25"/>
+      <c r="U59" s="25"/>
+      <c r="V59" s="25"/>
+      <c r="W59" s="25"/>
+      <c r="X59" s="25"/>
+      <c r="Y59" s="25"/>
+      <c r="Z59" s="25"/>
+    </row>
+    <row r="60" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A60" s="23">
+        <v>59</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D60" s="29">
+        <v>127</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G60" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="I60" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J60" s="42">
+        <v>12588888</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M60" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="N60" s="25"/>
+      <c r="O60" s="25"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="25"/>
+      <c r="S60" s="25"/>
+      <c r="T60" s="25"/>
+      <c r="U60" s="25"/>
+      <c r="V60" s="25"/>
+      <c r="W60" s="25"/>
+      <c r="X60" s="25"/>
+      <c r="Y60" s="25"/>
+      <c r="Z60" s="25"/>
+    </row>
+    <row r="61" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A61" s="23">
+        <v>60</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="29">
+        <v>234</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G61" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H61" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I61" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="J61" s="42">
+        <v>18252226</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M61" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
+      <c r="S61" s="25"/>
+      <c r="T61" s="25"/>
+      <c r="U61" s="25"/>
+      <c r="V61" s="25"/>
+      <c r="W61" s="25"/>
+      <c r="X61" s="25"/>
+      <c r="Y61" s="25"/>
+      <c r="Z61" s="25"/>
+    </row>
+    <row r="62" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A62" s="23">
+        <v>61</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D62" s="29">
+        <v>57</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G62" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I62" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="J62" s="42">
+        <v>18252226</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M62" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
+      <c r="S62" s="25"/>
+      <c r="T62" s="25"/>
+      <c r="U62" s="25"/>
+      <c r="V62" s="25"/>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+    </row>
+    <row r="63" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A63" s="23">
+        <v>62</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" s="29">
+        <v>443</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="G63" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H63" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I63" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="J63" s="42">
+        <v>18252226</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M63" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="N63" s="25"/>
+      <c r="O63" s="25"/>
+      <c r="P63" s="25"/>
+      <c r="Q63" s="25"/>
+      <c r="R63" s="25"/>
+      <c r="S63" s="25"/>
+      <c r="T63" s="25"/>
+      <c r="U63" s="25"/>
+      <c r="V63" s="25"/>
+      <c r="W63" s="25"/>
+      <c r="X63" s="25"/>
+      <c r="Y63" s="25"/>
+      <c r="Z63" s="25"/>
+    </row>
+    <row r="64" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A64" s="23">
+        <v>63</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="29">
+        <v>74</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F64" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I64" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="J64" s="42">
+        <v>18252226</v>
+      </c>
+      <c r="K64" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L64" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M64" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="N64" s="25"/>
+      <c r="O64" s="25"/>
+      <c r="P64" s="25"/>
+      <c r="Q64" s="25"/>
+      <c r="R64" s="25"/>
+      <c r="S64" s="25"/>
+      <c r="T64" s="25"/>
+      <c r="U64" s="25"/>
+      <c r="V64" s="25"/>
+      <c r="W64" s="25"/>
+      <c r="X64" s="25"/>
+      <c r="Y64" s="25"/>
+      <c r="Z64" s="25"/>
+    </row>
+    <row r="65" spans="1:26" ht="27" thickBot="1">
+      <c r="A65" s="23">
+        <v>64</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="29">
+        <v>233</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H65" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J65" s="42">
+        <v>10195214</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L65" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M65" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="N65" s="25"/>
+      <c r="O65" s="25"/>
+      <c r="P65" s="25"/>
+      <c r="Q65" s="25"/>
+      <c r="R65" s="25"/>
+      <c r="S65" s="25"/>
+      <c r="T65" s="25"/>
+      <c r="U65" s="25"/>
+      <c r="V65" s="25"/>
+      <c r="W65" s="25"/>
+      <c r="X65" s="25"/>
+      <c r="Y65" s="25"/>
+      <c r="Z65" s="25"/>
+    </row>
+    <row r="66" spans="1:26" ht="27" thickBot="1">
+      <c r="A66" s="23">
         <v>65</v>
       </c>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-    </row>
-    <row r="50" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A50" s="27">
-        <v>49</v>
-      </c>
-      <c r="B50" s="34" t="s">
+      <c r="B66" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C50" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D50" s="33">
-        <v>153</v>
-      </c>
-      <c r="E50" s="34" t="s">
+      <c r="C66" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="29">
+        <v>285</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G66" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I66" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J66" s="42">
+        <v>10195214</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M66" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="N66" s="25"/>
+      <c r="O66" s="25"/>
+      <c r="P66" s="25"/>
+      <c r="Q66" s="25"/>
+      <c r="R66" s="25"/>
+      <c r="S66" s="25"/>
+      <c r="T66" s="25"/>
+      <c r="U66" s="25"/>
+      <c r="V66" s="25"/>
+      <c r="W66" s="25"/>
+      <c r="X66" s="25"/>
+      <c r="Y66" s="25"/>
+      <c r="Z66" s="25"/>
+    </row>
+    <row r="67" spans="1:26" ht="27" thickBot="1">
+      <c r="A67" s="23">
+        <v>66</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="29">
+        <v>241</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H67" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="I67" s="25"/>
+      <c r="J67" s="36">
+        <v>8788941</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M67" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="N67" s="25"/>
+      <c r="O67" s="25"/>
+      <c r="P67" s="25"/>
+      <c r="Q67" s="25"/>
+      <c r="R67" s="25"/>
+      <c r="S67" s="25"/>
+      <c r="T67" s="25"/>
+      <c r="U67" s="25"/>
+      <c r="V67" s="25"/>
+      <c r="W67" s="25"/>
+      <c r="X67" s="25"/>
+      <c r="Y67" s="25"/>
+      <c r="Z67" s="25"/>
+    </row>
+    <row r="68" spans="1:26" ht="39.75" thickBot="1">
+      <c r="A68" s="23">
+        <v>67</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="29">
+        <v>264</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I68" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="J68" s="36">
+        <v>7531341</v>
+      </c>
+      <c r="K68" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M68" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="N68" s="25"/>
+      <c r="O68" s="25"/>
+      <c r="P68" s="25"/>
+      <c r="Q68" s="25"/>
+      <c r="R68" s="25"/>
+      <c r="S68" s="25"/>
+      <c r="T68" s="25"/>
+      <c r="U68" s="25"/>
+      <c r="V68" s="25"/>
+      <c r="W68" s="25"/>
+      <c r="X68" s="25"/>
+      <c r="Y68" s="25"/>
+      <c r="Z68" s="25"/>
+    </row>
+    <row r="69" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A69" s="23">
+        <v>68</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D69" s="29">
+        <v>64</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G69" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I69" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J69" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L69" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M69" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N69" s="25"/>
+      <c r="O69" s="25"/>
+      <c r="P69" s="25"/>
+      <c r="Q69" s="25"/>
+      <c r="R69" s="25"/>
+      <c r="S69" s="25"/>
+      <c r="T69" s="25"/>
+      <c r="U69" s="25"/>
+      <c r="V69" s="25"/>
+      <c r="W69" s="25"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="25"/>
+    </row>
+    <row r="70" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A70" s="23">
+        <v>69</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="29">
+        <v>147</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G70" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H70" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I70" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J70" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K70" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L70" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M70" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N70" s="25"/>
+      <c r="O70" s="25"/>
+      <c r="P70" s="25"/>
+      <c r="Q70" s="25"/>
+      <c r="R70" s="25"/>
+      <c r="S70" s="25"/>
+      <c r="T70" s="25"/>
+      <c r="U70" s="25"/>
+      <c r="V70" s="25"/>
+      <c r="W70" s="25"/>
+      <c r="X70" s="25"/>
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="25"/>
+    </row>
+    <row r="71" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A71" s="23">
+        <v>70</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="29">
+        <v>43</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F71" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I71" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J71" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M71" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N71" s="25"/>
+      <c r="O71" s="25"/>
+      <c r="P71" s="25"/>
+      <c r="Q71" s="25"/>
+      <c r="R71" s="25"/>
+      <c r="S71" s="25"/>
+      <c r="T71" s="25"/>
+      <c r="U71" s="25"/>
+      <c r="V71" s="25"/>
+      <c r="W71" s="25"/>
+      <c r="X71" s="25"/>
+      <c r="Y71" s="25"/>
+      <c r="Z71" s="25"/>
+    </row>
+    <row r="72" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A72" s="23">
+        <v>71</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="29">
+        <v>245</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F72" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G72" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H72" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I72" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J72" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K72" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L72" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M72" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N72" s="25"/>
+      <c r="O72" s="25"/>
+      <c r="P72" s="25"/>
+      <c r="Q72" s="25"/>
+      <c r="R72" s="25"/>
+      <c r="S72" s="25"/>
+      <c r="T72" s="25"/>
+      <c r="U72" s="25"/>
+      <c r="V72" s="25"/>
+      <c r="W72" s="25"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+    </row>
+    <row r="73" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A73" s="23">
+        <v>72</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="29">
+        <v>185</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I73" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J73" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L73" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M73" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N73" s="25"/>
+      <c r="O73" s="25"/>
+      <c r="P73" s="25"/>
+      <c r="Q73" s="25"/>
+      <c r="R73" s="25"/>
+      <c r="S73" s="25"/>
+      <c r="T73" s="25"/>
+      <c r="U73" s="25"/>
+      <c r="V73" s="25"/>
+      <c r="W73" s="25"/>
+      <c r="X73" s="25"/>
+      <c r="Y73" s="25"/>
+      <c r="Z73" s="25"/>
+    </row>
+    <row r="74" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A74" s="23">
+        <v>73</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="29">
+        <v>311</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H74" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I74" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J74" s="36">
+        <v>9158150</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L74" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M74" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="N74" s="25"/>
+      <c r="O74" s="25"/>
+      <c r="P74" s="25"/>
+      <c r="Q74" s="25"/>
+      <c r="R74" s="25"/>
+      <c r="S74" s="25"/>
+      <c r="T74" s="25"/>
+      <c r="U74" s="25"/>
+      <c r="V74" s="25"/>
+      <c r="W74" s="25"/>
+      <c r="X74" s="25"/>
+      <c r="Y74" s="25"/>
+      <c r="Z74" s="25"/>
+    </row>
+    <row r="75" spans="1:26" ht="27" thickBot="1">
+      <c r="A75" s="23">
+        <v>74</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" s="29">
+        <v>368</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H75" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I75" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J75" s="36">
+        <v>8957026</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L75" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M75" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="N75" s="25"/>
+      <c r="O75" s="25"/>
+      <c r="P75" s="25"/>
+      <c r="Q75" s="25"/>
+      <c r="R75" s="25"/>
+      <c r="S75" s="25"/>
+      <c r="T75" s="25"/>
+      <c r="U75" s="25"/>
+      <c r="V75" s="25"/>
+      <c r="W75" s="25"/>
+      <c r="X75" s="25"/>
+      <c r="Y75" s="25"/>
+      <c r="Z75" s="25"/>
+    </row>
+    <row r="76" spans="1:26" ht="27" thickBot="1">
+      <c r="A76" s="23">
+        <v>75</v>
+      </c>
+      <c r="B76" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D76" s="29">
+        <v>432</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G76" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I76" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J76" s="36">
+        <v>8957026</v>
+      </c>
+      <c r="K76" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L76" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M76" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="N76" s="25"/>
+      <c r="O76" s="25"/>
+      <c r="P76" s="25"/>
+      <c r="Q76" s="25"/>
+      <c r="R76" s="25"/>
+      <c r="S76" s="25"/>
+      <c r="T76" s="25"/>
+      <c r="U76" s="25"/>
+      <c r="V76" s="25"/>
+      <c r="W76" s="25"/>
+      <c r="X76" s="25"/>
+      <c r="Y76" s="25"/>
+      <c r="Z76" s="25"/>
+    </row>
+    <row r="77" spans="1:26" ht="39.75" thickBot="1">
+      <c r="A77" s="23">
+        <v>76</v>
+      </c>
+      <c r="B77" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="29">
+        <v>121</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G77" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I77" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="J77" s="36">
+        <v>8755487</v>
+      </c>
+      <c r="K77" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L77" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M77" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="N77" s="25"/>
+      <c r="O77" s="25"/>
+      <c r="P77" s="25"/>
+      <c r="Q77" s="25"/>
+      <c r="R77" s="25"/>
+      <c r="S77" s="25"/>
+      <c r="T77" s="25"/>
+      <c r="U77" s="25"/>
+      <c r="V77" s="25"/>
+      <c r="W77" s="25"/>
+      <c r="X77" s="25"/>
+      <c r="Y77" s="25"/>
+      <c r="Z77" s="25"/>
+    </row>
+    <row r="78" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A78" s="23">
+        <v>77</v>
+      </c>
+      <c r="B78" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="29">
+        <v>250</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F78" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G78" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I78" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J78" s="36">
+        <v>12499478</v>
+      </c>
+      <c r="K78" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L78" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M78" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N78" s="25"/>
+      <c r="O78" s="25"/>
+      <c r="P78" s="25"/>
+      <c r="Q78" s="25"/>
+      <c r="R78" s="25"/>
+      <c r="S78" s="25"/>
+      <c r="T78" s="25"/>
+      <c r="U78" s="25"/>
+      <c r="V78" s="25"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="25"/>
+      <c r="Y78" s="25"/>
+      <c r="Z78" s="25"/>
+    </row>
+    <row r="79" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A79" s="23">
+        <v>78</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="29">
+        <v>250</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I79" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J79" s="36">
+        <v>12499478</v>
+      </c>
+      <c r="K79" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L79" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M79" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N79" s="25"/>
+      <c r="O79" s="25"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="25"/>
+      <c r="R79" s="25"/>
+      <c r="S79" s="25"/>
+      <c r="T79" s="25"/>
+      <c r="U79" s="25"/>
+      <c r="V79" s="25"/>
+      <c r="W79" s="25"/>
+      <c r="X79" s="25"/>
+      <c r="Y79" s="25"/>
+      <c r="Z79" s="25"/>
+    </row>
+    <row r="80" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A80" s="23">
+        <v>79</v>
+      </c>
+      <c r="B80" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="29">
+        <v>245</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F80" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G80" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H80" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I80" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J80" s="36">
+        <v>12499478</v>
+      </c>
+      <c r="K80" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L80" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M80" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
+      <c r="R80" s="25"/>
+      <c r="S80" s="25"/>
+      <c r="T80" s="25"/>
+      <c r="U80" s="25"/>
+      <c r="V80" s="25"/>
+      <c r="W80" s="25"/>
+      <c r="X80" s="25"/>
+      <c r="Y80" s="25"/>
+      <c r="Z80" s="25"/>
+    </row>
+    <row r="81" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A81" s="23">
+        <v>80</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="29">
+        <v>245</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H81" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I81" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J81" s="36">
+        <v>12499478</v>
+      </c>
+      <c r="K81" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L81" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M81" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="N81" s="25"/>
+      <c r="O81" s="25"/>
+      <c r="P81" s="25"/>
+      <c r="Q81" s="25"/>
+      <c r="R81" s="25"/>
+      <c r="S81" s="25"/>
+      <c r="T81" s="25"/>
+      <c r="U81" s="25"/>
+      <c r="V81" s="25"/>
+      <c r="W81" s="25"/>
+      <c r="X81" s="25"/>
+      <c r="Y81" s="25"/>
+      <c r="Z81" s="25"/>
+    </row>
+    <row r="82" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A82" s="23">
+        <v>81</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="29">
+        <v>59</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I82" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="J82" s="36">
+        <v>11435464</v>
+      </c>
+      <c r="K82" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L82" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M82" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="N82" s="25"/>
+      <c r="O82" s="25"/>
+      <c r="P82" s="25"/>
+      <c r="Q82" s="25"/>
+      <c r="R82" s="25"/>
+      <c r="S82" s="25"/>
+      <c r="T82" s="25"/>
+      <c r="U82" s="25"/>
+      <c r="V82" s="25"/>
+      <c r="W82" s="25"/>
+      <c r="X82" s="25"/>
+      <c r="Y82" s="25"/>
+      <c r="Z82" s="25"/>
+    </row>
+    <row r="83" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A83" s="23">
+        <v>82</v>
+      </c>
+      <c r="B83" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="29">
+        <v>263</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F83" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G83" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H83" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I83" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J83" s="36">
+        <v>8651643</v>
+      </c>
+      <c r="K83" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L83" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M83" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="N83" s="25"/>
+      <c r="O83" s="25"/>
+      <c r="P83" s="25"/>
+      <c r="Q83" s="25"/>
+      <c r="R83" s="25"/>
+      <c r="S83" s="25"/>
+      <c r="T83" s="25"/>
+      <c r="U83" s="25"/>
+      <c r="V83" s="25"/>
+      <c r="W83" s="25"/>
+      <c r="X83" s="25"/>
+      <c r="Y83" s="25"/>
+      <c r="Z83" s="25"/>
+    </row>
+    <row r="84" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A84" s="23">
+        <v>83</v>
+      </c>
+      <c r="B84" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="29">
+        <v>266</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F84" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H84" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I84" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J84" s="36">
+        <v>27375219</v>
+      </c>
+      <c r="K84" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L84" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M84" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="N84" s="25"/>
+      <c r="O84" s="25"/>
+      <c r="P84" s="25"/>
+      <c r="Q84" s="25"/>
+      <c r="R84" s="25"/>
+      <c r="S84" s="25"/>
+      <c r="T84" s="25"/>
+      <c r="U84" s="25"/>
+      <c r="V84" s="25"/>
+      <c r="W84" s="25"/>
+      <c r="X84" s="25"/>
+      <c r="Y84" s="25"/>
+      <c r="Z84" s="25"/>
+    </row>
+    <row r="85" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A85" s="23">
+        <v>84</v>
+      </c>
+      <c r="B85" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="29">
+        <v>265</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H85" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="I85" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J85" s="36">
+        <v>27375219</v>
+      </c>
+      <c r="K85" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L85" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M85" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="N85" s="25"/>
+      <c r="O85" s="25"/>
+      <c r="P85" s="25"/>
+      <c r="Q85" s="25"/>
+      <c r="R85" s="25"/>
+      <c r="S85" s="25"/>
+      <c r="T85" s="25"/>
+      <c r="U85" s="25"/>
+      <c r="V85" s="25"/>
+      <c r="W85" s="25"/>
+      <c r="X85" s="25"/>
+      <c r="Y85" s="25"/>
+      <c r="Z85" s="25"/>
+    </row>
+    <row r="86" spans="1:26" ht="27" thickBot="1">
+      <c r="A86" s="23">
+        <v>85</v>
+      </c>
+      <c r="B86" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C86" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="29">
+        <v>229</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H86" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J86" s="44">
+        <v>16624571</v>
+      </c>
+      <c r="K86" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L86" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M86" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="N86" s="25"/>
+      <c r="O86" s="25"/>
+      <c r="P86" s="25"/>
+      <c r="Q86" s="25"/>
+      <c r="R86" s="25"/>
+      <c r="S86" s="25"/>
+      <c r="T86" s="25"/>
+      <c r="U86" s="25"/>
+      <c r="V86" s="25"/>
+      <c r="W86" s="25"/>
+      <c r="X86" s="25"/>
+      <c r="Y86" s="25"/>
+      <c r="Z86" s="25"/>
+    </row>
+    <row r="87" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A87" s="23">
+        <v>86</v>
+      </c>
+      <c r="B87" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="29">
+        <v>1314</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H87" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I87" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J87" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K87" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L87" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M87" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N87" s="25"/>
+      <c r="O87" s="25"/>
+      <c r="P87" s="25"/>
+      <c r="Q87" s="25"/>
+      <c r="R87" s="25"/>
+      <c r="S87" s="25"/>
+      <c r="T87" s="25"/>
+      <c r="U87" s="25"/>
+      <c r="V87" s="25"/>
+      <c r="W87" s="25"/>
+      <c r="X87" s="25"/>
+      <c r="Y87" s="25"/>
+      <c r="Z87" s="25"/>
+    </row>
+    <row r="88" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A88" s="23">
+        <v>87</v>
+      </c>
+      <c r="B88" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="29">
+        <v>711</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F88" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G88" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H88" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I88" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J88" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K88" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L88" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M88" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N88" s="25"/>
+      <c r="O88" s="25"/>
+      <c r="P88" s="25"/>
+      <c r="Q88" s="25"/>
+      <c r="R88" s="25"/>
+      <c r="S88" s="25"/>
+      <c r="T88" s="25"/>
+      <c r="U88" s="25"/>
+      <c r="V88" s="25"/>
+      <c r="W88" s="25"/>
+      <c r="X88" s="25"/>
+      <c r="Y88" s="25"/>
+      <c r="Z88" s="25"/>
+    </row>
+    <row r="89" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A89" s="23">
+        <v>88</v>
+      </c>
+      <c r="B89" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="29">
+        <v>865</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F89" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G89" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H89" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I89" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J89" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K89" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L89" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M89" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N89" s="25"/>
+      <c r="O89" s="25"/>
+      <c r="P89" s="25"/>
+      <c r="Q89" s="25"/>
+      <c r="R89" s="25"/>
+      <c r="S89" s="25"/>
+      <c r="T89" s="25"/>
+      <c r="U89" s="25"/>
+      <c r="V89" s="25"/>
+      <c r="W89" s="25"/>
+      <c r="X89" s="25"/>
+      <c r="Y89" s="25"/>
+      <c r="Z89" s="25"/>
+    </row>
+    <row r="90" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A90" s="23">
+        <v>89</v>
+      </c>
+      <c r="B90" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="29">
+        <v>610</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F90" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="G90" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I90" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J90" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K90" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L90" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M90" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N90" s="25"/>
+      <c r="O90" s="25"/>
+      <c r="P90" s="25"/>
+      <c r="Q90" s="25"/>
+      <c r="R90" s="25"/>
+      <c r="S90" s="25"/>
+      <c r="T90" s="25"/>
+      <c r="U90" s="25"/>
+      <c r="V90" s="25"/>
+      <c r="W90" s="25"/>
+      <c r="X90" s="25"/>
+      <c r="Y90" s="25"/>
+      <c r="Z90" s="25"/>
+    </row>
+    <row r="91" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A91" s="23">
+        <v>90</v>
+      </c>
+      <c r="B91" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="29">
+        <v>712</v>
+      </c>
+      <c r="E91" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I91" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J91" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K91" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L91" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M91" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N91" s="25"/>
+      <c r="O91" s="25"/>
+      <c r="P91" s="25"/>
+      <c r="Q91" s="25"/>
+      <c r="R91" s="25"/>
+      <c r="S91" s="25"/>
+      <c r="T91" s="25"/>
+      <c r="U91" s="25"/>
+      <c r="V91" s="25"/>
+      <c r="W91" s="25"/>
+      <c r="X91" s="25"/>
+      <c r="Y91" s="25"/>
+      <c r="Z91" s="25"/>
+    </row>
+    <row r="92" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A92" s="23">
+        <v>91</v>
+      </c>
+      <c r="B92" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="29">
+        <v>965</v>
+      </c>
+      <c r="E92" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F92" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H92" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I92" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J92" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K92" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L92" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M92" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N92" s="25"/>
+      <c r="O92" s="25"/>
+      <c r="P92" s="25"/>
+      <c r="Q92" s="25"/>
+      <c r="R92" s="25"/>
+      <c r="S92" s="25"/>
+      <c r="T92" s="25"/>
+      <c r="U92" s="25"/>
+      <c r="V92" s="25"/>
+      <c r="W92" s="25"/>
+      <c r="X92" s="25"/>
+      <c r="Y92" s="25"/>
+      <c r="Z92" s="25"/>
+    </row>
+    <row r="93" spans="1:26" ht="27" thickBot="1">
+      <c r="A93" s="23">
+        <v>92</v>
+      </c>
+      <c r="B93" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C93" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="29">
+        <v>442</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H93" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I93" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="J93" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K93" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L93" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M93" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N93" s="25"/>
+      <c r="O93" s="25"/>
+      <c r="P93" s="25"/>
+      <c r="Q93" s="25"/>
+      <c r="R93" s="25"/>
+      <c r="S93" s="25"/>
+      <c r="T93" s="25"/>
+      <c r="U93" s="25"/>
+      <c r="V93" s="25"/>
+      <c r="W93" s="25"/>
+      <c r="X93" s="25"/>
+      <c r="Y93" s="25"/>
+      <c r="Z93" s="25"/>
+    </row>
+    <row r="94" spans="1:26" ht="27" thickBot="1">
+      <c r="A94" s="23">
+        <v>93</v>
+      </c>
+      <c r="B94" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="29">
+        <v>727</v>
+      </c>
+      <c r="E94" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G94" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I94" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="J94" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K94" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L94" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M94" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N94" s="25"/>
+      <c r="O94" s="25"/>
+      <c r="P94" s="25"/>
+      <c r="Q94" s="25"/>
+      <c r="R94" s="25"/>
+      <c r="S94" s="25"/>
+      <c r="T94" s="25"/>
+      <c r="U94" s="25"/>
+      <c r="V94" s="25"/>
+      <c r="W94" s="25"/>
+      <c r="X94" s="25"/>
+      <c r="Y94" s="25"/>
+      <c r="Z94" s="25"/>
+    </row>
+    <row r="95" spans="1:26" ht="27" thickBot="1">
+      <c r="A95" s="23">
+        <v>94</v>
+      </c>
+      <c r="B95" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="D95" s="29">
+        <v>1327</v>
+      </c>
+      <c r="E95" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="F50" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="34" t="s">
+      <c r="F95" s="30"/>
+      <c r="G95" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H95" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I95" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="J95" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K95" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L95" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M95" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N95" s="25"/>
+      <c r="O95" s="25"/>
+      <c r="P95" s="25"/>
+      <c r="Q95" s="25"/>
+      <c r="R95" s="25"/>
+      <c r="S95" s="25"/>
+      <c r="T95" s="25"/>
+      <c r="U95" s="25"/>
+      <c r="V95" s="25"/>
+      <c r="W95" s="25"/>
+      <c r="X95" s="25"/>
+      <c r="Y95" s="25"/>
+      <c r="Z95" s="25"/>
+    </row>
+    <row r="96" spans="1:26" ht="27" thickBot="1">
+      <c r="A96" s="23">
+        <v>95</v>
+      </c>
+      <c r="B96" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" s="29">
+        <v>778</v>
+      </c>
+      <c r="E96" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F96" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I96" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="J96" s="36">
+        <v>29395675</v>
+      </c>
+      <c r="K96" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L96" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M96" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="N96" s="25"/>
+      <c r="O96" s="25"/>
+      <c r="P96" s="25"/>
+      <c r="Q96" s="25"/>
+      <c r="R96" s="25"/>
+      <c r="S96" s="25"/>
+      <c r="T96" s="25"/>
+      <c r="U96" s="25"/>
+      <c r="V96" s="25"/>
+      <c r="W96" s="25"/>
+      <c r="X96" s="25"/>
+      <c r="Y96" s="25"/>
+      <c r="Z96" s="25"/>
+    </row>
+    <row r="97" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A97" s="23">
+        <v>96</v>
+      </c>
+      <c r="B97" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C97" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" s="29">
+        <v>78</v>
+      </c>
+      <c r="E97" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F97" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="H50" s="34" t="s">
+      <c r="H97" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I97" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J97" s="36">
+        <v>14592868</v>
+      </c>
+      <c r="K97" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L97" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M97" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N97" s="25"/>
+      <c r="O97" s="25"/>
+      <c r="P97" s="25"/>
+      <c r="Q97" s="25"/>
+      <c r="R97" s="25"/>
+      <c r="S97" s="25"/>
+      <c r="T97" s="25"/>
+      <c r="U97" s="25"/>
+      <c r="V97" s="25"/>
+      <c r="W97" s="25"/>
+      <c r="X97" s="25"/>
+      <c r="Y97" s="25"/>
+      <c r="Z97" s="25"/>
+    </row>
+    <row r="98" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A98" s="23">
+        <v>97</v>
+      </c>
+      <c r="B98" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C98" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="29">
+        <v>221</v>
+      </c>
+      <c r="E98" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F98" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I98" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="J98" s="36">
+        <v>14592868</v>
+      </c>
+      <c r="K98" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L98" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M98" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N98" s="25"/>
+      <c r="O98" s="25"/>
+      <c r="P98" s="25"/>
+      <c r="Q98" s="25"/>
+      <c r="R98" s="25"/>
+      <c r="S98" s="25"/>
+      <c r="T98" s="25"/>
+      <c r="U98" s="25"/>
+      <c r="V98" s="25"/>
+      <c r="W98" s="25"/>
+      <c r="X98" s="25"/>
+      <c r="Y98" s="25"/>
+      <c r="Z98" s="25"/>
+    </row>
+    <row r="99" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A99" s="23">
+        <v>98</v>
+      </c>
+      <c r="B99" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="29">
+        <v>121</v>
+      </c>
+      <c r="E99" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="F99" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="G99" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I99" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J99" s="36">
+        <v>14592868</v>
+      </c>
+      <c r="K99" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L99" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M99" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N99" s="25"/>
+      <c r="O99" s="25"/>
+      <c r="P99" s="25"/>
+      <c r="Q99" s="25"/>
+      <c r="R99" s="25"/>
+      <c r="S99" s="25"/>
+      <c r="T99" s="25"/>
+      <c r="U99" s="25"/>
+      <c r="V99" s="25"/>
+      <c r="W99" s="25"/>
+      <c r="X99" s="25"/>
+      <c r="Y99" s="25"/>
+      <c r="Z99" s="25"/>
+    </row>
+    <row r="100" spans="1:26" ht="27" thickBot="1">
+      <c r="A100" s="23">
+        <v>99</v>
+      </c>
+      <c r="B100" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D100" s="29">
+        <v>256</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="I100" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J100" s="36">
+        <v>14592868</v>
+      </c>
+      <c r="K100" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L100" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M100" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="N100" s="25"/>
+      <c r="O100" s="25"/>
+      <c r="P100" s="25"/>
+      <c r="Q100" s="25"/>
+      <c r="R100" s="25"/>
+      <c r="S100" s="25"/>
+      <c r="T100" s="25"/>
+      <c r="U100" s="25"/>
+      <c r="V100" s="25"/>
+      <c r="W100" s="25"/>
+      <c r="X100" s="25"/>
+      <c r="Y100" s="25"/>
+      <c r="Z100" s="25"/>
+    </row>
+    <row r="101" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A101" s="29">
+        <v>100</v>
+      </c>
+      <c r="B101" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101" s="29">
+        <v>313</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="I50" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J50" s="33">
-        <v>9158151</v>
-      </c>
-      <c r="K50" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L50" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M50" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="N50" s="29"/>
-      <c r="O50" s="29"/>
-      <c r="P50" s="29"/>
-      <c r="Q50" s="29"/>
-      <c r="R50" s="29"/>
-      <c r="S50" s="29"/>
-      <c r="T50" s="29"/>
-      <c r="U50" s="29"/>
-      <c r="V50" s="29"/>
-      <c r="W50" s="29"/>
-      <c r="X50" s="29"/>
-      <c r="Y50" s="29"/>
-      <c r="Z50" s="29"/>
-    </row>
-    <row r="51" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A51" s="27">
-        <v>50</v>
-      </c>
-      <c r="B51" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="33">
-        <v>156</v>
-      </c>
-      <c r="E51" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G51" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H51" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I51" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J51" s="33">
-        <v>9158151</v>
-      </c>
-      <c r="K51" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L51" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M51" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="29"/>
-      <c r="T51" s="29"/>
-      <c r="U51" s="29"/>
-      <c r="V51" s="29"/>
-      <c r="W51" s="29"/>
-      <c r="X51" s="29"/>
-      <c r="Y51" s="29"/>
-      <c r="Z51" s="29"/>
-    </row>
-    <row r="52" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A52" s="27">
-        <v>51</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="33">
-        <v>254</v>
-      </c>
-      <c r="E52" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="G52" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I52" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J52" s="33">
-        <v>9158151</v>
-      </c>
-      <c r="K52" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L52" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M52" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-    </row>
-    <row r="53" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A53" s="27">
-        <v>52</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="33">
-        <v>269</v>
-      </c>
-      <c r="E53" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="F53" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="G53" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H53" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I53" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J53" s="33">
-        <v>7611281</v>
-      </c>
-      <c r="K53" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L53" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M53" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="N53" s="29"/>
-      <c r="O53" s="29"/>
-      <c r="P53" s="29"/>
-      <c r="Q53" s="29"/>
-      <c r="R53" s="29"/>
-      <c r="S53" s="29"/>
-      <c r="T53" s="29"/>
-      <c r="U53" s="29"/>
-      <c r="V53" s="29"/>
-      <c r="W53" s="29"/>
-      <c r="X53" s="29"/>
-      <c r="Y53" s="29"/>
-      <c r="Z53" s="29"/>
-    </row>
-    <row r="54" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A54" s="27">
-        <v>53</v>
-      </c>
-      <c r="B54" s="34" t="s">
+      <c r="I101" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J101" s="36">
+        <v>18806275</v>
+      </c>
+      <c r="K101" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L101" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M101" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="N101" s="25"/>
+      <c r="O101" s="25"/>
+      <c r="P101" s="25"/>
+      <c r="Q101" s="25"/>
+      <c r="R101" s="25"/>
+      <c r="S101" s="25"/>
+      <c r="T101" s="25"/>
+      <c r="U101" s="25"/>
+      <c r="V101" s="25"/>
+      <c r="W101" s="25"/>
+      <c r="X101" s="25"/>
+      <c r="Y101" s="25"/>
+      <c r="Z101" s="25"/>
+    </row>
+    <row r="102" spans="1:26" ht="27" thickBot="1">
+      <c r="A102" s="23">
+        <v>101</v>
+      </c>
+      <c r="B102" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="33">
-        <v>269</v>
-      </c>
-      <c r="E54" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="F54" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="G54" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H54" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I54" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J54" s="41">
-        <v>8872460</v>
-      </c>
-      <c r="K54" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L54" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M54" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
-      <c r="Q54" s="29"/>
-      <c r="R54" s="29"/>
-      <c r="S54" s="29"/>
-      <c r="T54" s="29"/>
-      <c r="U54" s="29"/>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
-      <c r="X54" s="29"/>
-      <c r="Y54" s="29"/>
-      <c r="Z54" s="29"/>
-    </row>
-    <row r="55" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A55" s="27">
-        <v>54</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" s="33">
-        <v>266</v>
-      </c>
-      <c r="E55" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="G55" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H55" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I55" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J55" s="41">
-        <v>8872460</v>
-      </c>
-      <c r="K55" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L55" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M55" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-    </row>
-    <row r="56" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A56" s="27">
-        <v>55</v>
-      </c>
-      <c r="B56" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="33">
-        <v>217</v>
-      </c>
-      <c r="E56" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="F56" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="G56" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H56" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I56" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J56" s="41">
-        <v>8872460</v>
-      </c>
-      <c r="K56" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L56" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M56" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
-      <c r="Q56" s="29"/>
-      <c r="R56" s="29"/>
-      <c r="S56" s="29"/>
-      <c r="T56" s="29"/>
-      <c r="U56" s="29"/>
-      <c r="V56" s="29"/>
-      <c r="W56" s="29"/>
-      <c r="X56" s="29"/>
-      <c r="Y56" s="29"/>
-      <c r="Z56" s="29"/>
-    </row>
-    <row r="57" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A57" s="27">
-        <v>56</v>
-      </c>
-      <c r="B57" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" s="33">
-        <v>267</v>
-      </c>
-      <c r="E57" s="34" t="s">
+      <c r="C102" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D102" s="29">
+        <v>311</v>
+      </c>
+      <c r="E102" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F102" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F57" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="H57" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I57" s="34"/>
-      <c r="J57" s="41">
-        <v>8872460</v>
-      </c>
-      <c r="K57" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L57" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M57" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="29"/>
-      <c r="T57" s="29"/>
-      <c r="U57" s="29"/>
-      <c r="V57" s="29"/>
-      <c r="W57" s="29"/>
-      <c r="X57" s="29"/>
-      <c r="Y57" s="29"/>
-      <c r="Z57" s="29"/>
-    </row>
-    <row r="58" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A58" s="33">
-        <v>14</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D58" s="33">
-        <v>249</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="G58" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H58" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I58" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J58" s="40">
-        <v>9221765</v>
-      </c>
-      <c r="K58" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L58" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M58" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-    </row>
-    <row r="59" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A59" s="33">
-        <v>14</v>
-      </c>
-      <c r="B59" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="33">
-        <v>418</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F59" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="H59" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I59" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="J59" s="40">
-        <v>16685696</v>
-      </c>
-      <c r="K59" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M59" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="N59" s="29"/>
-      <c r="O59" s="29"/>
-      <c r="P59" s="29"/>
-      <c r="Q59" s="29"/>
-      <c r="R59" s="29"/>
-      <c r="S59" s="29"/>
-      <c r="T59" s="29"/>
-      <c r="U59" s="29"/>
-      <c r="V59" s="29"/>
-      <c r="W59" s="29"/>
-      <c r="X59" s="29"/>
-      <c r="Y59" s="29"/>
-      <c r="Z59" s="29"/>
-    </row>
-    <row r="60" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A60" s="33">
-        <v>1</v>
-      </c>
-      <c r="B60" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="33">
-        <v>132</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="G60" s="34" t="s">
+      <c r="G102" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H60" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I60" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="J60" s="40">
-        <v>12588888</v>
-      </c>
-      <c r="K60" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L60" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M60" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
-      <c r="R60" s="29"/>
-      <c r="S60" s="29"/>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
-      <c r="W60" s="29"/>
-      <c r="X60" s="29"/>
-      <c r="Y60" s="29"/>
-      <c r="Z60" s="29"/>
-    </row>
-    <row r="61" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A61" s="33">
-        <v>2</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" s="33">
-        <v>127</v>
-      </c>
-      <c r="E61" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G61" s="34" t="s">
+      <c r="H102" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="I102" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J102" s="36">
+        <v>19544078</v>
+      </c>
+      <c r="K102" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L102" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M102" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="N102" s="25"/>
+      <c r="O102" s="25"/>
+      <c r="P102" s="25"/>
+      <c r="Q102" s="25"/>
+      <c r="R102" s="25"/>
+      <c r="S102" s="25"/>
+      <c r="T102" s="25"/>
+      <c r="U102" s="25"/>
+      <c r="V102" s="25"/>
+      <c r="W102" s="25"/>
+      <c r="X102" s="25"/>
+      <c r="Y102" s="25"/>
+      <c r="Z102" s="25"/>
+    </row>
+    <row r="103" spans="1:26" ht="27" thickBot="1">
+      <c r="A103" s="29">
+        <v>102</v>
+      </c>
+      <c r="B103" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="C103" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D103" s="29">
+        <v>15</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="G103" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H61" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="I61" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="J61" s="40">
-        <v>12588888</v>
-      </c>
-      <c r="K61" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="L61" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="M61" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
+      <c r="H103" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="I103" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="J103" s="36">
+        <v>19544078</v>
+      </c>
+      <c r="K103" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="L103" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="M103" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="N103" s="25"/>
+      <c r="O103" s="25"/>
+      <c r="P103" s="25"/>
+      <c r="Q103" s="25"/>
+      <c r="R103" s="25"/>
+      <c r="S103" s="25"/>
+      <c r="T103" s="25"/>
+      <c r="U103" s="25"/>
+      <c r="V103" s="25"/>
+      <c r="W103" s="25"/>
+      <c r="X103" s="25"/>
+      <c r="Y103" s="25"/>
+      <c r="Z103" s="25"/>
+    </row>
+    <row r="104" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A104" s="29"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="29"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="30"/>
+      <c r="J104" s="29"/>
+      <c r="K104" s="30"/>
+      <c r="L104" s="30"/>
+      <c r="M104" s="26"/>
+      <c r="N104" s="25"/>
+      <c r="O104" s="25"/>
+      <c r="P104" s="25"/>
+      <c r="Q104" s="25"/>
+      <c r="R104" s="25"/>
+      <c r="S104" s="25"/>
+      <c r="T104" s="25"/>
+      <c r="U104" s="25"/>
+      <c r="V104" s="25"/>
+      <c r="W104" s="25"/>
+      <c r="X104" s="25"/>
+      <c r="Y104" s="25"/>
+      <c r="Z104" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M101" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M7" r:id="rId1" xr:uid="{87A5E94E-2CC0-43A2-A62B-F1F66B9F07E8}"/>
@@ -3899,32 +6281,74 @@
     <hyperlink ref="M46" r:id="rId34" xr:uid="{5234AE53-586C-437C-8B1B-F9B9F5BAF4E5}"/>
     <hyperlink ref="M47" r:id="rId35" xr:uid="{E5AB601A-72DD-4DC0-8819-42479754DA94}"/>
     <hyperlink ref="M48" r:id="rId36" xr:uid="{40394FE4-79E6-4374-A6FF-90C7E820EEA1}"/>
-    <hyperlink ref="M49" r:id="rId37" xr:uid="{20B2AE89-5EE8-49AC-82D2-CE15E6BA653C}"/>
-    <hyperlink ref="M6" r:id="rId38" xr:uid="{73352BA5-3366-4855-BC7E-6BE3E374D9B4}"/>
-    <hyperlink ref="M45" r:id="rId39" xr:uid="{9A1BD006-F772-4B5D-940D-C6F60CC8D128}"/>
-    <hyperlink ref="M44" r:id="rId40" xr:uid="{12D56FAB-EBDE-4D7E-A804-230EBFB324A7}"/>
-    <hyperlink ref="M9" r:id="rId41" xr:uid="{B400455F-51D7-4740-ABEE-E22C5B3CA07D}"/>
-    <hyperlink ref="M11" r:id="rId42" xr:uid="{7EE75401-EAA0-45B7-8729-1DC6E2714FF0}"/>
-    <hyperlink ref="M13" r:id="rId43" xr:uid="{16ED0890-0655-427B-8DCC-FF29660630B5}"/>
-    <hyperlink ref="M15" r:id="rId44" xr:uid="{7D163924-2DED-4D6E-BC16-0D793BBA0824}"/>
-    <hyperlink ref="M8" r:id="rId45" xr:uid="{04EF7988-C49C-45E8-B843-46DE872A6143}"/>
-    <hyperlink ref="M10" r:id="rId46" xr:uid="{6043AAA8-E7DA-47C6-BC9A-10DF206C6C83}"/>
-    <hyperlink ref="M12" r:id="rId47" xr:uid="{8D891B94-37B5-4069-B1F9-34703F0DA97A}"/>
-    <hyperlink ref="M14" r:id="rId48" xr:uid="{F36E742E-D562-48D2-9D1B-0BE0564B9986}"/>
-    <hyperlink ref="M51" r:id="rId49" xr:uid="{A379B062-15C5-4914-B88F-3A83BF04D478}"/>
-    <hyperlink ref="M52" r:id="rId50" xr:uid="{297A788F-AAE4-44C5-BA15-F853A7F9707A}"/>
-    <hyperlink ref="M53" r:id="rId51" xr:uid="{3B4EFE48-42E5-4784-A67A-5FEFCF87F11C}"/>
-    <hyperlink ref="M50" r:id="rId52" xr:uid="{3DBB07B3-B058-42A4-8772-E266B4DD79F9}"/>
-    <hyperlink ref="M54" r:id="rId53" xr:uid="{2BC6AFD7-211A-4CBF-AC79-AE02E530B086}"/>
-    <hyperlink ref="M55" r:id="rId54" xr:uid="{F7A87068-80BE-4024-803F-85C50F0DEB8E}"/>
-    <hyperlink ref="M56" r:id="rId55" xr:uid="{79606C21-9CAD-480D-9F1F-236CB6C3173C}"/>
-    <hyperlink ref="M57" r:id="rId56" xr:uid="{637ACCB4-AA60-4599-BECD-20CA6D332165}"/>
-    <hyperlink ref="M58" r:id="rId57" xr:uid="{A78FD088-FEAC-4300-8C68-E03E3E2FC0D5}"/>
-    <hyperlink ref="M59" r:id="rId58" xr:uid="{43813E1F-9E2D-4988-AD96-C98268965EFF}"/>
-    <hyperlink ref="M60" r:id="rId59" xr:uid="{ACED4252-8ECF-48C4-B544-D228285A0631}"/>
-    <hyperlink ref="M61" r:id="rId60" xr:uid="{82F3DD28-A78A-44E8-AD35-D416503455F3}"/>
+    <hyperlink ref="M6" r:id="rId37" xr:uid="{73352BA5-3366-4855-BC7E-6BE3E374D9B4}"/>
+    <hyperlink ref="M45" r:id="rId38" xr:uid="{9A1BD006-F772-4B5D-940D-C6F60CC8D128}"/>
+    <hyperlink ref="M44" r:id="rId39" xr:uid="{12D56FAB-EBDE-4D7E-A804-230EBFB324A7}"/>
+    <hyperlink ref="M9" r:id="rId40" xr:uid="{B400455F-51D7-4740-ABEE-E22C5B3CA07D}"/>
+    <hyperlink ref="M11" r:id="rId41" xr:uid="{7EE75401-EAA0-45B7-8729-1DC6E2714FF0}"/>
+    <hyperlink ref="M13" r:id="rId42" xr:uid="{16ED0890-0655-427B-8DCC-FF29660630B5}"/>
+    <hyperlink ref="M15" r:id="rId43" xr:uid="{7D163924-2DED-4D6E-BC16-0D793BBA0824}"/>
+    <hyperlink ref="M8" r:id="rId44" xr:uid="{04EF7988-C49C-45E8-B843-46DE872A6143}"/>
+    <hyperlink ref="M10" r:id="rId45" xr:uid="{6043AAA8-E7DA-47C6-BC9A-10DF206C6C83}"/>
+    <hyperlink ref="M12" r:id="rId46" xr:uid="{8D891B94-37B5-4069-B1F9-34703F0DA97A}"/>
+    <hyperlink ref="M14" r:id="rId47" xr:uid="{F36E742E-D562-48D2-9D1B-0BE0564B9986}"/>
+    <hyperlink ref="M50" r:id="rId48" xr:uid="{A379B062-15C5-4914-B88F-3A83BF04D478}"/>
+    <hyperlink ref="M51" r:id="rId49" xr:uid="{297A788F-AAE4-44C5-BA15-F853A7F9707A}"/>
+    <hyperlink ref="M52" r:id="rId50" xr:uid="{3B4EFE48-42E5-4784-A67A-5FEFCF87F11C}"/>
+    <hyperlink ref="M49" r:id="rId51" xr:uid="{3DBB07B3-B058-42A4-8772-E266B4DD79F9}"/>
+    <hyperlink ref="M53" r:id="rId52" xr:uid="{2BC6AFD7-211A-4CBF-AC79-AE02E530B086}"/>
+    <hyperlink ref="M54" r:id="rId53" xr:uid="{F7A87068-80BE-4024-803F-85C50F0DEB8E}"/>
+    <hyperlink ref="M55" r:id="rId54" xr:uid="{79606C21-9CAD-480D-9F1F-236CB6C3173C}"/>
+    <hyperlink ref="M56" r:id="rId55" xr:uid="{637ACCB4-AA60-4599-BECD-20CA6D332165}"/>
+    <hyperlink ref="M57" r:id="rId56" xr:uid="{A78FD088-FEAC-4300-8C68-E03E3E2FC0D5}"/>
+    <hyperlink ref="M58" r:id="rId57" xr:uid="{43813E1F-9E2D-4988-AD96-C98268965EFF}"/>
+    <hyperlink ref="M59" r:id="rId58" xr:uid="{ACED4252-8ECF-48C4-B544-D228285A0631}"/>
+    <hyperlink ref="M60" r:id="rId59" xr:uid="{82F3DD28-A78A-44E8-AD35-D416503455F3}"/>
+    <hyperlink ref="M61" r:id="rId60" xr:uid="{ABC3429C-4B7F-463F-93D2-0460B00C8809}"/>
+    <hyperlink ref="M62" r:id="rId61" xr:uid="{77323968-040C-481E-9B03-90DCF52DC713}"/>
+    <hyperlink ref="M63" r:id="rId62" xr:uid="{0F313AED-3785-450B-BBB1-5DB080FD7E8E}"/>
+    <hyperlink ref="M64" r:id="rId63" xr:uid="{AF63059F-22C6-4F80-83D9-36B4EFE86A26}"/>
+    <hyperlink ref="M65" r:id="rId64" xr:uid="{4E7C5400-4019-45A2-9F4B-9F76CE9A2E9C}"/>
+    <hyperlink ref="M66" r:id="rId65" xr:uid="{E96021EB-511F-48AC-B320-807804E1789E}"/>
+    <hyperlink ref="M67" r:id="rId66" xr:uid="{A1954F6C-B85D-4BC7-AF41-5B5A970485B4}"/>
+    <hyperlink ref="M68" r:id="rId67" xr:uid="{A87AD91F-5A48-492D-8FC9-321F95732AF6}"/>
+    <hyperlink ref="M69" r:id="rId68" xr:uid="{90DAFD70-D518-4443-B264-5FA44510FB09}"/>
+    <hyperlink ref="M70" r:id="rId69" xr:uid="{04F1FF09-0DBF-470E-9366-FD7F70408934}"/>
+    <hyperlink ref="M71" r:id="rId70" xr:uid="{C099B4DA-1150-4B0A-B5DC-AB98F2D9B87B}"/>
+    <hyperlink ref="M72" r:id="rId71" xr:uid="{F8018741-117E-4EB8-A9F7-965DC2A8D663}"/>
+    <hyperlink ref="M73" r:id="rId72" xr:uid="{4037AAB5-DC5C-4EAF-8FA3-39DB5C5D3EBC}"/>
+    <hyperlink ref="M74" r:id="rId73" xr:uid="{C4FDD388-437A-4395-B37B-03D1867C4E67}"/>
+    <hyperlink ref="M75" r:id="rId74" xr:uid="{5DCD795C-7D6D-490E-8791-A8F234D04E48}"/>
+    <hyperlink ref="M76" r:id="rId75" xr:uid="{CE1E84ED-B4C5-40C9-9DAA-9095EDF8C422}"/>
+    <hyperlink ref="M77" r:id="rId76" xr:uid="{7C04E17D-2DE1-488C-BF52-BF49816A8107}"/>
+    <hyperlink ref="M78" r:id="rId77" xr:uid="{9B754242-FDDB-48A6-A082-28746827E2E3}"/>
+    <hyperlink ref="M79" r:id="rId78" xr:uid="{8F8A3F32-7BE8-4F85-AC32-1FB649406278}"/>
+    <hyperlink ref="M80" r:id="rId79" xr:uid="{9306CFD5-7DF7-4893-BCAE-01CCC5813971}"/>
+    <hyperlink ref="M81" r:id="rId80" xr:uid="{2870E944-C711-4A8D-8468-5A47C4815055}"/>
+    <hyperlink ref="M82" r:id="rId81" xr:uid="{32F7BBB5-FB8A-4326-894E-DEE35055BC73}"/>
+    <hyperlink ref="M83" r:id="rId82" xr:uid="{E83CB72F-BA24-409C-BA79-D4CA7559B3DE}"/>
+    <hyperlink ref="M84" r:id="rId83" xr:uid="{ECD22EA3-474D-4F60-9E2D-2517BA15C77A}"/>
+    <hyperlink ref="M85" r:id="rId84" xr:uid="{81F9502D-B4C1-400D-B4AE-10BC5E9EA116}"/>
+    <hyperlink ref="M86" r:id="rId85" xr:uid="{1951EFAE-FB45-481C-9DA4-2EE774F208D3}"/>
+    <hyperlink ref="M87" r:id="rId86" xr:uid="{FF411B55-D4C2-4B01-AA98-334544955491}"/>
+    <hyperlink ref="M88" r:id="rId87" xr:uid="{F4554E42-C381-449C-82F8-2A902F91A079}"/>
+    <hyperlink ref="M89" r:id="rId88" xr:uid="{2FAAC769-EE2D-47EA-8524-EADF126E2F0C}"/>
+    <hyperlink ref="M90" r:id="rId89" xr:uid="{731674E0-35D7-4927-80EB-F2A09FB4A391}"/>
+    <hyperlink ref="M93" r:id="rId90" xr:uid="{4A34DA10-891E-4305-8FB4-F5836ECFCD4D}"/>
+    <hyperlink ref="M96" r:id="rId91" xr:uid="{88CD6B1C-70C8-4DB6-B971-66A0A614D4CB}"/>
+    <hyperlink ref="M91" r:id="rId92" xr:uid="{7663FEBC-5AD8-4F0A-B958-C138CC3C6FD8}"/>
+    <hyperlink ref="M94" r:id="rId93" xr:uid="{FABAC870-38ED-41F5-9E13-C997D9B9E230}"/>
+    <hyperlink ref="M92" r:id="rId94" xr:uid="{72BE05CB-23EB-4499-A71B-057D0201F6A7}"/>
+    <hyperlink ref="M95" r:id="rId95" xr:uid="{D4B5740A-B5E6-4DB3-8D36-B305671C657E}"/>
+    <hyperlink ref="M97" r:id="rId96" xr:uid="{06B62B2B-F412-4802-A51C-8CA68A2C5341}"/>
+    <hyperlink ref="M98" r:id="rId97" xr:uid="{708EE928-EA0E-4928-B9D9-580FFC7F6FC4}"/>
+    <hyperlink ref="M99" r:id="rId98" xr:uid="{6E202567-F47D-4533-8420-5561977273C1}"/>
+    <hyperlink ref="M100" r:id="rId99" xr:uid="{EFAFA72C-28AC-4C3E-8F5F-EBAD08B96534}"/>
+    <hyperlink ref="M101" r:id="rId100" xr:uid="{54C3C719-642C-4FB4-935E-6F68F9FF1EA0}"/>
+    <hyperlink ref="M102" r:id="rId101" xr:uid="{1290A572-5479-4A05-97D5-318A168C36D3}"/>
+    <hyperlink ref="M103" r:id="rId102" xr:uid="{3AB4961F-FE7D-4AAE-9CF5-E909E911EB62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId61"/>
+  <pageSetup orientation="portrait" r:id="rId103"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -1,28 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D2342F-9CE0-44A8-9C21-1A8E088E31D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{22AA718B-3CF1-41F0-9FD9-24A00B70E52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11115" yWindow="4650" windowWidth="17085" windowHeight="11100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8715" yWindow="2700" windowWidth="18585" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
-  </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1856" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="201">
   <si>
     <t>OID</t>
   </si>
@@ -560,6 +557,90 @@
   </si>
   <si>
     <t>Cell-attached Patch-clamp</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1124/mol.110.066357</t>
+  </si>
+  <si>
+    <t>Nicotine dependence</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1074/jbc.m111.264044</t>
+  </si>
+  <si>
+    <t>Infantile parkinsonism</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.parkreldis.2020.02.003</t>
+  </si>
+  <si>
+    <t>No Effect</t>
+  </si>
+  <si>
+    <t>TEVC / FMP</t>
+  </si>
+  <si>
+    <t>FMP</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1074/jbc.m113.509356</t>
+  </si>
+  <si>
+    <t>CHRNA9</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nsmb.2900</t>
+  </si>
+  <si>
+    <t>same gene but different initial amino acids</t>
+  </si>
+  <si>
+    <t>Patch Clamp</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s00415-011-6204-9</t>
+  </si>
+  <si>
+    <t>Electromyography</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1136/jnnp.2008.148189</t>
+  </si>
+  <si>
+    <t>Slow-channel syndrome</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1113/jphysiol.2007.127977</t>
+  </si>
+  <si>
+    <t>Whole-cell clamp</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.97.7.3643</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1085/jgp.202012606</t>
+  </si>
+  <si>
+    <t>have another data which is conflicting at the start</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1073/pnas.1315775110</t>
+  </si>
+  <si>
+    <t>conflicting data from different papers</t>
+  </si>
+  <si>
+    <t>Single-channel recording</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/nature04156</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1085/jgp.116.3.449</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC5479107/</t>
   </si>
 </sst>
 </file>
@@ -662,7 +743,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -700,124 +781,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="65"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color indexed="65"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -910,15 +880,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -951,6 +912,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Excel Built-in Normal 1" xfId="1" xr:uid="{D585C33E-D382-4BD9-8030-CD231C838104}"/>
@@ -968,83 +936,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Hari Krishna M" refreshedDate="46104.773455439812" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="12" xr:uid="{D46278BB-AB3C-4D15-83D7-4E1858EF776D}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A138:A150" sheet="Sheet1"/>
-  </cacheSource>
-  <cacheFields count="1">
-    <cacheField name="137" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="138" maxValue="149"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="12">
-  <r>
-    <n v="138"/>
-  </r>
-  <r>
-    <n v="139"/>
-  </r>
-  <r>
-    <n v="140"/>
-  </r>
-  <r>
-    <n v="141"/>
-  </r>
-  <r>
-    <n v="142"/>
-  </r>
-  <r>
-    <n v="143"/>
-  </r>
-  <r>
-    <n v="144"/>
-  </r>
-  <r>
-    <n v="145"/>
-  </r>
-  <r>
-    <n v="146"/>
-  </r>
-  <r>
-    <n v="147"/>
-  </r>
-  <r>
-    <n v="148"/>
-  </r>
-  <r>
-    <n v="149"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4788376-CD48-4D24-BC20-55CDD9366BFD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="1">
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1309,111 +1200,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFE8A678-60F4-4B11-AD16-51D29C8607AD}">
-  <dimension ref="A3:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z191"/>
+  <dimension ref="A1:Z233"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="2" customWidth="1"/>
@@ -1508,7 +1296,7 @@
       <c r="L2" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="45" t="s">
+      <c r="M2" s="36" t="s">
         <v>56</v>
       </c>
       <c r="N2" s="21"/>
@@ -1560,7 +1348,7 @@
       <c r="L3" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="45" t="s">
+      <c r="M3" s="36" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="21"/>
@@ -1610,7 +1398,7 @@
       <c r="L4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="36" t="s">
         <v>56</v>
       </c>
       <c r="N4" s="21"/>
@@ -1660,7 +1448,7 @@
       <c r="L5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="45" t="s">
+      <c r="M5" s="36" t="s">
         <v>56</v>
       </c>
       <c r="N5" s="21"/>
@@ -1712,7 +1500,7 @@
       <c r="L6" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M6" s="46" t="s">
+      <c r="M6" s="37" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1751,7 +1539,7 @@
       <c r="L7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="M7" s="47" t="s">
+      <c r="M7" s="38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1790,7 +1578,7 @@
       <c r="L8" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M8" s="47" t="s">
+      <c r="M8" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N8" s="30" t="s">
@@ -1844,7 +1632,7 @@
       <c r="L9" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M9" s="47" t="s">
+      <c r="M9" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N9" s="30"/>
@@ -1896,7 +1684,7 @@
       <c r="L10" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M10" s="47" t="s">
+      <c r="M10" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N10" s="30"/>
@@ -1948,7 +1736,7 @@
       <c r="L11" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="47" t="s">
+      <c r="M11" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N11" s="30"/>
@@ -2000,7 +1788,7 @@
       <c r="L12" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="47" t="s">
+      <c r="M12" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N12" s="30"/>
@@ -2052,7 +1840,7 @@
       <c r="L13" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="47" t="s">
+      <c r="M13" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N13" s="30"/>
@@ -2104,7 +1892,7 @@
       <c r="L14" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N14" s="30"/>
@@ -2156,7 +1944,7 @@
       <c r="L15" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="47" t="s">
+      <c r="M15" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N15" s="30"/>
@@ -2210,7 +1998,7 @@
       <c r="L16" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="48" t="s">
+      <c r="M16" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2251,7 +2039,7 @@
       <c r="L17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="49" t="s">
+      <c r="M17" s="40" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2292,7 +2080,7 @@
       <c r="L18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M18" s="48" t="s">
+      <c r="M18" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2333,7 +2121,7 @@
       <c r="L19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M19" s="48" t="s">
+      <c r="M19" s="39" t="s">
         <v>41</v>
       </c>
       <c r="N19" s="8" t="s">
@@ -2377,7 +2165,7 @@
       <c r="L20" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M20" s="48" t="s">
+      <c r="M20" s="39" t="s">
         <v>41</v>
       </c>
       <c r="N20" s="8" t="s">
@@ -2421,7 +2209,7 @@
       <c r="L21" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="48" t="s">
+      <c r="M21" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2460,7 +2248,7 @@
       <c r="L22" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M22" s="48" t="s">
+      <c r="M22" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2501,7 +2289,7 @@
       <c r="L23" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M23" s="48" t="s">
+      <c r="M23" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2542,7 +2330,7 @@
       <c r="L24" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M24" s="48" t="s">
+      <c r="M24" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2583,7 +2371,7 @@
       <c r="L25" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M25" s="48" t="s">
+      <c r="M25" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2624,7 +2412,7 @@
       <c r="L26" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M26" s="48" t="s">
+      <c r="M26" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2665,7 +2453,7 @@
       <c r="L27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M27" s="48" t="s">
+      <c r="M27" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2704,7 +2492,7 @@
       <c r="L28" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M28" s="48" t="s">
+      <c r="M28" s="39" t="s">
         <v>41</v>
       </c>
       <c r="N28" s="8" t="s">
@@ -2746,7 +2534,7 @@
       <c r="L29" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M29" s="48" t="s">
+      <c r="M29" s="39" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2787,7 +2575,7 @@
       <c r="L30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="M30" s="46" t="s">
+      <c r="M30" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N30" s="15"/>
@@ -2841,7 +2629,7 @@
       <c r="L31" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="M31" s="46" t="s">
+      <c r="M31" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N31" s="15"/>
@@ -2895,7 +2683,7 @@
       <c r="L32" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="M32" s="46" t="s">
+      <c r="M32" s="37" t="s">
         <v>50</v>
       </c>
       <c r="N32" s="18"/>
@@ -2947,7 +2735,7 @@
       <c r="L33" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="M33" s="46" t="s">
+      <c r="M33" s="37" t="s">
         <v>52</v>
       </c>
       <c r="N33" s="18"/>
@@ -3001,7 +2789,7 @@
       <c r="L34" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="M34" s="46" t="s">
+      <c r="M34" s="37" t="s">
         <v>50</v>
       </c>
       <c r="N34" s="18"/>
@@ -3053,7 +2841,7 @@
       <c r="L35" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M35" s="50" t="s">
+      <c r="M35" s="41" t="s">
         <v>60</v>
       </c>
       <c r="N35" s="21"/>
@@ -3105,7 +2893,7 @@
       <c r="L36" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M36" s="50" t="s">
+      <c r="M36" s="41" t="s">
         <v>60</v>
       </c>
       <c r="N36" s="21"/>
@@ -3157,7 +2945,7 @@
       <c r="L37" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M37" s="50" t="s">
+      <c r="M37" s="41" t="s">
         <v>60</v>
       </c>
       <c r="N37" s="21"/>
@@ -3209,7 +2997,7 @@
       <c r="L38" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M38" s="50" t="s">
+      <c r="M38" s="41" t="s">
         <v>60</v>
       </c>
       <c r="N38" s="21"/>
@@ -3261,7 +3049,7 @@
       <c r="L39" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="45" t="s">
+      <c r="M39" s="36" t="s">
         <v>61</v>
       </c>
       <c r="N39" s="21"/>
@@ -3313,7 +3101,7 @@
       <c r="L40" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M40" s="45" t="s">
+      <c r="M40" s="36" t="s">
         <v>61</v>
       </c>
       <c r="N40" s="21"/>
@@ -3365,7 +3153,7 @@
       <c r="L41" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M41" s="50" t="s">
+      <c r="M41" s="41" t="s">
         <v>61</v>
       </c>
       <c r="N41" s="21"/>
@@ -3417,7 +3205,7 @@
       <c r="L42" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M42" s="45" t="s">
+      <c r="M42" s="36" t="s">
         <v>62</v>
       </c>
       <c r="N42" s="21"/>
@@ -3469,7 +3257,7 @@
       <c r="L43" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M43" s="45" t="s">
+      <c r="M43" s="36" t="s">
         <v>62</v>
       </c>
       <c r="N43" s="21"/>
@@ -3521,7 +3309,7 @@
       <c r="L44" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="M44" s="51" t="s">
+      <c r="M44" s="42" t="s">
         <v>56</v>
       </c>
       <c r="N44" s="26" t="s">
@@ -3575,7 +3363,7 @@
       <c r="L45" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="M45" s="51" t="s">
+      <c r="M45" s="42" t="s">
         <v>56</v>
       </c>
       <c r="N45" s="26"/>
@@ -3627,7 +3415,7 @@
       <c r="L46" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M46" s="45" t="s">
+      <c r="M46" s="36" t="s">
         <v>61</v>
       </c>
       <c r="N46" s="21"/>
@@ -3679,7 +3467,7 @@
       <c r="L47" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M47" s="45" t="s">
+      <c r="M47" s="36" t="s">
         <v>64</v>
       </c>
       <c r="N47" s="21"/>
@@ -3731,7 +3519,7 @@
       <c r="L48" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M48" s="45" t="s">
+      <c r="M48" s="36" t="s">
         <v>64</v>
       </c>
       <c r="N48" s="21"/>
@@ -3770,13 +3558,13 @@
       <c r="G49" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H49" s="52" t="s">
+      <c r="H49" s="43" t="s">
         <v>139</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J49" s="53">
+      <c r="J49" s="44">
         <v>40992289</v>
       </c>
       <c r="K49" s="35" t="s">
@@ -3785,10 +3573,12 @@
       <c r="L49" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M49" s="54" t="s">
+      <c r="M49" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="N49" s="30"/>
+      <c r="N49" s="30" t="s">
+        <v>184</v>
+      </c>
       <c r="O49" s="30"/>
       <c r="P49" s="30"/>
       <c r="Q49" s="30"/>
@@ -3830,7 +3620,7 @@
       <c r="I50" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="J50" s="53">
+      <c r="J50" s="44">
         <v>34999496</v>
       </c>
       <c r="K50" s="29" t="s">
@@ -3839,7 +3629,7 @@
       <c r="L50" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M50" s="54" t="s">
+      <c r="M50" s="45" t="s">
         <v>142</v>
       </c>
       <c r="N50" s="30"/>
@@ -3893,7 +3683,7 @@
       <c r="L51" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M51" s="54" t="s">
+      <c r="M51" s="45" t="s">
         <v>70</v>
       </c>
       <c r="N51" s="30"/>
@@ -3947,7 +3737,7 @@
       <c r="L52" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M52" s="45" t="s">
+      <c r="M52" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N52" s="21"/>
@@ -4001,7 +3791,7 @@
       <c r="L53" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M53" s="45" t="s">
+      <c r="M53" s="36" t="s">
         <v>70</v>
       </c>
       <c r="N53" s="21"/>
@@ -4046,7 +3836,7 @@
       <c r="I54" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="J54" s="53">
+      <c r="J54" s="44">
         <v>33216040</v>
       </c>
       <c r="K54" s="35" t="s">
@@ -4055,10 +3845,12 @@
       <c r="L54" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M54" s="54" t="s">
+      <c r="M54" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="N54" s="30"/>
+      <c r="N54" s="30" t="s">
+        <v>196</v>
+      </c>
       <c r="O54" s="30"/>
       <c r="P54" s="30"/>
       <c r="Q54" s="30"/>
@@ -4109,7 +3901,7 @@
       <c r="L55" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="M55" s="54" t="s">
+      <c r="M55" s="45" t="s">
         <v>70</v>
       </c>
       <c r="N55" s="30"/>
@@ -4163,7 +3955,7 @@
       <c r="L56" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M56" s="45" t="s">
+      <c r="M56" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N56" s="21"/>
@@ -4217,7 +4009,7 @@
       <c r="L57" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M57" s="45" t="s">
+      <c r="M57" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N57" s="21"/>
@@ -4271,7 +4063,7 @@
       <c r="L58" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M58" s="45" t="s">
+      <c r="M58" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N58" s="21"/>
@@ -4323,7 +4115,7 @@
       <c r="L59" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M59" s="45" t="s">
+      <c r="M59" s="36" t="s">
         <v>74</v>
       </c>
       <c r="N59" s="21"/>
@@ -4377,7 +4169,7 @@
       <c r="L60" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M60" s="50" t="s">
+      <c r="M60" s="41" t="s">
         <v>75</v>
       </c>
       <c r="N60" s="21"/>
@@ -4431,7 +4223,7 @@
       <c r="L61" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M61" s="45" t="s">
+      <c r="M61" s="36" t="s">
         <v>76</v>
       </c>
       <c r="N61" s="21"/>
@@ -4485,7 +4277,7 @@
       <c r="L62" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M62" s="45" t="s">
+      <c r="M62" s="36" t="s">
         <v>80</v>
       </c>
       <c r="N62" s="21"/>
@@ -4539,7 +4331,7 @@
       <c r="L63" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M63" s="45" t="s">
+      <c r="M63" s="36" t="s">
         <v>80</v>
       </c>
       <c r="N63" s="21"/>
@@ -4593,7 +4385,7 @@
       <c r="L64" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M64" s="45" t="s">
+      <c r="M64" s="36" t="s">
         <v>85</v>
       </c>
       <c r="N64" s="21"/>
@@ -4647,7 +4439,7 @@
       <c r="L65" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M65" s="45" t="s">
+      <c r="M65" s="36" t="s">
         <v>85</v>
       </c>
       <c r="N65" s="21"/>
@@ -4701,7 +4493,7 @@
       <c r="L66" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M66" s="45" t="s">
+      <c r="M66" s="36" t="s">
         <v>85</v>
       </c>
       <c r="N66" s="21"/>
@@ -4755,7 +4547,7 @@
       <c r="L67" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M67" s="45" t="s">
+      <c r="M67" s="36" t="s">
         <v>85</v>
       </c>
       <c r="N67" s="21"/>
@@ -4809,7 +4601,7 @@
       <c r="L68" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M68" s="45" t="s">
+      <c r="M68" s="36" t="s">
         <v>88</v>
       </c>
       <c r="N68" s="21"/>
@@ -4863,7 +4655,7 @@
       <c r="L69" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M69" s="45" t="s">
+      <c r="M69" s="36" t="s">
         <v>88</v>
       </c>
       <c r="N69" s="21"/>
@@ -4915,7 +4707,7 @@
       <c r="L70" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M70" s="50" t="s">
+      <c r="M70" s="41" t="s">
         <v>89</v>
       </c>
       <c r="N70" s="21"/>
@@ -4969,7 +4761,7 @@
       <c r="L71" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M71" s="45" t="s">
+      <c r="M71" s="36" t="s">
         <v>91</v>
       </c>
       <c r="N71" s="21"/>
@@ -5023,7 +4815,7 @@
       <c r="L72" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M72" s="45" t="s">
+      <c r="M72" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N72" s="21"/>
@@ -5077,7 +4869,7 @@
       <c r="L73" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M73" s="45" t="s">
+      <c r="M73" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N73" s="21"/>
@@ -5131,7 +4923,7 @@
       <c r="L74" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M74" s="45" t="s">
+      <c r="M74" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N74" s="21"/>
@@ -5185,7 +4977,7 @@
       <c r="L75" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M75" s="45" t="s">
+      <c r="M75" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N75" s="21"/>
@@ -5237,7 +5029,7 @@
       <c r="L76" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M76" s="45" t="s">
+      <c r="M76" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N76" s="21"/>
@@ -5291,7 +5083,7 @@
       <c r="L77" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M77" s="45" t="s">
+      <c r="M77" s="36" t="s">
         <v>92</v>
       </c>
       <c r="N77" s="21"/>
@@ -5345,7 +5137,7 @@
       <c r="L78" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M78" s="45" t="s">
+      <c r="M78" s="36" t="s">
         <v>94</v>
       </c>
       <c r="N78" s="21"/>
@@ -5399,7 +5191,7 @@
       <c r="L79" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M79" s="45" t="s">
+      <c r="M79" s="36" t="s">
         <v>94</v>
       </c>
       <c r="N79" s="21"/>
@@ -5453,7 +5245,7 @@
       <c r="L80" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M80" s="50" t="s">
+      <c r="M80" s="41" t="s">
         <v>96</v>
       </c>
       <c r="N80" s="21"/>
@@ -5507,7 +5299,7 @@
       <c r="L81" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M81" s="50" t="s">
+      <c r="M81" s="41" t="s">
         <v>97</v>
       </c>
       <c r="N81" s="21"/>
@@ -5561,7 +5353,7 @@
       <c r="L82" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M82" s="50" t="s">
+      <c r="M82" s="41" t="s">
         <v>97</v>
       </c>
       <c r="N82" s="21"/>
@@ -5615,7 +5407,7 @@
       <c r="L83" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M83" s="50" t="s">
+      <c r="M83" s="41" t="s">
         <v>97</v>
       </c>
       <c r="N83" s="21"/>
@@ -5669,7 +5461,7 @@
       <c r="L84" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M84" s="50" t="s">
+      <c r="M84" s="41" t="s">
         <v>97</v>
       </c>
       <c r="N84" s="21"/>
@@ -5723,7 +5515,7 @@
       <c r="L85" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M85" s="45" t="s">
+      <c r="M85" s="36" t="s">
         <v>99</v>
       </c>
       <c r="N85" s="21"/>
@@ -5777,7 +5569,7 @@
       <c r="L86" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M86" s="45" t="s">
+      <c r="M86" s="36" t="s">
         <v>100</v>
       </c>
       <c r="N86" s="21"/>
@@ -5831,7 +5623,7 @@
       <c r="L87" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M87" s="45" t="s">
+      <c r="M87" s="36" t="s">
         <v>101</v>
       </c>
       <c r="N87" s="21"/>
@@ -5885,7 +5677,7 @@
       <c r="L88" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M88" s="45" t="s">
+      <c r="M88" s="36" t="s">
         <v>101</v>
       </c>
       <c r="N88" s="21"/>
@@ -5902,7 +5694,7 @@
       <c r="Y88" s="21"/>
       <c r="Z88" s="21"/>
     </row>
-    <row r="89" spans="1:26" ht="27" thickBot="1">
+    <row r="89" spans="1:26" ht="15.75" thickBot="1">
       <c r="A89" s="19">
         <v>88</v>
       </c>
@@ -5939,7 +5731,7 @@
       <c r="L89" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M89" s="45" t="s">
+      <c r="M89" s="36" t="s">
         <v>102</v>
       </c>
       <c r="N89" s="21"/>
@@ -5993,7 +5785,7 @@
       <c r="L90" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M90" s="45" t="s">
+      <c r="M90" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N90" s="21"/>
@@ -6047,7 +5839,7 @@
       <c r="L91" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M91" s="45" t="s">
+      <c r="M91" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N91" s="21"/>
@@ -6101,7 +5893,7 @@
       <c r="L92" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M92" s="45" t="s">
+      <c r="M92" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N92" s="21"/>
@@ -6155,7 +5947,7 @@
       <c r="L93" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M93" s="45" t="s">
+      <c r="M93" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N93" s="21"/>
@@ -6209,7 +6001,7 @@
       <c r="L94" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M94" s="45" t="s">
+      <c r="M94" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N94" s="21"/>
@@ -6263,7 +6055,7 @@
       <c r="L95" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M95" s="45" t="s">
+      <c r="M95" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N95" s="21"/>
@@ -6317,7 +6109,7 @@
       <c r="L96" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M96" s="45" t="s">
+      <c r="M96" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N96" s="21"/>
@@ -6371,7 +6163,7 @@
       <c r="L97" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M97" s="45" t="s">
+      <c r="M97" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N97" s="21"/>
@@ -6423,7 +6215,7 @@
       <c r="L98" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M98" s="45" t="s">
+      <c r="M98" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N98" s="21"/>
@@ -6477,7 +6269,7 @@
       <c r="L99" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M99" s="45" t="s">
+      <c r="M99" s="36" t="s">
         <v>104</v>
       </c>
       <c r="N99" s="21"/>
@@ -6531,7 +6323,7 @@
       <c r="L100" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M100" s="45" t="s">
+      <c r="M100" s="36" t="s">
         <v>106</v>
       </c>
       <c r="N100" s="21"/>
@@ -6585,7 +6377,7 @@
       <c r="L101" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M101" s="45" t="s">
+      <c r="M101" s="36" t="s">
         <v>106</v>
       </c>
       <c r="N101" s="21"/>
@@ -6639,7 +6431,7 @@
       <c r="L102" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M102" s="45" t="s">
+      <c r="M102" s="36" t="s">
         <v>106</v>
       </c>
       <c r="N102" s="21"/>
@@ -6693,7 +6485,7 @@
       <c r="L103" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M103" s="45" t="s">
+      <c r="M103" s="36" t="s">
         <v>106</v>
       </c>
       <c r="N103" s="21"/>
@@ -6747,7 +6539,7 @@
       <c r="L104" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M104" s="45" t="s">
+      <c r="M104" s="36" t="s">
         <v>107</v>
       </c>
       <c r="N104" s="21"/>
@@ -6801,7 +6593,7 @@
       <c r="L105" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M105" s="45" t="s">
+      <c r="M105" s="36" t="s">
         <v>109</v>
       </c>
       <c r="N105" s="21"/>
@@ -6855,7 +6647,7 @@
       <c r="L106" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M106" s="45" t="s">
+      <c r="M106" s="36" t="s">
         <v>109</v>
       </c>
       <c r="N106" s="21"/>
@@ -6909,7 +6701,7 @@
       <c r="L107" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M107" s="50" t="s">
+      <c r="M107" s="41" t="s">
         <v>112</v>
       </c>
       <c r="N107" s="21"/>
@@ -6963,7 +6755,7 @@
       <c r="L108" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M108" s="45" t="s">
+      <c r="M108" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N108" s="21"/>
@@ -7017,7 +6809,7 @@
       <c r="L109" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M109" s="45" t="s">
+      <c r="M109" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N109" s="21"/>
@@ -7069,7 +6861,7 @@
       <c r="L110" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M110" s="45" t="s">
+      <c r="M110" s="36" t="s">
         <v>115</v>
       </c>
       <c r="N110" s="21"/>
@@ -7123,7 +6915,7 @@
       <c r="L111" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M111" s="45" t="s">
+      <c r="M111" s="36" t="s">
         <v>116</v>
       </c>
       <c r="N111" s="21"/>
@@ -7177,7 +6969,7 @@
       <c r="L112" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M112" s="50" t="s">
+      <c r="M112" s="41" t="s">
         <v>118</v>
       </c>
       <c r="N112" s="21"/>
@@ -7231,7 +7023,7 @@
       <c r="L113" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M113" s="45" t="s">
+      <c r="M113" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N113" s="21"/>
@@ -7285,7 +7077,7 @@
       <c r="L114" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M114" s="45" t="s">
+      <c r="M114" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N114" s="21"/>
@@ -7339,7 +7131,7 @@
       <c r="L115" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M115" s="45" t="s">
+      <c r="M115" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N115" s="21"/>
@@ -7393,7 +7185,7 @@
       <c r="L116" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M116" s="45" t="s">
+      <c r="M116" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N116" s="21"/>
@@ -7447,7 +7239,7 @@
       <c r="L117" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M117" s="45" t="s">
+      <c r="M117" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N117" s="21"/>
@@ -7501,7 +7293,7 @@
       <c r="L118" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M118" s="45" t="s">
+      <c r="M118" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N118" s="21"/>
@@ -7555,7 +7347,7 @@
       <c r="L119" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M119" s="45" t="s">
+      <c r="M119" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N119" s="21"/>
@@ -7609,7 +7401,7 @@
       <c r="L120" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M120" s="45" t="s">
+      <c r="M120" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N120" s="21"/>
@@ -7663,7 +7455,7 @@
       <c r="L121" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M121" s="45" t="s">
+      <c r="M121" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N121" s="21"/>
@@ -7717,7 +7509,7 @@
       <c r="L122" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M122" s="45" t="s">
+      <c r="M122" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N122" s="21"/>
@@ -7771,7 +7563,7 @@
       <c r="L123" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M123" s="45" t="s">
+      <c r="M123" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N123" s="21"/>
@@ -7825,7 +7617,7 @@
       <c r="L124" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M124" s="45" t="s">
+      <c r="M124" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N124" s="21"/>
@@ -7879,7 +7671,7 @@
       <c r="L125" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M125" s="45" t="s">
+      <c r="M125" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N125" s="21"/>
@@ -7933,7 +7725,7 @@
       <c r="L126" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M126" s="45" t="s">
+      <c r="M126" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N126" s="21"/>
@@ -7987,7 +7779,7 @@
       <c r="L127" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M127" s="45" t="s">
+      <c r="M127" s="36" t="s">
         <v>120</v>
       </c>
       <c r="N127" s="21"/>
@@ -8041,7 +7833,7 @@
       <c r="L128" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M128" s="50" t="s">
+      <c r="M128" s="41" t="s">
         <v>122</v>
       </c>
       <c r="N128" s="21"/>
@@ -8095,7 +7887,7 @@
       <c r="L129" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M129" s="50" t="s">
+      <c r="M129" s="41" t="s">
         <v>123</v>
       </c>
       <c r="N129" s="21"/>
@@ -8149,7 +7941,7 @@
       <c r="L130" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M130" s="45" t="s">
+      <c r="M130" s="36" t="s">
         <v>124</v>
       </c>
       <c r="N130" s="21"/>
@@ -8203,7 +7995,7 @@
       <c r="L131" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M131" s="45" t="s">
+      <c r="M131" s="36" t="s">
         <v>126</v>
       </c>
       <c r="N131" s="21"/>
@@ -8257,7 +8049,7 @@
       <c r="L132" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M132" s="45" t="s">
+      <c r="M132" s="36" t="s">
         <v>128</v>
       </c>
       <c r="N132" s="21"/>
@@ -8311,7 +8103,7 @@
       <c r="L133" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M133" s="45" t="s">
+      <c r="M133" s="36" t="s">
         <v>131</v>
       </c>
       <c r="N133" s="21"/>
@@ -8365,7 +8157,7 @@
       <c r="L134" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M134" s="45" t="s">
+      <c r="M134" s="36" t="s">
         <v>132</v>
       </c>
       <c r="N134" s="21"/>
@@ -8419,7 +8211,7 @@
       <c r="L135" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M135" s="45" t="s">
+      <c r="M135" s="36" t="s">
         <v>133</v>
       </c>
       <c r="N135" s="21"/>
@@ -8473,7 +8265,7 @@
       <c r="L136" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M136" s="45" t="s">
+      <c r="M136" s="36" t="s">
         <v>124</v>
       </c>
       <c r="N136" s="21"/>
@@ -8525,7 +8317,7 @@
       <c r="L137" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M137" s="50" t="s">
+      <c r="M137" s="41" t="s">
         <v>134</v>
       </c>
       <c r="N137" s="21"/>
@@ -8577,7 +8369,7 @@
       <c r="L138" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M138" s="50" t="s">
+      <c r="M138" s="41" t="s">
         <v>134</v>
       </c>
       <c r="N138" s="21"/>
@@ -8631,7 +8423,7 @@
       <c r="L139" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M139" s="45" t="s">
+      <c r="M139" s="36" t="s">
         <v>136</v>
       </c>
       <c r="N139" s="21"/>
@@ -8685,7 +8477,7 @@
       <c r="L140" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M140" s="50" t="s">
+      <c r="M140" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N140" s="21"/>
@@ -8739,7 +8531,7 @@
       <c r="L141" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M141" s="50" t="s">
+      <c r="M141" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N141" s="21"/>
@@ -8793,7 +8585,7 @@
       <c r="L142" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M142" s="50" t="s">
+      <c r="M142" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N142" s="21"/>
@@ -8847,7 +8639,7 @@
       <c r="L143" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M143" s="50" t="s">
+      <c r="M143" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N143" s="21"/>
@@ -8901,7 +8693,7 @@
       <c r="L144" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M144" s="50" t="s">
+      <c r="M144" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N144" s="21"/>
@@ -8955,7 +8747,7 @@
       <c r="L145" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M145" s="50" t="s">
+      <c r="M145" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N145" s="21"/>
@@ -9007,7 +8799,7 @@
       <c r="L146" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M146" s="50" t="s">
+      <c r="M146" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N146" s="21"/>
@@ -9061,7 +8853,7 @@
       <c r="L147" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M147" s="50" t="s">
+      <c r="M147" s="41" t="s">
         <v>143</v>
       </c>
       <c r="N147" s="21"/>
@@ -9115,7 +8907,7 @@
       <c r="L148" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M148" s="45" t="s">
+      <c r="M148" s="36" t="s">
         <v>144</v>
       </c>
       <c r="N148" s="21"/>
@@ -9169,7 +8961,7 @@
       <c r="L149" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M149" s="45" t="s">
+      <c r="M149" s="36" t="s">
         <v>144</v>
       </c>
       <c r="N149" s="21"/>
@@ -9223,7 +9015,7 @@
       <c r="L150" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M150" s="45" t="s">
+      <c r="M150" s="36" t="s">
         <v>144</v>
       </c>
       <c r="N150" s="21"/>
@@ -9277,7 +9069,7 @@
       <c r="L151" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M151" s="45" t="s">
+      <c r="M151" s="36" t="s">
         <v>148</v>
       </c>
       <c r="N151" s="21"/>
@@ -9331,7 +9123,7 @@
       <c r="L152" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M152" s="45" t="s">
+      <c r="M152" s="36" t="s">
         <v>148</v>
       </c>
       <c r="N152" s="21"/>
@@ -9385,7 +9177,7 @@
       <c r="L153" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M153" s="45" t="s">
+      <c r="M153" s="36" t="s">
         <v>148</v>
       </c>
       <c r="N153" s="21"/>
@@ -9439,7 +9231,7 @@
       <c r="L154" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M154" s="45" t="s">
+      <c r="M154" s="36" t="s">
         <v>148</v>
       </c>
       <c r="N154" s="21"/>
@@ -9493,7 +9285,7 @@
       <c r="L155" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M155" s="45" t="s">
+      <c r="M155" s="36" t="s">
         <v>148</v>
       </c>
       <c r="N155" s="21"/>
@@ -9545,7 +9337,7 @@
       <c r="L156" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M156" s="50" t="s">
+      <c r="M156" s="41" t="s">
         <v>149</v>
       </c>
       <c r="N156" s="21"/>
@@ -9597,7 +9389,7 @@
       <c r="L157" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M157" s="50" t="s">
+      <c r="M157" s="41" t="s">
         <v>149</v>
       </c>
       <c r="N157" s="21"/>
@@ -9649,7 +9441,7 @@
       <c r="L158" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M158" s="50" t="s">
+      <c r="M158" s="41" t="s">
         <v>149</v>
       </c>
       <c r="N158" s="21"/>
@@ -9701,7 +9493,7 @@
       <c r="L159" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M159" s="50" t="s">
+      <c r="M159" s="41" t="s">
         <v>149</v>
       </c>
       <c r="N159" s="21"/>
@@ -9753,7 +9545,7 @@
       <c r="L160" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M160" s="45" t="s">
+      <c r="M160" s="36" t="s">
         <v>151</v>
       </c>
       <c r="N160" s="21"/>
@@ -9805,7 +9597,7 @@
       <c r="L161" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M161" s="45" t="s">
+      <c r="M161" s="36" t="s">
         <v>151</v>
       </c>
       <c r="N161" s="21"/>
@@ -9859,7 +9651,7 @@
       <c r="L162" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M162" s="45" t="s">
+      <c r="M162" s="36" t="s">
         <v>153</v>
       </c>
       <c r="N162" s="21"/>
@@ -9913,7 +9705,7 @@
       <c r="L163" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M163" s="45" t="s">
+      <c r="M163" s="36" t="s">
         <v>153</v>
       </c>
       <c r="N163" s="21"/>
@@ -9967,7 +9759,7 @@
       <c r="L164" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M164" s="45" t="s">
+      <c r="M164" s="36" t="s">
         <v>153</v>
       </c>
       <c r="N164" s="21"/>
@@ -10021,7 +9813,7 @@
       <c r="L165" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M165" s="45" t="s">
+      <c r="M165" s="36" t="s">
         <v>155</v>
       </c>
       <c r="N165" s="21"/>
@@ -10075,7 +9867,7 @@
       <c r="L166" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M166" s="45" t="s">
+      <c r="M166" s="36" t="s">
         <v>156</v>
       </c>
       <c r="N166" s="21"/>
@@ -10129,7 +9921,7 @@
       <c r="L167" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M167" s="45" t="s">
+      <c r="M167" s="36" t="s">
         <v>156</v>
       </c>
       <c r="N167" s="21"/>
@@ -10183,7 +9975,7 @@
       <c r="L168" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M168" s="45" t="s">
+      <c r="M168" s="36" t="s">
         <v>156</v>
       </c>
       <c r="N168" s="21"/>
@@ -10228,7 +10020,7 @@
       <c r="I169" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J169" s="55">
+      <c r="J169" s="46">
         <v>12823585</v>
       </c>
       <c r="K169" s="23" t="s">
@@ -10237,7 +10029,7 @@
       <c r="L169" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M169" s="50" t="s">
+      <c r="M169" s="41" t="s">
         <v>157</v>
       </c>
       <c r="N169" s="21"/>
@@ -10282,7 +10074,7 @@
       <c r="I170" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="J170" s="55">
+      <c r="J170" s="46">
         <v>10802757</v>
       </c>
       <c r="K170" s="23" t="s">
@@ -10291,7 +10083,7 @@
       <c r="L170" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M170" s="50" t="s">
+      <c r="M170" s="41" t="s">
         <v>158</v>
       </c>
       <c r="N170" s="21"/>
@@ -10336,7 +10128,7 @@
       <c r="I171" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="J171" s="55">
+      <c r="J171" s="46">
         <v>29454195</v>
       </c>
       <c r="K171" s="23" t="s">
@@ -10345,7 +10137,7 @@
       <c r="L171" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M171" s="50" t="s">
+      <c r="M171" s="41" t="s">
         <v>162</v>
       </c>
       <c r="N171" s="21"/>
@@ -10390,7 +10182,7 @@
       <c r="I172" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="J172" s="55">
+      <c r="J172" s="46">
         <v>29454195</v>
       </c>
       <c r="K172" s="23" t="s">
@@ -10399,7 +10191,7 @@
       <c r="L172" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M172" s="50" t="s">
+      <c r="M172" s="41" t="s">
         <v>162</v>
       </c>
       <c r="N172" s="21"/>
@@ -10444,7 +10236,7 @@
       <c r="I173" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J173" s="55">
+      <c r="J173" s="46">
         <v>10563623</v>
       </c>
       <c r="K173" s="20" t="s">
@@ -10453,7 +10245,7 @@
       <c r="L173" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M173" s="45" t="s">
+      <c r="M173" s="36" t="s">
         <v>163</v>
       </c>
       <c r="N173" s="21"/>
@@ -10498,7 +10290,7 @@
       <c r="I174" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J174" s="55">
+      <c r="J174" s="46">
         <v>38454578</v>
       </c>
       <c r="K174" s="20" t="s">
@@ -10507,7 +10299,7 @@
       <c r="L174" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M174" s="45" t="s">
+      <c r="M174" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N174" s="21"/>
@@ -10552,7 +10344,7 @@
       <c r="I175" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J175" s="55">
+      <c r="J175" s="46">
         <v>38454578</v>
       </c>
       <c r="K175" s="20" t="s">
@@ -10561,7 +10353,7 @@
       <c r="L175" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M175" s="45" t="s">
+      <c r="M175" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N175" s="21"/>
@@ -10606,7 +10398,7 @@
       <c r="I176" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J176" s="55">
+      <c r="J176" s="46">
         <v>38454578</v>
       </c>
       <c r="K176" s="20" t="s">
@@ -10615,7 +10407,7 @@
       <c r="L176" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M176" s="45" t="s">
+      <c r="M176" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N176" s="21"/>
@@ -10660,7 +10452,7 @@
       <c r="I177" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J177" s="55">
+      <c r="J177" s="46">
         <v>38454578</v>
       </c>
       <c r="K177" s="20" t="s">
@@ -10669,7 +10461,7 @@
       <c r="L177" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M177" s="45" t="s">
+      <c r="M177" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N177" s="21"/>
@@ -10714,7 +10506,7 @@
       <c r="I178" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J178" s="55">
+      <c r="J178" s="46">
         <v>38454578</v>
       </c>
       <c r="K178" s="20" t="s">
@@ -10723,7 +10515,7 @@
       <c r="L178" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M178" s="45" t="s">
+      <c r="M178" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N178" s="21"/>
@@ -10768,7 +10560,7 @@
       <c r="I179" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J179" s="55">
+      <c r="J179" s="46">
         <v>38454578</v>
       </c>
       <c r="K179" s="20" t="s">
@@ -10777,7 +10569,7 @@
       <c r="L179" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M179" s="45" t="s">
+      <c r="M179" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N179" s="21"/>
@@ -10822,7 +10614,7 @@
       <c r="I180" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J180" s="55">
+      <c r="J180" s="46">
         <v>38454578</v>
       </c>
       <c r="K180" s="20" t="s">
@@ -10831,7 +10623,7 @@
       <c r="L180" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M180" s="45" t="s">
+      <c r="M180" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N180" s="21"/>
@@ -10876,7 +10668,7 @@
       <c r="I181" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J181" s="55">
+      <c r="J181" s="46">
         <v>38454578</v>
       </c>
       <c r="K181" s="20" t="s">
@@ -10885,7 +10677,7 @@
       <c r="L181" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M181" s="45" t="s">
+      <c r="M181" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N181" s="21"/>
@@ -10930,7 +10722,7 @@
       <c r="I182" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J182" s="55">
+      <c r="J182" s="46">
         <v>38454578</v>
       </c>
       <c r="K182" s="20" t="s">
@@ -10939,7 +10731,7 @@
       <c r="L182" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M182" s="45" t="s">
+      <c r="M182" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N182" s="21"/>
@@ -10984,7 +10776,7 @@
       <c r="I183" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="J183" s="55">
+      <c r="J183" s="46">
         <v>38454578</v>
       </c>
       <c r="K183" s="20" t="s">
@@ -10993,7 +10785,7 @@
       <c r="L183" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="M183" s="45" t="s">
+      <c r="M183" s="36" t="s">
         <v>166</v>
       </c>
       <c r="N183" s="21"/>
@@ -11020,7 +10812,7 @@
       <c r="C184" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D184" s="56">
+      <c r="D184" s="47">
         <v>261</v>
       </c>
       <c r="E184" s="21" t="s">
@@ -11038,7 +10830,7 @@
       <c r="I184" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="J184" s="55">
+      <c r="J184" s="46">
         <v>17132685</v>
       </c>
       <c r="K184" s="20" t="s">
@@ -11047,7 +10839,7 @@
       <c r="L184" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="M184" s="50" t="s">
+      <c r="M184" s="41" t="s">
         <v>167</v>
       </c>
       <c r="N184" s="21"/>
@@ -11074,7 +10866,7 @@
       <c r="C185" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D185" s="56">
+      <c r="D185" s="47">
         <v>258</v>
       </c>
       <c r="E185" s="21" t="s">
@@ -11090,7 +10882,7 @@
         <v>51</v>
       </c>
       <c r="I185" s="21"/>
-      <c r="J185" s="55">
+      <c r="J185" s="46">
         <v>17132685</v>
       </c>
       <c r="K185" s="20" t="s">
@@ -11099,7 +10891,7 @@
       <c r="L185" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="M185" s="50" t="s">
+      <c r="M185" s="41" t="s">
         <v>167</v>
       </c>
       <c r="N185" s="21"/>
@@ -11142,7 +10934,7 @@
         <v>51</v>
       </c>
       <c r="I186" s="21"/>
-      <c r="J186" s="55">
+      <c r="J186" s="46">
         <v>27645992</v>
       </c>
       <c r="K186" s="20" t="s">
@@ -11151,7 +10943,7 @@
       <c r="L186" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M186" s="50" t="s">
+      <c r="M186" s="41" t="s">
         <v>168</v>
       </c>
       <c r="N186" s="21"/>
@@ -11194,7 +10986,7 @@
         <v>51</v>
       </c>
       <c r="I187" s="21"/>
-      <c r="J187" s="55">
+      <c r="J187" s="46">
         <v>27645992</v>
       </c>
       <c r="K187" s="20" t="s">
@@ -11203,7 +10995,7 @@
       <c r="L187" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M187" s="50" t="s">
+      <c r="M187" s="41" t="s">
         <v>168</v>
       </c>
       <c r="N187" s="21"/>
@@ -11246,7 +11038,7 @@
         <v>51</v>
       </c>
       <c r="I188" s="21"/>
-      <c r="J188" s="55">
+      <c r="J188" s="46">
         <v>27645992</v>
       </c>
       <c r="K188" s="20" t="s">
@@ -11255,7 +11047,7 @@
       <c r="L188" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M188" s="50" t="s">
+      <c r="M188" s="41" t="s">
         <v>168</v>
       </c>
       <c r="N188" s="21"/>
@@ -11298,7 +11090,7 @@
         <v>51</v>
       </c>
       <c r="I189" s="21"/>
-      <c r="J189" s="55">
+      <c r="J189" s="46">
         <v>27645992</v>
       </c>
       <c r="K189" s="20" t="s">
@@ -11307,7 +11099,7 @@
       <c r="L189" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M189" s="50" t="s">
+      <c r="M189" s="41" t="s">
         <v>168</v>
       </c>
       <c r="N189" s="21"/>
@@ -11352,7 +11144,7 @@
       <c r="I190" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="J190" s="55">
+      <c r="J190" s="46">
         <v>32536355</v>
       </c>
       <c r="K190" s="20" t="s">
@@ -11361,7 +11153,7 @@
       <c r="L190" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M190" s="50" t="s">
+      <c r="M190" s="41" t="s">
         <v>171</v>
       </c>
       <c r="N190" s="21"/>
@@ -11378,20 +11170,46 @@
       <c r="Y190" s="21"/>
       <c r="Z190" s="21"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" thickBot="1">
-      <c r="A191" s="19"/>
-      <c r="B191" s="20"/>
-      <c r="C191" s="20"/>
-      <c r="D191" s="19"/>
-      <c r="E191" s="20"/>
-      <c r="F191" s="20"/>
-      <c r="G191" s="20"/>
-      <c r="H191" s="20"/>
-      <c r="I191" s="20"/>
-      <c r="J191" s="19"/>
-      <c r="K191" s="20"/>
-      <c r="L191" s="20"/>
-      <c r="M191" s="50"/>
+    <row r="191" spans="1:26" ht="27" thickBot="1">
+      <c r="A191" s="22">
+        <v>190</v>
+      </c>
+      <c r="B191" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C191" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" s="19">
+        <v>398</v>
+      </c>
+      <c r="E191" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F191" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G191" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H191" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I191" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="J191" s="46">
+        <v>20881005</v>
+      </c>
+      <c r="K191" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L191" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M191" s="41" t="s">
+        <v>173</v>
+      </c>
       <c r="N191" s="21"/>
       <c r="O191" s="21"/>
       <c r="P191" s="21"/>
@@ -11405,6 +11223,2230 @@
       <c r="X191" s="21"/>
       <c r="Y191" s="21"/>
       <c r="Z191" s="21"/>
+    </row>
+    <row r="192" spans="1:26" ht="27" thickBot="1">
+      <c r="A192" s="22">
+        <v>191</v>
+      </c>
+      <c r="B192" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C192" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D192" s="19">
+        <v>290</v>
+      </c>
+      <c r="E192" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F192" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G192" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H192" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I192" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="J192" s="46">
+        <v>21873428</v>
+      </c>
+      <c r="K192" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L192" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M192" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="N192" s="21"/>
+      <c r="O192" s="21"/>
+      <c r="P192" s="21"/>
+      <c r="Q192" s="21"/>
+      <c r="R192" s="21"/>
+      <c r="S192" s="21"/>
+      <c r="T192" s="21"/>
+      <c r="U192" s="21"/>
+      <c r="V192" s="21"/>
+      <c r="W192" s="21"/>
+      <c r="X192" s="21"/>
+      <c r="Y192" s="21"/>
+      <c r="Z192" s="21"/>
+    </row>
+    <row r="193" spans="1:26" ht="27" thickBot="1">
+      <c r="A193" s="22">
+        <v>192</v>
+      </c>
+      <c r="B193" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C193" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D193" s="19">
+        <v>143</v>
+      </c>
+      <c r="E193" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F193" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H193" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I193" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="J193" s="46">
+        <v>21873428</v>
+      </c>
+      <c r="K193" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L193" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M193" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="N193" s="21"/>
+      <c r="O193" s="21"/>
+      <c r="P193" s="21"/>
+      <c r="Q193" s="21"/>
+      <c r="R193" s="21"/>
+      <c r="S193" s="21"/>
+      <c r="T193" s="21"/>
+      <c r="U193" s="21"/>
+      <c r="V193" s="21"/>
+      <c r="W193" s="21"/>
+      <c r="X193" s="21"/>
+      <c r="Y193" s="21"/>
+      <c r="Z193" s="21"/>
+    </row>
+    <row r="194" spans="1:26" ht="27" thickBot="1">
+      <c r="A194" s="22">
+        <v>193</v>
+      </c>
+      <c r="B194" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C194" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D194" s="19">
+        <v>145</v>
+      </c>
+      <c r="E194" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F194" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G194" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H194" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I194" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="J194" s="46">
+        <v>21873428</v>
+      </c>
+      <c r="K194" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L194" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M194" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="N194" s="21"/>
+      <c r="O194" s="21"/>
+      <c r="P194" s="21"/>
+      <c r="Q194" s="21"/>
+      <c r="R194" s="21"/>
+      <c r="S194" s="21"/>
+      <c r="T194" s="21"/>
+      <c r="U194" s="21"/>
+      <c r="V194" s="21"/>
+      <c r="W194" s="21"/>
+      <c r="X194" s="21"/>
+      <c r="Y194" s="21"/>
+      <c r="Z194" s="21"/>
+    </row>
+    <row r="195" spans="1:26" ht="27" thickBot="1">
+      <c r="A195" s="22">
+        <v>194</v>
+      </c>
+      <c r="B195" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C195" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D195" s="19">
+        <v>176</v>
+      </c>
+      <c r="E195" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F195" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G195" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I195" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="J195" s="46">
+        <v>32120303</v>
+      </c>
+      <c r="K195" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L195" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M195" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="N195" s="21"/>
+      <c r="O195" s="21"/>
+      <c r="P195" s="21"/>
+      <c r="Q195" s="21"/>
+      <c r="R195" s="21"/>
+      <c r="S195" s="21"/>
+      <c r="T195" s="21"/>
+      <c r="U195" s="21"/>
+      <c r="V195" s="21"/>
+      <c r="W195" s="21"/>
+      <c r="X195" s="21"/>
+      <c r="Y195" s="21"/>
+      <c r="Z195" s="21"/>
+    </row>
+    <row r="196" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A196" s="22">
+        <v>195</v>
+      </c>
+      <c r="B196" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C196" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" s="19">
+        <v>211</v>
+      </c>
+      <c r="E196" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F196" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G196" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="H196" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="I196" s="21"/>
+      <c r="J196" s="46">
+        <v>24085295</v>
+      </c>
+      <c r="K196" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L196" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M196" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N196" s="21"/>
+      <c r="O196" s="21"/>
+      <c r="P196" s="21"/>
+      <c r="Q196" s="21"/>
+      <c r="R196" s="21"/>
+      <c r="S196" s="21"/>
+      <c r="T196" s="21"/>
+      <c r="U196" s="21"/>
+      <c r="V196" s="21"/>
+      <c r="W196" s="21"/>
+      <c r="X196" s="21"/>
+      <c r="Y196" s="21"/>
+      <c r="Z196" s="21"/>
+    </row>
+    <row r="197" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A197" s="22">
+        <v>196</v>
+      </c>
+      <c r="B197" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C197" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D197" s="19">
+        <v>223</v>
+      </c>
+      <c r="E197" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F197" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G197" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H197" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="I197" s="21"/>
+      <c r="J197" s="46">
+        <v>24085295</v>
+      </c>
+      <c r="K197" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L197" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M197" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N197" s="21"/>
+      <c r="O197" s="21"/>
+      <c r="P197" s="21"/>
+      <c r="Q197" s="21"/>
+      <c r="R197" s="21"/>
+      <c r="S197" s="21"/>
+      <c r="T197" s="21"/>
+      <c r="U197" s="21"/>
+      <c r="V197" s="21"/>
+      <c r="W197" s="21"/>
+      <c r="X197" s="21"/>
+      <c r="Y197" s="21"/>
+      <c r="Z197" s="21"/>
+    </row>
+    <row r="198" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A198" s="22">
+        <v>197</v>
+      </c>
+      <c r="B198" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C198" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D198" s="19">
+        <v>211</v>
+      </c>
+      <c r="E198" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F198" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G198" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="H198" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I198" s="21"/>
+      <c r="J198" s="46">
+        <v>24085295</v>
+      </c>
+      <c r="K198" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L198" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M198" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N198" s="21"/>
+      <c r="O198" s="21"/>
+      <c r="P198" s="21"/>
+      <c r="Q198" s="21"/>
+      <c r="R198" s="21"/>
+      <c r="S198" s="21"/>
+      <c r="T198" s="21"/>
+      <c r="U198" s="21"/>
+      <c r="V198" s="21"/>
+      <c r="W198" s="21"/>
+      <c r="X198" s="21"/>
+      <c r="Y198" s="21"/>
+      <c r="Z198" s="21"/>
+    </row>
+    <row r="199" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A199" s="22">
+        <v>198</v>
+      </c>
+      <c r="B199" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C199" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D199" s="19">
+        <v>223</v>
+      </c>
+      <c r="E199" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F199" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G199" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H199" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I199" s="21"/>
+      <c r="J199" s="46">
+        <v>24085295</v>
+      </c>
+      <c r="K199" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L199" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M199" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N199" s="21"/>
+      <c r="O199" s="21"/>
+      <c r="P199" s="21"/>
+      <c r="Q199" s="21"/>
+      <c r="R199" s="21"/>
+      <c r="S199" s="21"/>
+      <c r="T199" s="21"/>
+      <c r="U199" s="21"/>
+      <c r="V199" s="21"/>
+      <c r="W199" s="21"/>
+      <c r="X199" s="21"/>
+      <c r="Y199" s="21"/>
+      <c r="Z199" s="21"/>
+    </row>
+    <row r="200" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A200" s="22">
+        <v>199</v>
+      </c>
+      <c r="B200" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C200" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D200" s="19">
+        <v>147</v>
+      </c>
+      <c r="E200" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F200" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G200" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H200" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I200" s="21"/>
+      <c r="J200" s="46">
+        <v>25282151</v>
+      </c>
+      <c r="K200" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L200" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M200" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="N200" s="21"/>
+      <c r="O200" s="21"/>
+      <c r="P200" s="21"/>
+      <c r="Q200" s="21"/>
+      <c r="R200" s="21"/>
+      <c r="S200" s="21"/>
+      <c r="T200" s="21"/>
+      <c r="U200" s="21"/>
+      <c r="V200" s="21"/>
+      <c r="W200" s="21"/>
+      <c r="X200" s="21"/>
+      <c r="Y200" s="21"/>
+      <c r="Z200" s="21"/>
+    </row>
+    <row r="201" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A201" s="22">
+        <v>200</v>
+      </c>
+      <c r="B201" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C201" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D201" s="19">
+        <v>203</v>
+      </c>
+      <c r="E201" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F201" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G201" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H201" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I201" s="21"/>
+      <c r="J201" s="46">
+        <v>25282151</v>
+      </c>
+      <c r="K201" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L201" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M201" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="N201" s="21"/>
+      <c r="O201" s="21"/>
+      <c r="P201" s="21"/>
+      <c r="Q201" s="21"/>
+      <c r="R201" s="21"/>
+      <c r="S201" s="21"/>
+      <c r="T201" s="21"/>
+      <c r="U201" s="21"/>
+      <c r="V201" s="21"/>
+      <c r="W201" s="21"/>
+      <c r="X201" s="21"/>
+      <c r="Y201" s="21"/>
+      <c r="Z201" s="21"/>
+    </row>
+    <row r="202" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A202" s="22">
+        <v>201</v>
+      </c>
+      <c r="B202" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C202" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D202" s="22">
+        <v>268</v>
+      </c>
+      <c r="E202" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F202" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G202" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H202" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I202" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J202" s="46">
+        <v>21822932</v>
+      </c>
+      <c r="K202" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L202" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M202" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="N202" s="21"/>
+      <c r="O202" s="21"/>
+      <c r="P202" s="21"/>
+      <c r="Q202" s="21"/>
+      <c r="R202" s="21"/>
+      <c r="S202" s="21"/>
+      <c r="T202" s="21"/>
+      <c r="U202" s="21"/>
+      <c r="V202" s="21"/>
+      <c r="W202" s="21"/>
+      <c r="X202" s="21"/>
+      <c r="Y202" s="21"/>
+      <c r="Z202" s="21"/>
+    </row>
+    <row r="203" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A203" s="22">
+        <v>202</v>
+      </c>
+      <c r="B203" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C203" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D203" s="22">
+        <v>265</v>
+      </c>
+      <c r="E203" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F203" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G203" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H203" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="I203" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J203" s="46">
+        <v>21822932</v>
+      </c>
+      <c r="K203" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L203" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M203" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="N203" s="21"/>
+      <c r="O203" s="21"/>
+      <c r="P203" s="21"/>
+      <c r="Q203" s="21"/>
+      <c r="R203" s="21"/>
+      <c r="S203" s="21"/>
+      <c r="T203" s="21"/>
+      <c r="U203" s="21"/>
+      <c r="V203" s="21"/>
+      <c r="W203" s="21"/>
+      <c r="X203" s="21"/>
+      <c r="Y203" s="21"/>
+      <c r="Z203" s="21"/>
+    </row>
+    <row r="204" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A204" s="22">
+        <v>203</v>
+      </c>
+      <c r="B204" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C204" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D204" s="22">
+        <v>259</v>
+      </c>
+      <c r="E204" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F204" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G204" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H204" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="I204" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J204" s="46">
+        <v>19289485</v>
+      </c>
+      <c r="K204" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L204" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M204" s="41" t="s">
+        <v>188</v>
+      </c>
+      <c r="N204" s="21"/>
+      <c r="O204" s="21"/>
+      <c r="P204" s="21"/>
+      <c r="Q204" s="21"/>
+      <c r="R204" s="21"/>
+      <c r="S204" s="21"/>
+      <c r="T204" s="21"/>
+      <c r="U204" s="21"/>
+      <c r="V204" s="21"/>
+      <c r="W204" s="21"/>
+      <c r="X204" s="21"/>
+      <c r="Y204" s="21"/>
+      <c r="Z204" s="21"/>
+    </row>
+    <row r="205" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A205" s="22">
+        <v>204</v>
+      </c>
+      <c r="B205" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C205" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D205" s="22">
+        <v>265</v>
+      </c>
+      <c r="E205" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G205" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H205" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I205" s="23"/>
+      <c r="J205" s="46">
+        <v>27375219</v>
+      </c>
+      <c r="K205" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L205" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M205" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N205" s="21"/>
+      <c r="O205" s="21"/>
+      <c r="P205" s="21"/>
+      <c r="Q205" s="21"/>
+      <c r="R205" s="21"/>
+      <c r="S205" s="21"/>
+      <c r="T205" s="21"/>
+      <c r="U205" s="21"/>
+      <c r="V205" s="21"/>
+      <c r="W205" s="21"/>
+      <c r="X205" s="21"/>
+      <c r="Y205" s="21"/>
+      <c r="Z205" s="21"/>
+    </row>
+    <row r="206" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A206" s="22">
+        <v>205</v>
+      </c>
+      <c r="B206" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C206" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D206" s="22">
+        <v>265</v>
+      </c>
+      <c r="E206" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F206" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G206" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H206" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I206" s="23"/>
+      <c r="J206" s="46">
+        <v>27375219</v>
+      </c>
+      <c r="K206" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L206" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M206" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N206" s="21"/>
+      <c r="O206" s="21"/>
+      <c r="P206" s="21"/>
+      <c r="Q206" s="21"/>
+      <c r="R206" s="21"/>
+      <c r="S206" s="21"/>
+      <c r="T206" s="21"/>
+      <c r="U206" s="21"/>
+      <c r="V206" s="21"/>
+      <c r="W206" s="21"/>
+      <c r="X206" s="21"/>
+      <c r="Y206" s="21"/>
+      <c r="Z206" s="21"/>
+    </row>
+    <row r="207" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A207" s="22">
+        <v>206</v>
+      </c>
+      <c r="B207" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C207" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D207" s="22">
+        <v>255</v>
+      </c>
+      <c r="E207" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F207" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G207" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H207" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I207" s="23"/>
+      <c r="J207" s="46">
+        <v>27375219</v>
+      </c>
+      <c r="K207" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L207" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M207" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N207" s="21"/>
+      <c r="O207" s="21"/>
+      <c r="P207" s="21"/>
+      <c r="Q207" s="21"/>
+      <c r="R207" s="21"/>
+      <c r="S207" s="21"/>
+      <c r="T207" s="21"/>
+      <c r="U207" s="21"/>
+      <c r="V207" s="21"/>
+      <c r="W207" s="21"/>
+      <c r="X207" s="21"/>
+      <c r="Y207" s="21"/>
+      <c r="Z207" s="21"/>
+    </row>
+    <row r="208" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A208" s="22">
+        <v>207</v>
+      </c>
+      <c r="B208" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C208" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D208" s="22">
+        <v>269</v>
+      </c>
+      <c r="E208" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F208" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G208" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H208" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I208" s="23"/>
+      <c r="J208" s="46">
+        <v>27375219</v>
+      </c>
+      <c r="K208" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L208" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M208" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="N208" s="21"/>
+      <c r="O208" s="21"/>
+      <c r="P208" s="21"/>
+      <c r="Q208" s="21"/>
+      <c r="R208" s="21"/>
+      <c r="S208" s="21"/>
+      <c r="T208" s="21"/>
+      <c r="U208" s="21"/>
+      <c r="V208" s="21"/>
+      <c r="W208" s="21"/>
+      <c r="X208" s="21"/>
+      <c r="Y208" s="21"/>
+      <c r="Z208" s="21"/>
+    </row>
+    <row r="209" spans="1:26" ht="27" thickBot="1">
+      <c r="A209" s="22">
+        <v>208</v>
+      </c>
+      <c r="B209" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C209" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D209" s="22">
+        <v>259</v>
+      </c>
+      <c r="E209" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F209" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G209" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H209" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I209" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="J209" s="46">
+        <v>17272341</v>
+      </c>
+      <c r="K209" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L209" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M209" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="N209" s="21"/>
+      <c r="O209" s="21"/>
+      <c r="P209" s="21"/>
+      <c r="Q209" s="21"/>
+      <c r="R209" s="21"/>
+      <c r="S209" s="21"/>
+      <c r="T209" s="21"/>
+      <c r="U209" s="21"/>
+      <c r="V209" s="21"/>
+      <c r="W209" s="21"/>
+      <c r="X209" s="21"/>
+      <c r="Y209" s="21"/>
+      <c r="Z209" s="21"/>
+    </row>
+    <row r="210" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A210" s="22">
+        <v>209</v>
+      </c>
+      <c r="B210" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D210" s="22">
+        <v>248</v>
+      </c>
+      <c r="E210" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F210" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G210" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H210" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="I210" s="21"/>
+      <c r="J210" s="46">
+        <v>10716716</v>
+      </c>
+      <c r="K210" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L210" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M210" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="N210" s="21"/>
+      <c r="O210" s="21"/>
+      <c r="P210" s="21"/>
+      <c r="Q210" s="21"/>
+      <c r="R210" s="21"/>
+      <c r="S210" s="21"/>
+      <c r="T210" s="21"/>
+      <c r="U210" s="21"/>
+      <c r="V210" s="21"/>
+      <c r="W210" s="21"/>
+      <c r="X210" s="21"/>
+      <c r="Y210" s="21"/>
+      <c r="Z210" s="21"/>
+    </row>
+    <row r="211" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A211" s="22">
+        <v>210</v>
+      </c>
+      <c r="B211" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C211" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D211" s="22">
+        <v>185</v>
+      </c>
+      <c r="E211" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F211" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G211" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H211" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I211" s="21"/>
+      <c r="J211" s="46">
+        <v>32702089</v>
+      </c>
+      <c r="K211" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L211" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M211" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="N211" s="21"/>
+      <c r="O211" s="21"/>
+      <c r="P211" s="21"/>
+      <c r="Q211" s="21"/>
+      <c r="R211" s="21"/>
+      <c r="S211" s="21"/>
+      <c r="T211" s="21"/>
+      <c r="U211" s="21"/>
+      <c r="V211" s="21"/>
+      <c r="W211" s="21"/>
+      <c r="X211" s="21"/>
+      <c r="Y211" s="21"/>
+      <c r="Z211" s="21"/>
+    </row>
+    <row r="212" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A212" s="22">
+        <v>211</v>
+      </c>
+      <c r="B212" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C212" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D212" s="22">
+        <v>160</v>
+      </c>
+      <c r="E212" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F212" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G212" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H212" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I212" s="21"/>
+      <c r="J212" s="46">
+        <v>32702089</v>
+      </c>
+      <c r="K212" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L212" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M212" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="N212" s="21"/>
+      <c r="O212" s="21"/>
+      <c r="P212" s="21"/>
+      <c r="Q212" s="21"/>
+      <c r="R212" s="21"/>
+      <c r="S212" s="21"/>
+      <c r="T212" s="21"/>
+      <c r="U212" s="21"/>
+      <c r="V212" s="21"/>
+      <c r="W212" s="21"/>
+      <c r="X212" s="21"/>
+      <c r="Y212" s="21"/>
+      <c r="Z212" s="21"/>
+    </row>
+    <row r="213" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A213" s="22">
+        <v>212</v>
+      </c>
+      <c r="B213" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C213" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D213" s="22">
+        <v>158</v>
+      </c>
+      <c r="E213" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F213" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G213" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H213" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I213" s="21"/>
+      <c r="J213" s="46">
+        <v>32702089</v>
+      </c>
+      <c r="K213" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L213" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M213" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="N213" s="21"/>
+      <c r="O213" s="21"/>
+      <c r="P213" s="21"/>
+      <c r="Q213" s="21"/>
+      <c r="R213" s="21"/>
+      <c r="S213" s="21"/>
+      <c r="T213" s="21"/>
+      <c r="U213" s="21"/>
+      <c r="V213" s="21"/>
+      <c r="W213" s="21"/>
+      <c r="X213" s="21"/>
+      <c r="Y213" s="21"/>
+      <c r="Z213" s="21"/>
+    </row>
+    <row r="214" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A214" s="22">
+        <v>213</v>
+      </c>
+      <c r="B214" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C214" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D214" s="22">
+        <v>188</v>
+      </c>
+      <c r="E214" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F214" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G214" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H214" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I214" s="23"/>
+      <c r="J214" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K214" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L214" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M214" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N214" s="21"/>
+      <c r="O214" s="21"/>
+      <c r="P214" s="21"/>
+      <c r="Q214" s="21"/>
+      <c r="R214" s="21"/>
+      <c r="S214" s="21"/>
+      <c r="T214" s="21"/>
+      <c r="U214" s="21"/>
+      <c r="V214" s="21"/>
+      <c r="W214" s="21"/>
+      <c r="X214" s="21"/>
+      <c r="Y214" s="21"/>
+      <c r="Z214" s="21"/>
+    </row>
+    <row r="215" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A215" s="22">
+        <v>214</v>
+      </c>
+      <c r="B215" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C215" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D215" s="22">
+        <v>428</v>
+      </c>
+      <c r="E215" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F215" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G215" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H215" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I215" s="23"/>
+      <c r="J215" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K215" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L215" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M215" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N215" s="21"/>
+      <c r="O215" s="21"/>
+      <c r="P215" s="21"/>
+      <c r="Q215" s="21"/>
+      <c r="R215" s="21"/>
+      <c r="S215" s="21"/>
+      <c r="T215" s="21"/>
+      <c r="U215" s="21"/>
+      <c r="V215" s="21"/>
+      <c r="W215" s="21"/>
+      <c r="X215" s="21"/>
+      <c r="Y215" s="21"/>
+      <c r="Z215" s="21"/>
+    </row>
+    <row r="216" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A216" s="22">
+        <v>215</v>
+      </c>
+      <c r="B216" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C216" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D216" s="22">
+        <v>432</v>
+      </c>
+      <c r="E216" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F216" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G216" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H216" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I216" s="23"/>
+      <c r="J216" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K216" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L216" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M216" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N216" s="21"/>
+      <c r="O216" s="21"/>
+      <c r="P216" s="21"/>
+      <c r="Q216" s="21"/>
+      <c r="R216" s="21"/>
+      <c r="S216" s="21"/>
+      <c r="T216" s="21"/>
+      <c r="U216" s="21"/>
+      <c r="V216" s="21"/>
+      <c r="W216" s="21"/>
+      <c r="X216" s="21"/>
+      <c r="Y216" s="21"/>
+      <c r="Z216" s="21"/>
+    </row>
+    <row r="217" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A217" s="22">
+        <v>216</v>
+      </c>
+      <c r="B217" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C217" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D217" s="22">
+        <v>436</v>
+      </c>
+      <c r="E217" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F217" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G217" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H217" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I217" s="23"/>
+      <c r="J217" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K217" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L217" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M217" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N217" s="21"/>
+      <c r="O217" s="21"/>
+      <c r="P217" s="21"/>
+      <c r="Q217" s="21"/>
+      <c r="R217" s="21"/>
+      <c r="S217" s="21"/>
+      <c r="T217" s="21"/>
+      <c r="U217" s="21"/>
+      <c r="V217" s="21"/>
+      <c r="W217" s="21"/>
+      <c r="X217" s="21"/>
+      <c r="Y217" s="21"/>
+      <c r="Z217" s="21"/>
+    </row>
+    <row r="218" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A218" s="22">
+        <v>217</v>
+      </c>
+      <c r="B218" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C218" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D218" s="22">
+        <v>223</v>
+      </c>
+      <c r="E218" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F218" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G218" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H218" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I218" s="23"/>
+      <c r="J218" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K218" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L218" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M218" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N218" s="21"/>
+      <c r="O218" s="21"/>
+      <c r="P218" s="21"/>
+      <c r="Q218" s="21"/>
+      <c r="R218" s="21"/>
+      <c r="S218" s="21"/>
+      <c r="T218" s="21"/>
+      <c r="U218" s="21"/>
+      <c r="V218" s="21"/>
+      <c r="W218" s="21"/>
+      <c r="X218" s="21"/>
+      <c r="Y218" s="21"/>
+      <c r="Z218" s="21"/>
+    </row>
+    <row r="219" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A219" s="22">
+        <v>218</v>
+      </c>
+      <c r="B219" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C219" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D219" s="22">
+        <v>226</v>
+      </c>
+      <c r="E219" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F219" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G219" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H219" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I219" s="23"/>
+      <c r="J219" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K219" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L219" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M219" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N219" s="21"/>
+      <c r="O219" s="21"/>
+      <c r="P219" s="21"/>
+      <c r="Q219" s="21"/>
+      <c r="R219" s="21"/>
+      <c r="S219" s="21"/>
+      <c r="T219" s="21"/>
+      <c r="U219" s="21"/>
+      <c r="V219" s="21"/>
+      <c r="W219" s="21"/>
+      <c r="X219" s="21"/>
+      <c r="Y219" s="21"/>
+      <c r="Z219" s="21"/>
+    </row>
+    <row r="220" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A220" s="28">
+        <v>219</v>
+      </c>
+      <c r="B220" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C220" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D220" s="28">
+        <v>254</v>
+      </c>
+      <c r="E220" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F220" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G220" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H220" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="I220" s="29"/>
+      <c r="J220" s="49">
+        <v>24297903</v>
+      </c>
+      <c r="K220" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="L220" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="M220" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="N220" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="O220" s="30"/>
+      <c r="P220" s="30"/>
+      <c r="Q220" s="30"/>
+      <c r="R220" s="30"/>
+      <c r="S220" s="30"/>
+      <c r="T220" s="30"/>
+      <c r="U220" s="30"/>
+      <c r="V220" s="30"/>
+      <c r="W220" s="30"/>
+      <c r="X220" s="30"/>
+      <c r="Y220" s="30"/>
+      <c r="Z220" s="30"/>
+    </row>
+    <row r="221" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A221" s="22">
+        <v>220</v>
+      </c>
+      <c r="B221" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C221" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D221" s="22">
+        <v>281</v>
+      </c>
+      <c r="E221" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F221" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G221" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H221" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I221" s="23"/>
+      <c r="J221" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K221" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L221" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M221" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N221" s="21"/>
+      <c r="O221" s="21"/>
+      <c r="P221" s="21"/>
+      <c r="Q221" s="21"/>
+      <c r="R221" s="21"/>
+      <c r="S221" s="21"/>
+      <c r="T221" s="21"/>
+      <c r="U221" s="21"/>
+      <c r="V221" s="21"/>
+      <c r="W221" s="21"/>
+      <c r="X221" s="21"/>
+      <c r="Y221" s="21"/>
+      <c r="Z221" s="21"/>
+    </row>
+    <row r="222" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A222" s="22">
+        <v>221</v>
+      </c>
+      <c r="B222" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C222" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D222" s="22">
+        <v>288</v>
+      </c>
+      <c r="E222" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F222" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G222" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H222" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I222" s="23"/>
+      <c r="J222" s="46">
+        <v>24297903</v>
+      </c>
+      <c r="K222" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L222" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M222" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="N222" s="21"/>
+      <c r="O222" s="21"/>
+      <c r="P222" s="21"/>
+      <c r="Q222" s="21"/>
+      <c r="R222" s="21"/>
+      <c r="S222" s="21"/>
+      <c r="T222" s="21"/>
+      <c r="U222" s="21"/>
+      <c r="V222" s="21"/>
+      <c r="W222" s="21"/>
+      <c r="X222" s="21"/>
+      <c r="Y222" s="21"/>
+      <c r="Z222" s="21"/>
+    </row>
+    <row r="223" spans="1:26" ht="27" thickBot="1">
+      <c r="A223" s="22">
+        <v>222</v>
+      </c>
+      <c r="B223" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C223" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D223" s="22">
+        <v>209</v>
+      </c>
+      <c r="E223" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F223" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G223" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H223" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I223" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J223" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K223" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L223" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M223" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N223" s="21"/>
+      <c r="O223" s="21"/>
+      <c r="P223" s="21"/>
+      <c r="Q223" s="21"/>
+      <c r="R223" s="21"/>
+      <c r="S223" s="21"/>
+      <c r="T223" s="21"/>
+      <c r="U223" s="21"/>
+      <c r="V223" s="21"/>
+      <c r="W223" s="21"/>
+      <c r="X223" s="21"/>
+      <c r="Y223" s="21"/>
+      <c r="Z223" s="21"/>
+    </row>
+    <row r="224" spans="1:26" ht="27" thickBot="1">
+      <c r="A224" s="22">
+        <v>223</v>
+      </c>
+      <c r="B224" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C224" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D224" s="22">
+        <v>209</v>
+      </c>
+      <c r="E224" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F224" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G224" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H224" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I224" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J224" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K224" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L224" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M224" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N224" s="21"/>
+      <c r="O224" s="21"/>
+      <c r="P224" s="21"/>
+      <c r="Q224" s="21"/>
+      <c r="R224" s="21"/>
+      <c r="S224" s="21"/>
+      <c r="T224" s="21"/>
+      <c r="U224" s="21"/>
+      <c r="V224" s="21"/>
+      <c r="W224" s="21"/>
+      <c r="X224" s="21"/>
+      <c r="Y224" s="21"/>
+      <c r="Z224" s="21"/>
+    </row>
+    <row r="225" spans="1:26" ht="27" thickBot="1">
+      <c r="A225" s="22">
+        <v>224</v>
+      </c>
+      <c r="B225" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C225" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D225" s="22">
+        <v>45</v>
+      </c>
+      <c r="E225" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F225" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="G225" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H225" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I225" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J225" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K225" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L225" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M225" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N225" s="21"/>
+      <c r="O225" s="21"/>
+      <c r="P225" s="21"/>
+      <c r="Q225" s="21"/>
+      <c r="R225" s="21"/>
+      <c r="S225" s="21"/>
+      <c r="T225" s="21"/>
+      <c r="U225" s="21"/>
+      <c r="V225" s="21"/>
+      <c r="W225" s="21"/>
+      <c r="X225" s="21"/>
+      <c r="Y225" s="21"/>
+      <c r="Z225" s="21"/>
+    </row>
+    <row r="226" spans="1:26" ht="27" thickBot="1">
+      <c r="A226" s="22">
+        <v>225</v>
+      </c>
+      <c r="B226" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C226" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D226" s="22">
+        <v>45</v>
+      </c>
+      <c r="E226" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F226" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G226" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H226" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I226" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J226" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K226" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L226" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M226" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N226" s="21"/>
+      <c r="O226" s="21"/>
+      <c r="P226" s="21"/>
+      <c r="Q226" s="21"/>
+      <c r="R226" s="21"/>
+      <c r="S226" s="21"/>
+      <c r="T226" s="21"/>
+      <c r="U226" s="21"/>
+      <c r="V226" s="21"/>
+      <c r="W226" s="21"/>
+      <c r="X226" s="21"/>
+      <c r="Y226" s="21"/>
+      <c r="Z226" s="21"/>
+    </row>
+    <row r="227" spans="1:26" ht="27" thickBot="1">
+      <c r="A227" s="22">
+        <v>226</v>
+      </c>
+      <c r="B227" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C227" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D227" s="22">
+        <v>45</v>
+      </c>
+      <c r="E227" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F227" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H227" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I227" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J227" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K227" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L227" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M227" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N227" s="21"/>
+      <c r="O227" s="21"/>
+      <c r="P227" s="21"/>
+      <c r="Q227" s="21"/>
+      <c r="R227" s="21"/>
+      <c r="S227" s="21"/>
+      <c r="T227" s="21"/>
+      <c r="U227" s="21"/>
+      <c r="V227" s="21"/>
+      <c r="W227" s="21"/>
+      <c r="X227" s="21"/>
+      <c r="Y227" s="21"/>
+      <c r="Z227" s="21"/>
+    </row>
+    <row r="228" spans="1:26" ht="27" thickBot="1">
+      <c r="A228" s="22">
+        <v>227</v>
+      </c>
+      <c r="B228" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C228" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D228" s="22">
+        <v>46</v>
+      </c>
+      <c r="E228" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F228" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H228" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I228" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J228" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K228" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L228" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M228" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N228" s="21"/>
+      <c r="O228" s="21"/>
+      <c r="P228" s="21"/>
+      <c r="Q228" s="21"/>
+      <c r="R228" s="21"/>
+      <c r="S228" s="21"/>
+      <c r="T228" s="21"/>
+      <c r="U228" s="21"/>
+      <c r="V228" s="21"/>
+      <c r="W228" s="21"/>
+      <c r="X228" s="21"/>
+      <c r="Y228" s="21"/>
+      <c r="Z228" s="21"/>
+    </row>
+    <row r="229" spans="1:26" ht="27" thickBot="1">
+      <c r="A229" s="22">
+        <v>228</v>
+      </c>
+      <c r="B229" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C229" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D229" s="22">
+        <v>272</v>
+      </c>
+      <c r="E229" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F229" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G229" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H229" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I229" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J229" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K229" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L229" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M229" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N229" s="21"/>
+      <c r="O229" s="21"/>
+      <c r="P229" s="21"/>
+      <c r="Q229" s="21"/>
+      <c r="R229" s="21"/>
+      <c r="S229" s="21"/>
+      <c r="T229" s="21"/>
+      <c r="U229" s="21"/>
+      <c r="V229" s="21"/>
+      <c r="W229" s="21"/>
+      <c r="X229" s="21"/>
+      <c r="Y229" s="21"/>
+      <c r="Z229" s="21"/>
+    </row>
+    <row r="230" spans="1:26" ht="27" thickBot="1">
+      <c r="A230" s="22">
+        <v>229</v>
+      </c>
+      <c r="B230" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C230" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D230" s="22">
+        <v>269</v>
+      </c>
+      <c r="E230" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F230" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G230" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H230" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I230" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J230" s="46">
+        <v>16281039</v>
+      </c>
+      <c r="K230" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L230" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M230" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="N230" s="21"/>
+      <c r="O230" s="21"/>
+      <c r="P230" s="21"/>
+      <c r="Q230" s="21"/>
+      <c r="R230" s="21"/>
+      <c r="S230" s="21"/>
+      <c r="T230" s="21"/>
+      <c r="U230" s="21"/>
+      <c r="V230" s="21"/>
+      <c r="W230" s="21"/>
+      <c r="X230" s="21"/>
+      <c r="Y230" s="21"/>
+      <c r="Z230" s="21"/>
+    </row>
+    <row r="231" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A231" s="22">
+        <v>230</v>
+      </c>
+      <c r="B231" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C231" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D231" s="22">
+        <v>159</v>
+      </c>
+      <c r="E231" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F231" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G231" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H231" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I231" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J231" s="46">
+        <v>28690392</v>
+      </c>
+      <c r="K231" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L231" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M231" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="N231" s="21"/>
+      <c r="O231" s="21"/>
+      <c r="P231" s="21"/>
+      <c r="Q231" s="21"/>
+      <c r="R231" s="21"/>
+      <c r="S231" s="21"/>
+      <c r="T231" s="21"/>
+      <c r="U231" s="21"/>
+      <c r="V231" s="21"/>
+      <c r="W231" s="21"/>
+      <c r="X231" s="21"/>
+      <c r="Y231" s="21"/>
+      <c r="Z231" s="21"/>
+    </row>
+    <row r="232" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A232" s="22">
+        <v>231</v>
+      </c>
+      <c r="B232" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C232" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D232" s="22">
+        <v>235</v>
+      </c>
+      <c r="E232" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F232" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G232" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I232" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J232" s="46">
+        <v>28690392</v>
+      </c>
+      <c r="K232" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L232" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M232" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="N232" s="21"/>
+      <c r="O232" s="21"/>
+      <c r="P232" s="21"/>
+      <c r="Q232" s="21"/>
+      <c r="R232" s="21"/>
+      <c r="S232" s="21"/>
+      <c r="T232" s="21"/>
+      <c r="U232" s="21"/>
+      <c r="V232" s="21"/>
+      <c r="W232" s="21"/>
+      <c r="X232" s="21"/>
+      <c r="Y232" s="21"/>
+      <c r="Z232" s="21"/>
+    </row>
+    <row r="233" spans="1:26" ht="15.75" thickBot="1">
+      <c r="A233" s="22">
+        <v>232</v>
+      </c>
+      <c r="B233" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C233" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D233" s="22">
+        <v>411</v>
+      </c>
+      <c r="E233" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F233" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G233" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H233" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="I233" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="J233" s="46">
+        <v>10962020</v>
+      </c>
+      <c r="K233" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L233" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M233" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="N233" s="21"/>
+      <c r="O233" s="21"/>
+      <c r="P233" s="21"/>
+      <c r="Q233" s="21"/>
+      <c r="R233" s="21"/>
+      <c r="S233" s="21"/>
+      <c r="T233" s="21"/>
+      <c r="U233" s="21"/>
+      <c r="V233" s="21"/>
+      <c r="W233" s="21"/>
+      <c r="X233" s="21"/>
+      <c r="Y233" s="21"/>
+      <c r="Z233" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M139" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -11599,8 +13641,51 @@
     <hyperlink ref="M188" r:id="rId187" xr:uid="{CF5B4461-0859-49A2-A6E0-5CFD671F79DD}"/>
     <hyperlink ref="M189" r:id="rId188" xr:uid="{2888B6C2-771C-4EA2-B2A4-7428D0EE6B7F}"/>
     <hyperlink ref="M190" r:id="rId189" xr:uid="{664AFFA6-856A-465E-B5E5-D5324E991708}"/>
+    <hyperlink ref="M191" r:id="rId190" xr:uid="{6F4D62EC-6F57-42F8-9142-EFC4DD76B058}"/>
+    <hyperlink ref="M192" r:id="rId191" xr:uid="{1F2EA1B0-25A3-4C26-9D9D-BFACBBA29962}"/>
+    <hyperlink ref="M193" r:id="rId192" xr:uid="{D18E1C8E-CFED-4DBF-9C54-50F2AF3C95CA}"/>
+    <hyperlink ref="M194" r:id="rId193" xr:uid="{613533E6-CB25-4E9D-BB4E-3D8EDC09B526}"/>
+    <hyperlink ref="M195" r:id="rId194" xr:uid="{342AFA95-F3F3-41EA-BFAE-E48C608EF210}"/>
+    <hyperlink ref="M196" r:id="rId195" xr:uid="{868EC167-366E-4ABA-91C2-B72F64D42195}"/>
+    <hyperlink ref="M197" r:id="rId196" xr:uid="{FF5B79F2-C164-47AF-BE46-8CB51D6393C2}"/>
+    <hyperlink ref="M198" r:id="rId197" xr:uid="{F7AE58D3-4475-41E3-B763-27D262AE5433}"/>
+    <hyperlink ref="M199" r:id="rId198" xr:uid="{14459DE9-20D0-4022-9594-6FA82120BF75}"/>
+    <hyperlink ref="M200" r:id="rId199" xr:uid="{801673F5-C4DB-4E00-88E5-D8DEC9086269}"/>
+    <hyperlink ref="M201" r:id="rId200" xr:uid="{EDB6896F-96F0-4A86-AA85-06C151C3C6F8}"/>
+    <hyperlink ref="M202" r:id="rId201" xr:uid="{B250C3AB-0545-416B-95C2-229CD6B89646}"/>
+    <hyperlink ref="M203" r:id="rId202" xr:uid="{5D0DD250-9D38-4F11-A915-276C3DDC91BF}"/>
+    <hyperlink ref="M204" r:id="rId203" xr:uid="{D1619530-1555-4969-9ED8-F1E5F9DFD6A8}"/>
+    <hyperlink ref="M205" r:id="rId204" xr:uid="{FE19830E-BFA3-4CBC-8797-5364AC9C2D77}"/>
+    <hyperlink ref="M206" r:id="rId205" xr:uid="{B17E6127-D5BD-4354-9A57-B1E1028DA5FD}"/>
+    <hyperlink ref="M207" r:id="rId206" xr:uid="{3232EC9D-C98B-49E5-A420-39285728A51F}"/>
+    <hyperlink ref="M208" r:id="rId207" xr:uid="{5934685A-830D-4389-B7B1-240C77E2AAEF}"/>
+    <hyperlink ref="M209" r:id="rId208" xr:uid="{200C4C8C-B885-4FF4-B54B-46B4CC812D62}"/>
+    <hyperlink ref="M210" r:id="rId209" xr:uid="{C3373C37-9702-4B2F-AEA0-C061F768A55D}"/>
+    <hyperlink ref="M211" r:id="rId210" xr:uid="{EADC039A-3024-43F8-989A-3E2B0DDDEB9B}"/>
+    <hyperlink ref="M212" r:id="rId211" xr:uid="{8E650CE1-1429-4A67-B3ED-74C02D608D00}"/>
+    <hyperlink ref="M213" r:id="rId212" xr:uid="{3482D17A-5721-431A-B9C7-574ED9C1F960}"/>
+    <hyperlink ref="M214" r:id="rId213" xr:uid="{EA8E9582-272A-423D-AEE6-7FC087C574A1}"/>
+    <hyperlink ref="M215" r:id="rId214" xr:uid="{162ABAF6-F7B9-42BA-89CF-3BD51FB8BF80}"/>
+    <hyperlink ref="M216" r:id="rId215" xr:uid="{31188689-0944-4B23-B67A-639E2B113A65}"/>
+    <hyperlink ref="M218" r:id="rId216" xr:uid="{F69621A1-371D-4743-AD3A-13120E9D426C}"/>
+    <hyperlink ref="M220" r:id="rId217" xr:uid="{63B8E403-CCA6-4A09-BBA1-E2F2C2B81D52}"/>
+    <hyperlink ref="M222" r:id="rId218" xr:uid="{1C9C7A0B-C429-4117-A1DE-7276582B92B8}"/>
+    <hyperlink ref="M217" r:id="rId219" xr:uid="{D7ED2020-A0E7-4B19-8F51-8ABE23553B30}"/>
+    <hyperlink ref="M219" r:id="rId220" xr:uid="{EF666533-83A9-4376-A5B2-76A3A14E8C85}"/>
+    <hyperlink ref="M221" r:id="rId221" xr:uid="{6FC95C51-5492-47C3-890D-FCC99948D704}"/>
+    <hyperlink ref="M223" r:id="rId222" xr:uid="{944E074C-84BC-4391-AC68-E7ABA6307885}"/>
+    <hyperlink ref="M224" r:id="rId223" xr:uid="{F1C56F63-7112-4EA6-BEBC-B456786AC0FB}"/>
+    <hyperlink ref="M225" r:id="rId224" xr:uid="{48B797B8-C076-48BC-860D-DB8227CF0800}"/>
+    <hyperlink ref="M227" r:id="rId225" xr:uid="{77D73440-7162-48DB-89EB-308A16476429}"/>
+    <hyperlink ref="M229" r:id="rId226" xr:uid="{2CA164D9-779B-4C1C-83C5-63D73F6D473D}"/>
+    <hyperlink ref="M226" r:id="rId227" xr:uid="{890C5044-84E6-4358-8703-DE444A0235AE}"/>
+    <hyperlink ref="M228" r:id="rId228" xr:uid="{684E09C7-D309-4111-9825-571AE3B849BD}"/>
+    <hyperlink ref="M230" r:id="rId229" xr:uid="{8E1FDE5B-438F-42C1-B716-9EC6450E3237}"/>
+    <hyperlink ref="M233" r:id="rId230" xr:uid="{3F4C4585-C8E6-44AF-82B6-A3986F98D75E}"/>
+    <hyperlink ref="M232" r:id="rId231" xr:uid="{BD512CD7-0375-42DE-885C-8E1B13436BF6}"/>
+    <hyperlink ref="M231" r:id="rId232" xr:uid="{73963EED-C556-42C9-85CD-3F50006712E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId190"/>
+  <pageSetup orientation="portrait" r:id="rId233"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D987C0E-0A43-4541-A691-5BB187013F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223EBA5C-FCBD-4C3E-83B0-C865A5A59CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29265" yWindow="1035" windowWidth="18165" windowHeight="11130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24180" yWindow="2220" windowWidth="18165" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$414</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -24,21 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3898" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3945" uniqueCount="258">
   <si>
     <t>OID</t>
   </si>
@@ -559,9 +550,6 @@
     <t>https://doi.org/10.1016/j.parkreldis.2020.02.003</t>
   </si>
   <si>
-    <t>No Effect</t>
-  </si>
-  <si>
     <t>FMP</t>
   </si>
   <si>
@@ -646,9 +634,6 @@
     <t>Congenital Myasthenia</t>
   </si>
   <si>
-    <t>Neutral</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1172/jci34527</t>
   </si>
   <si>
@@ -739,9 +724,6 @@
     <t>Neuropathic Pain</t>
   </si>
   <si>
-    <t>GOF (Inhibition Resistance)</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1074/jbc.ra118.005649</t>
   </si>
   <si>
@@ -815,6 +797,12 @@
   </si>
   <si>
     <t>https://doi.org/10.1016/0896-6273(95)90080-2</t>
+  </si>
+  <si>
+    <t>Single Channel</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1172/JCI34527</t>
   </si>
 </sst>
 </file>
@@ -917,7 +905,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -955,13 +943,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1105,6 +1153,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Excel Built-in Normal 1" xfId="1" xr:uid="{D585C33E-D382-4BD9-8030-CD231C838104}"/>
@@ -1387,13 +1459,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z409"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Z415"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="2"/>
     <col min="6" max="6" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1447,7 +1520,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" thickBot="1">
+    <row r="2" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A2" s="18">
         <v>1</v>
       </c>
@@ -1499,7 +1572,7 @@
       <c r="Y2" s="20"/>
       <c r="Z2" s="20"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" thickBot="1">
+    <row r="3" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A3" s="18">
         <v>2</v>
       </c>
@@ -1551,7 +1624,7 @@
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" thickBot="1">
+    <row r="4" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A4" s="18">
         <v>3</v>
       </c>
@@ -1601,7 +1674,7 @@
       <c r="Y4" s="20"/>
       <c r="Z4" s="20"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" thickBot="1">
+    <row r="5" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A5" s="18">
         <v>4</v>
       </c>
@@ -1651,7 +1724,7 @@
       <c r="Y5" s="20"/>
       <c r="Z5" s="20"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" thickBot="1">
+    <row r="6" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A6" s="18">
         <v>5</v>
       </c>
@@ -2147,7 +2220,7 @@
       <c r="Y15" s="25"/>
       <c r="Z15" s="25"/>
     </row>
-    <row r="16" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="16" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A16" s="18">
         <v>15</v>
       </c>
@@ -2188,7 +2261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="11" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
+    <row r="17" spans="1:26" s="11" customFormat="1" ht="17.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A17" s="18">
         <v>16</v>
       </c>
@@ -2229,7 +2302,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="18" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A18" s="18">
         <v>17</v>
       </c>
@@ -2270,7 +2343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="19" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A19" s="18">
         <v>18</v>
       </c>
@@ -2314,7 +2387,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="20" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A20" s="18">
         <v>19</v>
       </c>
@@ -2358,7 +2431,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A21" s="18">
         <v>20</v>
       </c>
@@ -2399,7 +2472,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A22" s="18">
         <v>21</v>
       </c>
@@ -2438,7 +2511,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A23" s="18">
         <v>22</v>
       </c>
@@ -2479,7 +2552,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A24" s="18">
         <v>23</v>
       </c>
@@ -2520,7 +2593,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A25" s="18">
         <v>24</v>
       </c>
@@ -2561,7 +2634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A26" s="18">
         <v>25</v>
       </c>
@@ -2602,7 +2675,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A27" s="18">
         <v>26</v>
       </c>
@@ -2643,7 +2716,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A28" s="18">
         <v>27</v>
       </c>
@@ -2685,7 +2758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
+    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A29" s="18">
         <v>28</v>
       </c>
@@ -2724,7 +2797,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.75" thickBot="1">
+    <row r="30" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A30" s="18">
         <v>29</v>
       </c>
@@ -2778,7 +2851,7 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" thickBot="1">
+    <row r="31" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A31" s="18">
         <v>30</v>
       </c>
@@ -2832,7 +2905,7 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" thickBot="1">
+    <row r="32" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A32" s="18">
         <v>31</v>
       </c>
@@ -2886,7 +2959,7 @@
       <c r="Y32" s="17"/>
       <c r="Z32" s="17"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" thickBot="1">
+    <row r="33" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A33" s="18">
         <v>32</v>
       </c>
@@ -2938,7 +3011,7 @@
       <c r="Y33" s="17"/>
       <c r="Z33" s="17"/>
     </row>
-    <row r="34" spans="1:26" ht="39.75" thickBot="1">
+    <row r="34" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A34" s="18">
         <v>33</v>
       </c>
@@ -2992,7 +3065,7 @@
       <c r="Y34" s="17"/>
       <c r="Z34" s="17"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" thickBot="1">
+    <row r="35" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A35" s="18">
         <v>34</v>
       </c>
@@ -3044,7 +3117,7 @@
       <c r="Y35" s="20"/>
       <c r="Z35" s="20"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" thickBot="1">
+    <row r="36" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A36" s="18">
         <v>35</v>
       </c>
@@ -3096,7 +3169,7 @@
       <c r="Y36" s="20"/>
       <c r="Z36" s="20"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" thickBot="1">
+    <row r="37" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A37" s="18">
         <v>36</v>
       </c>
@@ -3148,7 +3221,7 @@
       <c r="Y37" s="20"/>
       <c r="Z37" s="20"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" thickBot="1">
+    <row r="38" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A38" s="18">
         <v>37</v>
       </c>
@@ -3200,7 +3273,7 @@
       <c r="Y38" s="20"/>
       <c r="Z38" s="20"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" thickBot="1">
+    <row r="39" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A39" s="18">
         <v>38</v>
       </c>
@@ -3252,7 +3325,7 @@
       <c r="Y39" s="20"/>
       <c r="Z39" s="20"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" thickBot="1">
+    <row r="40" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A40" s="18">
         <v>39</v>
       </c>
@@ -3304,7 +3377,7 @@
       <c r="Y40" s="20"/>
       <c r="Z40" s="20"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" thickBot="1">
+    <row r="41" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A41" s="18">
         <v>40</v>
       </c>
@@ -3356,7 +3429,7 @@
       <c r="Y41" s="20"/>
       <c r="Z41" s="20"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" thickBot="1">
+    <row r="42" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A42" s="18">
         <v>41</v>
       </c>
@@ -3408,7 +3481,7 @@
       <c r="Y42" s="20"/>
       <c r="Z42" s="20"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" thickBot="1">
+    <row r="43" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A43" s="18">
         <v>42</v>
       </c>
@@ -3460,7 +3533,7 @@
       <c r="Y43" s="20"/>
       <c r="Z43" s="20"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" thickBot="1">
+    <row r="44" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A44" s="18">
         <v>43</v>
       </c>
@@ -3512,7 +3585,7 @@
       <c r="Y44" s="20"/>
       <c r="Z44" s="20"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" thickBot="1">
+    <row r="45" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -3564,7 +3637,7 @@
       <c r="Y45" s="20"/>
       <c r="Z45" s="20"/>
     </row>
-    <row r="46" spans="1:26" s="7" customFormat="1" ht="30.75" thickBot="1">
+    <row r="46" spans="1:26" s="7" customFormat="1" ht="30.75" hidden="1" thickBot="1">
       <c r="A46" s="18">
         <v>45</v>
       </c>
@@ -3605,7 +3678,7 @@
         <v>135</v>
       </c>
       <c r="N46" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O46" s="25"/>
       <c r="P46" s="25"/>
@@ -3620,7 +3693,7 @@
       <c r="Y46" s="25"/>
       <c r="Z46" s="25"/>
     </row>
-    <row r="47" spans="1:26" s="7" customFormat="1" ht="27" thickBot="1">
+    <row r="47" spans="1:26" s="7" customFormat="1" ht="27" hidden="1" thickBot="1">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -3674,7 +3747,7 @@
       <c r="Y47" s="25"/>
       <c r="Z47" s="25"/>
     </row>
-    <row r="48" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
+    <row r="48" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A48" s="18">
         <v>47</v>
       </c>
@@ -3728,7 +3801,7 @@
       <c r="Y48" s="25"/>
       <c r="Z48" s="25"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" thickBot="1">
+    <row r="49" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A49" s="18">
         <v>48</v>
       </c>
@@ -3782,7 +3855,7 @@
       <c r="Y49" s="20"/>
       <c r="Z49" s="20"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" thickBot="1">
+    <row r="50" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A50" s="18">
         <v>49</v>
       </c>
@@ -3836,7 +3909,7 @@
       <c r="Y50" s="20"/>
       <c r="Z50" s="20"/>
     </row>
-    <row r="51" spans="1:26" s="7" customFormat="1" ht="27" thickBot="1">
+    <row r="51" spans="1:26" s="7" customFormat="1" ht="27" hidden="1" thickBot="1">
       <c r="A51" s="18">
         <v>50</v>
       </c>
@@ -3877,7 +3950,7 @@
         <v>132</v>
       </c>
       <c r="N51" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O51" s="25"/>
       <c r="P51" s="25"/>
@@ -3892,7 +3965,7 @@
       <c r="Y51" s="25"/>
       <c r="Z51" s="25"/>
     </row>
-    <row r="52" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
+    <row r="52" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A52" s="18">
         <v>51</v>
       </c>
@@ -3946,7 +4019,7 @@
       <c r="Y52" s="25"/>
       <c r="Z52" s="25"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" thickBot="1">
+    <row r="53" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A53" s="18">
         <v>52</v>
       </c>
@@ -4000,7 +4073,7 @@
       <c r="Y53" s="20"/>
       <c r="Z53" s="20"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" thickBot="1">
+    <row r="54" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A54" s="18">
         <v>53</v>
       </c>
@@ -4054,7 +4127,7 @@
       <c r="Y54" s="20"/>
       <c r="Z54" s="20"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" thickBot="1">
+    <row r="55" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A55" s="18">
         <v>54</v>
       </c>
@@ -4108,7 +4181,7 @@
       <c r="Y55" s="20"/>
       <c r="Z55" s="20"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" thickBot="1">
+    <row r="56" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A56" s="18">
         <v>55</v>
       </c>
@@ -4160,7 +4233,7 @@
       <c r="Y56" s="20"/>
       <c r="Z56" s="20"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" thickBot="1">
+    <row r="57" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A57" s="18">
         <v>56</v>
       </c>
@@ -4214,7 +4287,7 @@
       <c r="Y57" s="20"/>
       <c r="Z57" s="20"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" thickBot="1">
+    <row r="58" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A58" s="18">
         <v>57</v>
       </c>
@@ -4268,7 +4341,7 @@
       <c r="Y58" s="20"/>
       <c r="Z58" s="20"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" thickBot="1">
+    <row r="59" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A59" s="18">
         <v>58</v>
       </c>
@@ -4322,7 +4395,7 @@
       <c r="Y59" s="20"/>
       <c r="Z59" s="20"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" thickBot="1">
+    <row r="60" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A60" s="18">
         <v>59</v>
       </c>
@@ -4376,7 +4449,7 @@
       <c r="Y60" s="20"/>
       <c r="Z60" s="20"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" thickBot="1">
+    <row r="61" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A61" s="18">
         <v>60</v>
       </c>
@@ -4430,7 +4503,7 @@
       <c r="Y61" s="20"/>
       <c r="Z61" s="20"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" thickBot="1">
+    <row r="62" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A62" s="18">
         <v>61</v>
       </c>
@@ -4484,7 +4557,7 @@
       <c r="Y62" s="20"/>
       <c r="Z62" s="20"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" thickBot="1">
+    <row r="63" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A63" s="18">
         <v>62</v>
       </c>
@@ -4538,7 +4611,7 @@
       <c r="Y63" s="20"/>
       <c r="Z63" s="20"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" thickBot="1">
+    <row r="64" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A64" s="18">
         <v>63</v>
       </c>
@@ -4592,7 +4665,7 @@
       <c r="Y64" s="20"/>
       <c r="Z64" s="20"/>
     </row>
-    <row r="65" spans="1:26" ht="27" thickBot="1">
+    <row r="65" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A65" s="18">
         <v>64</v>
       </c>
@@ -4646,7 +4719,7 @@
       <c r="Y65" s="20"/>
       <c r="Z65" s="20"/>
     </row>
-    <row r="66" spans="1:26" ht="27" thickBot="1">
+    <row r="66" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A66" s="18">
         <v>65</v>
       </c>
@@ -4700,7 +4773,7 @@
       <c r="Y66" s="20"/>
       <c r="Z66" s="20"/>
     </row>
-    <row r="67" spans="1:26" ht="27" thickBot="1">
+    <row r="67" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A67" s="18">
         <v>66</v>
       </c>
@@ -4752,7 +4825,7 @@
       <c r="Y67" s="20"/>
       <c r="Z67" s="20"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" thickBot="1">
+    <row r="68" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A68" s="18">
         <v>67</v>
       </c>
@@ -4806,7 +4879,7 @@
       <c r="Y68" s="20"/>
       <c r="Z68" s="20"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" thickBot="1">
+    <row r="69" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A69" s="18">
         <v>68</v>
       </c>
@@ -4860,7 +4933,7 @@
       <c r="Y69" s="20"/>
       <c r="Z69" s="20"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" thickBot="1">
+    <row r="70" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A70" s="18">
         <v>69</v>
       </c>
@@ -4914,7 +4987,7 @@
       <c r="Y70" s="20"/>
       <c r="Z70" s="20"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" thickBot="1">
+    <row r="71" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A71" s="18">
         <v>70</v>
       </c>
@@ -4968,7 +5041,7 @@
       <c r="Y71" s="20"/>
       <c r="Z71" s="20"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" thickBot="1">
+    <row r="72" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A72" s="18">
         <v>71</v>
       </c>
@@ -5022,7 +5095,7 @@
       <c r="Y72" s="20"/>
       <c r="Z72" s="20"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" thickBot="1">
+    <row r="73" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A73" s="18">
         <v>72</v>
       </c>
@@ -5074,7 +5147,7 @@
       <c r="Y73" s="20"/>
       <c r="Z73" s="20"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" thickBot="1">
+    <row r="74" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A74" s="18">
         <v>73</v>
       </c>
@@ -5128,7 +5201,7 @@
       <c r="Y74" s="20"/>
       <c r="Z74" s="20"/>
     </row>
-    <row r="75" spans="1:26" ht="27" thickBot="1">
+    <row r="75" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A75" s="18">
         <v>74</v>
       </c>
@@ -5182,7 +5255,7 @@
       <c r="Y75" s="20"/>
       <c r="Z75" s="20"/>
     </row>
-    <row r="76" spans="1:26" ht="27" thickBot="1">
+    <row r="76" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A76" s="18">
         <v>75</v>
       </c>
@@ -5236,7 +5309,7 @@
       <c r="Y76" s="20"/>
       <c r="Z76" s="20"/>
     </row>
-    <row r="77" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
+    <row r="77" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A77" s="46">
         <v>76</v>
       </c>
@@ -5277,7 +5350,7 @@
         <v>92</v>
       </c>
       <c r="N77" s="52" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O77" s="52"/>
       <c r="P77" s="52"/>
@@ -5292,7 +5365,7 @@
       <c r="Y77" s="52"/>
       <c r="Z77" s="52"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" thickBot="1">
+    <row r="78" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A78" s="18">
         <v>77</v>
       </c>
@@ -5346,7 +5419,7 @@
       <c r="Y78" s="20"/>
       <c r="Z78" s="20"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" thickBot="1">
+    <row r="79" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A79" s="18">
         <v>78</v>
       </c>
@@ -5400,7 +5473,7 @@
       <c r="Y79" s="20"/>
       <c r="Z79" s="20"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" thickBot="1">
+    <row r="80" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A80" s="18">
         <v>79</v>
       </c>
@@ -5454,7 +5527,7 @@
       <c r="Y80" s="20"/>
       <c r="Z80" s="20"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" thickBot="1">
+    <row r="81" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A81" s="18">
         <v>80</v>
       </c>
@@ -5508,7 +5581,7 @@
       <c r="Y81" s="20"/>
       <c r="Z81" s="20"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" thickBot="1">
+    <row r="82" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A82" s="18">
         <v>81</v>
       </c>
@@ -5562,7 +5635,7 @@
       <c r="Y82" s="20"/>
       <c r="Z82" s="20"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" thickBot="1">
+    <row r="83" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A83" s="18">
         <v>82</v>
       </c>
@@ -5616,7 +5689,7 @@
       <c r="Y83" s="20"/>
       <c r="Z83" s="20"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" thickBot="1">
+    <row r="84" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A84" s="18">
         <v>83</v>
       </c>
@@ -5670,7 +5743,7 @@
       <c r="Y84" s="20"/>
       <c r="Z84" s="20"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" thickBot="1">
+    <row r="85" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A85" s="18">
         <v>84</v>
       </c>
@@ -5724,7 +5797,7 @@
       <c r="Y85" s="20"/>
       <c r="Z85" s="20"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" thickBot="1">
+    <row r="86" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A86" s="18">
         <v>85</v>
       </c>
@@ -5778,7 +5851,7 @@
       <c r="Y86" s="20"/>
       <c r="Z86" s="20"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" thickBot="1">
+    <row r="87" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A87" s="18">
         <v>86</v>
       </c>
@@ -5832,7 +5905,7 @@
       <c r="Y87" s="20"/>
       <c r="Z87" s="20"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" thickBot="1">
+    <row r="88" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A88" s="18">
         <v>87</v>
       </c>
@@ -5886,7 +5959,7 @@
       <c r="Y88" s="20"/>
       <c r="Z88" s="20"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" thickBot="1">
+    <row r="89" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A89" s="18">
         <v>88</v>
       </c>
@@ -5940,7 +6013,7 @@
       <c r="Y89" s="20"/>
       <c r="Z89" s="20"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" thickBot="1">
+    <row r="90" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A90" s="18">
         <v>89</v>
       </c>
@@ -5994,7 +6067,7 @@
       <c r="Y90" s="20"/>
       <c r="Z90" s="20"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" thickBot="1">
+    <row r="91" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A91" s="18">
         <v>90</v>
       </c>
@@ -6048,7 +6121,7 @@
       <c r="Y91" s="20"/>
       <c r="Z91" s="20"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" thickBot="1">
+    <row r="92" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A92" s="18">
         <v>91</v>
       </c>
@@ -6102,7 +6175,7 @@
       <c r="Y92" s="20"/>
       <c r="Z92" s="20"/>
     </row>
-    <row r="93" spans="1:26" ht="27" thickBot="1">
+    <row r="93" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A93" s="18">
         <v>92</v>
       </c>
@@ -6156,7 +6229,7 @@
       <c r="Y93" s="20"/>
       <c r="Z93" s="20"/>
     </row>
-    <row r="94" spans="1:26" ht="27" thickBot="1">
+    <row r="94" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A94" s="18">
         <v>93</v>
       </c>
@@ -6210,7 +6283,7 @@
       <c r="Y94" s="20"/>
       <c r="Z94" s="20"/>
     </row>
-    <row r="95" spans="1:26" ht="27" thickBot="1">
+    <row r="95" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A95" s="18">
         <v>94</v>
       </c>
@@ -6262,7 +6335,7 @@
       <c r="Y95" s="20"/>
       <c r="Z95" s="20"/>
     </row>
-    <row r="96" spans="1:26" ht="27" thickBot="1">
+    <row r="96" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A96" s="18">
         <v>95</v>
       </c>
@@ -6316,7 +6389,7 @@
       <c r="Y96" s="20"/>
       <c r="Z96" s="20"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" thickBot="1">
+    <row r="97" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A97" s="18">
         <v>96</v>
       </c>
@@ -6370,7 +6443,7 @@
       <c r="Y97" s="20"/>
       <c r="Z97" s="20"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" thickBot="1">
+    <row r="98" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A98" s="18">
         <v>97</v>
       </c>
@@ -6424,7 +6497,7 @@
       <c r="Y98" s="20"/>
       <c r="Z98" s="20"/>
     </row>
-    <row r="99" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
+    <row r="99" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A99" s="46">
         <v>98</v>
       </c>
@@ -6465,7 +6538,7 @@
         <v>101</v>
       </c>
       <c r="N99" s="52" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O99" s="52"/>
       <c r="P99" s="52"/>
@@ -6480,7 +6553,7 @@
       <c r="Y99" s="52"/>
       <c r="Z99" s="52"/>
     </row>
-    <row r="100" spans="1:26" ht="27" thickBot="1">
+    <row r="100" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A100" s="18">
         <v>99</v>
       </c>
@@ -6534,7 +6607,7 @@
       <c r="Y100" s="20"/>
       <c r="Z100" s="20"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" thickBot="1">
+    <row r="101" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A101" s="18">
         <v>100</v>
       </c>
@@ -6588,7 +6661,7 @@
       <c r="Y101" s="20"/>
       <c r="Z101" s="20"/>
     </row>
-    <row r="102" spans="1:26" ht="27" thickBot="1">
+    <row r="102" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A102" s="18">
         <v>101</v>
       </c>
@@ -6642,7 +6715,7 @@
       <c r="Y102" s="20"/>
       <c r="Z102" s="20"/>
     </row>
-    <row r="103" spans="1:26" ht="27" thickBot="1">
+    <row r="103" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A103" s="18">
         <v>102</v>
       </c>
@@ -6696,7 +6769,7 @@
       <c r="Y103" s="20"/>
       <c r="Z103" s="20"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" thickBot="1">
+    <row r="104" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A104" s="18">
         <v>103</v>
       </c>
@@ -6750,7 +6823,7 @@
       <c r="Y104" s="20"/>
       <c r="Z104" s="20"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" thickBot="1">
+    <row r="105" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A105" s="18">
         <v>104</v>
       </c>
@@ -6804,7 +6877,7 @@
       <c r="Y105" s="20"/>
       <c r="Z105" s="20"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" thickBot="1">
+    <row r="106" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A106" s="18">
         <v>105</v>
       </c>
@@ -6856,7 +6929,7 @@
       <c r="Y106" s="20"/>
       <c r="Z106" s="20"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" thickBot="1">
+    <row r="107" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A107" s="18">
         <v>106</v>
       </c>
@@ -6910,7 +6983,7 @@
       <c r="Y107" s="20"/>
       <c r="Z107" s="20"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" thickBot="1">
+    <row r="108" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A108" s="18">
         <v>107</v>
       </c>
@@ -6964,7 +7037,7 @@
       <c r="Y108" s="20"/>
       <c r="Z108" s="20"/>
     </row>
-    <row r="109" spans="1:26" ht="27" thickBot="1">
+    <row r="109" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A109" s="18">
         <v>108</v>
       </c>
@@ -7018,7 +7091,7 @@
       <c r="Y109" s="20"/>
       <c r="Z109" s="20"/>
     </row>
-    <row r="110" spans="1:26" ht="27" thickBot="1">
+    <row r="110" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A110" s="18">
         <v>109</v>
       </c>
@@ -7072,7 +7145,7 @@
       <c r="Y110" s="20"/>
       <c r="Z110" s="20"/>
     </row>
-    <row r="111" spans="1:26" ht="27" thickBot="1">
+    <row r="111" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A111" s="18">
         <v>110</v>
       </c>
@@ -7126,7 +7199,7 @@
       <c r="Y111" s="20"/>
       <c r="Z111" s="20"/>
     </row>
-    <row r="112" spans="1:26" ht="27" thickBot="1">
+    <row r="112" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A112" s="18">
         <v>111</v>
       </c>
@@ -7180,7 +7253,7 @@
       <c r="Y112" s="20"/>
       <c r="Z112" s="20"/>
     </row>
-    <row r="113" spans="1:26" ht="27" thickBot="1">
+    <row r="113" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A113" s="18">
         <v>112</v>
       </c>
@@ -7234,7 +7307,7 @@
       <c r="Y113" s="20"/>
       <c r="Z113" s="20"/>
     </row>
-    <row r="114" spans="1:26" ht="27" thickBot="1">
+    <row r="114" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A114" s="18">
         <v>113</v>
       </c>
@@ -7288,7 +7361,7 @@
       <c r="Y114" s="20"/>
       <c r="Z114" s="20"/>
     </row>
-    <row r="115" spans="1:26" ht="27" thickBot="1">
+    <row r="115" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A115" s="18">
         <v>114</v>
       </c>
@@ -7342,7 +7415,7 @@
       <c r="Y115" s="20"/>
       <c r="Z115" s="20"/>
     </row>
-    <row r="116" spans="1:26" ht="27" thickBot="1">
+    <row r="116" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A116" s="18">
         <v>115</v>
       </c>
@@ -7396,7 +7469,7 @@
       <c r="Y116" s="20"/>
       <c r="Z116" s="20"/>
     </row>
-    <row r="117" spans="1:26" ht="27" thickBot="1">
+    <row r="117" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A117" s="18">
         <v>116</v>
       </c>
@@ -7450,7 +7523,7 @@
       <c r="Y117" s="20"/>
       <c r="Z117" s="20"/>
     </row>
-    <row r="118" spans="1:26" ht="27" thickBot="1">
+    <row r="118" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A118" s="18">
         <v>117</v>
       </c>
@@ -7504,7 +7577,7 @@
       <c r="Y118" s="20"/>
       <c r="Z118" s="20"/>
     </row>
-    <row r="119" spans="1:26" ht="27" thickBot="1">
+    <row r="119" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A119" s="18">
         <v>118</v>
       </c>
@@ -7558,7 +7631,7 @@
       <c r="Y119" s="20"/>
       <c r="Z119" s="20"/>
     </row>
-    <row r="120" spans="1:26" ht="27" thickBot="1">
+    <row r="120" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A120" s="18">
         <v>119</v>
       </c>
@@ -7612,7 +7685,7 @@
       <c r="Y120" s="20"/>
       <c r="Z120" s="20"/>
     </row>
-    <row r="121" spans="1:26" ht="27" thickBot="1">
+    <row r="121" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A121" s="18">
         <v>120</v>
       </c>
@@ -7666,7 +7739,7 @@
       <c r="Y121" s="20"/>
       <c r="Z121" s="20"/>
     </row>
-    <row r="122" spans="1:26" ht="27" thickBot="1">
+    <row r="122" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A122" s="18">
         <v>121</v>
       </c>
@@ -7720,7 +7793,7 @@
       <c r="Y122" s="20"/>
       <c r="Z122" s="20"/>
     </row>
-    <row r="123" spans="1:26" ht="27" thickBot="1">
+    <row r="123" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A123" s="18">
         <v>122</v>
       </c>
@@ -7774,7 +7847,7 @@
       <c r="Y123" s="20"/>
       <c r="Z123" s="20"/>
     </row>
-    <row r="124" spans="1:26" ht="27" thickBot="1">
+    <row r="124" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A124" s="18">
         <v>123</v>
       </c>
@@ -7828,7 +7901,7 @@
       <c r="Y124" s="20"/>
       <c r="Z124" s="20"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" thickBot="1">
+    <row r="125" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A125" s="18">
         <v>124</v>
       </c>
@@ -7882,7 +7955,7 @@
       <c r="Y125" s="20"/>
       <c r="Z125" s="20"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" thickBot="1">
+    <row r="126" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A126" s="18">
         <v>125</v>
       </c>
@@ -7936,7 +8009,7 @@
       <c r="Y126" s="20"/>
       <c r="Z126" s="20"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" thickBot="1">
+    <row r="127" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A127" s="18">
         <v>126</v>
       </c>
@@ -7990,7 +8063,7 @@
       <c r="Y127" s="20"/>
       <c r="Z127" s="20"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" thickBot="1">
+    <row r="128" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A128" s="18">
         <v>127</v>
       </c>
@@ -8044,7 +8117,7 @@
       <c r="Y128" s="20"/>
       <c r="Z128" s="20"/>
     </row>
-    <row r="129" spans="1:26" ht="39.75" thickBot="1">
+    <row r="129" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A129" s="18">
         <v>128</v>
       </c>
@@ -8098,7 +8171,7 @@
       <c r="Y129" s="20"/>
       <c r="Z129" s="20"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" thickBot="1">
+    <row r="130" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A130" s="18">
         <v>129</v>
       </c>
@@ -8152,7 +8225,7 @@
       <c r="Y130" s="20"/>
       <c r="Z130" s="20"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" thickBot="1">
+    <row r="131" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A131" s="18">
         <v>130</v>
       </c>
@@ -8206,7 +8279,7 @@
       <c r="Y131" s="20"/>
       <c r="Z131" s="20"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" thickBot="1">
+    <row r="132" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A132" s="18">
         <v>131</v>
       </c>
@@ -8258,7 +8331,7 @@
       <c r="Y132" s="20"/>
       <c r="Z132" s="20"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" thickBot="1">
+    <row r="133" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A133" s="18">
         <v>132</v>
       </c>
@@ -8310,7 +8383,7 @@
       <c r="Y133" s="20"/>
       <c r="Z133" s="20"/>
     </row>
-    <row r="134" spans="1:26" ht="27" thickBot="1">
+    <row r="134" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A134" s="18">
         <v>133</v>
       </c>
@@ -8364,7 +8437,7 @@
       <c r="Y134" s="20"/>
       <c r="Z134" s="20"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" thickBot="1">
+    <row r="135" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A135" s="18">
         <v>134</v>
       </c>
@@ -8418,7 +8491,7 @@
       <c r="Y135" s="20"/>
       <c r="Z135" s="20"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" thickBot="1">
+    <row r="136" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A136" s="18">
         <v>135</v>
       </c>
@@ -8472,7 +8545,7 @@
       <c r="Y136" s="20"/>
       <c r="Z136" s="20"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" thickBot="1">
+    <row r="137" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A137" s="18">
         <v>136</v>
       </c>
@@ -8526,7 +8599,7 @@
       <c r="Y137" s="20"/>
       <c r="Z137" s="20"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" thickBot="1">
+    <row r="138" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A138" s="18">
         <v>137</v>
       </c>
@@ -8580,7 +8653,7 @@
       <c r="Y138" s="20"/>
       <c r="Z138" s="20"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" thickBot="1">
+    <row r="139" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A139" s="18">
         <v>138</v>
       </c>
@@ -8634,7 +8707,7 @@
       <c r="Y139" s="20"/>
       <c r="Z139" s="20"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" thickBot="1">
+    <row r="140" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A140" s="18">
         <v>139</v>
       </c>
@@ -8688,7 +8761,7 @@
       <c r="Y140" s="20"/>
       <c r="Z140" s="20"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" thickBot="1">
+    <row r="141" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A141" s="18">
         <v>140</v>
       </c>
@@ -8740,7 +8813,7 @@
       <c r="Y141" s="20"/>
       <c r="Z141" s="20"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" thickBot="1">
+    <row r="142" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A142" s="18">
         <v>141</v>
       </c>
@@ -8794,7 +8867,7 @@
       <c r="Y142" s="20"/>
       <c r="Z142" s="20"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" thickBot="1">
+    <row r="143" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A143" s="18">
         <v>142</v>
       </c>
@@ -8848,7 +8921,7 @@
       <c r="Y143" s="20"/>
       <c r="Z143" s="20"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" thickBot="1">
+    <row r="144" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A144" s="18">
         <v>143</v>
       </c>
@@ -8902,7 +8975,7 @@
       <c r="Y144" s="20"/>
       <c r="Z144" s="20"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" thickBot="1">
+    <row r="145" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A145" s="18">
         <v>144</v>
       </c>
@@ -8956,7 +9029,7 @@
       <c r="Y145" s="20"/>
       <c r="Z145" s="20"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" thickBot="1">
+    <row r="146" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A146" s="18">
         <v>145</v>
       </c>
@@ -9010,7 +9083,7 @@
       <c r="Y146" s="20"/>
       <c r="Z146" s="20"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" thickBot="1">
+    <row r="147" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A147" s="18">
         <v>146</v>
       </c>
@@ -9064,7 +9137,7 @@
       <c r="Y147" s="20"/>
       <c r="Z147" s="20"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" thickBot="1">
+    <row r="148" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A148" s="18">
         <v>147</v>
       </c>
@@ -9118,7 +9191,7 @@
       <c r="Y148" s="20"/>
       <c r="Z148" s="20"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" thickBot="1">
+    <row r="149" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A149" s="18">
         <v>148</v>
       </c>
@@ -9172,7 +9245,7 @@
       <c r="Y149" s="20"/>
       <c r="Z149" s="20"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1">
+    <row r="150" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A150" s="18">
         <v>149</v>
       </c>
@@ -9224,7 +9297,7 @@
       <c r="Y150" s="20"/>
       <c r="Z150" s="20"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1">
+    <row r="151" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A151" s="18">
         <v>150</v>
       </c>
@@ -9276,7 +9349,7 @@
       <c r="Y151" s="20"/>
       <c r="Z151" s="20"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1">
+    <row r="152" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A152" s="18">
         <v>151</v>
       </c>
@@ -9328,7 +9401,7 @@
       <c r="Y152" s="20"/>
       <c r="Z152" s="20"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1">
+    <row r="153" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A153" s="18">
         <v>152</v>
       </c>
@@ -9380,7 +9453,7 @@
       <c r="Y153" s="20"/>
       <c r="Z153" s="20"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1">
+    <row r="154" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A154" s="18">
         <v>153</v>
       </c>
@@ -9432,7 +9505,7 @@
       <c r="Y154" s="20"/>
       <c r="Z154" s="20"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1">
+    <row r="155" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A155" s="18">
         <v>154</v>
       </c>
@@ -9484,7 +9557,7 @@
       <c r="Y155" s="20"/>
       <c r="Z155" s="20"/>
     </row>
-    <row r="156" spans="1:26" ht="27" thickBot="1">
+    <row r="156" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A156" s="18">
         <v>155</v>
       </c>
@@ -9538,7 +9611,7 @@
       <c r="Y156" s="20"/>
       <c r="Z156" s="20"/>
     </row>
-    <row r="157" spans="1:26" ht="27" thickBot="1">
+    <row r="157" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A157" s="18">
         <v>156</v>
       </c>
@@ -9592,7 +9665,7 @@
       <c r="Y157" s="20"/>
       <c r="Z157" s="20"/>
     </row>
-    <row r="158" spans="1:26" ht="27" thickBot="1">
+    <row r="158" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A158" s="18">
         <v>157</v>
       </c>
@@ -9646,7 +9719,7 @@
       <c r="Y158" s="20"/>
       <c r="Z158" s="20"/>
     </row>
-    <row r="159" spans="1:26" ht="27" thickBot="1">
+    <row r="159" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A159" s="18">
         <v>158</v>
       </c>
@@ -9700,7 +9773,7 @@
       <c r="Y159" s="20"/>
       <c r="Z159" s="20"/>
     </row>
-    <row r="160" spans="1:26" ht="27" thickBot="1">
+    <row r="160" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A160" s="18">
         <v>159</v>
       </c>
@@ -9754,7 +9827,7 @@
       <c r="Y160" s="20"/>
       <c r="Z160" s="20"/>
     </row>
-    <row r="161" spans="1:26" ht="27" thickBot="1">
+    <row r="161" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A161" s="18">
         <v>160</v>
       </c>
@@ -9808,7 +9881,7 @@
       <c r="Y161" s="20"/>
       <c r="Z161" s="20"/>
     </row>
-    <row r="162" spans="1:26" ht="27" thickBot="1">
+    <row r="162" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A162" s="18">
         <v>161</v>
       </c>
@@ -9862,7 +9935,7 @@
       <c r="Y162" s="20"/>
       <c r="Z162" s="20"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" thickBot="1">
+    <row r="163" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A163" s="18">
         <v>162</v>
       </c>
@@ -9916,7 +9989,7 @@
       <c r="Y163" s="20"/>
       <c r="Z163" s="20"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" thickBot="1">
+    <row r="164" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A164" s="18">
         <v>163</v>
       </c>
@@ -9970,7 +10043,7 @@
       <c r="Y164" s="20"/>
       <c r="Z164" s="20"/>
     </row>
-    <row r="165" spans="1:26" ht="27" thickBot="1">
+    <row r="165" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A165" s="18">
         <v>164</v>
       </c>
@@ -10024,7 +10097,7 @@
       <c r="Y165" s="20"/>
       <c r="Z165" s="20"/>
     </row>
-    <row r="166" spans="1:26" ht="27" thickBot="1">
+    <row r="166" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A166" s="18">
         <v>165</v>
       </c>
@@ -10078,7 +10151,7 @@
       <c r="Y166" s="20"/>
       <c r="Z166" s="20"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1">
+    <row r="167" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A167" s="18">
         <v>166</v>
       </c>
@@ -10132,7 +10205,7 @@
       <c r="Y167" s="20"/>
       <c r="Z167" s="20"/>
     </row>
-    <row r="168" spans="1:26" ht="27" thickBot="1">
+    <row r="168" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A168" s="18">
         <v>167</v>
       </c>
@@ -10186,7 +10259,7 @@
       <c r="Y168" s="20"/>
       <c r="Z168" s="20"/>
     </row>
-    <row r="169" spans="1:26" ht="27" thickBot="1">
+    <row r="169" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A169" s="18">
         <v>168</v>
       </c>
@@ -10240,7 +10313,7 @@
       <c r="Y169" s="20"/>
       <c r="Z169" s="20"/>
     </row>
-    <row r="170" spans="1:26" ht="27" thickBot="1">
+    <row r="170" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A170" s="18">
         <v>169</v>
       </c>
@@ -10294,7 +10367,7 @@
       <c r="Y170" s="20"/>
       <c r="Z170" s="20"/>
     </row>
-    <row r="171" spans="1:26" ht="39.75" thickBot="1">
+    <row r="171" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A171" s="18">
         <v>170</v>
       </c>
@@ -10348,7 +10421,7 @@
       <c r="Y171" s="20"/>
       <c r="Z171" s="20"/>
     </row>
-    <row r="172" spans="1:26" ht="27" thickBot="1">
+    <row r="172" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A172" s="18">
         <v>171</v>
       </c>
@@ -10402,7 +10475,7 @@
       <c r="Y172" s="20"/>
       <c r="Z172" s="20"/>
     </row>
-    <row r="173" spans="1:26" ht="39.75" thickBot="1">
+    <row r="173" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A173" s="18">
         <v>172</v>
       </c>
@@ -10456,7 +10529,7 @@
       <c r="Y173" s="20"/>
       <c r="Z173" s="20"/>
     </row>
-    <row r="174" spans="1:26" ht="39.75" thickBot="1">
+    <row r="174" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A174" s="18">
         <v>173</v>
       </c>
@@ -10510,7 +10583,7 @@
       <c r="Y174" s="20"/>
       <c r="Z174" s="20"/>
     </row>
-    <row r="175" spans="1:26" ht="27" thickBot="1">
+    <row r="175" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A175" s="18">
         <v>174</v>
       </c>
@@ -10564,7 +10637,7 @@
       <c r="Y175" s="20"/>
       <c r="Z175" s="20"/>
     </row>
-    <row r="176" spans="1:26" ht="39.75" thickBot="1">
+    <row r="176" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A176" s="18">
         <v>175</v>
       </c>
@@ -10618,7 +10691,7 @@
       <c r="Y176" s="20"/>
       <c r="Z176" s="20"/>
     </row>
-    <row r="177" spans="1:26" ht="39.75" thickBot="1">
+    <row r="177" spans="1:26" ht="39.75" hidden="1" thickBot="1">
       <c r="A177" s="18">
         <v>176</v>
       </c>
@@ -10672,7 +10745,7 @@
       <c r="Y177" s="20"/>
       <c r="Z177" s="20"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" thickBot="1">
+    <row r="178" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A178" s="18">
         <v>177</v>
       </c>
@@ -10726,7 +10799,7 @@
       <c r="Y178" s="20"/>
       <c r="Z178" s="20"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" thickBot="1">
+    <row r="179" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A179" s="18">
         <v>178</v>
       </c>
@@ -10778,7 +10851,7 @@
       <c r="Y179" s="20"/>
       <c r="Z179" s="20"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" thickBot="1">
+    <row r="180" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A180" s="18">
         <v>179</v>
       </c>
@@ -10830,7 +10903,7 @@
       <c r="Y180" s="20"/>
       <c r="Z180" s="20"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" thickBot="1">
+    <row r="181" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A181" s="18">
         <v>180</v>
       </c>
@@ -10882,7 +10955,7 @@
       <c r="Y181" s="20"/>
       <c r="Z181" s="20"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" thickBot="1">
+    <row r="182" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A182" s="18">
         <v>181</v>
       </c>
@@ -10934,7 +11007,7 @@
       <c r="Y182" s="20"/>
       <c r="Z182" s="20"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" thickBot="1">
+    <row r="183" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A183" s="18">
         <v>182</v>
       </c>
@@ -10986,7 +11059,7 @@
       <c r="Y183" s="20"/>
       <c r="Z183" s="20"/>
     </row>
-    <row r="184" spans="1:26" ht="27" thickBot="1">
+    <row r="184" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A184" s="18">
         <v>183</v>
       </c>
@@ -11040,7 +11113,7 @@
       <c r="Y184" s="20"/>
       <c r="Z184" s="20"/>
     </row>
-    <row r="185" spans="1:26" ht="27" thickBot="1">
+    <row r="185" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A185" s="18">
         <v>184</v>
       </c>
@@ -11094,7 +11167,7 @@
       <c r="Y185" s="20"/>
       <c r="Z185" s="20"/>
     </row>
-    <row r="186" spans="1:26" ht="27" thickBot="1">
+    <row r="186" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A186" s="18">
         <v>185</v>
       </c>
@@ -11148,7 +11221,7 @@
       <c r="Y186" s="20"/>
       <c r="Z186" s="20"/>
     </row>
-    <row r="187" spans="1:26" ht="27" thickBot="1">
+    <row r="187" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A187" s="18">
         <v>186</v>
       </c>
@@ -11202,7 +11275,7 @@
       <c r="Y187" s="20"/>
       <c r="Z187" s="20"/>
     </row>
-    <row r="188" spans="1:26" ht="27" thickBot="1">
+    <row r="188" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A188" s="18">
         <v>187</v>
       </c>
@@ -11256,7 +11329,7 @@
       <c r="Y188" s="20"/>
       <c r="Z188" s="20"/>
     </row>
-    <row r="189" spans="1:26" ht="27" thickBot="1">
+    <row r="189" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A189" s="18">
         <v>188</v>
       </c>
@@ -11310,7 +11383,7 @@
       <c r="Y189" s="20"/>
       <c r="Z189" s="20"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" thickBot="1">
+    <row r="190" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A190" s="18">
         <v>189</v>
       </c>
@@ -11346,7 +11419,7 @@
         <v>45</v>
       </c>
       <c r="M190" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N190" s="20"/>
       <c r="O190" s="20"/>
@@ -11362,7 +11435,7 @@
       <c r="Y190" s="20"/>
       <c r="Z190" s="20"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" thickBot="1">
+    <row r="191" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A191" s="18">
         <v>190</v>
       </c>
@@ -11398,7 +11471,7 @@
         <v>45</v>
       </c>
       <c r="M191" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N191" s="20"/>
       <c r="O191" s="20"/>
@@ -11414,7 +11487,7 @@
       <c r="Y191" s="20"/>
       <c r="Z191" s="20"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" thickBot="1">
+    <row r="192" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A192" s="18">
         <v>191</v>
       </c>
@@ -11433,11 +11506,11 @@
       <c r="F192" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="G192" s="19" t="s">
+      <c r="G192" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H192" s="19" t="s">
         <v>173</v>
-      </c>
-      <c r="H192" s="19" t="s">
-        <v>174</v>
       </c>
       <c r="I192" s="20"/>
       <c r="J192" s="40">
@@ -11450,7 +11523,7 @@
         <v>45</v>
       </c>
       <c r="M192" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N192" s="20"/>
       <c r="O192" s="20"/>
@@ -11466,7 +11539,7 @@
       <c r="Y192" s="20"/>
       <c r="Z192" s="20"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" thickBot="1">
+    <row r="193" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A193" s="18">
         <v>192</v>
       </c>
@@ -11489,7 +11562,7 @@
         <v>16</v>
       </c>
       <c r="H193" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I193" s="20"/>
       <c r="J193" s="40">
@@ -11502,7 +11575,7 @@
         <v>45</v>
       </c>
       <c r="M193" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N193" s="20"/>
       <c r="O193" s="20"/>
@@ -11518,12 +11591,12 @@
       <c r="Y193" s="20"/>
       <c r="Z193" s="20"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" thickBot="1">
+    <row r="194" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A194" s="18">
         <v>193</v>
       </c>
       <c r="B194" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C194" s="19" t="s">
         <v>34</v>
@@ -11554,7 +11627,7 @@
         <v>45</v>
       </c>
       <c r="M194" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N194" s="20"/>
       <c r="O194" s="20"/>
@@ -11570,12 +11643,12 @@
       <c r="Y194" s="20"/>
       <c r="Z194" s="20"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" thickBot="1">
+    <row r="195" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A195" s="18">
         <v>194</v>
       </c>
       <c r="B195" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C195" s="19" t="s">
         <v>34</v>
@@ -11606,7 +11679,7 @@
         <v>45</v>
       </c>
       <c r="M195" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N195" s="20"/>
       <c r="O195" s="20"/>
@@ -11622,7 +11695,7 @@
       <c r="Y195" s="20"/>
       <c r="Z195" s="20"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" thickBot="1">
+    <row r="196" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A196" s="18">
         <v>195</v>
       </c>
@@ -11660,7 +11733,7 @@
         <v>45</v>
       </c>
       <c r="M196" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N196" s="20"/>
       <c r="O196" s="20"/>
@@ -11676,7 +11749,7 @@
       <c r="Y196" s="20"/>
       <c r="Z196" s="20"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" thickBot="1">
+    <row r="197" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A197" s="18">
         <v>196</v>
       </c>
@@ -11699,7 +11772,7 @@
         <v>33</v>
       </c>
       <c r="H197" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I197" s="22" t="s">
         <v>66</v>
@@ -11714,7 +11787,7 @@
         <v>45</v>
       </c>
       <c r="M197" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N197" s="20"/>
       <c r="O197" s="20"/>
@@ -11730,7 +11803,7 @@
       <c r="Y197" s="20"/>
       <c r="Z197" s="20"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" thickBot="1">
+    <row r="198" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A198" s="18">
         <v>197</v>
       </c>
@@ -11753,7 +11826,7 @@
         <v>33</v>
       </c>
       <c r="H198" s="22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I198" s="22" t="s">
         <v>66</v>
@@ -11768,7 +11841,7 @@
         <v>45</v>
       </c>
       <c r="M198" s="36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N198" s="20"/>
       <c r="O198" s="20"/>
@@ -11784,7 +11857,7 @@
       <c r="Y198" s="20"/>
       <c r="Z198" s="20"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" thickBot="1">
+    <row r="199" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A199" s="18">
         <v>198</v>
       </c>
@@ -11836,7 +11909,7 @@
       <c r="Y199" s="20"/>
       <c r="Z199" s="20"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" thickBot="1">
+    <row r="200" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A200" s="18">
         <v>199</v>
       </c>
@@ -11888,7 +11961,7 @@
       <c r="Y200" s="20"/>
       <c r="Z200" s="20"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" thickBot="1">
+    <row r="201" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A201" s="18">
         <v>200</v>
       </c>
@@ -11940,7 +12013,7 @@
       <c r="Y201" s="20"/>
       <c r="Z201" s="20"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" thickBot="1">
+    <row r="202" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A202" s="18">
         <v>201</v>
       </c>
@@ -11992,7 +12065,7 @@
       <c r="Y202" s="20"/>
       <c r="Z202" s="20"/>
     </row>
-    <row r="203" spans="1:26" ht="27" thickBot="1">
+    <row r="203" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A203" s="18">
         <v>202</v>
       </c>
@@ -12018,7 +12091,7 @@
         <v>65</v>
       </c>
       <c r="I203" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J203" s="40">
         <v>17272341</v>
@@ -12030,7 +12103,7 @@
         <v>45</v>
       </c>
       <c r="M203" s="36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N203" s="20"/>
       <c r="O203" s="20"/>
@@ -12046,7 +12119,7 @@
       <c r="Y203" s="20"/>
       <c r="Z203" s="20"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" thickBot="1">
+    <row r="204" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A204" s="18">
         <v>203</v>
       </c>
@@ -12069,7 +12142,7 @@
         <v>33</v>
       </c>
       <c r="H204" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I204" s="20"/>
       <c r="J204" s="40">
@@ -12082,7 +12155,7 @@
         <v>45</v>
       </c>
       <c r="M204" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N204" s="20"/>
       <c r="O204" s="20"/>
@@ -12098,7 +12171,7 @@
       <c r="Y204" s="20"/>
       <c r="Z204" s="20"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" thickBot="1">
+    <row r="205" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A205" s="18">
         <v>204</v>
       </c>
@@ -12134,7 +12207,7 @@
         <v>45</v>
       </c>
       <c r="M205" s="36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N205" s="20"/>
       <c r="O205" s="20"/>
@@ -12150,7 +12223,7 @@
       <c r="Y205" s="20"/>
       <c r="Z205" s="20"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" thickBot="1">
+    <row r="206" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A206" s="18">
         <v>205</v>
       </c>
@@ -12186,7 +12259,7 @@
         <v>45</v>
       </c>
       <c r="M206" s="36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N206" s="20"/>
       <c r="O206" s="20"/>
@@ -12202,7 +12275,7 @@
       <c r="Y206" s="20"/>
       <c r="Z206" s="20"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" thickBot="1">
+    <row r="207" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A207" s="18">
         <v>206</v>
       </c>
@@ -12238,7 +12311,7 @@
         <v>45</v>
       </c>
       <c r="M207" s="36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N207" s="20"/>
       <c r="O207" s="20"/>
@@ -12254,7 +12327,7 @@
       <c r="Y207" s="20"/>
       <c r="Z207" s="20"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" thickBot="1">
+    <row r="208" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A208" s="18">
         <v>207</v>
       </c>
@@ -12290,7 +12363,7 @@
         <v>45</v>
       </c>
       <c r="M208" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N208" s="20"/>
       <c r="O208" s="20"/>
@@ -12306,7 +12379,7 @@
       <c r="Y208" s="20"/>
       <c r="Z208" s="20"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" thickBot="1">
+    <row r="209" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A209" s="18">
         <v>208</v>
       </c>
@@ -12342,7 +12415,7 @@
         <v>45</v>
       </c>
       <c r="M209" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N209" s="20"/>
       <c r="O209" s="20"/>
@@ -12358,7 +12431,7 @@
       <c r="Y209" s="20"/>
       <c r="Z209" s="20"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" thickBot="1">
+    <row r="210" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A210" s="18">
         <v>209</v>
       </c>
@@ -12394,7 +12467,7 @@
         <v>45</v>
       </c>
       <c r="M210" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N210" s="20"/>
       <c r="O210" s="20"/>
@@ -12410,7 +12483,7 @@
       <c r="Y210" s="20"/>
       <c r="Z210" s="20"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" thickBot="1">
+    <row r="211" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A211" s="18">
         <v>210</v>
       </c>
@@ -12446,7 +12519,7 @@
         <v>45</v>
       </c>
       <c r="M211" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N211" s="20"/>
       <c r="O211" s="20"/>
@@ -12462,7 +12535,7 @@
       <c r="Y211" s="20"/>
       <c r="Z211" s="20"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" thickBot="1">
+    <row r="212" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A212" s="18">
         <v>211</v>
       </c>
@@ -12498,7 +12571,7 @@
         <v>45</v>
       </c>
       <c r="M212" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N212" s="20"/>
       <c r="O212" s="20"/>
@@ -12514,7 +12587,7 @@
       <c r="Y212" s="20"/>
       <c r="Z212" s="20"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" thickBot="1">
+    <row r="213" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A213" s="18">
         <v>212</v>
       </c>
@@ -12550,7 +12623,7 @@
         <v>45</v>
       </c>
       <c r="M213" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N213" s="20"/>
       <c r="O213" s="20"/>
@@ -12566,7 +12639,7 @@
       <c r="Y213" s="20"/>
       <c r="Z213" s="20"/>
     </row>
-    <row r="214" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
+    <row r="214" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A214" s="18">
         <v>213</v>
       </c>
@@ -12602,10 +12675,10 @@
         <v>45</v>
       </c>
       <c r="M214" s="44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N214" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O214" s="25"/>
       <c r="P214" s="25"/>
@@ -12620,7 +12693,7 @@
       <c r="Y214" s="25"/>
       <c r="Z214" s="25"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" thickBot="1">
+    <row r="215" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A215" s="18">
         <v>214</v>
       </c>
@@ -12656,7 +12729,7 @@
         <v>45</v>
       </c>
       <c r="M215" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N215" s="20"/>
       <c r="O215" s="20"/>
@@ -12672,7 +12745,7 @@
       <c r="Y215" s="20"/>
       <c r="Z215" s="20"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" thickBot="1">
+    <row r="216" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A216" s="18">
         <v>215</v>
       </c>
@@ -12708,7 +12781,7 @@
         <v>45</v>
       </c>
       <c r="M216" s="36" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N216" s="20"/>
       <c r="O216" s="20"/>
@@ -12724,7 +12797,7 @@
       <c r="Y216" s="20"/>
       <c r="Z216" s="20"/>
     </row>
-    <row r="217" spans="1:26" ht="27" thickBot="1">
+    <row r="217" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A217" s="18">
         <v>216</v>
       </c>
@@ -12747,7 +12820,7 @@
         <v>16</v>
       </c>
       <c r="H217" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I217" s="22" t="s">
         <v>85</v>
@@ -12762,7 +12835,7 @@
         <v>45</v>
       </c>
       <c r="M217" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N217" s="20"/>
       <c r="O217" s="20"/>
@@ -12778,7 +12851,7 @@
       <c r="Y217" s="20"/>
       <c r="Z217" s="20"/>
     </row>
-    <row r="218" spans="1:26" ht="27" thickBot="1">
+    <row r="218" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A218" s="18">
         <v>217</v>
       </c>
@@ -12801,7 +12874,7 @@
         <v>16</v>
       </c>
       <c r="H218" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I218" s="22" t="s">
         <v>85</v>
@@ -12816,7 +12889,7 @@
         <v>45</v>
       </c>
       <c r="M218" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N218" s="20"/>
       <c r="O218" s="20"/>
@@ -12832,7 +12905,7 @@
       <c r="Y218" s="20"/>
       <c r="Z218" s="20"/>
     </row>
-    <row r="219" spans="1:26" ht="27" thickBot="1">
+    <row r="219" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A219" s="18">
         <v>218</v>
       </c>
@@ -12855,7 +12928,7 @@
         <v>16</v>
       </c>
       <c r="H219" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I219" s="22" t="s">
         <v>85</v>
@@ -12870,7 +12943,7 @@
         <v>45</v>
       </c>
       <c r="M219" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N219" s="20"/>
       <c r="O219" s="20"/>
@@ -12886,7 +12959,7 @@
       <c r="Y219" s="20"/>
       <c r="Z219" s="20"/>
     </row>
-    <row r="220" spans="1:26" ht="27" thickBot="1">
+    <row r="220" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A220" s="18">
         <v>219</v>
       </c>
@@ -12909,7 +12982,7 @@
         <v>16</v>
       </c>
       <c r="H220" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I220" s="22" t="s">
         <v>85</v>
@@ -12924,7 +12997,7 @@
         <v>45</v>
       </c>
       <c r="M220" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N220" s="20"/>
       <c r="O220" s="20"/>
@@ -12940,7 +13013,7 @@
       <c r="Y220" s="20"/>
       <c r="Z220" s="20"/>
     </row>
-    <row r="221" spans="1:26" ht="27" thickBot="1">
+    <row r="221" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A221" s="18">
         <v>220</v>
       </c>
@@ -12963,7 +13036,7 @@
         <v>16</v>
       </c>
       <c r="H221" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I221" s="22" t="s">
         <v>85</v>
@@ -12978,7 +13051,7 @@
         <v>45</v>
       </c>
       <c r="M221" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N221" s="20"/>
       <c r="O221" s="20"/>
@@ -12994,7 +13067,7 @@
       <c r="Y221" s="20"/>
       <c r="Z221" s="20"/>
     </row>
-    <row r="222" spans="1:26" ht="27" thickBot="1">
+    <row r="222" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A222" s="18">
         <v>221</v>
       </c>
@@ -13017,7 +13090,7 @@
         <v>16</v>
       </c>
       <c r="H222" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I222" s="22" t="s">
         <v>85</v>
@@ -13032,7 +13105,7 @@
         <v>45</v>
       </c>
       <c r="M222" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N222" s="20"/>
       <c r="O222" s="20"/>
@@ -13048,7 +13121,7 @@
       <c r="Y222" s="20"/>
       <c r="Z222" s="20"/>
     </row>
-    <row r="223" spans="1:26" ht="27" thickBot="1">
+    <row r="223" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A223" s="18">
         <v>222</v>
       </c>
@@ -13071,7 +13144,7 @@
         <v>16</v>
       </c>
       <c r="H223" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I223" s="22" t="s">
         <v>85</v>
@@ -13086,7 +13159,7 @@
         <v>45</v>
       </c>
       <c r="M223" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N223" s="20"/>
       <c r="O223" s="20"/>
@@ -13102,7 +13175,7 @@
       <c r="Y223" s="20"/>
       <c r="Z223" s="20"/>
     </row>
-    <row r="224" spans="1:26" ht="27" thickBot="1">
+    <row r="224" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A224" s="18">
         <v>223</v>
       </c>
@@ -13125,7 +13198,7 @@
         <v>33</v>
       </c>
       <c r="H224" s="22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I224" s="22" t="s">
         <v>85</v>
@@ -13140,7 +13213,7 @@
         <v>45</v>
       </c>
       <c r="M224" s="36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N224" s="20"/>
       <c r="O224" s="20"/>
@@ -13156,7 +13229,7 @@
       <c r="Y224" s="20"/>
       <c r="Z224" s="20"/>
     </row>
-    <row r="225" spans="1:26" ht="15.75" thickBot="1">
+    <row r="225" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A225" s="18">
         <v>224</v>
       </c>
@@ -13194,7 +13267,7 @@
         <v>45</v>
       </c>
       <c r="M225" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N225" s="20"/>
       <c r="O225" s="20"/>
@@ -13210,7 +13283,7 @@
       <c r="Y225" s="20"/>
       <c r="Z225" s="20"/>
     </row>
-    <row r="226" spans="1:26" ht="15.75" thickBot="1">
+    <row r="226" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A226" s="18">
         <v>225</v>
       </c>
@@ -13248,7 +13321,7 @@
         <v>45</v>
       </c>
       <c r="M226" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N226" s="20"/>
       <c r="O226" s="20"/>
@@ -13264,7 +13337,7 @@
       <c r="Y226" s="20"/>
       <c r="Z226" s="20"/>
     </row>
-    <row r="227" spans="1:26" ht="15.75" thickBot="1">
+    <row r="227" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A227" s="18">
         <v>226</v>
       </c>
@@ -13302,7 +13375,7 @@
         <v>45</v>
       </c>
       <c r="M227" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N227" s="20"/>
       <c r="O227" s="20"/>
@@ -13318,7 +13391,7 @@
       <c r="Y227" s="20"/>
       <c r="Z227" s="20"/>
     </row>
-    <row r="228" spans="1:26" ht="15.75" thickBot="1">
+    <row r="228" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A228" s="18">
         <v>227</v>
       </c>
@@ -13341,7 +13414,7 @@
         <v>16</v>
       </c>
       <c r="H228" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I228" s="22" t="s">
         <v>85</v>
@@ -13356,7 +13429,7 @@
         <v>45</v>
       </c>
       <c r="M228" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N228" s="20"/>
       <c r="O228" s="20"/>
@@ -13372,7 +13445,7 @@
       <c r="Y228" s="20"/>
       <c r="Z228" s="20"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" thickBot="1">
+    <row r="229" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A229" s="18">
         <v>228</v>
       </c>
@@ -13395,7 +13468,7 @@
         <v>16</v>
       </c>
       <c r="H229" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I229" s="22" t="s">
         <v>85</v>
@@ -13410,7 +13483,7 @@
         <v>45</v>
       </c>
       <c r="M229" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N229" s="20"/>
       <c r="O229" s="20"/>
@@ -13426,7 +13499,7 @@
       <c r="Y229" s="20"/>
       <c r="Z229" s="20"/>
     </row>
-    <row r="230" spans="1:26" ht="15.75" thickBot="1">
+    <row r="230" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A230" s="18">
         <v>229</v>
       </c>
@@ -13464,7 +13537,7 @@
         <v>45</v>
       </c>
       <c r="M230" s="36" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N230" s="20"/>
       <c r="O230" s="20"/>
@@ -13480,7 +13553,7 @@
       <c r="Y230" s="20"/>
       <c r="Z230" s="20"/>
     </row>
-    <row r="231" spans="1:26" ht="15.75" thickBot="1">
+    <row r="231" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A231" s="18">
         <v>230</v>
       </c>
@@ -13516,7 +13589,7 @@
         <v>45</v>
       </c>
       <c r="M231" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N231" s="20"/>
       <c r="O231" s="20"/>
@@ -13532,7 +13605,7 @@
       <c r="Y231" s="20"/>
       <c r="Z231" s="20"/>
     </row>
-    <row r="232" spans="1:26" ht="15.75" thickBot="1">
+    <row r="232" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A232" s="18">
         <v>231</v>
       </c>
@@ -13568,7 +13641,7 @@
         <v>45</v>
       </c>
       <c r="M232" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N232" s="20"/>
       <c r="O232" s="20"/>
@@ -13584,7 +13657,7 @@
       <c r="Y232" s="20"/>
       <c r="Z232" s="20"/>
     </row>
-    <row r="233" spans="1:26" ht="15.75" thickBot="1">
+    <row r="233" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A233" s="18">
         <v>232</v>
       </c>
@@ -13620,7 +13693,7 @@
         <v>45</v>
       </c>
       <c r="M233" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N233" s="20"/>
       <c r="O233" s="20"/>
@@ -13636,7 +13709,7 @@
       <c r="Y233" s="20"/>
       <c r="Z233" s="20"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" thickBot="1">
+    <row r="234" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A234" s="18">
         <v>233</v>
       </c>
@@ -13672,7 +13745,7 @@
         <v>45</v>
       </c>
       <c r="M234" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N234" s="20"/>
       <c r="O234" s="20"/>
@@ -13688,7 +13761,7 @@
       <c r="Y234" s="20"/>
       <c r="Z234" s="20"/>
     </row>
-    <row r="235" spans="1:26" ht="15.75" thickBot="1">
+    <row r="235" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A235" s="18">
         <v>234</v>
       </c>
@@ -13724,7 +13797,7 @@
         <v>45</v>
       </c>
       <c r="M235" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N235" s="20"/>
       <c r="O235" s="20"/>
@@ -13740,7 +13813,7 @@
       <c r="Y235" s="20"/>
       <c r="Z235" s="20"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" thickBot="1">
+    <row r="236" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A236" s="18">
         <v>235</v>
       </c>
@@ -13778,7 +13851,7 @@
         <v>45</v>
       </c>
       <c r="M236" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N236" s="20"/>
       <c r="O236" s="20"/>
@@ -13794,7 +13867,7 @@
       <c r="Y236" s="20"/>
       <c r="Z236" s="20"/>
     </row>
-    <row r="237" spans="1:26" ht="27" thickBot="1">
+    <row r="237" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A237" s="18">
         <v>236</v>
       </c>
@@ -13820,7 +13893,7 @@
         <v>65</v>
       </c>
       <c r="I237" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J237" s="40">
         <v>18398509</v>
@@ -13832,7 +13905,7 @@
         <v>45</v>
       </c>
       <c r="M237" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N237" s="20"/>
       <c r="O237" s="20"/>
@@ -13848,7 +13921,7 @@
       <c r="Y237" s="20"/>
       <c r="Z237" s="20"/>
     </row>
-    <row r="238" spans="1:26" ht="27" thickBot="1">
+    <row r="238" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A238" s="18">
         <v>237</v>
       </c>
@@ -13874,7 +13947,7 @@
         <v>65</v>
       </c>
       <c r="I238" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J238" s="40">
         <v>18398509</v>
@@ -13886,7 +13959,7 @@
         <v>45</v>
       </c>
       <c r="M238" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N238" s="20"/>
       <c r="O238" s="20"/>
@@ -13902,7 +13975,7 @@
       <c r="Y238" s="20"/>
       <c r="Z238" s="20"/>
     </row>
-    <row r="239" spans="1:26" ht="15.75" thickBot="1">
+    <row r="239" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A239" s="18">
         <v>238</v>
       </c>
@@ -13938,7 +14011,7 @@
         <v>45</v>
       </c>
       <c r="M239" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N239" s="20"/>
       <c r="O239" s="20"/>
@@ -13954,7 +14027,7 @@
       <c r="Y239" s="20"/>
       <c r="Z239" s="20"/>
     </row>
-    <row r="240" spans="1:26" ht="27" thickBot="1">
+    <row r="240" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A240" s="18">
         <v>239</v>
       </c>
@@ -13977,7 +14050,7 @@
         <v>16</v>
       </c>
       <c r="H240" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I240" s="22" t="s">
         <v>85</v>
@@ -13992,7 +14065,7 @@
         <v>45</v>
       </c>
       <c r="M240" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N240" s="20"/>
       <c r="O240" s="20"/>
@@ -14008,7 +14081,7 @@
       <c r="Y240" s="20"/>
       <c r="Z240" s="20"/>
     </row>
-    <row r="241" spans="1:26" ht="27" thickBot="1">
+    <row r="241" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A241" s="18">
         <v>240</v>
       </c>
@@ -14031,7 +14104,7 @@
         <v>16</v>
       </c>
       <c r="H241" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I241" s="22" t="s">
         <v>85</v>
@@ -14046,7 +14119,7 @@
         <v>45</v>
       </c>
       <c r="M241" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N241" s="20"/>
       <c r="O241" s="20"/>
@@ -14062,7 +14135,7 @@
       <c r="Y241" s="20"/>
       <c r="Z241" s="20"/>
     </row>
-    <row r="242" spans="1:26" ht="27" thickBot="1">
+    <row r="242" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A242" s="18">
         <v>241</v>
       </c>
@@ -14085,7 +14158,7 @@
         <v>16</v>
       </c>
       <c r="H242" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I242" s="22"/>
       <c r="J242" s="40">
@@ -14098,7 +14171,7 @@
         <v>45</v>
       </c>
       <c r="M242" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N242" s="20"/>
       <c r="O242" s="20"/>
@@ -14114,7 +14187,7 @@
       <c r="Y242" s="20"/>
       <c r="Z242" s="20"/>
     </row>
-    <row r="243" spans="1:26" ht="27" thickBot="1">
+    <row r="243" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A243" s="18">
         <v>242</v>
       </c>
@@ -14137,7 +14210,7 @@
         <v>33</v>
       </c>
       <c r="H243" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I243" s="22"/>
       <c r="J243" s="40">
@@ -14150,7 +14223,7 @@
         <v>45</v>
       </c>
       <c r="M243" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N243" s="20"/>
       <c r="O243" s="20"/>
@@ -14166,7 +14239,7 @@
       <c r="Y243" s="20"/>
       <c r="Z243" s="20"/>
     </row>
-    <row r="244" spans="1:26" ht="27" thickBot="1">
+    <row r="244" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A244" s="18">
         <v>243</v>
       </c>
@@ -14189,7 +14262,7 @@
         <v>16</v>
       </c>
       <c r="H244" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I244" s="22"/>
       <c r="J244" s="40">
@@ -14202,7 +14275,7 @@
         <v>45</v>
       </c>
       <c r="M244" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N244" s="20"/>
       <c r="O244" s="20"/>
@@ -14218,7 +14291,7 @@
       <c r="Y244" s="20"/>
       <c r="Z244" s="20"/>
     </row>
-    <row r="245" spans="1:26" ht="15.75" thickBot="1">
+    <row r="245" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A245" s="18">
         <v>244</v>
       </c>
@@ -14241,7 +14314,7 @@
         <v>16</v>
       </c>
       <c r="H245" s="22" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I245" s="22" t="s">
         <v>85</v>
@@ -14256,7 +14329,7 @@
         <v>45</v>
       </c>
       <c r="M245" s="36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="N245" s="20"/>
       <c r="O245" s="20"/>
@@ -14272,7 +14345,7 @@
       <c r="Y245" s="20"/>
       <c r="Z245" s="20"/>
     </row>
-    <row r="246" spans="1:26" ht="15.75" thickBot="1">
+    <row r="246" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A246" s="18">
         <v>245</v>
       </c>
@@ -14310,7 +14383,7 @@
         <v>45</v>
       </c>
       <c r="M246" s="36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N246" s="20"/>
       <c r="O246" s="20"/>
@@ -14349,7 +14422,7 @@
         <v>35</v>
       </c>
       <c r="H247" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I247" s="22" t="s">
         <v>66</v>
@@ -14364,7 +14437,7 @@
         <v>45</v>
       </c>
       <c r="M247" s="36" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="N247" s="20"/>
       <c r="O247" s="20"/>
@@ -14380,7 +14453,7 @@
       <c r="Y247" s="20"/>
       <c r="Z247" s="20"/>
     </row>
-    <row r="248" spans="1:26" ht="15.75" thickBot="1">
+    <row r="248" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A248" s="18">
         <v>247</v>
       </c>
@@ -14418,7 +14491,7 @@
         <v>45</v>
       </c>
       <c r="M248" s="36" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N248" s="20"/>
       <c r="O248" s="20"/>
@@ -14434,7 +14507,7 @@
       <c r="Y248" s="20"/>
       <c r="Z248" s="20"/>
     </row>
-    <row r="249" spans="1:26" ht="15.75" thickBot="1">
+    <row r="249" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A249" s="18">
         <v>248</v>
       </c>
@@ -14472,7 +14545,7 @@
         <v>45</v>
       </c>
       <c r="M249" s="36" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N249" s="20"/>
       <c r="O249" s="20"/>
@@ -14488,7 +14561,7 @@
       <c r="Y249" s="20"/>
       <c r="Z249" s="20"/>
     </row>
-    <row r="250" spans="1:26" ht="27" thickBot="1">
+    <row r="250" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A250" s="18">
         <v>249</v>
       </c>
@@ -14511,7 +14584,7 @@
         <v>16</v>
       </c>
       <c r="H250" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I250" s="22" t="s">
         <v>106</v>
@@ -14526,7 +14599,7 @@
         <v>45</v>
       </c>
       <c r="M250" s="36" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N250" s="20"/>
       <c r="O250" s="20"/>
@@ -14542,7 +14615,7 @@
       <c r="Y250" s="20"/>
       <c r="Z250" s="20"/>
     </row>
-    <row r="251" spans="1:26" ht="27" thickBot="1">
+    <row r="251" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A251" s="18">
         <v>250</v>
       </c>
@@ -14565,7 +14638,7 @@
         <v>33</v>
       </c>
       <c r="H251" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I251" s="22" t="s">
         <v>106</v>
@@ -14580,7 +14653,7 @@
         <v>45</v>
       </c>
       <c r="M251" s="36" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N251" s="20"/>
       <c r="O251" s="20"/>
@@ -14596,7 +14669,7 @@
       <c r="Y251" s="20"/>
       <c r="Z251" s="20"/>
     </row>
-    <row r="252" spans="1:26" ht="15.75" thickBot="1">
+    <row r="252" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A252" s="18">
         <v>251</v>
       </c>
@@ -14619,10 +14692,10 @@
         <v>33</v>
       </c>
       <c r="H252" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I252" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J252" s="40">
         <v>19628475</v>
@@ -14650,7 +14723,7 @@
       <c r="Y252" s="20"/>
       <c r="Z252" s="20"/>
     </row>
-    <row r="253" spans="1:26" ht="15.75" thickBot="1">
+    <row r="253" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A253" s="18">
         <v>252</v>
       </c>
@@ -14669,14 +14742,14 @@
       <c r="F253" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G253" s="22" t="s">
-        <v>202</v>
+      <c r="G253" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="H253" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I253" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J253" s="40">
         <v>19628475</v>
@@ -14704,7 +14777,7 @@
       <c r="Y253" s="20"/>
       <c r="Z253" s="20"/>
     </row>
-    <row r="254" spans="1:26" ht="15.75" thickBot="1">
+    <row r="254" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A254" s="18">
         <v>253</v>
       </c>
@@ -14727,10 +14800,10 @@
         <v>33</v>
       </c>
       <c r="H254" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I254" s="22" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J254" s="40">
         <v>19628475</v>
@@ -14758,7 +14831,7 @@
       <c r="Y254" s="20"/>
       <c r="Z254" s="20"/>
     </row>
-    <row r="255" spans="1:26" ht="15.75" thickBot="1">
+    <row r="255" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A255" s="18">
         <v>254</v>
       </c>
@@ -14781,7 +14854,7 @@
         <v>16</v>
       </c>
       <c r="H255" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I255" s="22" t="s">
         <v>85</v>
@@ -14796,7 +14869,7 @@
         <v>45</v>
       </c>
       <c r="M255" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N255" s="20"/>
       <c r="O255" s="20"/>
@@ -14812,7 +14885,7 @@
       <c r="Y255" s="20"/>
       <c r="Z255" s="20"/>
     </row>
-    <row r="256" spans="1:26" ht="15.75" thickBot="1">
+    <row r="256" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A256" s="18">
         <v>255</v>
       </c>
@@ -14850,7 +14923,7 @@
         <v>45</v>
       </c>
       <c r="M256" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N256" s="20"/>
       <c r="O256" s="20"/>
@@ -14866,7 +14939,7 @@
       <c r="Y256" s="20"/>
       <c r="Z256" s="20"/>
     </row>
-    <row r="257" spans="1:26" ht="15.75" thickBot="1">
+    <row r="257" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A257" s="18">
         <v>256</v>
       </c>
@@ -14889,7 +14962,7 @@
         <v>16</v>
       </c>
       <c r="H257" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I257" s="20"/>
       <c r="J257" s="40">
@@ -14902,7 +14975,7 @@
         <v>45</v>
       </c>
       <c r="M257" s="36" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N257" s="20"/>
       <c r="O257" s="20"/>
@@ -14918,7 +14991,7 @@
       <c r="Y257" s="20"/>
       <c r="Z257" s="20"/>
     </row>
-    <row r="258" spans="1:26" ht="15.75" thickBot="1">
+    <row r="258" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A258" s="18">
         <v>257</v>
       </c>
@@ -14970,7 +15043,7 @@
       <c r="Y258" s="20"/>
       <c r="Z258" s="20"/>
     </row>
-    <row r="259" spans="1:26" ht="15.75" thickBot="1">
+    <row r="259" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A259" s="18">
         <v>258</v>
       </c>
@@ -15006,7 +15079,7 @@
         <v>45</v>
       </c>
       <c r="M259" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N259" s="20"/>
       <c r="O259" s="20"/>
@@ -15022,7 +15095,7 @@
       <c r="Y259" s="20"/>
       <c r="Z259" s="20"/>
     </row>
-    <row r="260" spans="1:26" ht="15.75" thickBot="1">
+    <row r="260" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A260" s="18">
         <v>259</v>
       </c>
@@ -15058,7 +15131,7 @@
         <v>45</v>
       </c>
       <c r="M260" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N260" s="20"/>
       <c r="O260" s="20"/>
@@ -15074,12 +15147,12 @@
       <c r="Y260" s="20"/>
       <c r="Z260" s="20"/>
     </row>
-    <row r="261" spans="1:26" ht="15.75" thickBot="1">
+    <row r="261" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A261" s="18">
         <v>260</v>
       </c>
       <c r="B261" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C261" s="22" t="s">
         <v>34</v>
@@ -15110,7 +15183,7 @@
         <v>45</v>
       </c>
       <c r="M261" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N261" s="20"/>
       <c r="O261" s="20"/>
@@ -15126,7 +15199,7 @@
       <c r="Y261" s="20"/>
       <c r="Z261" s="20"/>
     </row>
-    <row r="262" spans="1:26" ht="15.75" thickBot="1">
+    <row r="262" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A262" s="18">
         <v>261</v>
       </c>
@@ -15162,7 +15235,7 @@
         <v>45</v>
       </c>
       <c r="M262" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N262" s="20"/>
       <c r="O262" s="20"/>
@@ -15178,7 +15251,7 @@
       <c r="Y262" s="20"/>
       <c r="Z262" s="20"/>
     </row>
-    <row r="263" spans="1:26" ht="15.75" thickBot="1">
+    <row r="263" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A263" s="18">
         <v>262</v>
       </c>
@@ -15214,7 +15287,7 @@
         <v>45</v>
       </c>
       <c r="M263" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N263" s="20"/>
       <c r="O263" s="20"/>
@@ -15230,7 +15303,7 @@
       <c r="Y263" s="20"/>
       <c r="Z263" s="20"/>
     </row>
-    <row r="264" spans="1:26" ht="15.75" thickBot="1">
+    <row r="264" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A264" s="18">
         <v>263</v>
       </c>
@@ -15266,7 +15339,7 @@
         <v>45</v>
       </c>
       <c r="M264" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N264" s="20"/>
       <c r="O264" s="20"/>
@@ -15282,12 +15355,12 @@
       <c r="Y264" s="20"/>
       <c r="Z264" s="20"/>
     </row>
-    <row r="265" spans="1:26" ht="15.75" thickBot="1">
+    <row r="265" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A265" s="18">
         <v>264</v>
       </c>
       <c r="B265" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C265" s="22" t="s">
         <v>34</v>
@@ -15318,7 +15391,7 @@
         <v>45</v>
       </c>
       <c r="M265" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N265" s="20"/>
       <c r="O265" s="20"/>
@@ -15334,7 +15407,7 @@
       <c r="Y265" s="20"/>
       <c r="Z265" s="20"/>
     </row>
-    <row r="266" spans="1:26" ht="15.75" thickBot="1">
+    <row r="266" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A266" s="18">
         <v>265</v>
       </c>
@@ -15370,7 +15443,7 @@
         <v>45</v>
       </c>
       <c r="M266" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N266" s="20"/>
       <c r="O266" s="20"/>
@@ -15386,7 +15459,7 @@
       <c r="Y266" s="20"/>
       <c r="Z266" s="20"/>
     </row>
-    <row r="267" spans="1:26" ht="15.75" thickBot="1">
+    <row r="267" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A267" s="18">
         <v>266</v>
       </c>
@@ -15422,7 +15495,7 @@
         <v>45</v>
       </c>
       <c r="M267" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N267" s="20"/>
       <c r="O267" s="20"/>
@@ -15438,7 +15511,7 @@
       <c r="Y267" s="20"/>
       <c r="Z267" s="20"/>
     </row>
-    <row r="268" spans="1:26" ht="15.75" thickBot="1">
+    <row r="268" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A268" s="18">
         <v>267</v>
       </c>
@@ -15474,7 +15547,7 @@
         <v>45</v>
       </c>
       <c r="M268" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N268" s="20"/>
       <c r="O268" s="20"/>
@@ -15490,7 +15563,7 @@
       <c r="Y268" s="20"/>
       <c r="Z268" s="20"/>
     </row>
-    <row r="269" spans="1:26" ht="15.75" thickBot="1">
+    <row r="269" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A269" s="18">
         <v>268</v>
       </c>
@@ -15526,7 +15599,7 @@
         <v>45</v>
       </c>
       <c r="M269" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N269" s="20"/>
       <c r="O269" s="20"/>
@@ -15542,7 +15615,7 @@
       <c r="Y269" s="20"/>
       <c r="Z269" s="20"/>
     </row>
-    <row r="270" spans="1:26" ht="15.75" thickBot="1">
+    <row r="270" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A270" s="18">
         <v>269</v>
       </c>
@@ -15578,7 +15651,7 @@
         <v>45</v>
       </c>
       <c r="M270" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N270" s="20"/>
       <c r="O270" s="20"/>
@@ -15594,7 +15667,7 @@
       <c r="Y270" s="20"/>
       <c r="Z270" s="20"/>
     </row>
-    <row r="271" spans="1:26" ht="15.75" thickBot="1">
+    <row r="271" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A271" s="18">
         <v>270</v>
       </c>
@@ -15630,7 +15703,7 @@
         <v>45</v>
       </c>
       <c r="M271" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N271" s="20"/>
       <c r="O271" s="20"/>
@@ -15646,7 +15719,7 @@
       <c r="Y271" s="20"/>
       <c r="Z271" s="20"/>
     </row>
-    <row r="272" spans="1:26" ht="15.75" thickBot="1">
+    <row r="272" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A272" s="18">
         <v>271</v>
       </c>
@@ -15682,7 +15755,7 @@
         <v>45</v>
       </c>
       <c r="M272" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N272" s="20"/>
       <c r="O272" s="20"/>
@@ -15698,7 +15771,7 @@
       <c r="Y272" s="20"/>
       <c r="Z272" s="20"/>
     </row>
-    <row r="273" spans="1:26" ht="15.75" thickBot="1">
+    <row r="273" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A273" s="18">
         <v>272</v>
       </c>
@@ -15721,7 +15794,7 @@
         <v>40</v>
       </c>
       <c r="H273" s="22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I273" s="20"/>
       <c r="J273" s="40">
@@ -15734,7 +15807,7 @@
         <v>45</v>
       </c>
       <c r="M273" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N273" s="20"/>
       <c r="O273" s="20"/>
@@ -15750,7 +15823,7 @@
       <c r="Y273" s="20"/>
       <c r="Z273" s="20"/>
     </row>
-    <row r="274" spans="1:26" ht="15.75" thickBot="1">
+    <row r="274" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A274" s="18">
         <v>273</v>
       </c>
@@ -15773,7 +15846,7 @@
         <v>40</v>
       </c>
       <c r="H274" s="22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I274" s="20"/>
       <c r="J274" s="40">
@@ -15786,7 +15859,7 @@
         <v>45</v>
       </c>
       <c r="M274" s="36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N274" s="20"/>
       <c r="O274" s="20"/>
@@ -15802,7 +15875,7 @@
       <c r="Y274" s="20"/>
       <c r="Z274" s="20"/>
     </row>
-    <row r="275" spans="1:26" ht="15.75" thickBot="1">
+    <row r="275" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A275" s="18">
         <v>274</v>
       </c>
@@ -15838,7 +15911,7 @@
         <v>45</v>
       </c>
       <c r="M275" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N275" s="20"/>
       <c r="O275" s="20"/>
@@ -15854,7 +15927,7 @@
       <c r="Y275" s="20"/>
       <c r="Z275" s="20"/>
     </row>
-    <row r="276" spans="1:26" ht="15.75" thickBot="1">
+    <row r="276" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A276" s="18">
         <v>275</v>
       </c>
@@ -15890,7 +15963,7 @@
         <v>45</v>
       </c>
       <c r="M276" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N276" s="20"/>
       <c r="O276" s="20"/>
@@ -15906,7 +15979,7 @@
       <c r="Y276" s="20"/>
       <c r="Z276" s="20"/>
     </row>
-    <row r="277" spans="1:26" ht="15.75" thickBot="1">
+    <row r="277" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A277" s="18">
         <v>276</v>
       </c>
@@ -15942,7 +16015,7 @@
         <v>45</v>
       </c>
       <c r="M277" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N277" s="20"/>
       <c r="O277" s="20"/>
@@ -15958,7 +16031,7 @@
       <c r="Y277" s="20"/>
       <c r="Z277" s="20"/>
     </row>
-    <row r="278" spans="1:26" ht="15.75" thickBot="1">
+    <row r="278" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A278" s="18">
         <v>277</v>
       </c>
@@ -15994,7 +16067,7 @@
         <v>45</v>
       </c>
       <c r="M278" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N278" s="20"/>
       <c r="O278" s="20"/>
@@ -16010,7 +16083,7 @@
       <c r="Y278" s="20"/>
       <c r="Z278" s="20"/>
     </row>
-    <row r="279" spans="1:26" ht="15.75" thickBot="1">
+    <row r="279" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A279" s="18">
         <v>278</v>
       </c>
@@ -16046,7 +16119,7 @@
         <v>45</v>
       </c>
       <c r="M279" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N279" s="20"/>
       <c r="O279" s="20"/>
@@ -16062,7 +16135,7 @@
       <c r="Y279" s="20"/>
       <c r="Z279" s="20"/>
     </row>
-    <row r="280" spans="1:26" ht="15.75" thickBot="1">
+    <row r="280" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A280" s="18">
         <v>279</v>
       </c>
@@ -16098,7 +16171,7 @@
         <v>45</v>
       </c>
       <c r="M280" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N280" s="20"/>
       <c r="O280" s="20"/>
@@ -16114,7 +16187,7 @@
       <c r="Y280" s="20"/>
       <c r="Z280" s="20"/>
     </row>
-    <row r="281" spans="1:26" ht="15.75" thickBot="1">
+    <row r="281" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A281" s="18">
         <v>280</v>
       </c>
@@ -16150,7 +16223,7 @@
         <v>45</v>
       </c>
       <c r="M281" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N281" s="20"/>
       <c r="O281" s="20"/>
@@ -16166,7 +16239,7 @@
       <c r="Y281" s="20"/>
       <c r="Z281" s="20"/>
     </row>
-    <row r="282" spans="1:26" ht="15.75" thickBot="1">
+    <row r="282" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A282" s="18">
         <v>281</v>
       </c>
@@ -16202,7 +16275,7 @@
         <v>45</v>
       </c>
       <c r="M282" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N282" s="20"/>
       <c r="O282" s="20"/>
@@ -16218,7 +16291,7 @@
       <c r="Y282" s="20"/>
       <c r="Z282" s="20"/>
     </row>
-    <row r="283" spans="1:26" ht="15.75" thickBot="1">
+    <row r="283" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A283" s="18">
         <v>282</v>
       </c>
@@ -16254,7 +16327,7 @@
         <v>45</v>
       </c>
       <c r="M283" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N283" s="20"/>
       <c r="O283" s="20"/>
@@ -16270,7 +16343,7 @@
       <c r="Y283" s="20"/>
       <c r="Z283" s="20"/>
     </row>
-    <row r="284" spans="1:26" ht="15.75" thickBot="1">
+    <row r="284" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A284" s="18">
         <v>283</v>
       </c>
@@ -16306,7 +16379,7 @@
         <v>45</v>
       </c>
       <c r="M284" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N284" s="20"/>
       <c r="O284" s="20"/>
@@ -16322,7 +16395,7 @@
       <c r="Y284" s="20"/>
       <c r="Z284" s="20"/>
     </row>
-    <row r="285" spans="1:26" ht="15.75" thickBot="1">
+    <row r="285" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A285" s="18">
         <v>284</v>
       </c>
@@ -16358,7 +16431,7 @@
         <v>45</v>
       </c>
       <c r="M285" s="36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N285" s="20"/>
       <c r="O285" s="20"/>
@@ -16374,7 +16447,7 @@
       <c r="Y285" s="20"/>
       <c r="Z285" s="20"/>
     </row>
-    <row r="286" spans="1:26" ht="15.75" thickBot="1">
+    <row r="286" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A286" s="18">
         <v>285</v>
       </c>
@@ -16410,7 +16483,7 @@
         <v>45</v>
       </c>
       <c r="M286" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N286" s="20"/>
       <c r="O286" s="20"/>
@@ -16426,7 +16499,7 @@
       <c r="Y286" s="20"/>
       <c r="Z286" s="20"/>
     </row>
-    <row r="287" spans="1:26" ht="15.75" thickBot="1">
+    <row r="287" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A287" s="18">
         <v>286</v>
       </c>
@@ -16462,7 +16535,7 @@
         <v>45</v>
       </c>
       <c r="M287" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N287" s="20"/>
       <c r="O287" s="20"/>
@@ -16478,7 +16551,7 @@
       <c r="Y287" s="20"/>
       <c r="Z287" s="20"/>
     </row>
-    <row r="288" spans="1:26" ht="15.75" thickBot="1">
+    <row r="288" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A288" s="18">
         <v>287</v>
       </c>
@@ -16514,7 +16587,7 @@
         <v>45</v>
       </c>
       <c r="M288" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N288" s="20"/>
       <c r="O288" s="20"/>
@@ -16530,7 +16603,7 @@
       <c r="Y288" s="20"/>
       <c r="Z288" s="20"/>
     </row>
-    <row r="289" spans="1:26" ht="15.75" thickBot="1">
+    <row r="289" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A289" s="18">
         <v>288</v>
       </c>
@@ -16566,7 +16639,7 @@
         <v>45</v>
       </c>
       <c r="M289" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N289" s="20"/>
       <c r="O289" s="20"/>
@@ -16582,7 +16655,7 @@
       <c r="Y289" s="20"/>
       <c r="Z289" s="20"/>
     </row>
-    <row r="290" spans="1:26" ht="15.75" thickBot="1">
+    <row r="290" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A290" s="18">
         <v>289</v>
       </c>
@@ -16618,7 +16691,7 @@
         <v>45</v>
       </c>
       <c r="M290" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N290" s="20"/>
       <c r="O290" s="20"/>
@@ -16634,7 +16707,7 @@
       <c r="Y290" s="20"/>
       <c r="Z290" s="20"/>
     </row>
-    <row r="291" spans="1:26" ht="15.75" thickBot="1">
+    <row r="291" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A291" s="18">
         <v>290</v>
       </c>
@@ -16670,7 +16743,7 @@
         <v>45</v>
       </c>
       <c r="M291" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N291" s="20"/>
       <c r="O291" s="20"/>
@@ -16686,7 +16759,7 @@
       <c r="Y291" s="20"/>
       <c r="Z291" s="20"/>
     </row>
-    <row r="292" spans="1:26" ht="15.75" thickBot="1">
+    <row r="292" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A292" s="18">
         <v>291</v>
       </c>
@@ -16722,7 +16795,7 @@
         <v>45</v>
       </c>
       <c r="M292" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N292" s="20"/>
       <c r="O292" s="20"/>
@@ -16738,7 +16811,7 @@
       <c r="Y292" s="20"/>
       <c r="Z292" s="20"/>
     </row>
-    <row r="293" spans="1:26" ht="15.75" thickBot="1">
+    <row r="293" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A293" s="18">
         <v>292</v>
       </c>
@@ -16776,7 +16849,7 @@
         <v>45</v>
       </c>
       <c r="M293" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N293" s="20"/>
       <c r="O293" s="20"/>
@@ -16792,7 +16865,7 @@
       <c r="Y293" s="20"/>
       <c r="Z293" s="20"/>
     </row>
-    <row r="294" spans="1:26" ht="15.75" thickBot="1">
+    <row r="294" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A294" s="18">
         <v>293</v>
       </c>
@@ -16828,7 +16901,7 @@
         <v>45</v>
       </c>
       <c r="M294" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N294" s="20"/>
       <c r="O294" s="20"/>
@@ -16844,7 +16917,7 @@
       <c r="Y294" s="20"/>
       <c r="Z294" s="20"/>
     </row>
-    <row r="295" spans="1:26" ht="15.75" thickBot="1">
+    <row r="295" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A295" s="18">
         <v>294</v>
       </c>
@@ -16880,7 +16953,7 @@
         <v>45</v>
       </c>
       <c r="M295" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N295" s="20"/>
       <c r="O295" s="20"/>
@@ -16896,7 +16969,7 @@
       <c r="Y295" s="20"/>
       <c r="Z295" s="20"/>
     </row>
-    <row r="296" spans="1:26" ht="15.75" thickBot="1">
+    <row r="296" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A296" s="18">
         <v>295</v>
       </c>
@@ -16932,7 +17005,7 @@
         <v>45</v>
       </c>
       <c r="M296" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N296" s="20"/>
       <c r="O296" s="20"/>
@@ -16948,7 +17021,7 @@
       <c r="Y296" s="20"/>
       <c r="Z296" s="20"/>
     </row>
-    <row r="297" spans="1:26" ht="15.75" thickBot="1">
+    <row r="297" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A297" s="18">
         <v>296</v>
       </c>
@@ -16984,7 +17057,7 @@
         <v>45</v>
       </c>
       <c r="M297" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N297" s="20"/>
       <c r="O297" s="20"/>
@@ -17000,7 +17073,7 @@
       <c r="Y297" s="20"/>
       <c r="Z297" s="20"/>
     </row>
-    <row r="298" spans="1:26" ht="15.75" thickBot="1">
+    <row r="298" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A298" s="18">
         <v>297</v>
       </c>
@@ -17036,7 +17109,7 @@
         <v>45</v>
       </c>
       <c r="M298" s="45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N298" s="20"/>
       <c r="O298" s="20"/>
@@ -17052,7 +17125,7 @@
       <c r="Y298" s="20"/>
       <c r="Z298" s="20"/>
     </row>
-    <row r="299" spans="1:26" ht="15.75" thickBot="1">
+    <row r="299" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A299" s="18">
         <v>298</v>
       </c>
@@ -17090,7 +17163,7 @@
         <v>45</v>
       </c>
       <c r="M299" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N299" s="20"/>
       <c r="O299" s="20"/>
@@ -17106,7 +17179,7 @@
       <c r="Y299" s="20"/>
       <c r="Z299" s="20"/>
     </row>
-    <row r="300" spans="1:26" ht="15.75" thickBot="1">
+    <row r="300" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A300" s="18">
         <v>299</v>
       </c>
@@ -17142,7 +17215,7 @@
         <v>45</v>
       </c>
       <c r="M300" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N300" s="20"/>
       <c r="O300" s="20"/>
@@ -17158,7 +17231,7 @@
       <c r="Y300" s="20"/>
       <c r="Z300" s="20"/>
     </row>
-    <row r="301" spans="1:26" ht="27" thickBot="1">
+    <row r="301" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A301" s="18">
         <v>300</v>
       </c>
@@ -17179,7 +17252,7 @@
         <v>16</v>
       </c>
       <c r="H301" s="22" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I301" s="22"/>
       <c r="J301" s="40">
@@ -17192,7 +17265,7 @@
         <v>45</v>
       </c>
       <c r="M301" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N301" s="20"/>
       <c r="O301" s="20"/>
@@ -17208,7 +17281,7 @@
       <c r="Y301" s="20"/>
       <c r="Z301" s="20"/>
     </row>
-    <row r="302" spans="1:26" ht="15.75" thickBot="1">
+    <row r="302" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A302" s="18">
         <v>301</v>
       </c>
@@ -17242,7 +17315,7 @@
         <v>45</v>
       </c>
       <c r="M302" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N302" s="20"/>
       <c r="O302" s="20"/>
@@ -17258,7 +17331,7 @@
       <c r="Y302" s="20"/>
       <c r="Z302" s="20"/>
     </row>
-    <row r="303" spans="1:26" ht="15.75" thickBot="1">
+    <row r="303" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A303" s="18">
         <v>302</v>
       </c>
@@ -17292,7 +17365,7 @@
         <v>45</v>
       </c>
       <c r="M303" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N303" s="20"/>
       <c r="O303" s="20"/>
@@ -17308,12 +17381,12 @@
       <c r="Y303" s="20"/>
       <c r="Z303" s="20"/>
     </row>
-    <row r="304" spans="1:26" ht="15.75" thickBot="1">
+    <row r="304" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A304" s="18">
         <v>303</v>
       </c>
       <c r="B304" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C304" s="22" t="s">
         <v>53</v>
@@ -17342,7 +17415,7 @@
         <v>45</v>
       </c>
       <c r="M304" s="36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N304" s="20"/>
       <c r="O304" s="20"/>
@@ -17358,7 +17431,7 @@
       <c r="Y304" s="20"/>
       <c r="Z304" s="20"/>
     </row>
-    <row r="305" spans="1:26" ht="27" thickBot="1">
+    <row r="305" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A305" s="18">
         <v>304</v>
       </c>
@@ -17381,7 +17454,7 @@
         <v>16</v>
       </c>
       <c r="H305" s="22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I305" s="22" t="s">
         <v>85</v>
@@ -17396,7 +17469,7 @@
         <v>45</v>
       </c>
       <c r="M305" s="36" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N305" s="20"/>
       <c r="O305" s="20"/>
@@ -17412,7 +17485,7 @@
       <c r="Y305" s="20"/>
       <c r="Z305" s="20"/>
     </row>
-    <row r="306" spans="1:26" ht="15.75" thickBot="1">
+    <row r="306" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A306" s="18">
         <v>305</v>
       </c>
@@ -17450,7 +17523,7 @@
         <v>45</v>
       </c>
       <c r="M306" s="36" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N306" s="20"/>
       <c r="O306" s="20"/>
@@ -17466,7 +17539,7 @@
       <c r="Y306" s="20"/>
       <c r="Z306" s="20"/>
     </row>
-    <row r="307" spans="1:26" ht="15.75" thickBot="1">
+    <row r="307" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A307" s="18">
         <v>306</v>
       </c>
@@ -17502,7 +17575,7 @@
         <v>45</v>
       </c>
       <c r="M307" s="36" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N307" s="20"/>
       <c r="O307" s="20"/>
@@ -17518,7 +17591,7 @@
       <c r="Y307" s="20"/>
       <c r="Z307" s="20"/>
     </row>
-    <row r="308" spans="1:26" ht="15.75" thickBot="1">
+    <row r="308" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A308" s="18">
         <v>307</v>
       </c>
@@ -17570,7 +17643,7 @@
       <c r="Y308" s="20"/>
       <c r="Z308" s="20"/>
     </row>
-    <row r="309" spans="1:26" ht="15.75" thickBot="1">
+    <row r="309" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A309" s="18">
         <v>308</v>
       </c>
@@ -17622,7 +17695,7 @@
       <c r="Y309" s="20"/>
       <c r="Z309" s="20"/>
     </row>
-    <row r="310" spans="1:26" ht="15.75" thickBot="1">
+    <row r="310" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A310" s="18">
         <v>309</v>
       </c>
@@ -17658,7 +17731,7 @@
         <v>45</v>
       </c>
       <c r="M310" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N310" s="20"/>
       <c r="O310" s="20"/>
@@ -17674,7 +17747,7 @@
       <c r="Y310" s="20"/>
       <c r="Z310" s="20"/>
     </row>
-    <row r="311" spans="1:26" ht="15.75" thickBot="1">
+    <row r="311" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A311" s="18">
         <v>310</v>
       </c>
@@ -17710,7 +17783,7 @@
         <v>45</v>
       </c>
       <c r="M311" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N311" s="20"/>
       <c r="O311" s="20"/>
@@ -17726,7 +17799,7 @@
       <c r="Y311" s="20"/>
       <c r="Z311" s="20"/>
     </row>
-    <row r="312" spans="1:26" ht="15.75" thickBot="1">
+    <row r="312" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A312" s="18">
         <v>311</v>
       </c>
@@ -17762,7 +17835,7 @@
         <v>45</v>
       </c>
       <c r="M312" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N312" s="20"/>
       <c r="O312" s="20"/>
@@ -17778,7 +17851,7 @@
       <c r="Y312" s="20"/>
       <c r="Z312" s="20"/>
     </row>
-    <row r="313" spans="1:26" ht="15.75" thickBot="1">
+    <row r="313" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A313" s="18">
         <v>312</v>
       </c>
@@ -17814,7 +17887,7 @@
         <v>45</v>
       </c>
       <c r="M313" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N313" s="20"/>
       <c r="O313" s="20"/>
@@ -17830,7 +17903,7 @@
       <c r="Y313" s="20"/>
       <c r="Z313" s="20"/>
     </row>
-    <row r="314" spans="1:26" ht="15.75" thickBot="1">
+    <row r="314" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A314" s="18">
         <v>313</v>
       </c>
@@ -17866,7 +17939,7 @@
         <v>45</v>
       </c>
       <c r="M314" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N314" s="20"/>
       <c r="O314" s="20"/>
@@ -17882,7 +17955,7 @@
       <c r="Y314" s="20"/>
       <c r="Z314" s="20"/>
     </row>
-    <row r="315" spans="1:26" ht="15.75" thickBot="1">
+    <row r="315" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A315" s="18">
         <v>314</v>
       </c>
@@ -17918,7 +17991,7 @@
         <v>45</v>
       </c>
       <c r="M315" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N315" s="20"/>
       <c r="O315" s="20"/>
@@ -17934,7 +18007,7 @@
       <c r="Y315" s="20"/>
       <c r="Z315" s="20"/>
     </row>
-    <row r="316" spans="1:26" ht="15.75" thickBot="1">
+    <row r="316" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A316" s="18">
         <v>315</v>
       </c>
@@ -17970,7 +18043,7 @@
         <v>45</v>
       </c>
       <c r="M316" s="36" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N316" s="20"/>
       <c r="O316" s="20"/>
@@ -17986,7 +18059,7 @@
       <c r="Y316" s="20"/>
       <c r="Z316" s="20"/>
     </row>
-    <row r="317" spans="1:26" ht="27" thickBot="1">
+    <row r="317" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A317" s="18">
         <v>316</v>
       </c>
@@ -18005,14 +18078,14 @@
       <c r="F317" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G317" s="22" t="s">
-        <v>202</v>
+      <c r="G317" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="H317" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I317" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J317" s="40">
         <v>30249616</v>
@@ -18024,7 +18097,7 @@
         <v>45</v>
       </c>
       <c r="M317" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N317" s="20"/>
       <c r="O317" s="20"/>
@@ -18040,7 +18113,7 @@
       <c r="Y317" s="20"/>
       <c r="Z317" s="20"/>
     </row>
-    <row r="318" spans="1:26" ht="27" thickBot="1">
+    <row r="318" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A318" s="18">
         <v>317</v>
       </c>
@@ -18059,14 +18132,14 @@
       <c r="F318" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G318" s="22" t="s">
-        <v>202</v>
+      <c r="G318" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="H318" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I318" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J318" s="40">
         <v>30249616</v>
@@ -18078,7 +18151,7 @@
         <v>45</v>
       </c>
       <c r="M318" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N318" s="20"/>
       <c r="O318" s="20"/>
@@ -18094,7 +18167,7 @@
       <c r="Y318" s="20"/>
       <c r="Z318" s="20"/>
     </row>
-    <row r="319" spans="1:26" ht="27" thickBot="1">
+    <row r="319" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A319" s="18">
         <v>318</v>
       </c>
@@ -18113,14 +18186,14 @@
       <c r="F319" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G319" s="22" t="s">
-        <v>202</v>
+      <c r="G319" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="H319" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I319" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J319" s="40">
         <v>30249616</v>
@@ -18132,7 +18205,7 @@
         <v>45</v>
       </c>
       <c r="M319" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N319" s="20"/>
       <c r="O319" s="20"/>
@@ -18148,7 +18221,7 @@
       <c r="Y319" s="20"/>
       <c r="Z319" s="20"/>
     </row>
-    <row r="320" spans="1:26" ht="39.75" thickBot="1">
+    <row r="320" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A320" s="18">
         <v>319</v>
       </c>
@@ -18168,13 +18241,13 @@
         <v>19</v>
       </c>
       <c r="G320" s="22" t="s">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="H320" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I320" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J320" s="40">
         <v>30249616</v>
@@ -18186,7 +18259,7 @@
         <v>45</v>
       </c>
       <c r="M320" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N320" s="20"/>
       <c r="O320" s="20"/>
@@ -18202,7 +18275,7 @@
       <c r="Y320" s="20"/>
       <c r="Z320" s="20"/>
     </row>
-    <row r="321" spans="1:26" ht="27" thickBot="1">
+    <row r="321" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A321" s="18">
         <v>320</v>
       </c>
@@ -18221,14 +18294,14 @@
       <c r="F321" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="G321" s="22" t="s">
-        <v>202</v>
+      <c r="G321" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="H321" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I321" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J321" s="40">
         <v>30249616</v>
@@ -18240,7 +18313,7 @@
         <v>45</v>
       </c>
       <c r="M321" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N321" s="20"/>
       <c r="O321" s="20"/>
@@ -18256,7 +18329,7 @@
       <c r="Y321" s="20"/>
       <c r="Z321" s="20"/>
     </row>
-    <row r="322" spans="1:26" ht="39.75" thickBot="1">
+    <row r="322" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A322" s="18">
         <v>321</v>
       </c>
@@ -18276,13 +18349,13 @@
         <v>58</v>
       </c>
       <c r="G322" s="22" t="s">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="H322" s="22" t="s">
         <v>50</v>
       </c>
       <c r="I322" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J322" s="40">
         <v>30249616</v>
@@ -18294,7 +18367,7 @@
         <v>45</v>
       </c>
       <c r="M322" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N322" s="20"/>
       <c r="O322" s="20"/>
@@ -18310,7 +18383,7 @@
       <c r="Y322" s="20"/>
       <c r="Z322" s="20"/>
     </row>
-    <row r="323" spans="1:26" ht="15.75" thickBot="1">
+    <row r="323" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A323" s="18">
         <v>322</v>
       </c>
@@ -18346,7 +18419,7 @@
         <v>45</v>
       </c>
       <c r="M323" s="36" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N323" s="20"/>
       <c r="O323" s="20"/>
@@ -18362,7 +18435,7 @@
       <c r="Y323" s="20"/>
       <c r="Z323" s="20"/>
     </row>
-    <row r="324" spans="1:26" ht="15.75" thickBot="1">
+    <row r="324" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A324" s="18">
         <v>323</v>
       </c>
@@ -18398,7 +18471,7 @@
         <v>45</v>
       </c>
       <c r="M324" s="36" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N324" s="20"/>
       <c r="O324" s="20"/>
@@ -18414,7 +18487,7 @@
       <c r="Y324" s="20"/>
       <c r="Z324" s="20"/>
     </row>
-    <row r="325" spans="1:26" ht="15.75" thickBot="1">
+    <row r="325" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A325" s="18">
         <v>324</v>
       </c>
@@ -18437,7 +18510,7 @@
         <v>33</v>
       </c>
       <c r="H325" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I325" s="22" t="s">
         <v>66</v>
@@ -18452,7 +18525,7 @@
         <v>45</v>
       </c>
       <c r="M325" s="36" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N325" s="20"/>
       <c r="O325" s="20"/>
@@ -18468,7 +18541,7 @@
       <c r="Y325" s="20"/>
       <c r="Z325" s="20"/>
     </row>
-    <row r="326" spans="1:26" ht="15.75" thickBot="1">
+    <row r="326" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A326" s="18">
         <v>325</v>
       </c>
@@ -18491,7 +18564,7 @@
         <v>33</v>
       </c>
       <c r="H326" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I326" s="22" t="s">
         <v>66</v>
@@ -18506,7 +18579,7 @@
         <v>45</v>
       </c>
       <c r="M326" s="36" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N326" s="20"/>
       <c r="O326" s="20"/>
@@ -18522,7 +18595,7 @@
       <c r="Y326" s="20"/>
       <c r="Z326" s="20"/>
     </row>
-    <row r="327" spans="1:26" ht="15.75" thickBot="1">
+    <row r="327" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A327" s="18">
         <v>326</v>
       </c>
@@ -18558,7 +18631,7 @@
         <v>45</v>
       </c>
       <c r="M327" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N327" s="20"/>
       <c r="O327" s="20"/>
@@ -18574,7 +18647,7 @@
       <c r="Y327" s="20"/>
       <c r="Z327" s="20"/>
     </row>
-    <row r="328" spans="1:26" ht="15.75" thickBot="1">
+    <row r="328" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A328" s="18">
         <v>327</v>
       </c>
@@ -18610,7 +18683,7 @@
         <v>45</v>
       </c>
       <c r="M328" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N328" s="20"/>
       <c r="O328" s="20"/>
@@ -18626,7 +18699,7 @@
       <c r="Y328" s="20"/>
       <c r="Z328" s="20"/>
     </row>
-    <row r="329" spans="1:26" ht="15.75" thickBot="1">
+    <row r="329" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A329" s="18">
         <v>328</v>
       </c>
@@ -18662,7 +18735,7 @@
         <v>45</v>
       </c>
       <c r="M329" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N329" s="20"/>
       <c r="O329" s="20"/>
@@ -18678,7 +18751,7 @@
       <c r="Y329" s="20"/>
       <c r="Z329" s="20"/>
     </row>
-    <row r="330" spans="1:26" ht="15.75" thickBot="1">
+    <row r="330" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A330" s="18">
         <v>329</v>
       </c>
@@ -18714,7 +18787,7 @@
         <v>45</v>
       </c>
       <c r="M330" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N330" s="20"/>
       <c r="O330" s="20"/>
@@ -18730,7 +18803,7 @@
       <c r="Y330" s="20"/>
       <c r="Z330" s="20"/>
     </row>
-    <row r="331" spans="1:26" ht="15.75" thickBot="1">
+    <row r="331" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A331" s="18">
         <v>330</v>
       </c>
@@ -18766,7 +18839,7 @@
         <v>45</v>
       </c>
       <c r="M331" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N331" s="20"/>
       <c r="O331" s="20"/>
@@ -18782,7 +18855,7 @@
       <c r="Y331" s="20"/>
       <c r="Z331" s="20"/>
     </row>
-    <row r="332" spans="1:26" ht="15.75" thickBot="1">
+    <row r="332" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A332" s="18">
         <v>331</v>
       </c>
@@ -18818,7 +18891,7 @@
         <v>45</v>
       </c>
       <c r="M332" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N332" s="20"/>
       <c r="O332" s="20"/>
@@ -18834,7 +18907,7 @@
       <c r="Y332" s="20"/>
       <c r="Z332" s="20"/>
     </row>
-    <row r="333" spans="1:26" ht="15.75" thickBot="1">
+    <row r="333" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A333" s="18">
         <v>332</v>
       </c>
@@ -18872,7 +18945,7 @@
         <v>45</v>
       </c>
       <c r="M333" s="36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N333" s="20"/>
       <c r="O333" s="20"/>
@@ -18888,7 +18961,7 @@
       <c r="Y333" s="20"/>
       <c r="Z333" s="20"/>
     </row>
-    <row r="334" spans="1:26" ht="15.75" thickBot="1">
+    <row r="334" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A334" s="18">
         <v>333</v>
       </c>
@@ -18914,7 +18987,7 @@
         <v>65</v>
       </c>
       <c r="I334" s="22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J334" s="40">
         <v>25264167</v>
@@ -18926,7 +18999,7 @@
         <v>45</v>
       </c>
       <c r="M334" s="36" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N334" s="20"/>
       <c r="O334" s="20"/>
@@ -18942,7 +19015,7 @@
       <c r="Y334" s="20"/>
       <c r="Z334" s="20"/>
     </row>
-    <row r="335" spans="1:26" ht="15.75" thickBot="1">
+    <row r="335" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A335" s="18">
         <v>334</v>
       </c>
@@ -18965,7 +19038,7 @@
         <v>16</v>
       </c>
       <c r="H335" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I335" s="22"/>
       <c r="J335" s="40">
@@ -18978,7 +19051,7 @@
         <v>45</v>
       </c>
       <c r="M335" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N335" s="20"/>
       <c r="O335" s="20"/>
@@ -18994,7 +19067,7 @@
       <c r="Y335" s="20"/>
       <c r="Z335" s="20"/>
     </row>
-    <row r="336" spans="1:26" ht="15.75" thickBot="1">
+    <row r="336" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A336" s="18">
         <v>335</v>
       </c>
@@ -19017,7 +19090,7 @@
         <v>16</v>
       </c>
       <c r="H336" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I336" s="22"/>
       <c r="J336" s="40">
@@ -19030,7 +19103,7 @@
         <v>45</v>
       </c>
       <c r="M336" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N336" s="20"/>
       <c r="O336" s="20"/>
@@ -19046,7 +19119,7 @@
       <c r="Y336" s="20"/>
       <c r="Z336" s="20"/>
     </row>
-    <row r="337" spans="1:26" ht="15.75" thickBot="1">
+    <row r="337" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A337" s="18">
         <v>336</v>
       </c>
@@ -19069,7 +19142,7 @@
         <v>16</v>
       </c>
       <c r="H337" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I337" s="22"/>
       <c r="J337" s="40">
@@ -19082,7 +19155,7 @@
         <v>45</v>
       </c>
       <c r="M337" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N337" s="20"/>
       <c r="O337" s="20"/>
@@ -19098,7 +19171,7 @@
       <c r="Y337" s="20"/>
       <c r="Z337" s="20"/>
     </row>
-    <row r="338" spans="1:26" ht="15.75" thickBot="1">
+    <row r="338" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A338" s="18">
         <v>337</v>
       </c>
@@ -19121,7 +19194,7 @@
         <v>16</v>
       </c>
       <c r="H338" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I338" s="22"/>
       <c r="J338" s="40">
@@ -19134,7 +19207,7 @@
         <v>45</v>
       </c>
       <c r="M338" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N338" s="20"/>
       <c r="O338" s="20"/>
@@ -19150,7 +19223,7 @@
       <c r="Y338" s="20"/>
       <c r="Z338" s="20"/>
     </row>
-    <row r="339" spans="1:26" ht="27" thickBot="1">
+    <row r="339" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A339" s="18">
         <v>338</v>
       </c>
@@ -19173,7 +19246,7 @@
         <v>16</v>
       </c>
       <c r="H339" s="22" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I339" s="22" t="s">
         <v>85</v>
@@ -19204,7 +19277,7 @@
       <c r="Y339" s="20"/>
       <c r="Z339" s="20"/>
     </row>
-    <row r="340" spans="1:26" ht="27" thickBot="1">
+    <row r="340" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A340" s="18">
         <v>339</v>
       </c>
@@ -19227,7 +19300,7 @@
         <v>16</v>
       </c>
       <c r="H340" s="22" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I340" s="22" t="s">
         <v>85</v>
@@ -19258,7 +19331,7 @@
       <c r="Y340" s="20"/>
       <c r="Z340" s="20"/>
     </row>
-    <row r="341" spans="1:26" ht="15.75" thickBot="1">
+    <row r="341" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A341" s="18">
         <v>340</v>
       </c>
@@ -19296,7 +19369,7 @@
         <v>45</v>
       </c>
       <c r="M341" s="36" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N341" s="20"/>
       <c r="O341" s="20"/>
@@ -19312,7 +19385,7 @@
       <c r="Y341" s="20"/>
       <c r="Z341" s="20"/>
     </row>
-    <row r="342" spans="1:26" ht="15.75" thickBot="1">
+    <row r="342" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A342" s="18">
         <v>341</v>
       </c>
@@ -19335,7 +19408,7 @@
         <v>33</v>
       </c>
       <c r="H342" s="22" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I342" s="22" t="s">
         <v>66</v>
@@ -19350,7 +19423,7 @@
         <v>45</v>
       </c>
       <c r="M342" s="36" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N342" s="20"/>
       <c r="O342" s="20"/>
@@ -19366,7 +19439,7 @@
       <c r="Y342" s="20"/>
       <c r="Z342" s="20"/>
     </row>
-    <row r="343" spans="1:26" ht="15.75" thickBot="1">
+    <row r="343" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A343" s="18">
         <v>342</v>
       </c>
@@ -19389,7 +19462,7 @@
         <v>16</v>
       </c>
       <c r="H343" s="22" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I343" s="22" t="s">
         <v>85</v>
@@ -19404,7 +19477,7 @@
         <v>45</v>
       </c>
       <c r="M343" s="36" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N343" s="20"/>
       <c r="O343" s="20"/>
@@ -19420,7 +19493,7 @@
       <c r="Y343" s="20"/>
       <c r="Z343" s="20"/>
     </row>
-    <row r="344" spans="1:26" ht="15.75" thickBot="1">
+    <row r="344" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A344" s="18">
         <v>343</v>
       </c>
@@ -19458,7 +19531,7 @@
         <v>45</v>
       </c>
       <c r="M344" s="31" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N344" s="20"/>
       <c r="O344" s="20"/>
@@ -19474,7 +19547,7 @@
       <c r="Y344" s="20"/>
       <c r="Z344" s="20"/>
     </row>
-    <row r="345" spans="1:26" ht="27" thickBot="1">
+    <row r="345" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A345" s="18">
         <v>344</v>
       </c>
@@ -19497,10 +19570,10 @@
         <v>33</v>
       </c>
       <c r="H345" s="22" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I345" s="22" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J345" s="40">
         <v>35466948</v>
@@ -19512,7 +19585,7 @@
         <v>45</v>
       </c>
       <c r="M345" s="36" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N345" s="20"/>
       <c r="O345" s="20"/>
@@ -19528,7 +19601,7 @@
       <c r="Y345" s="20"/>
       <c r="Z345" s="20"/>
     </row>
-    <row r="346" spans="1:26" ht="15.75" thickBot="1">
+    <row r="346" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A346" s="18">
         <v>345</v>
       </c>
@@ -19564,7 +19637,7 @@
         <v>45</v>
       </c>
       <c r="M346" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N346" s="20"/>
       <c r="O346" s="20"/>
@@ -19580,7 +19653,7 @@
       <c r="Y346" s="20"/>
       <c r="Z346" s="20"/>
     </row>
-    <row r="347" spans="1:26" ht="15.75" thickBot="1">
+    <row r="347" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A347" s="18">
         <v>346</v>
       </c>
@@ -19616,7 +19689,7 @@
         <v>45</v>
       </c>
       <c r="M347" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N347" s="20"/>
       <c r="O347" s="20"/>
@@ -19632,7 +19705,7 @@
       <c r="Y347" s="20"/>
       <c r="Z347" s="20"/>
     </row>
-    <row r="348" spans="1:26" ht="15.75" thickBot="1">
+    <row r="348" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A348" s="18">
         <v>347</v>
       </c>
@@ -19668,7 +19741,7 @@
         <v>45</v>
       </c>
       <c r="M348" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N348" s="20"/>
       <c r="O348" s="20"/>
@@ -19684,7 +19757,7 @@
       <c r="Y348" s="20"/>
       <c r="Z348" s="20"/>
     </row>
-    <row r="349" spans="1:26" ht="15.75" thickBot="1">
+    <row r="349" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A349" s="18">
         <v>348</v>
       </c>
@@ -19720,7 +19793,7 @@
         <v>45</v>
       </c>
       <c r="M349" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N349" s="20"/>
       <c r="O349" s="20"/>
@@ -19736,7 +19809,7 @@
       <c r="Y349" s="20"/>
       <c r="Z349" s="20"/>
     </row>
-    <row r="350" spans="1:26" ht="15.75" thickBot="1">
+    <row r="350" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A350" s="18">
         <v>349</v>
       </c>
@@ -19772,7 +19845,7 @@
         <v>45</v>
       </c>
       <c r="M350" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N350" s="20"/>
       <c r="O350" s="20"/>
@@ -19788,7 +19861,7 @@
       <c r="Y350" s="20"/>
       <c r="Z350" s="20"/>
     </row>
-    <row r="351" spans="1:26" ht="15.75" thickBot="1">
+    <row r="351" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A351" s="18">
         <v>350</v>
       </c>
@@ -19824,7 +19897,7 @@
         <v>45</v>
       </c>
       <c r="M351" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N351" s="20"/>
       <c r="O351" s="20"/>
@@ -19840,7 +19913,7 @@
       <c r="Y351" s="20"/>
       <c r="Z351" s="20"/>
     </row>
-    <row r="352" spans="1:26" ht="15.75" thickBot="1">
+    <row r="352" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A352" s="18">
         <v>351</v>
       </c>
@@ -19876,7 +19949,7 @@
         <v>45</v>
       </c>
       <c r="M352" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N352" s="20"/>
       <c r="O352" s="20"/>
@@ -19892,7 +19965,7 @@
       <c r="Y352" s="20"/>
       <c r="Z352" s="20"/>
     </row>
-    <row r="353" spans="1:26" ht="15.75" thickBot="1">
+    <row r="353" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A353" s="18">
         <v>352</v>
       </c>
@@ -19928,7 +20001,7 @@
         <v>45</v>
       </c>
       <c r="M353" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N353" s="20"/>
       <c r="O353" s="20"/>
@@ -19944,7 +20017,7 @@
       <c r="Y353" s="20"/>
       <c r="Z353" s="20"/>
     </row>
-    <row r="354" spans="1:26" ht="15.75" thickBot="1">
+    <row r="354" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A354" s="18">
         <v>353</v>
       </c>
@@ -19980,7 +20053,7 @@
         <v>45</v>
       </c>
       <c r="M354" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N354" s="20"/>
       <c r="O354" s="20"/>
@@ -19996,7 +20069,7 @@
       <c r="Y354" s="20"/>
       <c r="Z354" s="20"/>
     </row>
-    <row r="355" spans="1:26" ht="15.75" thickBot="1">
+    <row r="355" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A355" s="18">
         <v>354</v>
       </c>
@@ -20032,7 +20105,7 @@
         <v>45</v>
       </c>
       <c r="M355" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N355" s="20"/>
       <c r="O355" s="20"/>
@@ -20048,7 +20121,7 @@
       <c r="Y355" s="20"/>
       <c r="Z355" s="20"/>
     </row>
-    <row r="356" spans="1:26" ht="15.75" thickBot="1">
+    <row r="356" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A356" s="18">
         <v>355</v>
       </c>
@@ -20084,7 +20157,7 @@
         <v>45</v>
       </c>
       <c r="M356" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N356" s="20"/>
       <c r="O356" s="20"/>
@@ -20100,7 +20173,7 @@
       <c r="Y356" s="20"/>
       <c r="Z356" s="20"/>
     </row>
-    <row r="357" spans="1:26" ht="15.75" thickBot="1">
+    <row r="357" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A357" s="18">
         <v>356</v>
       </c>
@@ -20136,7 +20209,7 @@
         <v>45</v>
       </c>
       <c r="M357" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N357" s="20"/>
       <c r="O357" s="20"/>
@@ -20152,7 +20225,7 @@
       <c r="Y357" s="20"/>
       <c r="Z357" s="20"/>
     </row>
-    <row r="358" spans="1:26" ht="15.75" thickBot="1">
+    <row r="358" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A358" s="18">
         <v>357</v>
       </c>
@@ -20188,7 +20261,7 @@
         <v>45</v>
       </c>
       <c r="M358" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N358" s="20"/>
       <c r="O358" s="20"/>
@@ -20204,7 +20277,7 @@
       <c r="Y358" s="20"/>
       <c r="Z358" s="20"/>
     </row>
-    <row r="359" spans="1:26" ht="15.75" thickBot="1">
+    <row r="359" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A359" s="18">
         <v>358</v>
       </c>
@@ -20240,7 +20313,7 @@
         <v>45</v>
       </c>
       <c r="M359" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N359" s="20"/>
       <c r="O359" s="20"/>
@@ -20256,7 +20329,7 @@
       <c r="Y359" s="20"/>
       <c r="Z359" s="20"/>
     </row>
-    <row r="360" spans="1:26" ht="15.75" thickBot="1">
+    <row r="360" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A360" s="18">
         <v>359</v>
       </c>
@@ -20292,7 +20365,7 @@
         <v>45</v>
       </c>
       <c r="M360" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N360" s="20"/>
       <c r="O360" s="20"/>
@@ -20308,7 +20381,7 @@
       <c r="Y360" s="20"/>
       <c r="Z360" s="20"/>
     </row>
-    <row r="361" spans="1:26" ht="15.75" thickBot="1">
+    <row r="361" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A361" s="18">
         <v>360</v>
       </c>
@@ -20344,7 +20417,7 @@
         <v>45</v>
       </c>
       <c r="M361" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N361" s="20"/>
       <c r="O361" s="20"/>
@@ -20360,7 +20433,7 @@
       <c r="Y361" s="20"/>
       <c r="Z361" s="20"/>
     </row>
-    <row r="362" spans="1:26" ht="15.75" thickBot="1">
+    <row r="362" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A362" s="18">
         <v>361</v>
       </c>
@@ -20396,7 +20469,7 @@
         <v>45</v>
       </c>
       <c r="M362" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N362" s="20"/>
       <c r="O362" s="20"/>
@@ -20412,7 +20485,7 @@
       <c r="Y362" s="20"/>
       <c r="Z362" s="20"/>
     </row>
-    <row r="363" spans="1:26" ht="15.75" thickBot="1">
+    <row r="363" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A363" s="18">
         <v>362</v>
       </c>
@@ -20448,7 +20521,7 @@
         <v>45</v>
       </c>
       <c r="M363" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N363" s="20"/>
       <c r="O363" s="20"/>
@@ -20464,7 +20537,7 @@
       <c r="Y363" s="20"/>
       <c r="Z363" s="20"/>
     </row>
-    <row r="364" spans="1:26" ht="15.75" thickBot="1">
+    <row r="364" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A364" s="18">
         <v>363</v>
       </c>
@@ -20500,7 +20573,7 @@
         <v>45</v>
       </c>
       <c r="M364" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N364" s="20"/>
       <c r="O364" s="20"/>
@@ -20516,7 +20589,7 @@
       <c r="Y364" s="20"/>
       <c r="Z364" s="20"/>
     </row>
-    <row r="365" spans="1:26" ht="15.75" thickBot="1">
+    <row r="365" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A365" s="18">
         <v>364</v>
       </c>
@@ -20552,7 +20625,7 @@
         <v>45</v>
       </c>
       <c r="M365" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N365" s="20"/>
       <c r="O365" s="20"/>
@@ -20568,7 +20641,7 @@
       <c r="Y365" s="20"/>
       <c r="Z365" s="20"/>
     </row>
-    <row r="366" spans="1:26" ht="15.75" thickBot="1">
+    <row r="366" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A366" s="18">
         <v>365</v>
       </c>
@@ -20604,7 +20677,7 @@
         <v>45</v>
       </c>
       <c r="M366" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N366" s="20"/>
       <c r="O366" s="20"/>
@@ -20620,7 +20693,7 @@
       <c r="Y366" s="20"/>
       <c r="Z366" s="20"/>
     </row>
-    <row r="367" spans="1:26" ht="15.75" thickBot="1">
+    <row r="367" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A367" s="18">
         <v>366</v>
       </c>
@@ -20656,7 +20729,7 @@
         <v>45</v>
       </c>
       <c r="M367" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N367" s="20"/>
       <c r="O367" s="20"/>
@@ -20672,7 +20745,7 @@
       <c r="Y367" s="20"/>
       <c r="Z367" s="20"/>
     </row>
-    <row r="368" spans="1:26" ht="15.75" thickBot="1">
+    <row r="368" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A368" s="18">
         <v>367</v>
       </c>
@@ -20708,7 +20781,7 @@
         <v>45</v>
       </c>
       <c r="M368" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N368" s="20"/>
       <c r="O368" s="20"/>
@@ -20724,7 +20797,7 @@
       <c r="Y368" s="20"/>
       <c r="Z368" s="20"/>
     </row>
-    <row r="369" spans="1:26" ht="15.75" thickBot="1">
+    <row r="369" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A369" s="18">
         <v>368</v>
       </c>
@@ -20760,7 +20833,7 @@
         <v>45</v>
       </c>
       <c r="M369" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N369" s="20"/>
       <c r="O369" s="20"/>
@@ -20776,7 +20849,7 @@
       <c r="Y369" s="20"/>
       <c r="Z369" s="20"/>
     </row>
-    <row r="370" spans="1:26" ht="15.75" thickBot="1">
+    <row r="370" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A370" s="18">
         <v>369</v>
       </c>
@@ -20812,7 +20885,7 @@
         <v>45</v>
       </c>
       <c r="M370" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N370" s="20"/>
       <c r="O370" s="20"/>
@@ -20828,7 +20901,7 @@
       <c r="Y370" s="20"/>
       <c r="Z370" s="20"/>
     </row>
-    <row r="371" spans="1:26" ht="15.75" thickBot="1">
+    <row r="371" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A371" s="18">
         <v>370</v>
       </c>
@@ -20864,7 +20937,7 @@
         <v>45</v>
       </c>
       <c r="M371" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N371" s="20"/>
       <c r="O371" s="20"/>
@@ -20880,7 +20953,7 @@
       <c r="Y371" s="20"/>
       <c r="Z371" s="20"/>
     </row>
-    <row r="372" spans="1:26" ht="15.75" thickBot="1">
+    <row r="372" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A372" s="18">
         <v>371</v>
       </c>
@@ -20916,7 +20989,7 @@
         <v>45</v>
       </c>
       <c r="M372" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N372" s="20"/>
       <c r="O372" s="20"/>
@@ -20932,7 +21005,7 @@
       <c r="Y372" s="20"/>
       <c r="Z372" s="20"/>
     </row>
-    <row r="373" spans="1:26" ht="15.75" thickBot="1">
+    <row r="373" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A373" s="18">
         <v>372</v>
       </c>
@@ -20968,7 +21041,7 @@
         <v>45</v>
       </c>
       <c r="M373" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N373" s="20"/>
       <c r="O373" s="20"/>
@@ -20984,7 +21057,7 @@
       <c r="Y373" s="20"/>
       <c r="Z373" s="20"/>
     </row>
-    <row r="374" spans="1:26" ht="15.75" thickBot="1">
+    <row r="374" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A374" s="18">
         <v>373</v>
       </c>
@@ -21020,7 +21093,7 @@
         <v>45</v>
       </c>
       <c r="M374" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N374" s="20"/>
       <c r="O374" s="20"/>
@@ -21036,7 +21109,7 @@
       <c r="Y374" s="20"/>
       <c r="Z374" s="20"/>
     </row>
-    <row r="375" spans="1:26" ht="15.75" thickBot="1">
+    <row r="375" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A375" s="18">
         <v>374</v>
       </c>
@@ -21072,7 +21145,7 @@
         <v>45</v>
       </c>
       <c r="M375" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N375" s="20"/>
       <c r="O375" s="20"/>
@@ -21088,7 +21161,7 @@
       <c r="Y375" s="20"/>
       <c r="Z375" s="20"/>
     </row>
-    <row r="376" spans="1:26" ht="15.75" thickBot="1">
+    <row r="376" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A376" s="18">
         <v>375</v>
       </c>
@@ -21124,7 +21197,7 @@
         <v>45</v>
       </c>
       <c r="M376" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N376" s="20"/>
       <c r="O376" s="20"/>
@@ -21140,7 +21213,7 @@
       <c r="Y376" s="20"/>
       <c r="Z376" s="20"/>
     </row>
-    <row r="377" spans="1:26" ht="15.75" thickBot="1">
+    <row r="377" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A377" s="18">
         <v>376</v>
       </c>
@@ -21176,7 +21249,7 @@
         <v>45</v>
       </c>
       <c r="M377" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N377" s="20"/>
       <c r="O377" s="20"/>
@@ -21192,7 +21265,7 @@
       <c r="Y377" s="20"/>
       <c r="Z377" s="20"/>
     </row>
-    <row r="378" spans="1:26" ht="27" thickBot="1">
+    <row r="378" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A378" s="18">
         <v>377</v>
       </c>
@@ -21228,7 +21301,7 @@
         <v>45</v>
       </c>
       <c r="M378" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N378" s="20"/>
       <c r="O378" s="20"/>
@@ -21244,7 +21317,7 @@
       <c r="Y378" s="20"/>
       <c r="Z378" s="20"/>
     </row>
-    <row r="379" spans="1:26" ht="27" thickBot="1">
+    <row r="379" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A379" s="18">
         <v>378</v>
       </c>
@@ -21280,7 +21353,7 @@
         <v>45</v>
       </c>
       <c r="M379" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N379" s="20"/>
       <c r="O379" s="20"/>
@@ -21296,7 +21369,7 @@
       <c r="Y379" s="20"/>
       <c r="Z379" s="20"/>
     </row>
-    <row r="380" spans="1:26" ht="27" thickBot="1">
+    <row r="380" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A380" s="18">
         <v>379</v>
       </c>
@@ -21332,7 +21405,7 @@
         <v>45</v>
       </c>
       <c r="M380" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N380" s="20"/>
       <c r="O380" s="20"/>
@@ -21348,7 +21421,7 @@
       <c r="Y380" s="20"/>
       <c r="Z380" s="20"/>
     </row>
-    <row r="381" spans="1:26" ht="27" thickBot="1">
+    <row r="381" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A381" s="18">
         <v>380</v>
       </c>
@@ -21384,7 +21457,7 @@
         <v>45</v>
       </c>
       <c r="M381" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N381" s="20"/>
       <c r="O381" s="20"/>
@@ -21400,7 +21473,7 @@
       <c r="Y381" s="20"/>
       <c r="Z381" s="20"/>
     </row>
-    <row r="382" spans="1:26" ht="27" thickBot="1">
+    <row r="382" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A382" s="18">
         <v>381</v>
       </c>
@@ -21436,7 +21509,7 @@
         <v>45</v>
       </c>
       <c r="M382" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N382" s="20"/>
       <c r="O382" s="20"/>
@@ -21452,7 +21525,7 @@
       <c r="Y382" s="20"/>
       <c r="Z382" s="20"/>
     </row>
-    <row r="383" spans="1:26" ht="27" thickBot="1">
+    <row r="383" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A383" s="18">
         <v>382</v>
       </c>
@@ -21488,7 +21561,7 @@
         <v>45</v>
       </c>
       <c r="M383" s="36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N383" s="20"/>
       <c r="O383" s="20"/>
@@ -21504,7 +21577,7 @@
       <c r="Y383" s="20"/>
       <c r="Z383" s="20"/>
     </row>
-    <row r="384" spans="1:26" ht="15.75" thickBot="1">
+    <row r="384" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A384" s="18">
         <v>383</v>
       </c>
@@ -21558,7 +21631,7 @@
       <c r="Y384" s="20"/>
       <c r="Z384" s="20"/>
     </row>
-    <row r="385" spans="1:26" ht="15.75" thickBot="1">
+    <row r="385" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A385" s="18">
         <v>384</v>
       </c>
@@ -21612,7 +21685,7 @@
       <c r="Y385" s="20"/>
       <c r="Z385" s="20"/>
     </row>
-    <row r="386" spans="1:26" ht="15.75" thickBot="1">
+    <row r="386" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A386" s="18">
         <v>385</v>
       </c>
@@ -21666,7 +21739,7 @@
       <c r="Y386" s="20"/>
       <c r="Z386" s="20"/>
     </row>
-    <row r="387" spans="1:26" ht="15.75" thickBot="1">
+    <row r="387" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A387" s="18">
         <v>386</v>
       </c>
@@ -21720,7 +21793,7 @@
       <c r="Y387" s="20"/>
       <c r="Z387" s="20"/>
     </row>
-    <row r="388" spans="1:26" ht="15.75" thickBot="1">
+    <row r="388" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A388" s="18">
         <v>387</v>
       </c>
@@ -21774,7 +21847,7 @@
       <c r="Y388" s="20"/>
       <c r="Z388" s="20"/>
     </row>
-    <row r="389" spans="1:26" ht="15.75" thickBot="1">
+    <row r="389" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A389" s="18">
         <v>388</v>
       </c>
@@ -21828,7 +21901,7 @@
       <c r="Y389" s="20"/>
       <c r="Z389" s="20"/>
     </row>
-    <row r="390" spans="1:26" ht="15.75" thickBot="1">
+    <row r="390" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A390" s="18">
         <v>389</v>
       </c>
@@ -21864,7 +21937,7 @@
         <v>45</v>
       </c>
       <c r="M390" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N390" s="20"/>
       <c r="O390" s="20"/>
@@ -21880,7 +21953,7 @@
       <c r="Y390" s="20"/>
       <c r="Z390" s="20"/>
     </row>
-    <row r="391" spans="1:26" ht="15.75" thickBot="1">
+    <row r="391" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A391" s="18">
         <v>390</v>
       </c>
@@ -21914,7 +21987,7 @@
         <v>45</v>
       </c>
       <c r="M391" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N391" s="20"/>
       <c r="O391" s="20"/>
@@ -21930,7 +22003,7 @@
       <c r="Y391" s="20"/>
       <c r="Z391" s="20"/>
     </row>
-    <row r="392" spans="1:26" ht="15.75" thickBot="1">
+    <row r="392" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A392" s="18">
         <v>391</v>
       </c>
@@ -21966,7 +22039,7 @@
         <v>45</v>
       </c>
       <c r="M392" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N392" s="20"/>
       <c r="O392" s="20"/>
@@ -21982,7 +22055,7 @@
       <c r="Y392" s="20"/>
       <c r="Z392" s="20"/>
     </row>
-    <row r="393" spans="1:26" ht="15.75" thickBot="1">
+    <row r="393" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A393" s="18">
         <v>392</v>
       </c>
@@ -22018,7 +22091,7 @@
         <v>45</v>
       </c>
       <c r="M393" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N393" s="20"/>
       <c r="O393" s="20"/>
@@ -22034,7 +22107,7 @@
       <c r="Y393" s="20"/>
       <c r="Z393" s="20"/>
     </row>
-    <row r="394" spans="1:26" ht="15.75" thickBot="1">
+    <row r="394" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A394" s="18">
         <v>393</v>
       </c>
@@ -22068,7 +22141,7 @@
         <v>45</v>
       </c>
       <c r="M394" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N394" s="20"/>
       <c r="O394" s="20"/>
@@ -22084,7 +22157,7 @@
       <c r="Y394" s="20"/>
       <c r="Z394" s="20"/>
     </row>
-    <row r="395" spans="1:26" ht="15.75" thickBot="1">
+    <row r="395" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A395" s="18">
         <v>394</v>
       </c>
@@ -22118,7 +22191,7 @@
         <v>45</v>
       </c>
       <c r="M395" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N395" s="20"/>
       <c r="O395" s="20"/>
@@ -22134,7 +22207,7 @@
       <c r="Y395" s="20"/>
       <c r="Z395" s="20"/>
     </row>
-    <row r="396" spans="1:26" ht="15.75" thickBot="1">
+    <row r="396" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A396" s="18">
         <v>395</v>
       </c>
@@ -22168,7 +22241,7 @@
         <v>45</v>
       </c>
       <c r="M396" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N396" s="20"/>
       <c r="O396" s="20"/>
@@ -22184,7 +22257,7 @@
       <c r="Y396" s="20"/>
       <c r="Z396" s="20"/>
     </row>
-    <row r="397" spans="1:26" ht="15.75" thickBot="1">
+    <row r="397" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A397" s="18">
         <v>396</v>
       </c>
@@ -22222,7 +22295,7 @@
         <v>45</v>
       </c>
       <c r="M397" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N397" s="20"/>
       <c r="O397" s="20"/>
@@ -22238,7 +22311,7 @@
       <c r="Y397" s="20"/>
       <c r="Z397" s="20"/>
     </row>
-    <row r="398" spans="1:26" ht="15.75" thickBot="1">
+    <row r="398" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A398" s="18">
         <v>397</v>
       </c>
@@ -22276,7 +22349,7 @@
         <v>45</v>
       </c>
       <c r="M398" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N398" s="20"/>
       <c r="O398" s="20"/>
@@ -22292,7 +22365,7 @@
       <c r="Y398" s="20"/>
       <c r="Z398" s="20"/>
     </row>
-    <row r="399" spans="1:26" ht="15.75" thickBot="1">
+    <row r="399" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A399" s="18">
         <v>398</v>
       </c>
@@ -22328,7 +22401,7 @@
         <v>45</v>
       </c>
       <c r="M399" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N399" s="20"/>
       <c r="O399" s="20"/>
@@ -22344,7 +22417,7 @@
       <c r="Y399" s="20"/>
       <c r="Z399" s="20"/>
     </row>
-    <row r="400" spans="1:26" ht="15.75" thickBot="1">
+    <row r="400" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A400" s="18">
         <v>399</v>
       </c>
@@ -22380,7 +22453,7 @@
         <v>45</v>
       </c>
       <c r="M400" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N400" s="20"/>
       <c r="O400" s="20"/>
@@ -22396,7 +22469,7 @@
       <c r="Y400" s="20"/>
       <c r="Z400" s="20"/>
     </row>
-    <row r="401" spans="1:26" ht="15.75" thickBot="1">
+    <row r="401" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A401" s="18">
         <v>400</v>
       </c>
@@ -22432,7 +22505,7 @@
         <v>45</v>
       </c>
       <c r="M401" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N401" s="20"/>
       <c r="O401" s="20"/>
@@ -22448,7 +22521,7 @@
       <c r="Y401" s="20"/>
       <c r="Z401" s="20"/>
     </row>
-    <row r="402" spans="1:26" ht="15.75" thickBot="1">
+    <row r="402" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A402" s="18">
         <v>401</v>
       </c>
@@ -22484,7 +22557,7 @@
         <v>45</v>
       </c>
       <c r="M402" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N402" s="20"/>
       <c r="O402" s="20"/>
@@ -22500,7 +22573,7 @@
       <c r="Y402" s="20"/>
       <c r="Z402" s="20"/>
     </row>
-    <row r="403" spans="1:26" ht="15.75" thickBot="1">
+    <row r="403" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A403" s="18">
         <v>402</v>
       </c>
@@ -22536,7 +22609,7 @@
         <v>45</v>
       </c>
       <c r="M403" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N403" s="20"/>
       <c r="O403" s="20"/>
@@ -22552,12 +22625,12 @@
       <c r="Y403" s="20"/>
       <c r="Z403" s="20"/>
     </row>
-    <row r="404" spans="1:26" ht="27" thickBot="1">
+    <row r="404" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A404" s="18">
         <v>403</v>
       </c>
       <c r="B404" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C404" s="22" t="s">
         <v>34</v>
@@ -22578,7 +22651,7 @@
         <v>65</v>
       </c>
       <c r="I404" s="22" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J404" s="40">
         <v>36891870</v>
@@ -22590,7 +22663,7 @@
         <v>45</v>
       </c>
       <c r="M404" s="36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N404" s="20"/>
       <c r="O404" s="20"/>
@@ -22606,12 +22679,12 @@
       <c r="Y404" s="20"/>
       <c r="Z404" s="20"/>
     </row>
-    <row r="405" spans="1:26" ht="27" thickBot="1">
+    <row r="405" spans="1:26" ht="27" hidden="1" thickBot="1">
       <c r="A405" s="18">
         <v>404</v>
       </c>
       <c r="B405" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C405" s="22" t="s">
         <v>81</v>
@@ -22632,7 +22705,7 @@
         <v>65</v>
       </c>
       <c r="I405" s="22" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J405" s="40">
         <v>36891870</v>
@@ -22644,7 +22717,7 @@
         <v>45</v>
       </c>
       <c r="M405" s="36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N405" s="20"/>
       <c r="O405" s="20"/>
@@ -22660,7 +22733,7 @@
       <c r="Y405" s="20"/>
       <c r="Z405" s="20"/>
     </row>
-    <row r="406" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
+    <row r="406" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
       <c r="A406" s="18">
         <v>405</v>
       </c>
@@ -22698,10 +22771,10 @@
         <v>45</v>
       </c>
       <c r="M406" s="51" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N406" s="52" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O406" s="52"/>
       <c r="P406" s="52"/>
@@ -22716,7 +22789,7 @@
       <c r="Y406" s="52"/>
       <c r="Z406" s="52"/>
     </row>
-    <row r="407" spans="1:26" ht="15.75" thickBot="1">
+    <row r="407" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A407" s="18">
         <v>406</v>
       </c>
@@ -22754,7 +22827,7 @@
         <v>45</v>
       </c>
       <c r="M407" s="36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N407" s="20"/>
       <c r="O407" s="20"/>
@@ -22770,7 +22843,7 @@
       <c r="Y407" s="20"/>
       <c r="Z407" s="20"/>
     </row>
-    <row r="408" spans="1:26" ht="15.75" thickBot="1">
+    <row r="408" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A408" s="18">
         <v>407</v>
       </c>
@@ -22808,7 +22881,7 @@
         <v>45</v>
       </c>
       <c r="M408" s="36" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="N408" s="20"/>
       <c r="O408" s="20"/>
@@ -22824,7 +22897,7 @@
       <c r="Y408" s="20"/>
       <c r="Z408" s="20"/>
     </row>
-    <row r="409" spans="1:26" ht="15.75" thickBot="1">
+    <row r="409" spans="1:26" ht="15.75" hidden="1" thickBot="1">
       <c r="A409" s="18">
         <v>408</v>
       </c>
@@ -22862,7 +22935,7 @@
         <v>45</v>
       </c>
       <c r="M409" s="36" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N409" s="20"/>
       <c r="O409" s="20"/>
@@ -22878,8 +22951,281 @@
       <c r="Y409" s="20"/>
       <c r="Z409" s="20"/>
     </row>
+    <row r="410" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+      <c r="A410" s="18">
+        <v>409</v>
+      </c>
+      <c r="B410" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C410" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D410" s="21">
+        <v>44</v>
+      </c>
+      <c r="E410" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F410" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G410" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H410" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="I410" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="J410" s="40">
+        <v>25264167</v>
+      </c>
+      <c r="K410" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L410" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="M410" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="N410" s="20"/>
+      <c r="O410" s="20"/>
+      <c r="P410" s="20"/>
+      <c r="Q410" s="20"/>
+      <c r="R410" s="20"/>
+      <c r="S410" s="20"/>
+      <c r="T410" s="20"/>
+      <c r="U410" s="20"/>
+      <c r="V410" s="20"/>
+      <c r="W410" s="20"/>
+      <c r="X410" s="20"/>
+      <c r="Y410" s="20"/>
+      <c r="Z410" s="20"/>
+    </row>
+    <row r="411" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+      <c r="A411" s="18">
+        <v>410</v>
+      </c>
+      <c r="B411" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C411" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D411" s="21">
+        <v>304</v>
+      </c>
+      <c r="E411" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F411" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G411" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H411" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="I411" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="J411" s="40">
+        <v>25264167</v>
+      </c>
+      <c r="K411" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L411" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="M411" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="N411" s="20"/>
+      <c r="O411" s="20"/>
+      <c r="P411" s="20"/>
+      <c r="Q411" s="20"/>
+      <c r="R411" s="20"/>
+      <c r="S411" s="20"/>
+      <c r="T411" s="20"/>
+      <c r="U411" s="20"/>
+      <c r="V411" s="20"/>
+      <c r="W411" s="20"/>
+      <c r="X411" s="20"/>
+      <c r="Y411" s="20"/>
+      <c r="Z411" s="20"/>
+    </row>
+    <row r="412" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+      <c r="A412" s="18">
+        <v>411</v>
+      </c>
+      <c r="B412" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="C412" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D412" s="58">
+        <v>40</v>
+      </c>
+      <c r="E412" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F412" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="G412" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H412" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="I412" s="59"/>
+      <c r="J412" s="40">
+        <v>18398509</v>
+      </c>
+      <c r="K412" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L412" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="M412" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="N412" s="20"/>
+      <c r="O412" s="20"/>
+      <c r="P412" s="20"/>
+      <c r="Q412" s="20"/>
+      <c r="R412" s="20"/>
+      <c r="S412" s="20"/>
+      <c r="T412" s="20"/>
+      <c r="U412" s="20"/>
+      <c r="V412" s="20"/>
+      <c r="W412" s="20"/>
+      <c r="X412" s="20"/>
+      <c r="Y412" s="20"/>
+      <c r="Z412" s="20"/>
+    </row>
+    <row r="413" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+      <c r="A413" s="18">
+        <v>412</v>
+      </c>
+      <c r="B413" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C413" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D413" s="61">
+        <v>41</v>
+      </c>
+      <c r="E413" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F413" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G413" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H413" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="I413" s="62"/>
+      <c r="J413" s="40">
+        <v>18398509</v>
+      </c>
+      <c r="K413" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L413" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="M413" s="64" t="s">
+        <v>257</v>
+      </c>
+      <c r="N413" s="20"/>
+      <c r="O413" s="20"/>
+      <c r="P413" s="20"/>
+      <c r="Q413" s="20"/>
+      <c r="R413" s="20"/>
+      <c r="S413" s="20"/>
+      <c r="T413" s="20"/>
+      <c r="U413" s="20"/>
+      <c r="V413" s="20"/>
+      <c r="W413" s="20"/>
+      <c r="X413" s="20"/>
+      <c r="Y413" s="20"/>
+      <c r="Z413" s="20"/>
+    </row>
+    <row r="414" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+      <c r="A414" s="18">
+        <v>413</v>
+      </c>
+      <c r="B414" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C414" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D414" s="61">
+        <v>43</v>
+      </c>
+      <c r="E414" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="F414" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="G414" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H414" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="I414" s="62"/>
+      <c r="J414" s="40">
+        <v>18398509</v>
+      </c>
+      <c r="K414" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="L414" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="M414" s="63" t="s">
+        <v>257</v>
+      </c>
+      <c r="N414" s="20"/>
+      <c r="O414" s="20"/>
+      <c r="P414" s="20"/>
+      <c r="Q414" s="20"/>
+      <c r="R414" s="20"/>
+      <c r="S414" s="20"/>
+      <c r="T414" s="20"/>
+      <c r="U414" s="20"/>
+      <c r="V414" s="20"/>
+      <c r="W414" s="20"/>
+      <c r="X414" s="20"/>
+      <c r="Y414" s="20"/>
+      <c r="Z414" s="20"/>
+    </row>
+    <row r="415" spans="1:26" ht="15.75" thickBot="1">
+      <c r="K415" s="22"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M345" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M414" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="LOF/GOF"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M7" r:id="rId1" xr:uid="{87A5E94E-2CC0-43A2-A62B-F1F66B9F07E8}"/>
@@ -23290,8 +23636,13 @@
     <hyperlink ref="M407" r:id="rId406" xr:uid="{5023AAC8-A13C-40E8-B69B-3EACC32D3930}"/>
     <hyperlink ref="M408" r:id="rId407" xr:uid="{8C911905-77BA-4210-8CC8-8976ED75344B}"/>
     <hyperlink ref="M409" r:id="rId408" xr:uid="{75537FBC-6EB9-4488-BE83-4F559D4C28DC}"/>
+    <hyperlink ref="M410" r:id="rId409" xr:uid="{285AE8CC-4E92-4B8E-AA88-69E524DCE719}"/>
+    <hyperlink ref="M411" r:id="rId410" xr:uid="{E0B29D79-3645-4C58-A6CE-AB9ED4C3EECF}"/>
+    <hyperlink ref="M412" r:id="rId411" xr:uid="{365A4292-70EB-4884-A834-7442943134EE}"/>
+    <hyperlink ref="M413" r:id="rId412" xr:uid="{A2234747-BF8D-406A-9BE2-17B6A045EE53}"/>
+    <hyperlink ref="M414" r:id="rId413" xr:uid="{146AE2B4-2AE8-410E-B2E7-1FFA7ECE6501}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId409"/>
+  <pageSetup orientation="portrait" r:id="rId414"/>
 </worksheet>
 </file>
--- a/nachr_db_manual.xlsx
+++ b/nachr_db_manual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\Downloads\Computational Chemistry\Variant-Effect-Predictor-for-nAChRs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223EBA5C-FCBD-4C3E-83B0-C865A5A59CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1915D2FD-A4B9-43B1-8D4D-439971672D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24180" yWindow="2220" windowWidth="18165" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7575" yWindow="3495" windowWidth="18165" windowHeight="10290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1459,7 +1459,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z415"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -1520,7 +1519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="2" spans="1:26" ht="15.75" thickBot="1">
       <c r="A2" s="18">
         <v>1</v>
       </c>
@@ -1572,7 +1571,7 @@
       <c r="Y2" s="20"/>
       <c r="Z2" s="20"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="3" spans="1:26" ht="15.75" thickBot="1">
       <c r="A3" s="18">
         <v>2</v>
       </c>
@@ -1624,7 +1623,7 @@
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="4" spans="1:26" ht="15.75" thickBot="1">
       <c r="A4" s="18">
         <v>3</v>
       </c>
@@ -1674,7 +1673,7 @@
       <c r="Y4" s="20"/>
       <c r="Z4" s="20"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="5" spans="1:26" ht="15.75" thickBot="1">
       <c r="A5" s="18">
         <v>4</v>
       </c>
@@ -1724,7 +1723,7 @@
       <c r="Y5" s="20"/>
       <c r="Z5" s="20"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="6" spans="1:26" ht="15.75" thickBot="1">
       <c r="A6" s="18">
         <v>5</v>
       </c>
@@ -2220,7 +2219,7 @@
       <c r="Y15" s="25"/>
       <c r="Z15" s="25"/>
     </row>
-    <row r="16" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="16" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A16" s="18">
         <v>15</v>
       </c>
@@ -2261,7 +2260,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="11" customFormat="1" ht="17.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="17" spans="1:26" s="11" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
       <c r="A17" s="18">
         <v>16</v>
       </c>
@@ -2302,7 +2301,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="18" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A18" s="18">
         <v>17</v>
       </c>
@@ -2343,7 +2342,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="19" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A19" s="18">
         <v>18</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="20" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A20" s="18">
         <v>19</v>
       </c>
@@ -2431,7 +2430,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="21" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A21" s="18">
         <v>20</v>
       </c>
@@ -2472,7 +2471,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="22" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A22" s="18">
         <v>21</v>
       </c>
@@ -2511,7 +2510,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="23" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A23" s="18">
         <v>22</v>
       </c>
@@ -2552,7 +2551,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="24" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A24" s="18">
         <v>23</v>
       </c>
@@ -2593,7 +2592,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="25" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A25" s="18">
         <v>24</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="26" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A26" s="18">
         <v>25</v>
       </c>
@@ -2675,7 +2674,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="27" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A27" s="18">
         <v>26</v>
       </c>
@@ -2716,7 +2715,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="28" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A28" s="18">
         <v>27</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="29" spans="1:26" s="8" customFormat="1" ht="15.75" thickBot="1">
       <c r="A29" s="18">
         <v>28</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="30" spans="1:26" ht="15.75" thickBot="1">
       <c r="A30" s="18">
         <v>29</v>
       </c>
@@ -2851,7 +2850,7 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="31" spans="1:26" ht="15.75" thickBot="1">
       <c r="A31" s="18">
         <v>30</v>
       </c>
@@ -2905,7 +2904,7 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="32" spans="1:26" ht="15.75" thickBot="1">
       <c r="A32" s="18">
         <v>31</v>
       </c>
@@ -2959,7 +2958,7 @@
       <c r="Y32" s="17"/>
       <c r="Z32" s="17"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="33" spans="1:26" ht="15.75" thickBot="1">
       <c r="A33" s="18">
         <v>32</v>
       </c>
@@ -3011,7 +3010,7 @@
       <c r="Y33" s="17"/>
       <c r="Z33" s="17"/>
     </row>
-    <row r="34" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="34" spans="1:26" ht="39.75" thickBot="1">
       <c r="A34" s="18">
         <v>33</v>
       </c>
@@ -3065,7 +3064,7 @@
       <c r="Y34" s="17"/>
       <c r="Z34" s="17"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="35" spans="1:26" ht="15.75" thickBot="1">
       <c r="A35" s="18">
         <v>34</v>
       </c>
@@ -3117,7 +3116,7 @@
       <c r="Y35" s="20"/>
       <c r="Z35" s="20"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="36" spans="1:26" ht="15.75" thickBot="1">
       <c r="A36" s="18">
         <v>35</v>
       </c>
@@ -3169,7 +3168,7 @@
       <c r="Y36" s="20"/>
       <c r="Z36" s="20"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="37" spans="1:26" ht="15.75" thickBot="1">
       <c r="A37" s="18">
         <v>36</v>
       </c>
@@ -3221,7 +3220,7 @@
       <c r="Y37" s="20"/>
       <c r="Z37" s="20"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="38" spans="1:26" ht="15.75" thickBot="1">
       <c r="A38" s="18">
         <v>37</v>
       </c>
@@ -3273,7 +3272,7 @@
       <c r="Y38" s="20"/>
       <c r="Z38" s="20"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="39" spans="1:26" ht="15.75" thickBot="1">
       <c r="A39" s="18">
         <v>38</v>
       </c>
@@ -3325,7 +3324,7 @@
       <c r="Y39" s="20"/>
       <c r="Z39" s="20"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="40" spans="1:26" ht="15.75" thickBot="1">
       <c r="A40" s="18">
         <v>39</v>
       </c>
@@ -3377,7 +3376,7 @@
       <c r="Y40" s="20"/>
       <c r="Z40" s="20"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="41" spans="1:26" ht="15.75" thickBot="1">
       <c r="A41" s="18">
         <v>40</v>
       </c>
@@ -3429,7 +3428,7 @@
       <c r="Y41" s="20"/>
       <c r="Z41" s="20"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="42" spans="1:26" ht="15.75" thickBot="1">
       <c r="A42" s="18">
         <v>41</v>
       </c>
@@ -3481,7 +3480,7 @@
       <c r="Y42" s="20"/>
       <c r="Z42" s="20"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="43" spans="1:26" ht="15.75" thickBot="1">
       <c r="A43" s="18">
         <v>42</v>
       </c>
@@ -3533,7 +3532,7 @@
       <c r="Y43" s="20"/>
       <c r="Z43" s="20"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="44" spans="1:26" ht="15.75" thickBot="1">
       <c r="A44" s="18">
         <v>43</v>
       </c>
@@ -3585,7 +3584,7 @@
       <c r="Y44" s="20"/>
       <c r="Z44" s="20"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="45" spans="1:26" ht="15.75" thickBot="1">
       <c r="A45" s="18">
         <v>44</v>
       </c>
@@ -3637,7 +3636,7 @@
       <c r="Y45" s="20"/>
       <c r="Z45" s="20"/>
     </row>
-    <row r="46" spans="1:26" s="7" customFormat="1" ht="30.75" hidden="1" thickBot="1">
+    <row r="46" spans="1:26" s="7" customFormat="1" ht="30.75" thickBot="1">
       <c r="A46" s="18">
         <v>45</v>
       </c>
@@ -3693,7 +3692,7 @@
       <c r="Y46" s="25"/>
       <c r="Z46" s="25"/>
     </row>
-    <row r="47" spans="1:26" s="7" customFormat="1" ht="27" hidden="1" thickBot="1">
+    <row r="47" spans="1:26" s="7" customFormat="1" ht="27" thickBot="1">
       <c r="A47" s="18">
         <v>46</v>
       </c>
@@ -3747,7 +3746,7 @@
       <c r="Y47" s="25"/>
       <c r="Z47" s="25"/>
     </row>
-    <row r="48" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="48" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
       <c r="A48" s="18">
         <v>47</v>
       </c>
@@ -3801,7 +3800,7 @@
       <c r="Y48" s="25"/>
       <c r="Z48" s="25"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="49" spans="1:26" ht="15.75" thickBot="1">
       <c r="A49" s="18">
         <v>48</v>
       </c>
@@ -3855,7 +3854,7 @@
       <c r="Y49" s="20"/>
       <c r="Z49" s="20"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="50" spans="1:26" ht="15.75" thickBot="1">
       <c r="A50" s="18">
         <v>49</v>
       </c>
@@ -3909,7 +3908,7 @@
       <c r="Y50" s="20"/>
       <c r="Z50" s="20"/>
     </row>
-    <row r="51" spans="1:26" s="7" customFormat="1" ht="27" hidden="1" thickBot="1">
+    <row r="51" spans="1:26" s="7" customFormat="1" ht="27" thickBot="1">
       <c r="A51" s="18">
         <v>50</v>
       </c>
@@ -3965,7 +3964,7 @@
       <c r="Y51" s="25"/>
       <c r="Z51" s="25"/>
     </row>
-    <row r="52" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="52" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
       <c r="A52" s="18">
         <v>51</v>
       </c>
@@ -4019,7 +4018,7 @@
       <c r="Y52" s="25"/>
       <c r="Z52" s="25"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="53" spans="1:26" ht="15.75" thickBot="1">
       <c r="A53" s="18">
         <v>52</v>
       </c>
@@ -4073,7 +4072,7 @@
       <c r="Y53" s="20"/>
       <c r="Z53" s="20"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="54" spans="1:26" ht="15.75" thickBot="1">
       <c r="A54" s="18">
         <v>53</v>
       </c>
@@ -4127,7 +4126,7 @@
       <c r="Y54" s="20"/>
       <c r="Z54" s="20"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="55" spans="1:26" ht="15.75" thickBot="1">
       <c r="A55" s="18">
         <v>54</v>
       </c>
@@ -4181,7 +4180,7 @@
       <c r="Y55" s="20"/>
       <c r="Z55" s="20"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="56" spans="1:26" ht="15.75" thickBot="1">
       <c r="A56" s="18">
         <v>55</v>
       </c>
@@ -4233,7 +4232,7 @@
       <c r="Y56" s="20"/>
       <c r="Z56" s="20"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="57" spans="1:26" ht="15.75" thickBot="1">
       <c r="A57" s="18">
         <v>56</v>
       </c>
@@ -4287,7 +4286,7 @@
       <c r="Y57" s="20"/>
       <c r="Z57" s="20"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="58" spans="1:26" ht="15.75" thickBot="1">
       <c r="A58" s="18">
         <v>57</v>
       </c>
@@ -4341,7 +4340,7 @@
       <c r="Y58" s="20"/>
       <c r="Z58" s="20"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="59" spans="1:26" ht="15.75" thickBot="1">
       <c r="A59" s="18">
         <v>58</v>
       </c>
@@ -4395,7 +4394,7 @@
       <c r="Y59" s="20"/>
       <c r="Z59" s="20"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="60" spans="1:26" ht="15.75" thickBot="1">
       <c r="A60" s="18">
         <v>59</v>
       </c>
@@ -4449,7 +4448,7 @@
       <c r="Y60" s="20"/>
       <c r="Z60" s="20"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="61" spans="1:26" ht="15.75" thickBot="1">
       <c r="A61" s="18">
         <v>60</v>
       </c>
@@ -4503,7 +4502,7 @@
       <c r="Y61" s="20"/>
       <c r="Z61" s="20"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="62" spans="1:26" ht="15.75" thickBot="1">
       <c r="A62" s="18">
         <v>61</v>
       </c>
@@ -4557,7 +4556,7 @@
       <c r="Y62" s="20"/>
       <c r="Z62" s="20"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="63" spans="1:26" ht="15.75" thickBot="1">
       <c r="A63" s="18">
         <v>62</v>
       </c>
@@ -4611,7 +4610,7 @@
       <c r="Y63" s="20"/>
       <c r="Z63" s="20"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="64" spans="1:26" ht="15.75" thickBot="1">
       <c r="A64" s="18">
         <v>63</v>
       </c>
@@ -4665,7 +4664,7 @@
       <c r="Y64" s="20"/>
       <c r="Z64" s="20"/>
     </row>
-    <row r="65" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="65" spans="1:26" ht="27" thickBot="1">
       <c r="A65" s="18">
         <v>64</v>
       </c>
@@ -4719,7 +4718,7 @@
       <c r="Y65" s="20"/>
       <c r="Z65" s="20"/>
     </row>
-    <row r="66" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="66" spans="1:26" ht="27" thickBot="1">
       <c r="A66" s="18">
         <v>65</v>
       </c>
@@ -4773,7 +4772,7 @@
       <c r="Y66" s="20"/>
       <c r="Z66" s="20"/>
     </row>
-    <row r="67" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="67" spans="1:26" ht="27" thickBot="1">
       <c r="A67" s="18">
         <v>66</v>
       </c>
@@ -4825,7 +4824,7 @@
       <c r="Y67" s="20"/>
       <c r="Z67" s="20"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="68" spans="1:26" ht="15.75" thickBot="1">
       <c r="A68" s="18">
         <v>67</v>
       </c>
@@ -4879,7 +4878,7 @@
       <c r="Y68" s="20"/>
       <c r="Z68" s="20"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="69" spans="1:26" ht="15.75" thickBot="1">
       <c r="A69" s="18">
         <v>68</v>
       </c>
@@ -4933,7 +4932,7 @@
       <c r="Y69" s="20"/>
       <c r="Z69" s="20"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="70" spans="1:26" ht="15.75" thickBot="1">
       <c r="A70" s="18">
         <v>69</v>
       </c>
@@ -4987,7 +4986,7 @@
       <c r="Y70" s="20"/>
       <c r="Z70" s="20"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="71" spans="1:26" ht="15.75" thickBot="1">
       <c r="A71" s="18">
         <v>70</v>
       </c>
@@ -5041,7 +5040,7 @@
       <c r="Y71" s="20"/>
       <c r="Z71" s="20"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="72" spans="1:26" ht="15.75" thickBot="1">
       <c r="A72" s="18">
         <v>71</v>
       </c>
@@ -5095,7 +5094,7 @@
       <c r="Y72" s="20"/>
       <c r="Z72" s="20"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="73" spans="1:26" ht="15.75" thickBot="1">
       <c r="A73" s="18">
         <v>72</v>
       </c>
@@ -5147,7 +5146,7 @@
       <c r="Y73" s="20"/>
       <c r="Z73" s="20"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="74" spans="1:26" ht="15.75" thickBot="1">
       <c r="A74" s="18">
         <v>73</v>
       </c>
@@ -5201,7 +5200,7 @@
       <c r="Y74" s="20"/>
       <c r="Z74" s="20"/>
     </row>
-    <row r="75" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="75" spans="1:26" ht="27" thickBot="1">
       <c r="A75" s="18">
         <v>74</v>
       </c>
@@ -5255,7 +5254,7 @@
       <c r="Y75" s="20"/>
       <c r="Z75" s="20"/>
     </row>
-    <row r="76" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="76" spans="1:26" ht="27" thickBot="1">
       <c r="A76" s="18">
         <v>75</v>
       </c>
@@ -5309,7 +5308,7 @@
       <c r="Y76" s="20"/>
       <c r="Z76" s="20"/>
     </row>
-    <row r="77" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="77" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
       <c r="A77" s="46">
         <v>76</v>
       </c>
@@ -5365,7 +5364,7 @@
       <c r="Y77" s="52"/>
       <c r="Z77" s="52"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="78" spans="1:26" ht="15.75" thickBot="1">
       <c r="A78" s="18">
         <v>77</v>
       </c>
@@ -5419,7 +5418,7 @@
       <c r="Y78" s="20"/>
       <c r="Z78" s="20"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="79" spans="1:26" ht="15.75" thickBot="1">
       <c r="A79" s="18">
         <v>78</v>
       </c>
@@ -5473,7 +5472,7 @@
       <c r="Y79" s="20"/>
       <c r="Z79" s="20"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="80" spans="1:26" ht="15.75" thickBot="1">
       <c r="A80" s="18">
         <v>79</v>
       </c>
@@ -5527,7 +5526,7 @@
       <c r="Y80" s="20"/>
       <c r="Z80" s="20"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="81" spans="1:26" ht="15.75" thickBot="1">
       <c r="A81" s="18">
         <v>80</v>
       </c>
@@ -5581,7 +5580,7 @@
       <c r="Y81" s="20"/>
       <c r="Z81" s="20"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="82" spans="1:26" ht="15.75" thickBot="1">
       <c r="A82" s="18">
         <v>81</v>
       </c>
@@ -5635,7 +5634,7 @@
       <c r="Y82" s="20"/>
       <c r="Z82" s="20"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="83" spans="1:26" ht="15.75" thickBot="1">
       <c r="A83" s="18">
         <v>82</v>
       </c>
@@ -5689,7 +5688,7 @@
       <c r="Y83" s="20"/>
       <c r="Z83" s="20"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="84" spans="1:26" ht="15.75" thickBot="1">
       <c r="A84" s="18">
         <v>83</v>
       </c>
@@ -5743,7 +5742,7 @@
       <c r="Y84" s="20"/>
       <c r="Z84" s="20"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="85" spans="1:26" ht="15.75" thickBot="1">
       <c r="A85" s="18">
         <v>84</v>
       </c>
@@ -5797,7 +5796,7 @@
       <c r="Y85" s="20"/>
       <c r="Z85" s="20"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="86" spans="1:26" ht="15.75" thickBot="1">
       <c r="A86" s="18">
         <v>85</v>
       </c>
@@ -5851,7 +5850,7 @@
       <c r="Y86" s="20"/>
       <c r="Z86" s="20"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="87" spans="1:26" ht="15.75" thickBot="1">
       <c r="A87" s="18">
         <v>86</v>
       </c>
@@ -5905,7 +5904,7 @@
       <c r="Y87" s="20"/>
       <c r="Z87" s="20"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="88" spans="1:26" ht="15.75" thickBot="1">
       <c r="A88" s="18">
         <v>87</v>
       </c>
@@ -5959,7 +5958,7 @@
       <c r="Y88" s="20"/>
       <c r="Z88" s="20"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="89" spans="1:26" ht="15.75" thickBot="1">
       <c r="A89" s="18">
         <v>88</v>
       </c>
@@ -6013,7 +6012,7 @@
       <c r="Y89" s="20"/>
       <c r="Z89" s="20"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="90" spans="1:26" ht="15.75" thickBot="1">
       <c r="A90" s="18">
         <v>89</v>
       </c>
@@ -6067,7 +6066,7 @@
       <c r="Y90" s="20"/>
       <c r="Z90" s="20"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="91" spans="1:26" ht="15.75" thickBot="1">
       <c r="A91" s="18">
         <v>90</v>
       </c>
@@ -6121,7 +6120,7 @@
       <c r="Y91" s="20"/>
       <c r="Z91" s="20"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="92" spans="1:26" ht="15.75" thickBot="1">
       <c r="A92" s="18">
         <v>91</v>
       </c>
@@ -6175,7 +6174,7 @@
       <c r="Y92" s="20"/>
       <c r="Z92" s="20"/>
     </row>
-    <row r="93" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="93" spans="1:26" ht="27" thickBot="1">
       <c r="A93" s="18">
         <v>92</v>
       </c>
@@ -6229,7 +6228,7 @@
       <c r="Y93" s="20"/>
       <c r="Z93" s="20"/>
     </row>
-    <row r="94" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="94" spans="1:26" ht="27" thickBot="1">
       <c r="A94" s="18">
         <v>93</v>
       </c>
@@ -6283,7 +6282,7 @@
       <c r="Y94" s="20"/>
       <c r="Z94" s="20"/>
     </row>
-    <row r="95" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="95" spans="1:26" ht="27" thickBot="1">
       <c r="A95" s="18">
         <v>94</v>
       </c>
@@ -6335,7 +6334,7 @@
       <c r="Y95" s="20"/>
       <c r="Z95" s="20"/>
     </row>
-    <row r="96" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="96" spans="1:26" ht="27" thickBot="1">
       <c r="A96" s="18">
         <v>95</v>
       </c>
@@ -6389,7 +6388,7 @@
       <c r="Y96" s="20"/>
       <c r="Z96" s="20"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="97" spans="1:26" ht="15.75" thickBot="1">
       <c r="A97" s="18">
         <v>96</v>
       </c>
@@ -6443,7 +6442,7 @@
       <c r="Y97" s="20"/>
       <c r="Z97" s="20"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="98" spans="1:26" ht="15.75" thickBot="1">
       <c r="A98" s="18">
         <v>97</v>
       </c>
@@ -6497,7 +6496,7 @@
       <c r="Y98" s="20"/>
       <c r="Z98" s="20"/>
     </row>
-    <row r="99" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="99" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
       <c r="A99" s="46">
         <v>98</v>
       </c>
@@ -6553,7 +6552,7 @@
       <c r="Y99" s="52"/>
       <c r="Z99" s="52"/>
     </row>
-    <row r="100" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="100" spans="1:26" ht="27" thickBot="1">
       <c r="A100" s="18">
         <v>99</v>
       </c>
@@ -6607,7 +6606,7 @@
       <c r="Y100" s="20"/>
       <c r="Z100" s="20"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="101" spans="1:26" ht="15.75" thickBot="1">
       <c r="A101" s="18">
         <v>100</v>
       </c>
@@ -6661,7 +6660,7 @@
       <c r="Y101" s="20"/>
       <c r="Z101" s="20"/>
     </row>
-    <row r="102" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="102" spans="1:26" ht="27" thickBot="1">
       <c r="A102" s="18">
         <v>101</v>
       </c>
@@ -6715,7 +6714,7 @@
       <c r="Y102" s="20"/>
       <c r="Z102" s="20"/>
     </row>
-    <row r="103" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="103" spans="1:26" ht="27" thickBot="1">
       <c r="A103" s="18">
         <v>102</v>
       </c>
@@ -6769,7 +6768,7 @@
       <c r="Y103" s="20"/>
       <c r="Z103" s="20"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="104" spans="1:26" ht="15.75" thickBot="1">
       <c r="A104" s="18">
         <v>103</v>
       </c>
@@ -6823,7 +6822,7 @@
       <c r="Y104" s="20"/>
       <c r="Z104" s="20"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="105" spans="1:26" ht="15.75" thickBot="1">
       <c r="A105" s="18">
         <v>104</v>
       </c>
@@ -6877,7 +6876,7 @@
       <c r="Y105" s="20"/>
       <c r="Z105" s="20"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="106" spans="1:26" ht="15.75" thickBot="1">
       <c r="A106" s="18">
         <v>105</v>
       </c>
@@ -6929,7 +6928,7 @@
       <c r="Y106" s="20"/>
       <c r="Z106" s="20"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="107" spans="1:26" ht="15.75" thickBot="1">
       <c r="A107" s="18">
         <v>106</v>
       </c>
@@ -6983,7 +6982,7 @@
       <c r="Y107" s="20"/>
       <c r="Z107" s="20"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="108" spans="1:26" ht="15.75" thickBot="1">
       <c r="A108" s="18">
         <v>107</v>
       </c>
@@ -7037,7 +7036,7 @@
       <c r="Y108" s="20"/>
       <c r="Z108" s="20"/>
     </row>
-    <row r="109" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="109" spans="1:26" ht="27" thickBot="1">
       <c r="A109" s="18">
         <v>108</v>
       </c>
@@ -7091,7 +7090,7 @@
       <c r="Y109" s="20"/>
       <c r="Z109" s="20"/>
     </row>
-    <row r="110" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="110" spans="1:26" ht="27" thickBot="1">
       <c r="A110" s="18">
         <v>109</v>
       </c>
@@ -7145,7 +7144,7 @@
       <c r="Y110" s="20"/>
       <c r="Z110" s="20"/>
     </row>
-    <row r="111" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="111" spans="1:26" ht="27" thickBot="1">
       <c r="A111" s="18">
         <v>110</v>
       </c>
@@ -7199,7 +7198,7 @@
       <c r="Y111" s="20"/>
       <c r="Z111" s="20"/>
     </row>
-    <row r="112" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="112" spans="1:26" ht="27" thickBot="1">
       <c r="A112" s="18">
         <v>111</v>
       </c>
@@ -7253,7 +7252,7 @@
       <c r="Y112" s="20"/>
       <c r="Z112" s="20"/>
     </row>
-    <row r="113" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="113" spans="1:26" ht="27" thickBot="1">
       <c r="A113" s="18">
         <v>112</v>
       </c>
@@ -7307,7 +7306,7 @@
       <c r="Y113" s="20"/>
       <c r="Z113" s="20"/>
     </row>
-    <row r="114" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="114" spans="1:26" ht="27" thickBot="1">
       <c r="A114" s="18">
         <v>113</v>
       </c>
@@ -7361,7 +7360,7 @@
       <c r="Y114" s="20"/>
       <c r="Z114" s="20"/>
     </row>
-    <row r="115" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="115" spans="1:26" ht="27" thickBot="1">
       <c r="A115" s="18">
         <v>114</v>
       </c>
@@ -7415,7 +7414,7 @@
       <c r="Y115" s="20"/>
       <c r="Z115" s="20"/>
     </row>
-    <row r="116" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="116" spans="1:26" ht="27" thickBot="1">
       <c r="A116" s="18">
         <v>115</v>
       </c>
@@ -7469,7 +7468,7 @@
       <c r="Y116" s="20"/>
       <c r="Z116" s="20"/>
     </row>
-    <row r="117" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="117" spans="1:26" ht="27" thickBot="1">
       <c r="A117" s="18">
         <v>116</v>
       </c>
@@ -7523,7 +7522,7 @@
       <c r="Y117" s="20"/>
       <c r="Z117" s="20"/>
     </row>
-    <row r="118" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="118" spans="1:26" ht="27" thickBot="1">
       <c r="A118" s="18">
         <v>117</v>
       </c>
@@ -7577,7 +7576,7 @@
       <c r="Y118" s="20"/>
       <c r="Z118" s="20"/>
     </row>
-    <row r="119" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="119" spans="1:26" ht="27" thickBot="1">
       <c r="A119" s="18">
         <v>118</v>
       </c>
@@ -7631,7 +7630,7 @@
       <c r="Y119" s="20"/>
       <c r="Z119" s="20"/>
     </row>
-    <row r="120" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="120" spans="1:26" ht="27" thickBot="1">
       <c r="A120" s="18">
         <v>119</v>
       </c>
@@ -7685,7 +7684,7 @@
       <c r="Y120" s="20"/>
       <c r="Z120" s="20"/>
     </row>
-    <row r="121" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="121" spans="1:26" ht="27" thickBot="1">
       <c r="A121" s="18">
         <v>120</v>
       </c>
@@ -7739,7 +7738,7 @@
       <c r="Y121" s="20"/>
       <c r="Z121" s="20"/>
     </row>
-    <row r="122" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="122" spans="1:26" ht="27" thickBot="1">
       <c r="A122" s="18">
         <v>121</v>
       </c>
@@ -7793,7 +7792,7 @@
       <c r="Y122" s="20"/>
       <c r="Z122" s="20"/>
     </row>
-    <row r="123" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="123" spans="1:26" ht="27" thickBot="1">
       <c r="A123" s="18">
         <v>122</v>
       </c>
@@ -7847,7 +7846,7 @@
       <c r="Y123" s="20"/>
       <c r="Z123" s="20"/>
     </row>
-    <row r="124" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="124" spans="1:26" ht="27" thickBot="1">
       <c r="A124" s="18">
         <v>123</v>
       </c>
@@ -7901,7 +7900,7 @@
       <c r="Y124" s="20"/>
       <c r="Z124" s="20"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="125" spans="1:26" ht="15.75" thickBot="1">
       <c r="A125" s="18">
         <v>124</v>
       </c>
@@ -7955,7 +7954,7 @@
       <c r="Y125" s="20"/>
       <c r="Z125" s="20"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="126" spans="1:26" ht="15.75" thickBot="1">
       <c r="A126" s="18">
         <v>125</v>
       </c>
@@ -8009,7 +8008,7 @@
       <c r="Y126" s="20"/>
       <c r="Z126" s="20"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="127" spans="1:26" ht="15.75" thickBot="1">
       <c r="A127" s="18">
         <v>126</v>
       </c>
@@ -8063,7 +8062,7 @@
       <c r="Y127" s="20"/>
       <c r="Z127" s="20"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="128" spans="1:26" ht="15.75" thickBot="1">
       <c r="A128" s="18">
         <v>127</v>
       </c>
@@ -8117,7 +8116,7 @@
       <c r="Y128" s="20"/>
       <c r="Z128" s="20"/>
     </row>
-    <row r="129" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="129" spans="1:26" ht="39.75" thickBot="1">
       <c r="A129" s="18">
         <v>128</v>
       </c>
@@ -8171,7 +8170,7 @@
       <c r="Y129" s="20"/>
       <c r="Z129" s="20"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="130" spans="1:26" ht="15.75" thickBot="1">
       <c r="A130" s="18">
         <v>129</v>
       </c>
@@ -8225,7 +8224,7 @@
       <c r="Y130" s="20"/>
       <c r="Z130" s="20"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="131" spans="1:26" ht="15.75" thickBot="1">
       <c r="A131" s="18">
         <v>130</v>
       </c>
@@ -8279,7 +8278,7 @@
       <c r="Y131" s="20"/>
       <c r="Z131" s="20"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="132" spans="1:26" ht="15.75" thickBot="1">
       <c r="A132" s="18">
         <v>131</v>
       </c>
@@ -8331,7 +8330,7 @@
       <c r="Y132" s="20"/>
       <c r="Z132" s="20"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="133" spans="1:26" ht="15.75" thickBot="1">
       <c r="A133" s="18">
         <v>132</v>
       </c>
@@ -8383,7 +8382,7 @@
       <c r="Y133" s="20"/>
       <c r="Z133" s="20"/>
     </row>
-    <row r="134" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="134" spans="1:26" ht="27" thickBot="1">
       <c r="A134" s="18">
         <v>133</v>
       </c>
@@ -8437,7 +8436,7 @@
       <c r="Y134" s="20"/>
       <c r="Z134" s="20"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="135" spans="1:26" ht="15.75" thickBot="1">
       <c r="A135" s="18">
         <v>134</v>
       </c>
@@ -8491,7 +8490,7 @@
       <c r="Y135" s="20"/>
       <c r="Z135" s="20"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="136" spans="1:26" ht="15.75" thickBot="1">
       <c r="A136" s="18">
         <v>135</v>
       </c>
@@ -8545,7 +8544,7 @@
       <c r="Y136" s="20"/>
       <c r="Z136" s="20"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="137" spans="1:26" ht="15.75" thickBot="1">
       <c r="A137" s="18">
         <v>136</v>
       </c>
@@ -8599,7 +8598,7 @@
       <c r="Y137" s="20"/>
       <c r="Z137" s="20"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="138" spans="1:26" ht="15.75" thickBot="1">
       <c r="A138" s="18">
         <v>137</v>
       </c>
@@ -8653,7 +8652,7 @@
       <c r="Y138" s="20"/>
       <c r="Z138" s="20"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="139" spans="1:26" ht="15.75" thickBot="1">
       <c r="A139" s="18">
         <v>138</v>
       </c>
@@ -8707,7 +8706,7 @@
       <c r="Y139" s="20"/>
       <c r="Z139" s="20"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="140" spans="1:26" ht="15.75" thickBot="1">
       <c r="A140" s="18">
         <v>139</v>
       </c>
@@ -8761,7 +8760,7 @@
       <c r="Y140" s="20"/>
       <c r="Z140" s="20"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="141" spans="1:26" ht="15.75" thickBot="1">
       <c r="A141" s="18">
         <v>140</v>
       </c>
@@ -8813,7 +8812,7 @@
       <c r="Y141" s="20"/>
       <c r="Z141" s="20"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="142" spans="1:26" ht="15.75" thickBot="1">
       <c r="A142" s="18">
         <v>141</v>
       </c>
@@ -8867,7 +8866,7 @@
       <c r="Y142" s="20"/>
       <c r="Z142" s="20"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="143" spans="1:26" ht="15.75" thickBot="1">
       <c r="A143" s="18">
         <v>142</v>
       </c>
@@ -8921,7 +8920,7 @@
       <c r="Y143" s="20"/>
       <c r="Z143" s="20"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="144" spans="1:26" ht="15.75" thickBot="1">
       <c r="A144" s="18">
         <v>143</v>
       </c>
@@ -8975,7 +8974,7 @@
       <c r="Y144" s="20"/>
       <c r="Z144" s="20"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="145" spans="1:26" ht="15.75" thickBot="1">
       <c r="A145" s="18">
         <v>144</v>
       </c>
@@ -9029,7 +9028,7 @@
       <c r="Y145" s="20"/>
       <c r="Z145" s="20"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="146" spans="1:26" ht="15.75" thickBot="1">
       <c r="A146" s="18">
         <v>145</v>
       </c>
@@ -9083,7 +9082,7 @@
       <c r="Y146" s="20"/>
       <c r="Z146" s="20"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="147" spans="1:26" ht="15.75" thickBot="1">
       <c r="A147" s="18">
         <v>146</v>
       </c>
@@ -9137,7 +9136,7 @@
       <c r="Y147" s="20"/>
       <c r="Z147" s="20"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="148" spans="1:26" ht="15.75" thickBot="1">
       <c r="A148" s="18">
         <v>147</v>
       </c>
@@ -9191,7 +9190,7 @@
       <c r="Y148" s="20"/>
       <c r="Z148" s="20"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="149" spans="1:26" ht="15.75" thickBot="1">
       <c r="A149" s="18">
         <v>148</v>
       </c>
@@ -9245,7 +9244,7 @@
       <c r="Y149" s="20"/>
       <c r="Z149" s="20"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="150" spans="1:26" ht="15.75" thickBot="1">
       <c r="A150" s="18">
         <v>149</v>
       </c>
@@ -9297,7 +9296,7 @@
       <c r="Y150" s="20"/>
       <c r="Z150" s="20"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="151" spans="1:26" ht="15.75" thickBot="1">
       <c r="A151" s="18">
         <v>150</v>
       </c>
@@ -9349,7 +9348,7 @@
       <c r="Y151" s="20"/>
       <c r="Z151" s="20"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="152" spans="1:26" ht="15.75" thickBot="1">
       <c r="A152" s="18">
         <v>151</v>
       </c>
@@ -9401,7 +9400,7 @@
       <c r="Y152" s="20"/>
       <c r="Z152" s="20"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="153" spans="1:26" ht="15.75" thickBot="1">
       <c r="A153" s="18">
         <v>152</v>
       </c>
@@ -9453,7 +9452,7 @@
       <c r="Y153" s="20"/>
       <c r="Z153" s="20"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="154" spans="1:26" ht="15.75" thickBot="1">
       <c r="A154" s="18">
         <v>153</v>
       </c>
@@ -9505,7 +9504,7 @@
       <c r="Y154" s="20"/>
       <c r="Z154" s="20"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="155" spans="1:26" ht="15.75" thickBot="1">
       <c r="A155" s="18">
         <v>154</v>
       </c>
@@ -9557,7 +9556,7 @@
       <c r="Y155" s="20"/>
       <c r="Z155" s="20"/>
     </row>
-    <row r="156" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="156" spans="1:26" ht="27" thickBot="1">
       <c r="A156" s="18">
         <v>155</v>
       </c>
@@ -9611,7 +9610,7 @@
       <c r="Y156" s="20"/>
       <c r="Z156" s="20"/>
     </row>
-    <row r="157" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="157" spans="1:26" ht="27" thickBot="1">
       <c r="A157" s="18">
         <v>156</v>
       </c>
@@ -9665,7 +9664,7 @@
       <c r="Y157" s="20"/>
       <c r="Z157" s="20"/>
     </row>
-    <row r="158" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="158" spans="1:26" ht="27" thickBot="1">
       <c r="A158" s="18">
         <v>157</v>
       </c>
@@ -9719,7 +9718,7 @@
       <c r="Y158" s="20"/>
       <c r="Z158" s="20"/>
     </row>
-    <row r="159" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="159" spans="1:26" ht="27" thickBot="1">
       <c r="A159" s="18">
         <v>158</v>
       </c>
@@ -9773,7 +9772,7 @@
       <c r="Y159" s="20"/>
       <c r="Z159" s="20"/>
     </row>
-    <row r="160" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="160" spans="1:26" ht="27" thickBot="1">
       <c r="A160" s="18">
         <v>159</v>
       </c>
@@ -9827,7 +9826,7 @@
       <c r="Y160" s="20"/>
       <c r="Z160" s="20"/>
     </row>
-    <row r="161" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="161" spans="1:26" ht="27" thickBot="1">
       <c r="A161" s="18">
         <v>160</v>
       </c>
@@ -9881,7 +9880,7 @@
       <c r="Y161" s="20"/>
       <c r="Z161" s="20"/>
     </row>
-    <row r="162" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="162" spans="1:26" ht="27" thickBot="1">
       <c r="A162" s="18">
         <v>161</v>
       </c>
@@ -9935,7 +9934,7 @@
       <c r="Y162" s="20"/>
       <c r="Z162" s="20"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="163" spans="1:26" ht="15.75" thickBot="1">
       <c r="A163" s="18">
         <v>162</v>
       </c>
@@ -9989,7 +9988,7 @@
       <c r="Y163" s="20"/>
       <c r="Z163" s="20"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="164" spans="1:26" ht="15.75" thickBot="1">
       <c r="A164" s="18">
         <v>163</v>
       </c>
@@ -10043,7 +10042,7 @@
       <c r="Y164" s="20"/>
       <c r="Z164" s="20"/>
     </row>
-    <row r="165" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="165" spans="1:26" ht="27" thickBot="1">
       <c r="A165" s="18">
         <v>164</v>
       </c>
@@ -10097,7 +10096,7 @@
       <c r="Y165" s="20"/>
       <c r="Z165" s="20"/>
     </row>
-    <row r="166" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="166" spans="1:26" ht="27" thickBot="1">
       <c r="A166" s="18">
         <v>165</v>
       </c>
@@ -10151,7 +10150,7 @@
       <c r="Y166" s="20"/>
       <c r="Z166" s="20"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="167" spans="1:26" ht="15.75" thickBot="1">
       <c r="A167" s="18">
         <v>166</v>
       </c>
@@ -10205,7 +10204,7 @@
       <c r="Y167" s="20"/>
       <c r="Z167" s="20"/>
     </row>
-    <row r="168" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="168" spans="1:26" ht="27" thickBot="1">
       <c r="A168" s="18">
         <v>167</v>
       </c>
@@ -10259,7 +10258,7 @@
       <c r="Y168" s="20"/>
       <c r="Z168" s="20"/>
     </row>
-    <row r="169" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="169" spans="1:26" ht="27" thickBot="1">
       <c r="A169" s="18">
         <v>168</v>
       </c>
@@ -10313,7 +10312,7 @@
       <c r="Y169" s="20"/>
       <c r="Z169" s="20"/>
     </row>
-    <row r="170" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="170" spans="1:26" ht="27" thickBot="1">
       <c r="A170" s="18">
         <v>169</v>
       </c>
@@ -10367,7 +10366,7 @@
       <c r="Y170" s="20"/>
       <c r="Z170" s="20"/>
     </row>
-    <row r="171" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="171" spans="1:26" ht="39.75" thickBot="1">
       <c r="A171" s="18">
         <v>170</v>
       </c>
@@ -10421,7 +10420,7 @@
       <c r="Y171" s="20"/>
       <c r="Z171" s="20"/>
     </row>
-    <row r="172" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="172" spans="1:26" ht="27" thickBot="1">
       <c r="A172" s="18">
         <v>171</v>
       </c>
@@ -10475,7 +10474,7 @@
       <c r="Y172" s="20"/>
       <c r="Z172" s="20"/>
     </row>
-    <row r="173" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="173" spans="1:26" ht="39.75" thickBot="1">
       <c r="A173" s="18">
         <v>172</v>
       </c>
@@ -10529,7 +10528,7 @@
       <c r="Y173" s="20"/>
       <c r="Z173" s="20"/>
     </row>
-    <row r="174" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="174" spans="1:26" ht="39.75" thickBot="1">
       <c r="A174" s="18">
         <v>173</v>
       </c>
@@ -10583,7 +10582,7 @@
       <c r="Y174" s="20"/>
       <c r="Z174" s="20"/>
     </row>
-    <row r="175" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="175" spans="1:26" ht="27" thickBot="1">
       <c r="A175" s="18">
         <v>174</v>
       </c>
@@ -10637,7 +10636,7 @@
       <c r="Y175" s="20"/>
       <c r="Z175" s="20"/>
     </row>
-    <row r="176" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="176" spans="1:26" ht="39.75" thickBot="1">
       <c r="A176" s="18">
         <v>175</v>
       </c>
@@ -10691,7 +10690,7 @@
       <c r="Y176" s="20"/>
       <c r="Z176" s="20"/>
     </row>
-    <row r="177" spans="1:26" ht="39.75" hidden="1" thickBot="1">
+    <row r="177" spans="1:26" ht="39.75" thickBot="1">
       <c r="A177" s="18">
         <v>176</v>
       </c>
@@ -10745,7 +10744,7 @@
       <c r="Y177" s="20"/>
       <c r="Z177" s="20"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="178" spans="1:26" ht="15.75" thickBot="1">
       <c r="A178" s="18">
         <v>177</v>
       </c>
@@ -10799,7 +10798,7 @@
       <c r="Y178" s="20"/>
       <c r="Z178" s="20"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="179" spans="1:26" ht="15.75" thickBot="1">
       <c r="A179" s="18">
         <v>178</v>
       </c>
@@ -10851,7 +10850,7 @@
       <c r="Y179" s="20"/>
       <c r="Z179" s="20"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="180" spans="1:26" ht="15.75" thickBot="1">
       <c r="A180" s="18">
         <v>179</v>
       </c>
@@ -10903,7 +10902,7 @@
       <c r="Y180" s="20"/>
       <c r="Z180" s="20"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="181" spans="1:26" ht="15.75" thickBot="1">
       <c r="A181" s="18">
         <v>180</v>
       </c>
@@ -10955,7 +10954,7 @@
       <c r="Y181" s="20"/>
       <c r="Z181" s="20"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="182" spans="1:26" ht="15.75" thickBot="1">
       <c r="A182" s="18">
         <v>181</v>
       </c>
@@ -11007,7 +11006,7 @@
       <c r="Y182" s="20"/>
       <c r="Z182" s="20"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="183" spans="1:26" ht="15.75" thickBot="1">
       <c r="A183" s="18">
         <v>182</v>
       </c>
@@ -11059,7 +11058,7 @@
       <c r="Y183" s="20"/>
       <c r="Z183" s="20"/>
     </row>
-    <row r="184" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="184" spans="1:26" ht="27" thickBot="1">
       <c r="A184" s="18">
         <v>183</v>
       </c>
@@ -11113,7 +11112,7 @@
       <c r="Y184" s="20"/>
       <c r="Z184" s="20"/>
     </row>
-    <row r="185" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="185" spans="1:26" ht="27" thickBot="1">
       <c r="A185" s="18">
         <v>184</v>
       </c>
@@ -11167,7 +11166,7 @@
       <c r="Y185" s="20"/>
       <c r="Z185" s="20"/>
     </row>
-    <row r="186" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="186" spans="1:26" ht="27" thickBot="1">
       <c r="A186" s="18">
         <v>185</v>
       </c>
@@ -11221,7 +11220,7 @@
       <c r="Y186" s="20"/>
       <c r="Z186" s="20"/>
     </row>
-    <row r="187" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="187" spans="1:26" ht="27" thickBot="1">
       <c r="A187" s="18">
         <v>186</v>
       </c>
@@ -11275,7 +11274,7 @@
       <c r="Y187" s="20"/>
       <c r="Z187" s="20"/>
     </row>
-    <row r="188" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="188" spans="1:26" ht="27" thickBot="1">
       <c r="A188" s="18">
         <v>187</v>
       </c>
@@ -11329,7 +11328,7 @@
       <c r="Y188" s="20"/>
       <c r="Z188" s="20"/>
     </row>
-    <row r="189" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="189" spans="1:26" ht="27" thickBot="1">
       <c r="A189" s="18">
         <v>188</v>
       </c>
@@ -11383,7 +11382,7 @@
       <c r="Y189" s="20"/>
       <c r="Z189" s="20"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="190" spans="1:26" ht="15.75" thickBot="1">
       <c r="A190" s="18">
         <v>189</v>
       </c>
@@ -11435,7 +11434,7 @@
       <c r="Y190" s="20"/>
       <c r="Z190" s="20"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="191" spans="1:26" ht="15.75" thickBot="1">
       <c r="A191" s="18">
         <v>190</v>
       </c>
@@ -11487,7 +11486,7 @@
       <c r="Y191" s="20"/>
       <c r="Z191" s="20"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="192" spans="1:26" ht="15.75" thickBot="1">
       <c r="A192" s="18">
         <v>191</v>
       </c>
@@ -11539,7 +11538,7 @@
       <c r="Y192" s="20"/>
       <c r="Z192" s="20"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="193" spans="1:26" ht="15.75" thickBot="1">
       <c r="A193" s="18">
         <v>192</v>
       </c>
@@ -11591,7 +11590,7 @@
       <c r="Y193" s="20"/>
       <c r="Z193" s="20"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="194" spans="1:26" ht="15.75" thickBot="1">
       <c r="A194" s="18">
         <v>193</v>
       </c>
@@ -11643,7 +11642,7 @@
       <c r="Y194" s="20"/>
       <c r="Z194" s="20"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="195" spans="1:26" ht="15.75" thickBot="1">
       <c r="A195" s="18">
         <v>194</v>
       </c>
@@ -11695,7 +11694,7 @@
       <c r="Y195" s="20"/>
       <c r="Z195" s="20"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="196" spans="1:26" ht="15.75" thickBot="1">
       <c r="A196" s="18">
         <v>195</v>
       </c>
@@ -11749,7 +11748,7 @@
       <c r="Y196" s="20"/>
       <c r="Z196" s="20"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="197" spans="1:26" ht="15.75" thickBot="1">
       <c r="A197" s="18">
         <v>196</v>
       </c>
@@ -11803,7 +11802,7 @@
       <c r="Y197" s="20"/>
       <c r="Z197" s="20"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="198" spans="1:26" ht="15.75" thickBot="1">
       <c r="A198" s="18">
         <v>197</v>
       </c>
@@ -11857,7 +11856,7 @@
       <c r="Y198" s="20"/>
       <c r="Z198" s="20"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="199" spans="1:26" ht="15.75" thickBot="1">
       <c r="A199" s="18">
         <v>198</v>
       </c>
@@ -11909,7 +11908,7 @@
       <c r="Y199" s="20"/>
       <c r="Z199" s="20"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="200" spans="1:26" ht="15.75" thickBot="1">
       <c r="A200" s="18">
         <v>199</v>
       </c>
@@ -11961,7 +11960,7 @@
       <c r="Y200" s="20"/>
       <c r="Z200" s="20"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="201" spans="1:26" ht="15.75" thickBot="1">
       <c r="A201" s="18">
         <v>200</v>
       </c>
@@ -12013,7 +12012,7 @@
       <c r="Y201" s="20"/>
       <c r="Z201" s="20"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="202" spans="1:26" ht="15.75" thickBot="1">
       <c r="A202" s="18">
         <v>201</v>
       </c>
@@ -12065,7 +12064,7 @@
       <c r="Y202" s="20"/>
       <c r="Z202" s="20"/>
     </row>
-    <row r="203" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="203" spans="1:26" ht="27" thickBot="1">
       <c r="A203" s="18">
         <v>202</v>
       </c>
@@ -12119,7 +12118,7 @@
       <c r="Y203" s="20"/>
       <c r="Z203" s="20"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="204" spans="1:26" ht="15.75" thickBot="1">
       <c r="A204" s="18">
         <v>203</v>
       </c>
@@ -12171,7 +12170,7 @@
       <c r="Y204" s="20"/>
       <c r="Z204" s="20"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="205" spans="1:26" ht="15.75" thickBot="1">
       <c r="A205" s="18">
         <v>204</v>
       </c>
@@ -12223,7 +12222,7 @@
       <c r="Y205" s="20"/>
       <c r="Z205" s="20"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="206" spans="1:26" ht="15.75" thickBot="1">
       <c r="A206" s="18">
         <v>205</v>
       </c>
@@ -12275,7 +12274,7 @@
       <c r="Y206" s="20"/>
       <c r="Z206" s="20"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="207" spans="1:26" ht="15.75" thickBot="1">
       <c r="A207" s="18">
         <v>206</v>
       </c>
@@ -12327,7 +12326,7 @@
       <c r="Y207" s="20"/>
       <c r="Z207" s="20"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="208" spans="1:26" ht="15.75" thickBot="1">
       <c r="A208" s="18">
         <v>207</v>
       </c>
@@ -12379,7 +12378,7 @@
       <c r="Y208" s="20"/>
       <c r="Z208" s="20"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="209" spans="1:26" ht="15.75" thickBot="1">
       <c r="A209" s="18">
         <v>208</v>
       </c>
@@ -12431,7 +12430,7 @@
       <c r="Y209" s="20"/>
       <c r="Z209" s="20"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="210" spans="1:26" ht="15.75" thickBot="1">
       <c r="A210" s="18">
         <v>209</v>
       </c>
@@ -12483,7 +12482,7 @@
       <c r="Y210" s="20"/>
       <c r="Z210" s="20"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="211" spans="1:26" ht="15.75" thickBot="1">
       <c r="A211" s="18">
         <v>210</v>
       </c>
@@ -12535,7 +12534,7 @@
       <c r="Y211" s="20"/>
       <c r="Z211" s="20"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="212" spans="1:26" ht="15.75" thickBot="1">
       <c r="A212" s="18">
         <v>211</v>
       </c>
@@ -12587,7 +12586,7 @@
       <c r="Y212" s="20"/>
       <c r="Z212" s="20"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="213" spans="1:26" ht="15.75" thickBot="1">
       <c r="A213" s="18">
         <v>212</v>
       </c>
@@ -12639,7 +12638,7 @@
       <c r="Y213" s="20"/>
       <c r="Z213" s="20"/>
     </row>
-    <row r="214" spans="1:26" s="7" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="214" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1">
       <c r="A214" s="18">
         <v>213</v>
       </c>
@@ -12693,7 +12692,7 @@
       <c r="Y214" s="25"/>
       <c r="Z214" s="25"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="215" spans="1:26" ht="15.75" thickBot="1">
       <c r="A215" s="18">
         <v>214</v>
       </c>
@@ -12745,7 +12744,7 @@
       <c r="Y215" s="20"/>
       <c r="Z215" s="20"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="216" spans="1:26" ht="15.75" thickBot="1">
       <c r="A216" s="18">
         <v>215</v>
       </c>
@@ -12797,7 +12796,7 @@
       <c r="Y216" s="20"/>
       <c r="Z216" s="20"/>
     </row>
-    <row r="217" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="217" spans="1:26" ht="27" thickBot="1">
       <c r="A217" s="18">
         <v>216</v>
       </c>
@@ -12851,7 +12850,7 @@
       <c r="Y217" s="20"/>
       <c r="Z217" s="20"/>
     </row>
-    <row r="218" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="218" spans="1:26" ht="27" thickBot="1">
       <c r="A218" s="18">
         <v>217</v>
       </c>
@@ -12905,7 +12904,7 @@
       <c r="Y218" s="20"/>
       <c r="Z218" s="20"/>
     </row>
-    <row r="219" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="219" spans="1:26" ht="27" thickBot="1">
       <c r="A219" s="18">
         <v>218</v>
       </c>
@@ -12959,7 +12958,7 @@
       <c r="Y219" s="20"/>
       <c r="Z219" s="20"/>
     </row>
-    <row r="220" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="220" spans="1:26" ht="27" thickBot="1">
       <c r="A220" s="18">
         <v>219</v>
       </c>
@@ -13013,7 +13012,7 @@
       <c r="Y220" s="20"/>
       <c r="Z220" s="20"/>
     </row>
-    <row r="221" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="221" spans="1:26" ht="27" thickBot="1">
       <c r="A221" s="18">
         <v>220</v>
       </c>
@@ -13067,7 +13066,7 @@
       <c r="Y221" s="20"/>
       <c r="Z221" s="20"/>
     </row>
-    <row r="222" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="222" spans="1:26" ht="27" thickBot="1">
       <c r="A222" s="18">
         <v>221</v>
       </c>
@@ -13121,7 +13120,7 @@
       <c r="Y222" s="20"/>
       <c r="Z222" s="20"/>
     </row>
-    <row r="223" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="223" spans="1:26" ht="27" thickBot="1">
       <c r="A223" s="18">
         <v>222</v>
       </c>
@@ -13175,7 +13174,7 @@
       <c r="Y223" s="20"/>
       <c r="Z223" s="20"/>
     </row>
-    <row r="224" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="224" spans="1:26" ht="27" thickBot="1">
       <c r="A224" s="18">
         <v>223</v>
       </c>
@@ -13229,7 +13228,7 @@
       <c r="Y224" s="20"/>
       <c r="Z224" s="20"/>
     </row>
-    <row r="225" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="225" spans="1:26" ht="15.75" thickBot="1">
       <c r="A225" s="18">
         <v>224</v>
       </c>
@@ -13283,7 +13282,7 @@
       <c r="Y225" s="20"/>
       <c r="Z225" s="20"/>
     </row>
-    <row r="226" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="226" spans="1:26" ht="15.75" thickBot="1">
       <c r="A226" s="18">
         <v>225</v>
       </c>
@@ -13337,7 +13336,7 @@
       <c r="Y226" s="20"/>
       <c r="Z226" s="20"/>
     </row>
-    <row r="227" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="227" spans="1:26" ht="15.75" thickBot="1">
       <c r="A227" s="18">
         <v>226</v>
       </c>
@@ -13391,7 +13390,7 @@
       <c r="Y227" s="20"/>
       <c r="Z227" s="20"/>
     </row>
-    <row r="228" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="228" spans="1:26" ht="15.75" thickBot="1">
       <c r="A228" s="18">
         <v>227</v>
       </c>
@@ -13445,7 +13444,7 @@
       <c r="Y228" s="20"/>
       <c r="Z228" s="20"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="229" spans="1:26" ht="15.75" thickBot="1">
       <c r="A229" s="18">
         <v>228</v>
       </c>
@@ -13499,7 +13498,7 @@
       <c r="Y229" s="20"/>
       <c r="Z229" s="20"/>
     </row>
-    <row r="230" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="230" spans="1:26" ht="15.75" thickBot="1">
       <c r="A230" s="18">
         <v>229</v>
       </c>
@@ -13553,7 +13552,7 @@
       <c r="Y230" s="20"/>
       <c r="Z230" s="20"/>
     </row>
-    <row r="231" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="231" spans="1:26" ht="15.75" thickBot="1">
       <c r="A231" s="18">
         <v>230</v>
       </c>
@@ -13605,7 +13604,7 @@
       <c r="Y231" s="20"/>
       <c r="Z231" s="20"/>
     </row>
-    <row r="232" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="232" spans="1:26" ht="15.75" thickBot="1">
       <c r="A232" s="18">
         <v>231</v>
       </c>
@@ -13657,7 +13656,7 @@
       <c r="Y232" s="20"/>
       <c r="Z232" s="20"/>
     </row>
-    <row r="233" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="233" spans="1:26" ht="15.75" thickBot="1">
       <c r="A233" s="18">
         <v>232</v>
       </c>
@@ -13709,7 +13708,7 @@
       <c r="Y233" s="20"/>
       <c r="Z233" s="20"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="234" spans="1:26" ht="15.75" thickBot="1">
       <c r="A234" s="18">
         <v>233</v>
       </c>
@@ -13761,7 +13760,7 @@
       <c r="Y234" s="20"/>
       <c r="Z234" s="20"/>
     </row>
-    <row r="235" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="235" spans="1:26" ht="15.75" thickBot="1">
       <c r="A235" s="18">
         <v>234</v>
       </c>
@@ -13813,7 +13812,7 @@
       <c r="Y235" s="20"/>
       <c r="Z235" s="20"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="236" spans="1:26" ht="15.75" thickBot="1">
       <c r="A236" s="18">
         <v>235</v>
       </c>
@@ -13867,7 +13866,7 @@
       <c r="Y236" s="20"/>
       <c r="Z236" s="20"/>
     </row>
-    <row r="237" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="237" spans="1:26" ht="27" thickBot="1">
       <c r="A237" s="18">
         <v>236</v>
       </c>
@@ -13921,7 +13920,7 @@
       <c r="Y237" s="20"/>
       <c r="Z237" s="20"/>
     </row>
-    <row r="238" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="238" spans="1:26" ht="27" thickBot="1">
       <c r="A238" s="18">
         <v>237</v>
       </c>
@@ -13975,7 +13974,7 @@
       <c r="Y238" s="20"/>
       <c r="Z238" s="20"/>
     </row>
-    <row r="239" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="239" spans="1:26" ht="15.75" thickBot="1">
       <c r="A239" s="18">
         <v>238</v>
       </c>
@@ -14027,7 +14026,7 @@
       <c r="Y239" s="20"/>
       <c r="Z239" s="20"/>
     </row>
-    <row r="240" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="240" spans="1:26" ht="27" thickBot="1">
       <c r="A240" s="18">
         <v>239</v>
       </c>
@@ -14081,7 +14080,7 @@
       <c r="Y240" s="20"/>
       <c r="Z240" s="20"/>
     </row>
-    <row r="241" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="241" spans="1:26" ht="27" thickBot="1">
       <c r="A241" s="18">
         <v>240</v>
       </c>
@@ -14135,7 +14134,7 @@
       <c r="Y241" s="20"/>
       <c r="Z241" s="20"/>
     </row>
-    <row r="242" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="242" spans="1:26" ht="27" thickBot="1">
       <c r="A242" s="18">
         <v>241</v>
       </c>
@@ -14187,7 +14186,7 @@
       <c r="Y242" s="20"/>
       <c r="Z242" s="20"/>
     </row>
-    <row r="243" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="243" spans="1:26" ht="27" thickBot="1">
       <c r="A243" s="18">
         <v>242</v>
       </c>
@@ -14239,7 +14238,7 @@
       <c r="Y243" s="20"/>
       <c r="Z243" s="20"/>
     </row>
-    <row r="244" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="244" spans="1:26" ht="27" thickBot="1">
       <c r="A244" s="18">
         <v>243</v>
       </c>
@@ -14291,7 +14290,7 @@
       <c r="Y244" s="20"/>
       <c r="Z244" s="20"/>
     </row>
-    <row r="245" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="245" spans="1:26" ht="15.75" thickBot="1">
       <c r="A245" s="18">
         <v>244</v>
       </c>
@@ -14345,7 +14344,7 @@
       <c r="Y245" s="20"/>
       <c r="Z245" s="20"/>
     </row>
-    <row r="246" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="246" spans="1:26" ht="15.75" thickBot="1">
       <c r="A246" s="18">
         <v>245</v>
       </c>
@@ -14453,7 +14452,7 @@
       <c r="Y247" s="20"/>
       <c r="Z247" s="20"/>
     </row>
-    <row r="248" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="248" spans="1:26" ht="15.75" thickBot="1">
       <c r="A248" s="18">
         <v>247</v>
       </c>
@@ -14507,7 +14506,7 @@
       <c r="Y248" s="20"/>
       <c r="Z248" s="20"/>
     </row>
-    <row r="249" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="249" spans="1:26" ht="15.75" thickBot="1">
       <c r="A249" s="18">
         <v>248</v>
       </c>
@@ -14561,7 +14560,7 @@
       <c r="Y249" s="20"/>
       <c r="Z249" s="20"/>
     </row>
-    <row r="250" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="250" spans="1:26" ht="27" thickBot="1">
       <c r="A250" s="18">
         <v>249</v>
       </c>
@@ -14615,7 +14614,7 @@
       <c r="Y250" s="20"/>
       <c r="Z250" s="20"/>
     </row>
-    <row r="251" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="251" spans="1:26" ht="27" thickBot="1">
       <c r="A251" s="18">
         <v>250</v>
       </c>
@@ -14669,7 +14668,7 @@
       <c r="Y251" s="20"/>
       <c r="Z251" s="20"/>
     </row>
-    <row r="252" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="252" spans="1:26" ht="15.75" thickBot="1">
       <c r="A252" s="18">
         <v>251</v>
       </c>
@@ -14723,7 +14722,7 @@
       <c r="Y252" s="20"/>
       <c r="Z252" s="20"/>
     </row>
-    <row r="253" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="253" spans="1:26" ht="15.75" thickBot="1">
       <c r="A253" s="18">
         <v>252</v>
       </c>
@@ -14777,7 +14776,7 @@
       <c r="Y253" s="20"/>
       <c r="Z253" s="20"/>
     </row>
-    <row r="254" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="254" spans="1:26" ht="15.75" thickBot="1">
       <c r="A254" s="18">
         <v>253</v>
       </c>
@@ -14831,7 +14830,7 @@
       <c r="Y254" s="20"/>
       <c r="Z254" s="20"/>
     </row>
-    <row r="255" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="255" spans="1:26" ht="15.75" thickBot="1">
       <c r="A255" s="18">
         <v>254</v>
       </c>
@@ -14885,7 +14884,7 @@
       <c r="Y255" s="20"/>
       <c r="Z255" s="20"/>
     </row>
-    <row r="256" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="256" spans="1:26" ht="15.75" thickBot="1">
       <c r="A256" s="18">
         <v>255</v>
       </c>
@@ -14939,7 +14938,7 @@
       <c r="Y256" s="20"/>
       <c r="Z256" s="20"/>
     </row>
-    <row r="257" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="257" spans="1:26" ht="15.75" thickBot="1">
       <c r="A257" s="18">
         <v>256</v>
       </c>
@@ -14991,7 +14990,7 @@
       <c r="Y257" s="20"/>
       <c r="Z257" s="20"/>
     </row>
-    <row r="258" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="258" spans="1:26" ht="15.75" thickBot="1">
       <c r="A258" s="18">
         <v>257</v>
       </c>
@@ -15043,7 +15042,7 @@
       <c r="Y258" s="20"/>
       <c r="Z258" s="20"/>
     </row>
-    <row r="259" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="259" spans="1:26" ht="15.75" thickBot="1">
       <c r="A259" s="18">
         <v>258</v>
       </c>
@@ -15095,7 +15094,7 @@
       <c r="Y259" s="20"/>
       <c r="Z259" s="20"/>
     </row>
-    <row r="260" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="260" spans="1:26" ht="15.75" thickBot="1">
       <c r="A260" s="18">
         <v>259</v>
       </c>
@@ -15147,7 +15146,7 @@
       <c r="Y260" s="20"/>
       <c r="Z260" s="20"/>
     </row>
-    <row r="261" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="261" spans="1:26" ht="15.75" thickBot="1">
       <c r="A261" s="18">
         <v>260</v>
       </c>
@@ -15199,7 +15198,7 @@
       <c r="Y261" s="20"/>
       <c r="Z261" s="20"/>
     </row>
-    <row r="262" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="262" spans="1:26" ht="15.75" thickBot="1">
       <c r="A262" s="18">
         <v>261</v>
       </c>
@@ -15251,7 +15250,7 @@
       <c r="Y262" s="20"/>
       <c r="Z262" s="20"/>
     </row>
-    <row r="263" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="263" spans="1:26" ht="15.75" thickBot="1">
       <c r="A263" s="18">
         <v>262</v>
       </c>
@@ -15303,7 +15302,7 @@
       <c r="Y263" s="20"/>
       <c r="Z263" s="20"/>
     </row>
-    <row r="264" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="264" spans="1:26" ht="15.75" thickBot="1">
       <c r="A264" s="18">
         <v>263</v>
       </c>
@@ -15355,7 +15354,7 @@
       <c r="Y264" s="20"/>
       <c r="Z264" s="20"/>
     </row>
-    <row r="265" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="265" spans="1:26" ht="15.75" thickBot="1">
       <c r="A265" s="18">
         <v>264</v>
       </c>
@@ -15407,7 +15406,7 @@
       <c r="Y265" s="20"/>
       <c r="Z265" s="20"/>
     </row>
-    <row r="266" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="266" spans="1:26" ht="15.75" thickBot="1">
       <c r="A266" s="18">
         <v>265</v>
       </c>
@@ -15459,7 +15458,7 @@
       <c r="Y266" s="20"/>
       <c r="Z266" s="20"/>
     </row>
-    <row r="267" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="267" spans="1:26" ht="15.75" thickBot="1">
       <c r="A267" s="18">
         <v>266</v>
       </c>
@@ -15511,7 +15510,7 @@
       <c r="Y267" s="20"/>
       <c r="Z267" s="20"/>
     </row>
-    <row r="268" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="268" spans="1:26" ht="15.75" thickBot="1">
       <c r="A268" s="18">
         <v>267</v>
       </c>
@@ -15563,7 +15562,7 @@
       <c r="Y268" s="20"/>
       <c r="Z268" s="20"/>
     </row>
-    <row r="269" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="269" spans="1:26" ht="15.75" thickBot="1">
       <c r="A269" s="18">
         <v>268</v>
       </c>
@@ -15615,7 +15614,7 @@
       <c r="Y269" s="20"/>
       <c r="Z269" s="20"/>
     </row>
-    <row r="270" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="270" spans="1:26" ht="15.75" thickBot="1">
       <c r="A270" s="18">
         <v>269</v>
       </c>
@@ -15667,7 +15666,7 @@
       <c r="Y270" s="20"/>
       <c r="Z270" s="20"/>
     </row>
-    <row r="271" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="271" spans="1:26" ht="15.75" thickBot="1">
       <c r="A271" s="18">
         <v>270</v>
       </c>
@@ -15719,7 +15718,7 @@
       <c r="Y271" s="20"/>
       <c r="Z271" s="20"/>
     </row>
-    <row r="272" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="272" spans="1:26" ht="15.75" thickBot="1">
       <c r="A272" s="18">
         <v>271</v>
       </c>
@@ -15771,7 +15770,7 @@
       <c r="Y272" s="20"/>
       <c r="Z272" s="20"/>
     </row>
-    <row r="273" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="273" spans="1:26" ht="15.75" thickBot="1">
       <c r="A273" s="18">
         <v>272</v>
       </c>
@@ -15823,7 +15822,7 @@
       <c r="Y273" s="20"/>
       <c r="Z273" s="20"/>
     </row>
-    <row r="274" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="274" spans="1:26" ht="15.75" thickBot="1">
       <c r="A274" s="18">
         <v>273</v>
       </c>
@@ -15875,7 +15874,7 @@
       <c r="Y274" s="20"/>
       <c r="Z274" s="20"/>
     </row>
-    <row r="275" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="275" spans="1:26" ht="15.75" thickBot="1">
       <c r="A275" s="18">
         <v>274</v>
       </c>
@@ -15927,7 +15926,7 @@
       <c r="Y275" s="20"/>
       <c r="Z275" s="20"/>
     </row>
-    <row r="276" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="276" spans="1:26" ht="15.75" thickBot="1">
       <c r="A276" s="18">
         <v>275</v>
       </c>
@@ -15979,7 +15978,7 @@
       <c r="Y276" s="20"/>
       <c r="Z276" s="20"/>
     </row>
-    <row r="277" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="277" spans="1:26" ht="15.75" thickBot="1">
       <c r="A277" s="18">
         <v>276</v>
       </c>
@@ -16031,7 +16030,7 @@
       <c r="Y277" s="20"/>
       <c r="Z277" s="20"/>
     </row>
-    <row r="278" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="278" spans="1:26" ht="15.75" thickBot="1">
       <c r="A278" s="18">
         <v>277</v>
       </c>
@@ -16083,7 +16082,7 @@
       <c r="Y278" s="20"/>
       <c r="Z278" s="20"/>
     </row>
-    <row r="279" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="279" spans="1:26" ht="15.75" thickBot="1">
       <c r="A279" s="18">
         <v>278</v>
       </c>
@@ -16135,7 +16134,7 @@
       <c r="Y279" s="20"/>
       <c r="Z279" s="20"/>
     </row>
-    <row r="280" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="280" spans="1:26" ht="15.75" thickBot="1">
       <c r="A280" s="18">
         <v>279</v>
       </c>
@@ -16187,7 +16186,7 @@
       <c r="Y280" s="20"/>
       <c r="Z280" s="20"/>
     </row>
-    <row r="281" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="281" spans="1:26" ht="15.75" thickBot="1">
       <c r="A281" s="18">
         <v>280</v>
       </c>
@@ -16239,7 +16238,7 @@
       <c r="Y281" s="20"/>
       <c r="Z281" s="20"/>
     </row>
-    <row r="282" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="282" spans="1:26" ht="15.75" thickBot="1">
       <c r="A282" s="18">
         <v>281</v>
       </c>
@@ -16291,7 +16290,7 @@
       <c r="Y282" s="20"/>
       <c r="Z282" s="20"/>
     </row>
-    <row r="283" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="283" spans="1:26" ht="15.75" thickBot="1">
       <c r="A283" s="18">
         <v>282</v>
       </c>
@@ -16343,7 +16342,7 @@
       <c r="Y283" s="20"/>
       <c r="Z283" s="20"/>
     </row>
-    <row r="284" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="284" spans="1:26" ht="15.75" thickBot="1">
       <c r="A284" s="18">
         <v>283</v>
       </c>
@@ -16395,7 +16394,7 @@
       <c r="Y284" s="20"/>
       <c r="Z284" s="20"/>
     </row>
-    <row r="285" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="285" spans="1:26" ht="15.75" thickBot="1">
       <c r="A285" s="18">
         <v>284</v>
       </c>
@@ -16447,7 +16446,7 @@
       <c r="Y285" s="20"/>
       <c r="Z285" s="20"/>
     </row>
-    <row r="286" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="286" spans="1:26" ht="15.75" thickBot="1">
       <c r="A286" s="18">
         <v>285</v>
       </c>
@@ -16499,7 +16498,7 @@
       <c r="Y286" s="20"/>
       <c r="Z286" s="20"/>
     </row>
-    <row r="287" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="287" spans="1:26" ht="15.75" thickBot="1">
       <c r="A287" s="18">
         <v>286</v>
       </c>
@@ -16551,7 +16550,7 @@
       <c r="Y287" s="20"/>
       <c r="Z287" s="20"/>
     </row>
-    <row r="288" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="288" spans="1:26" ht="15.75" thickBot="1">
       <c r="A288" s="18">
         <v>287</v>
       </c>
@@ -16603,7 +16602,7 @@
       <c r="Y288" s="20"/>
       <c r="Z288" s="20"/>
     </row>
-    <row r="289" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="289" spans="1:26" ht="15.75" thickBot="1">
       <c r="A289" s="18">
         <v>288</v>
       </c>
@@ -16655,7 +16654,7 @@
       <c r="Y289" s="20"/>
       <c r="Z289" s="20"/>
     </row>
-    <row r="290" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="290" spans="1:26" ht="15.75" thickBot="1">
       <c r="A290" s="18">
         <v>289</v>
       </c>
@@ -16707,7 +16706,7 @@
       <c r="Y290" s="20"/>
       <c r="Z290" s="20"/>
     </row>
-    <row r="291" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="291" spans="1:26" ht="15.75" thickBot="1">
       <c r="A291" s="18">
         <v>290</v>
       </c>
@@ -16759,7 +16758,7 @@
       <c r="Y291" s="20"/>
       <c r="Z291" s="20"/>
     </row>
-    <row r="292" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="292" spans="1:26" ht="15.75" thickBot="1">
       <c r="A292" s="18">
         <v>291</v>
       </c>
@@ -16811,7 +16810,7 @@
       <c r="Y292" s="20"/>
       <c r="Z292" s="20"/>
     </row>
-    <row r="293" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="293" spans="1:26" ht="15.75" thickBot="1">
       <c r="A293" s="18">
         <v>292</v>
       </c>
@@ -16865,7 +16864,7 @@
       <c r="Y293" s="20"/>
       <c r="Z293" s="20"/>
     </row>
-    <row r="294" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="294" spans="1:26" ht="15.75" thickBot="1">
       <c r="A294" s="18">
         <v>293</v>
       </c>
@@ -16917,7 +16916,7 @@
       <c r="Y294" s="20"/>
       <c r="Z294" s="20"/>
     </row>
-    <row r="295" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="295" spans="1:26" ht="15.75" thickBot="1">
       <c r="A295" s="18">
         <v>294</v>
       </c>
@@ -16969,7 +16968,7 @@
       <c r="Y295" s="20"/>
       <c r="Z295" s="20"/>
     </row>
-    <row r="296" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="296" spans="1:26" ht="15.75" thickBot="1">
       <c r="A296" s="18">
         <v>295</v>
       </c>
@@ -17021,7 +17020,7 @@
       <c r="Y296" s="20"/>
       <c r="Z296" s="20"/>
     </row>
-    <row r="297" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="297" spans="1:26" ht="15.75" thickBot="1">
       <c r="A297" s="18">
         <v>296</v>
       </c>
@@ -17073,7 +17072,7 @@
       <c r="Y297" s="20"/>
       <c r="Z297" s="20"/>
     </row>
-    <row r="298" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="298" spans="1:26" ht="15.75" thickBot="1">
       <c r="A298" s="18">
         <v>297</v>
       </c>
@@ -17125,7 +17124,7 @@
       <c r="Y298" s="20"/>
       <c r="Z298" s="20"/>
     </row>
-    <row r="299" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="299" spans="1:26" ht="15.75" thickBot="1">
       <c r="A299" s="18">
         <v>298</v>
       </c>
@@ -17179,7 +17178,7 @@
       <c r="Y299" s="20"/>
       <c r="Z299" s="20"/>
     </row>
-    <row r="300" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="300" spans="1:26" ht="15.75" thickBot="1">
       <c r="A300" s="18">
         <v>299</v>
       </c>
@@ -17231,7 +17230,7 @@
       <c r="Y300" s="20"/>
       <c r="Z300" s="20"/>
     </row>
-    <row r="301" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="301" spans="1:26" ht="27" thickBot="1">
       <c r="A301" s="18">
         <v>300</v>
       </c>
@@ -17281,7 +17280,7 @@
       <c r="Y301" s="20"/>
       <c r="Z301" s="20"/>
     </row>
-    <row r="302" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="302" spans="1:26" ht="15.75" thickBot="1">
       <c r="A302" s="18">
         <v>301</v>
       </c>
@@ -17331,7 +17330,7 @@
       <c r="Y302" s="20"/>
       <c r="Z302" s="20"/>
     </row>
-    <row r="303" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="303" spans="1:26" ht="15.75" thickBot="1">
       <c r="A303" s="18">
         <v>302</v>
       </c>
@@ -17381,7 +17380,7 @@
       <c r="Y303" s="20"/>
       <c r="Z303" s="20"/>
     </row>
-    <row r="304" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="304" spans="1:26" ht="15.75" thickBot="1">
       <c r="A304" s="18">
         <v>303</v>
       </c>
@@ -17431,7 +17430,7 @@
       <c r="Y304" s="20"/>
       <c r="Z304" s="20"/>
     </row>
-    <row r="305" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="305" spans="1:26" ht="27" thickBot="1">
       <c r="A305" s="18">
         <v>304</v>
       </c>
@@ -17485,7 +17484,7 @@
       <c r="Y305" s="20"/>
       <c r="Z305" s="20"/>
     </row>
-    <row r="306" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="306" spans="1:26" ht="15.75" thickBot="1">
       <c r="A306" s="18">
         <v>305</v>
       </c>
@@ -17539,7 +17538,7 @@
       <c r="Y306" s="20"/>
       <c r="Z306" s="20"/>
     </row>
-    <row r="307" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="307" spans="1:26" ht="15.75" thickBot="1">
       <c r="A307" s="18">
         <v>306</v>
       </c>
@@ -17591,7 +17590,7 @@
       <c r="Y307" s="20"/>
       <c r="Z307" s="20"/>
     </row>
-    <row r="308" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="308" spans="1:26" ht="15.75" thickBot="1">
       <c r="A308" s="18">
         <v>307</v>
       </c>
@@ -17643,7 +17642,7 @@
       <c r="Y308" s="20"/>
       <c r="Z308" s="20"/>
     </row>
-    <row r="309" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="309" spans="1:26" ht="15.75" thickBot="1">
       <c r="A309" s="18">
         <v>308</v>
       </c>
@@ -17695,7 +17694,7 @@
       <c r="Y309" s="20"/>
       <c r="Z309" s="20"/>
     </row>
-    <row r="310" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="310" spans="1:26" ht="15.75" thickBot="1">
       <c r="A310" s="18">
         <v>309</v>
       </c>
@@ -17747,7 +17746,7 @@
       <c r="Y310" s="20"/>
       <c r="Z310" s="20"/>
     </row>
-    <row r="311" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="311" spans="1:26" ht="15.75" thickBot="1">
       <c r="A311" s="18">
         <v>310</v>
       </c>
@@ -17799,7 +17798,7 @@
       <c r="Y311" s="20"/>
       <c r="Z311" s="20"/>
     </row>
-    <row r="312" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="312" spans="1:26" ht="15.75" thickBot="1">
       <c r="A312" s="18">
         <v>311</v>
       </c>
@@ -17851,7 +17850,7 @@
       <c r="Y312" s="20"/>
       <c r="Z312" s="20"/>
     </row>
-    <row r="313" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="313" spans="1:26" ht="15.75" thickBot="1">
       <c r="A313" s="18">
         <v>312</v>
       </c>
@@ -17903,7 +17902,7 @@
       <c r="Y313" s="20"/>
       <c r="Z313" s="20"/>
     </row>
-    <row r="314" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="314" spans="1:26" ht="15.75" thickBot="1">
       <c r="A314" s="18">
         <v>313</v>
       </c>
@@ -17955,7 +17954,7 @@
       <c r="Y314" s="20"/>
       <c r="Z314" s="20"/>
     </row>
-    <row r="315" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="315" spans="1:26" ht="15.75" thickBot="1">
       <c r="A315" s="18">
         <v>314</v>
       </c>
@@ -18007,7 +18006,7 @@
       <c r="Y315" s="20"/>
       <c r="Z315" s="20"/>
     </row>
-    <row r="316" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="316" spans="1:26" ht="15.75" thickBot="1">
       <c r="A316" s="18">
         <v>315</v>
       </c>
@@ -18059,7 +18058,7 @@
       <c r="Y316" s="20"/>
       <c r="Z316" s="20"/>
     </row>
-    <row r="317" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="317" spans="1:26" ht="27" thickBot="1">
       <c r="A317" s="18">
         <v>316</v>
       </c>
@@ -18113,7 +18112,7 @@
       <c r="Y317" s="20"/>
       <c r="Z317" s="20"/>
     </row>
-    <row r="318" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="318" spans="1:26" ht="27" thickBot="1">
       <c r="A318" s="18">
         <v>317</v>
       </c>
@@ -18167,7 +18166,7 @@
       <c r="Y318" s="20"/>
       <c r="Z318" s="20"/>
     </row>
-    <row r="319" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="319" spans="1:26" ht="27" thickBot="1">
       <c r="A319" s="18">
         <v>318</v>
       </c>
@@ -18221,7 +18220,7 @@
       <c r="Y319" s="20"/>
       <c r="Z319" s="20"/>
     </row>
-    <row r="320" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="320" spans="1:26" ht="27" thickBot="1">
       <c r="A320" s="18">
         <v>319</v>
       </c>
@@ -18275,7 +18274,7 @@
       <c r="Y320" s="20"/>
       <c r="Z320" s="20"/>
     </row>
-    <row r="321" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="321" spans="1:26" ht="27" thickBot="1">
       <c r="A321" s="18">
         <v>320</v>
       </c>
@@ -18329,7 +18328,7 @@
       <c r="Y321" s="20"/>
       <c r="Z321" s="20"/>
     </row>
-    <row r="322" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="322" spans="1:26" ht="27" thickBot="1">
       <c r="A322" s="18">
         <v>321</v>
       </c>
@@ -18383,7 +18382,7 @@
       <c r="Y322" s="20"/>
       <c r="Z322" s="20"/>
     </row>
-    <row r="323" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="323" spans="1:26" ht="15.75" thickBot="1">
       <c r="A323" s="18">
         <v>322</v>
       </c>
@@ -18435,7 +18434,7 @@
       <c r="Y323" s="20"/>
       <c r="Z323" s="20"/>
     </row>
-    <row r="324" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="324" spans="1:26" ht="15.75" thickBot="1">
       <c r="A324" s="18">
         <v>323</v>
       </c>
@@ -18487,7 +18486,7 @@
       <c r="Y324" s="20"/>
       <c r="Z324" s="20"/>
     </row>
-    <row r="325" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="325" spans="1:26" ht="15.75" thickBot="1">
       <c r="A325" s="18">
         <v>324</v>
       </c>
@@ -18541,7 +18540,7 @@
       <c r="Y325" s="20"/>
       <c r="Z325" s="20"/>
     </row>
-    <row r="326" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="326" spans="1:26" ht="15.75" thickBot="1">
       <c r="A326" s="18">
         <v>325</v>
       </c>
@@ -18595,7 +18594,7 @@
       <c r="Y326" s="20"/>
       <c r="Z326" s="20"/>
     </row>
-    <row r="327" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="327" spans="1:26" ht="15.75" thickBot="1">
       <c r="A327" s="18">
         <v>326</v>
       </c>
@@ -18647,7 +18646,7 @@
       <c r="Y327" s="20"/>
       <c r="Z327" s="20"/>
     </row>
-    <row r="328" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="328" spans="1:26" ht="15.75" thickBot="1">
       <c r="A328" s="18">
         <v>327</v>
       </c>
@@ -18699,7 +18698,7 @@
       <c r="Y328" s="20"/>
       <c r="Z328" s="20"/>
     </row>
-    <row r="329" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="329" spans="1:26" ht="15.75" thickBot="1">
       <c r="A329" s="18">
         <v>328</v>
       </c>
@@ -18751,7 +18750,7 @@
       <c r="Y329" s="20"/>
       <c r="Z329" s="20"/>
     </row>
-    <row r="330" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="330" spans="1:26" ht="15.75" thickBot="1">
       <c r="A330" s="18">
         <v>329</v>
       </c>
@@ -18803,7 +18802,7 @@
       <c r="Y330" s="20"/>
       <c r="Z330" s="20"/>
     </row>
-    <row r="331" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="331" spans="1:26" ht="15.75" thickBot="1">
       <c r="A331" s="18">
         <v>330</v>
       </c>
@@ -18855,7 +18854,7 @@
       <c r="Y331" s="20"/>
       <c r="Z331" s="20"/>
     </row>
-    <row r="332" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="332" spans="1:26" ht="15.75" thickBot="1">
       <c r="A332" s="18">
         <v>331</v>
       </c>
@@ -18907,7 +18906,7 @@
       <c r="Y332" s="20"/>
       <c r="Z332" s="20"/>
     </row>
-    <row r="333" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="333" spans="1:26" ht="15.75" thickBot="1">
       <c r="A333" s="18">
         <v>332</v>
       </c>
@@ -18961,7 +18960,7 @@
       <c r="Y333" s="20"/>
       <c r="Z333" s="20"/>
     </row>
-    <row r="334" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="334" spans="1:26" ht="15.75" thickBot="1">
       <c r="A334" s="18">
         <v>333</v>
       </c>
@@ -19015,7 +19014,7 @@
       <c r="Y334" s="20"/>
       <c r="Z334" s="20"/>
     </row>
-    <row r="335" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="335" spans="1:26" ht="15.75" thickBot="1">
       <c r="A335" s="18">
         <v>334</v>
       </c>
@@ -19067,7 +19066,7 @@
       <c r="Y335" s="20"/>
       <c r="Z335" s="20"/>
     </row>
-    <row r="336" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="336" spans="1:26" ht="15.75" thickBot="1">
       <c r="A336" s="18">
         <v>335</v>
       </c>
@@ -19119,7 +19118,7 @@
       <c r="Y336" s="20"/>
       <c r="Z336" s="20"/>
     </row>
-    <row r="337" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="337" spans="1:26" ht="15.75" thickBot="1">
       <c r="A337" s="18">
         <v>336</v>
       </c>
@@ -19171,7 +19170,7 @@
       <c r="Y337" s="20"/>
       <c r="Z337" s="20"/>
     </row>
-    <row r="338" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="338" spans="1:26" ht="15.75" thickBot="1">
       <c r="A338" s="18">
         <v>337</v>
       </c>
@@ -19223,7 +19222,7 @@
       <c r="Y338" s="20"/>
       <c r="Z338" s="20"/>
     </row>
-    <row r="339" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="339" spans="1:26" ht="27" thickBot="1">
       <c r="A339" s="18">
         <v>338</v>
       </c>
@@ -19277,7 +19276,7 @@
       <c r="Y339" s="20"/>
       <c r="Z339" s="20"/>
     </row>
-    <row r="340" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="340" spans="1:26" ht="27" thickBot="1">
       <c r="A340" s="18">
         <v>339</v>
       </c>
@@ -19331,7 +19330,7 @@
       <c r="Y340" s="20"/>
       <c r="Z340" s="20"/>
     </row>
-    <row r="341" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="341" spans="1:26" ht="15.75" thickBot="1">
       <c r="A341" s="18">
         <v>340</v>
       </c>
@@ -19385,7 +19384,7 @@
       <c r="Y341" s="20"/>
       <c r="Z341" s="20"/>
     </row>
-    <row r="342" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="342" spans="1:26" ht="15.75" thickBot="1">
       <c r="A342" s="18">
         <v>341</v>
       </c>
@@ -19439,7 +19438,7 @@
       <c r="Y342" s="20"/>
       <c r="Z342" s="20"/>
     </row>
-    <row r="343" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="343" spans="1:26" ht="15.75" thickBot="1">
       <c r="A343" s="18">
         <v>342</v>
       </c>
@@ -19493,7 +19492,7 @@
       <c r="Y343" s="20"/>
       <c r="Z343" s="20"/>
     </row>
-    <row r="344" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="344" spans="1:26" ht="15.75" thickBot="1">
       <c r="A344" s="18">
         <v>343</v>
       </c>
@@ -19547,7 +19546,7 @@
       <c r="Y344" s="20"/>
       <c r="Z344" s="20"/>
     </row>
-    <row r="345" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="345" spans="1:26" ht="27" thickBot="1">
       <c r="A345" s="18">
         <v>344</v>
       </c>
@@ -19601,7 +19600,7 @@
       <c r="Y345" s="20"/>
       <c r="Z345" s="20"/>
     </row>
-    <row r="346" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="346" spans="1:26" ht="15.75" thickBot="1">
       <c r="A346" s="18">
         <v>345</v>
       </c>
@@ -19653,7 +19652,7 @@
       <c r="Y346" s="20"/>
       <c r="Z346" s="20"/>
     </row>
-    <row r="347" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="347" spans="1:26" ht="15.75" thickBot="1">
       <c r="A347" s="18">
         <v>346</v>
       </c>
@@ -19705,7 +19704,7 @@
       <c r="Y347" s="20"/>
       <c r="Z347" s="20"/>
     </row>
-    <row r="348" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="348" spans="1:26" ht="15.75" thickBot="1">
       <c r="A348" s="18">
         <v>347</v>
       </c>
@@ -19757,7 +19756,7 @@
       <c r="Y348" s="20"/>
       <c r="Z348" s="20"/>
     </row>
-    <row r="349" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="349" spans="1:26" ht="15.75" thickBot="1">
       <c r="A349" s="18">
         <v>348</v>
       </c>
@@ -19809,7 +19808,7 @@
       <c r="Y349" s="20"/>
       <c r="Z349" s="20"/>
     </row>
-    <row r="350" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="350" spans="1:26" ht="15.75" thickBot="1">
       <c r="A350" s="18">
         <v>349</v>
       </c>
@@ -19861,7 +19860,7 @@
       <c r="Y350" s="20"/>
       <c r="Z350" s="20"/>
     </row>
-    <row r="351" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="351" spans="1:26" ht="15.75" thickBot="1">
       <c r="A351" s="18">
         <v>350</v>
       </c>
@@ -19913,7 +19912,7 @@
       <c r="Y351" s="20"/>
       <c r="Z351" s="20"/>
     </row>
-    <row r="352" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="352" spans="1:26" ht="15.75" thickBot="1">
       <c r="A352" s="18">
         <v>351</v>
       </c>
@@ -19965,7 +19964,7 @@
       <c r="Y352" s="20"/>
       <c r="Z352" s="20"/>
     </row>
-    <row r="353" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="353" spans="1:26" ht="15.75" thickBot="1">
       <c r="A353" s="18">
         <v>352</v>
       </c>
@@ -20017,7 +20016,7 @@
       <c r="Y353" s="20"/>
       <c r="Z353" s="20"/>
     </row>
-    <row r="354" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="354" spans="1:26" ht="15.75" thickBot="1">
       <c r="A354" s="18">
         <v>353</v>
       </c>
@@ -20069,7 +20068,7 @@
       <c r="Y354" s="20"/>
       <c r="Z354" s="20"/>
     </row>
-    <row r="355" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="355" spans="1:26" ht="15.75" thickBot="1">
       <c r="A355" s="18">
         <v>354</v>
       </c>
@@ -20121,7 +20120,7 @@
       <c r="Y355" s="20"/>
       <c r="Z355" s="20"/>
     </row>
-    <row r="356" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="356" spans="1:26" ht="15.75" thickBot="1">
       <c r="A356" s="18">
         <v>355</v>
       </c>
@@ -20173,7 +20172,7 @@
       <c r="Y356" s="20"/>
       <c r="Z356" s="20"/>
     </row>
-    <row r="357" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="357" spans="1:26" ht="15.75" thickBot="1">
       <c r="A357" s="18">
         <v>356</v>
       </c>
@@ -20225,7 +20224,7 @@
       <c r="Y357" s="20"/>
       <c r="Z357" s="20"/>
     </row>
-    <row r="358" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="358" spans="1:26" ht="15.75" thickBot="1">
       <c r="A358" s="18">
         <v>357</v>
       </c>
@@ -20277,7 +20276,7 @@
       <c r="Y358" s="20"/>
       <c r="Z358" s="20"/>
     </row>
-    <row r="359" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="359" spans="1:26" ht="15.75" thickBot="1">
       <c r="A359" s="18">
         <v>358</v>
       </c>
@@ -20329,7 +20328,7 @@
       <c r="Y359" s="20"/>
       <c r="Z359" s="20"/>
     </row>
-    <row r="360" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="360" spans="1:26" ht="15.75" thickBot="1">
       <c r="A360" s="18">
         <v>359</v>
       </c>
@@ -20381,7 +20380,7 @@
       <c r="Y360" s="20"/>
       <c r="Z360" s="20"/>
     </row>
-    <row r="361" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="361" spans="1:26" ht="15.75" thickBot="1">
       <c r="A361" s="18">
         <v>360</v>
       </c>
@@ -20433,7 +20432,7 @@
       <c r="Y361" s="20"/>
       <c r="Z361" s="20"/>
     </row>
-    <row r="362" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="362" spans="1:26" ht="15.75" thickBot="1">
       <c r="A362" s="18">
         <v>361</v>
       </c>
@@ -20485,7 +20484,7 @@
       <c r="Y362" s="20"/>
       <c r="Z362" s="20"/>
     </row>
-    <row r="363" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="363" spans="1:26" ht="15.75" thickBot="1">
       <c r="A363" s="18">
         <v>362</v>
       </c>
@@ -20537,7 +20536,7 @@
       <c r="Y363" s="20"/>
       <c r="Z363" s="20"/>
     </row>
-    <row r="364" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="364" spans="1:26" ht="15.75" thickBot="1">
       <c r="A364" s="18">
         <v>363</v>
       </c>
@@ -20589,7 +20588,7 @@
       <c r="Y364" s="20"/>
       <c r="Z364" s="20"/>
     </row>
-    <row r="365" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="365" spans="1:26" ht="15.75" thickBot="1">
       <c r="A365" s="18">
         <v>364</v>
       </c>
@@ -20641,7 +20640,7 @@
       <c r="Y365" s="20"/>
       <c r="Z365" s="20"/>
     </row>
-    <row r="366" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="366" spans="1:26" ht="15.75" thickBot="1">
       <c r="A366" s="18">
         <v>365</v>
       </c>
@@ -20693,7 +20692,7 @@
       <c r="Y366" s="20"/>
       <c r="Z366" s="20"/>
     </row>
-    <row r="367" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="367" spans="1:26" ht="15.75" thickBot="1">
       <c r="A367" s="18">
         <v>366</v>
       </c>
@@ -20745,7 +20744,7 @@
       <c r="Y367" s="20"/>
       <c r="Z367" s="20"/>
     </row>
-    <row r="368" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="368" spans="1:26" ht="15.75" thickBot="1">
       <c r="A368" s="18">
         <v>367</v>
       </c>
@@ -20797,7 +20796,7 @@
       <c r="Y368" s="20"/>
       <c r="Z368" s="20"/>
     </row>
-    <row r="369" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="369" spans="1:26" ht="15.75" thickBot="1">
       <c r="A369" s="18">
         <v>368</v>
       </c>
@@ -20849,7 +20848,7 @@
       <c r="Y369" s="20"/>
       <c r="Z369" s="20"/>
     </row>
-    <row r="370" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="370" spans="1:26" ht="15.75" thickBot="1">
       <c r="A370" s="18">
         <v>369</v>
       </c>
@@ -20901,7 +20900,7 @@
       <c r="Y370" s="20"/>
       <c r="Z370" s="20"/>
     </row>
-    <row r="371" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="371" spans="1:26" ht="15.75" thickBot="1">
       <c r="A371" s="18">
         <v>370</v>
       </c>
@@ -20953,7 +20952,7 @@
       <c r="Y371" s="20"/>
       <c r="Z371" s="20"/>
     </row>
-    <row r="372" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="372" spans="1:26" ht="15.75" thickBot="1">
       <c r="A372" s="18">
         <v>371</v>
       </c>
@@ -21005,7 +21004,7 @@
       <c r="Y372" s="20"/>
       <c r="Z372" s="20"/>
     </row>
-    <row r="373" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="373" spans="1:26" ht="15.75" thickBot="1">
       <c r="A373" s="18">
         <v>372</v>
       </c>
@@ -21057,7 +21056,7 @@
       <c r="Y373" s="20"/>
       <c r="Z373" s="20"/>
     </row>
-    <row r="374" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="374" spans="1:26" ht="15.75" thickBot="1">
       <c r="A374" s="18">
         <v>373</v>
       </c>
@@ -21109,7 +21108,7 @@
       <c r="Y374" s="20"/>
       <c r="Z374" s="20"/>
     </row>
-    <row r="375" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="375" spans="1:26" ht="15.75" thickBot="1">
       <c r="A375" s="18">
         <v>374</v>
       </c>
@@ -21161,7 +21160,7 @@
       <c r="Y375" s="20"/>
       <c r="Z375" s="20"/>
     </row>
-    <row r="376" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="376" spans="1:26" ht="15.75" thickBot="1">
       <c r="A376" s="18">
         <v>375</v>
       </c>
@@ -21213,7 +21212,7 @@
       <c r="Y376" s="20"/>
       <c r="Z376" s="20"/>
     </row>
-    <row r="377" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="377" spans="1:26" ht="15.75" thickBot="1">
       <c r="A377" s="18">
         <v>376</v>
       </c>
@@ -21265,7 +21264,7 @@
       <c r="Y377" s="20"/>
       <c r="Z377" s="20"/>
     </row>
-    <row r="378" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="378" spans="1:26" ht="27" thickBot="1">
       <c r="A378" s="18">
         <v>377</v>
       </c>
@@ -21317,7 +21316,7 @@
       <c r="Y378" s="20"/>
       <c r="Z378" s="20"/>
     </row>
-    <row r="379" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="379" spans="1:26" ht="27" thickBot="1">
       <c r="A379" s="18">
         <v>378</v>
       </c>
@@ -21369,7 +21368,7 @@
       <c r="Y379" s="20"/>
       <c r="Z379" s="20"/>
     </row>
-    <row r="380" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="380" spans="1:26" ht="27" thickBot="1">
       <c r="A380" s="18">
         <v>379</v>
       </c>
@@ -21421,7 +21420,7 @@
       <c r="Y380" s="20"/>
       <c r="Z380" s="20"/>
     </row>
-    <row r="381" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="381" spans="1:26" ht="27" thickBot="1">
       <c r="A381" s="18">
         <v>380</v>
       </c>
@@ -21473,7 +21472,7 @@
       <c r="Y381" s="20"/>
       <c r="Z381" s="20"/>
     </row>
-    <row r="382" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="382" spans="1:26" ht="27" thickBot="1">
       <c r="A382" s="18">
         <v>381</v>
       </c>
@@ -21525,7 +21524,7 @@
       <c r="Y382" s="20"/>
       <c r="Z382" s="20"/>
     </row>
-    <row r="383" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="383" spans="1:26" ht="27" thickBot="1">
       <c r="A383" s="18">
         <v>382</v>
       </c>
@@ -21577,7 +21576,7 @@
       <c r="Y383" s="20"/>
       <c r="Z383" s="20"/>
     </row>
-    <row r="384" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="384" spans="1:26" ht="15.75" thickBot="1">
       <c r="A384" s="18">
         <v>383</v>
       </c>
@@ -21631,7 +21630,7 @@
       <c r="Y384" s="20"/>
       <c r="Z384" s="20"/>
     </row>
-    <row r="385" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="385" spans="1:26" ht="15.75" thickBot="1">
       <c r="A385" s="18">
         <v>384</v>
       </c>
@@ -21685,7 +21684,7 @@
       <c r="Y385" s="20"/>
       <c r="Z385" s="20"/>
     </row>
-    <row r="386" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="386" spans="1:26" ht="15.75" thickBot="1">
       <c r="A386" s="18">
         <v>385</v>
       </c>
@@ -21739,7 +21738,7 @@
       <c r="Y386" s="20"/>
       <c r="Z386" s="20"/>
     </row>
-    <row r="387" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="387" spans="1:26" ht="15.75" thickBot="1">
       <c r="A387" s="18">
         <v>386</v>
       </c>
@@ -21793,7 +21792,7 @@
       <c r="Y387" s="20"/>
       <c r="Z387" s="20"/>
     </row>
-    <row r="388" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="388" spans="1:26" ht="15.75" thickBot="1">
       <c r="A388" s="18">
         <v>387</v>
       </c>
@@ -21847,7 +21846,7 @@
       <c r="Y388" s="20"/>
       <c r="Z388" s="20"/>
     </row>
-    <row r="389" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="389" spans="1:26" ht="15.75" thickBot="1">
       <c r="A389" s="18">
         <v>388</v>
       </c>
@@ -21901,7 +21900,7 @@
       <c r="Y389" s="20"/>
       <c r="Z389" s="20"/>
     </row>
-    <row r="390" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="390" spans="1:26" ht="15.75" thickBot="1">
       <c r="A390" s="18">
         <v>389</v>
       </c>
@@ -21953,7 +21952,7 @@
       <c r="Y390" s="20"/>
       <c r="Z390" s="20"/>
     </row>
-    <row r="391" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="391" spans="1:26" ht="15.75" thickBot="1">
       <c r="A391" s="18">
         <v>390</v>
       </c>
@@ -22003,7 +22002,7 @@
       <c r="Y391" s="20"/>
       <c r="Z391" s="20"/>
     </row>
-    <row r="392" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="392" spans="1:26" ht="15.75" thickBot="1">
       <c r="A392" s="18">
         <v>391</v>
       </c>
@@ -22055,7 +22054,7 @@
       <c r="Y392" s="20"/>
       <c r="Z392" s="20"/>
     </row>
-    <row r="393" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="393" spans="1:26" ht="15.75" thickBot="1">
       <c r="A393" s="18">
         <v>392</v>
       </c>
@@ -22107,7 +22106,7 @@
       <c r="Y393" s="20"/>
       <c r="Z393" s="20"/>
     </row>
-    <row r="394" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="394" spans="1:26" ht="15.75" thickBot="1">
       <c r="A394" s="18">
         <v>393</v>
       </c>
@@ -22157,7 +22156,7 @@
       <c r="Y394" s="20"/>
       <c r="Z394" s="20"/>
     </row>
-    <row r="395" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="395" spans="1:26" ht="15.75" thickBot="1">
       <c r="A395" s="18">
         <v>394</v>
       </c>
@@ -22207,7 +22206,7 @@
       <c r="Y395" s="20"/>
       <c r="Z395" s="20"/>
     </row>
-    <row r="396" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="396" spans="1:26" ht="15.75" thickBot="1">
       <c r="A396" s="18">
         <v>395</v>
       </c>
@@ -22257,7 +22256,7 @@
       <c r="Y396" s="20"/>
       <c r="Z396" s="20"/>
     </row>
-    <row r="397" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="397" spans="1:26" ht="15.75" thickBot="1">
       <c r="A397" s="18">
         <v>396</v>
       </c>
@@ -22311,7 +22310,7 @@
       <c r="Y397" s="20"/>
       <c r="Z397" s="20"/>
     </row>
-    <row r="398" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="398" spans="1:26" ht="15.75" thickBot="1">
       <c r="A398" s="18">
         <v>397</v>
       </c>
@@ -22365,7 +22364,7 @@
       <c r="Y398" s="20"/>
       <c r="Z398" s="20"/>
     </row>
-    <row r="399" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="399" spans="1:26" ht="15.75" thickBot="1">
       <c r="A399" s="18">
         <v>398</v>
       </c>
@@ -22417,7 +22416,7 @@
       <c r="Y399" s="20"/>
       <c r="Z399" s="20"/>
     </row>
-    <row r="400" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="400" spans="1:26" ht="15.75" thickBot="1">
       <c r="A400" s="18">
         <v>399</v>
       </c>
@@ -22469,7 +22468,7 @@
       <c r="Y400" s="20"/>
       <c r="Z400" s="20"/>
     </row>
-    <row r="401" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="401" spans="1:26" ht="15.75" thickBot="1">
       <c r="A401" s="18">
         <v>400</v>
       </c>
@@ -22521,7 +22520,7 @@
       <c r="Y401" s="20"/>
       <c r="Z401" s="20"/>
     </row>
-    <row r="402" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="402" spans="1:26" ht="15.75" thickBot="1">
       <c r="A402" s="18">
         <v>401</v>
       </c>
@@ -22573,7 +22572,7 @@
       <c r="Y402" s="20"/>
       <c r="Z402" s="20"/>
     </row>
-    <row r="403" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="403" spans="1:26" ht="15.75" thickBot="1">
       <c r="A403" s="18">
         <v>402</v>
       </c>
@@ -22625,7 +22624,7 @@
       <c r="Y403" s="20"/>
       <c r="Z403" s="20"/>
     </row>
-    <row r="404" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="404" spans="1:26" ht="27" thickBot="1">
       <c r="A404" s="18">
         <v>403</v>
       </c>
@@ -22679,7 +22678,7 @@
       <c r="Y404" s="20"/>
       <c r="Z404" s="20"/>
     </row>
-    <row r="405" spans="1:26" ht="27" hidden="1" thickBot="1">
+    <row r="405" spans="1:26" ht="27" thickBot="1">
       <c r="A405" s="18">
         <v>404</v>
       </c>
@@ -22733,7 +22732,7 @@
       <c r="Y405" s="20"/>
       <c r="Z405" s="20"/>
     </row>
-    <row r="406" spans="1:26" s="53" customFormat="1" ht="15.75" hidden="1" thickBot="1">
+    <row r="406" spans="1:26" s="53" customFormat="1" ht="15.75" thickBot="1">
       <c r="A406" s="18">
         <v>405</v>
       </c>
@@ -22789,7 +22788,7 @@
       <c r="Y406" s="52"/>
       <c r="Z406" s="52"/>
     </row>
-    <row r="407" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="407" spans="1:26" ht="15.75" thickBot="1">
       <c r="A407" s="18">
         <v>406</v>
       </c>
@@ -22843,7 +22842,7 @@
       <c r="Y407" s="20"/>
       <c r="Z407" s="20"/>
     </row>
-    <row r="408" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="408" spans="1:26" ht="15.75" thickBot="1">
       <c r="A408" s="18">
         <v>407</v>
       </c>
@@ -22897,7 +22896,7 @@
       <c r="Y408" s="20"/>
       <c r="Z408" s="20"/>
     </row>
-    <row r="409" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="409" spans="1:26" ht="15.75" thickBot="1">
       <c r="A409" s="18">
         <v>408</v>
       </c>
@@ -22951,7 +22950,7 @@
       <c r="Y409" s="20"/>
       <c r="Z409" s="20"/>
     </row>
-    <row r="410" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="410" spans="1:26" ht="15.75" thickBot="1">
       <c r="A410" s="18">
         <v>409</v>
       </c>
@@ -23005,7 +23004,7 @@
       <c r="Y410" s="20"/>
       <c r="Z410" s="20"/>
     </row>
-    <row r="411" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="411" spans="1:26" ht="15.75" thickBot="1">
       <c r="A411" s="18">
         <v>410</v>
       </c>
@@ -23059,7 +23058,7 @@
       <c r="Y411" s="20"/>
       <c r="Z411" s="20"/>
     </row>
-    <row r="412" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="412" spans="1:26" ht="15.75" thickBot="1">
       <c r="A412" s="18">
         <v>411</v>
       </c>
@@ -23111,7 +23110,7 @@
       <c r="Y412" s="20"/>
       <c r="Z412" s="20"/>
     </row>
-    <row r="413" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="413" spans="1:26" ht="15.75" thickBot="1">
       <c r="A413" s="18">
         <v>412</v>
       </c>
@@ -23163,7 +23162,7 @@
       <c r="Y413" s="20"/>
       <c r="Z413" s="20"/>
     </row>
-    <row r="414" spans="1:26" ht="15.75" hidden="1" thickBot="1">
+    <row r="414" spans="1:26" ht="15.75" thickBot="1">
       <c r="A414" s="18">
         <v>413</v>
       </c>
@@ -23219,13 +23218,7 @@
       <c r="K415" s="22"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M414" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="LOF/GOF"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M414" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="M7" r:id="rId1" xr:uid="{87A5E94E-2CC0-43A2-A62B-F1F66B9F07E8}"/>
